--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-28.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-28.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="92">
   <si>
     <t>League</t>
   </si>
@@ -254,6 +254,42 @@
   </si>
   <si>
     <t>SnapshotTS</t>
+  </si>
+  <si>
+    <t>Ecuadorian Serie A</t>
+  </si>
+  <si>
+    <t>Swedish Superettan</t>
+  </si>
+  <si>
+    <t>2026-07-28</t>
+  </si>
+  <si>
+    <t>00:00:00</t>
+  </si>
+  <si>
+    <t>17:00:00</t>
+  </si>
+  <si>
+    <t>Deportivo Cuenca</t>
+  </si>
+  <si>
+    <t>Landskrona</t>
+  </si>
+  <si>
+    <t>Helsingborgs</t>
+  </si>
+  <si>
+    <t>Emelec</t>
+  </si>
+  <si>
+    <t>Norrkoping</t>
+  </si>
+  <si>
+    <t>United IK Nordic</t>
+  </si>
+  <si>
+    <t>2026-07-26 01:52:46</t>
   </si>
 </sst>
 </file>
@@ -585,7 +621,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB1"/>
+  <dimension ref="A1:CB4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -828,6 +864,732 @@
       </c>
       <c r="CB1" t="s">
         <v>79</v>
+      </c>
+    </row>
+    <row r="2" spans="1:80">
+      <c r="A2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E2" t="s">
+        <v>88</v>
+      </c>
+      <c r="F2">
+        <v>2.34</v>
+      </c>
+      <c r="G2">
+        <v>2.68</v>
+      </c>
+      <c r="H2">
+        <v>3.3</v>
+      </c>
+      <c r="I2">
+        <v>3.9</v>
+      </c>
+      <c r="J2">
+        <v>2.88</v>
+      </c>
+      <c r="K2">
+        <v>3.35</v>
+      </c>
+      <c r="L2">
+        <v>1.46</v>
+      </c>
+      <c r="M2">
+        <v>1.11</v>
+      </c>
+      <c r="N2">
+        <v>2.58</v>
+      </c>
+      <c r="O2">
+        <v>1.49</v>
+      </c>
+      <c r="P2">
+        <v>1.53</v>
+      </c>
+      <c r="Q2">
+        <v>2.46</v>
+      </c>
+      <c r="R2">
+        <v>1.19</v>
+      </c>
+      <c r="S2">
+        <v>5</v>
+      </c>
+      <c r="T2">
+        <v>2.02</v>
+      </c>
+      <c r="U2">
+        <v>1.79</v>
+      </c>
+      <c r="V2">
+        <v>1.34</v>
+      </c>
+      <c r="W2">
+        <v>1.6</v>
+      </c>
+      <c r="X2">
+        <v>9.4</v>
+      </c>
+      <c r="Y2">
+        <v>10.5</v>
+      </c>
+      <c r="Z2">
+        <v>29</v>
+      </c>
+      <c r="AA2">
+        <v>100</v>
+      </c>
+      <c r="AB2">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AC2">
+        <v>7.4</v>
+      </c>
+      <c r="AD2">
+        <v>16.5</v>
+      </c>
+      <c r="AE2">
+        <v>60</v>
+      </c>
+      <c r="AF2">
+        <v>15.5</v>
+      </c>
+      <c r="AG2">
+        <v>13</v>
+      </c>
+      <c r="AH2">
+        <v>23</v>
+      </c>
+      <c r="AI2">
+        <v>100</v>
+      </c>
+      <c r="AJ2">
+        <v>48</v>
+      </c>
+      <c r="AK2">
+        <v>38</v>
+      </c>
+      <c r="AL2">
+        <v>90</v>
+      </c>
+      <c r="AM2">
+        <v>210</v>
+      </c>
+      <c r="AN2">
+        <v>46</v>
+      </c>
+      <c r="AO2">
+        <v>90</v>
+      </c>
+      <c r="AP2">
+        <v>7.6</v>
+      </c>
+      <c r="AQ2">
+        <v>7.6</v>
+      </c>
+      <c r="AR2">
+        <v>17</v>
+      </c>
+      <c r="AS2">
+        <v>7.4</v>
+      </c>
+      <c r="AT2">
+        <v>6.6</v>
+      </c>
+      <c r="AU2">
+        <v>6</v>
+      </c>
+      <c r="AV2">
+        <v>13</v>
+      </c>
+      <c r="AW2">
+        <v>7.2</v>
+      </c>
+      <c r="AX2">
+        <v>12.5</v>
+      </c>
+      <c r="AY2">
+        <v>10.5</v>
+      </c>
+      <c r="AZ2">
+        <v>18.5</v>
+      </c>
+      <c r="BA2">
+        <v>7.4</v>
+      </c>
+      <c r="BB2">
+        <v>25</v>
+      </c>
+      <c r="BC2">
+        <v>23</v>
+      </c>
+      <c r="BD2">
+        <v>7.4</v>
+      </c>
+      <c r="BE2">
+        <v>8</v>
+      </c>
+      <c r="BF2">
+        <v>27</v>
+      </c>
+      <c r="BG2">
+        <v>7.6</v>
+      </c>
+      <c r="BH2">
+        <v>2.84</v>
+      </c>
+      <c r="BI2">
+        <v>2.48</v>
+      </c>
+      <c r="BJ2">
+        <v>11.5</v>
+      </c>
+      <c r="BK2">
+        <v>5.6</v>
+      </c>
+      <c r="BL2">
+        <v>1000</v>
+      </c>
+      <c r="BM2">
+        <v>10</v>
+      </c>
+      <c r="BN2">
+        <v>5.3</v>
+      </c>
+      <c r="BO2">
+        <v>3.95</v>
+      </c>
+      <c r="BP2">
+        <v>23</v>
+      </c>
+      <c r="BQ2">
+        <v>7.4</v>
+      </c>
+      <c r="BR2">
+        <v>46</v>
+      </c>
+      <c r="BS2">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BT2">
+        <v>6.8</v>
+      </c>
+      <c r="BU2">
+        <v>4.9</v>
+      </c>
+      <c r="BV2">
+        <v>36</v>
+      </c>
+      <c r="BW2">
+        <v>8.4</v>
+      </c>
+      <c r="BX2">
+        <v>60</v>
+      </c>
+      <c r="BY2">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BZ2">
+        <v>50</v>
+      </c>
+      <c r="CA2">
+        <v>9</v>
+      </c>
+      <c r="CB2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="3" spans="1:80">
+      <c r="A3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B3" t="s">
+        <v>82</v>
+      </c>
+      <c r="C3" t="s">
+        <v>84</v>
+      </c>
+      <c r="D3" t="s">
+        <v>86</v>
+      </c>
+      <c r="E3" t="s">
+        <v>89</v>
+      </c>
+      <c r="F3">
+        <v>3.35</v>
+      </c>
+      <c r="G3">
+        <v>3.75</v>
+      </c>
+      <c r="H3">
+        <v>2.08</v>
+      </c>
+      <c r="I3">
+        <v>2.24</v>
+      </c>
+      <c r="J3">
+        <v>3.7</v>
+      </c>
+      <c r="K3">
+        <v>4.2</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3">
+        <v>0</v>
+      </c>
+      <c r="O3">
+        <v>0</v>
+      </c>
+      <c r="P3">
+        <v>2.2</v>
+      </c>
+      <c r="Q3">
+        <v>1.7</v>
+      </c>
+      <c r="R3">
+        <v>0</v>
+      </c>
+      <c r="S3">
+        <v>0</v>
+      </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
+      <c r="U3">
+        <v>0</v>
+      </c>
+      <c r="V3">
+        <v>0</v>
+      </c>
+      <c r="W3">
+        <v>0</v>
+      </c>
+      <c r="X3">
+        <v>0</v>
+      </c>
+      <c r="Y3">
+        <v>0</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+      <c r="AA3">
+        <v>0</v>
+      </c>
+      <c r="AB3">
+        <v>0</v>
+      </c>
+      <c r="AC3">
+        <v>0</v>
+      </c>
+      <c r="AD3">
+        <v>0</v>
+      </c>
+      <c r="AE3">
+        <v>0</v>
+      </c>
+      <c r="AF3">
+        <v>0</v>
+      </c>
+      <c r="AG3">
+        <v>0</v>
+      </c>
+      <c r="AH3">
+        <v>0</v>
+      </c>
+      <c r="AI3">
+        <v>0</v>
+      </c>
+      <c r="AJ3">
+        <v>0</v>
+      </c>
+      <c r="AK3">
+        <v>0</v>
+      </c>
+      <c r="AL3">
+        <v>0</v>
+      </c>
+      <c r="AM3">
+        <v>0</v>
+      </c>
+      <c r="AN3">
+        <v>0</v>
+      </c>
+      <c r="AO3">
+        <v>0</v>
+      </c>
+      <c r="AP3">
+        <v>0</v>
+      </c>
+      <c r="AQ3">
+        <v>0</v>
+      </c>
+      <c r="AR3">
+        <v>0</v>
+      </c>
+      <c r="AS3">
+        <v>0</v>
+      </c>
+      <c r="AT3">
+        <v>0</v>
+      </c>
+      <c r="AU3">
+        <v>0</v>
+      </c>
+      <c r="AV3">
+        <v>0</v>
+      </c>
+      <c r="AW3">
+        <v>0</v>
+      </c>
+      <c r="AX3">
+        <v>0</v>
+      </c>
+      <c r="AY3">
+        <v>0</v>
+      </c>
+      <c r="AZ3">
+        <v>0</v>
+      </c>
+      <c r="BA3">
+        <v>0</v>
+      </c>
+      <c r="BB3">
+        <v>0</v>
+      </c>
+      <c r="BC3">
+        <v>0</v>
+      </c>
+      <c r="BD3">
+        <v>0</v>
+      </c>
+      <c r="BE3">
+        <v>0</v>
+      </c>
+      <c r="BF3">
+        <v>0</v>
+      </c>
+      <c r="BG3">
+        <v>0</v>
+      </c>
+      <c r="BH3">
+        <v>0</v>
+      </c>
+      <c r="BI3">
+        <v>0</v>
+      </c>
+      <c r="BJ3">
+        <v>0</v>
+      </c>
+      <c r="BK3">
+        <v>0</v>
+      </c>
+      <c r="BL3">
+        <v>0</v>
+      </c>
+      <c r="BM3">
+        <v>0</v>
+      </c>
+      <c r="BN3">
+        <v>0</v>
+      </c>
+      <c r="BO3">
+        <v>0</v>
+      </c>
+      <c r="BP3">
+        <v>0</v>
+      </c>
+      <c r="BQ3">
+        <v>0</v>
+      </c>
+      <c r="BR3">
+        <v>0</v>
+      </c>
+      <c r="BS3">
+        <v>0</v>
+      </c>
+      <c r="BT3">
+        <v>0</v>
+      </c>
+      <c r="BU3">
+        <v>0</v>
+      </c>
+      <c r="BV3">
+        <v>0</v>
+      </c>
+      <c r="BW3">
+        <v>0</v>
+      </c>
+      <c r="BX3">
+        <v>0</v>
+      </c>
+      <c r="BY3">
+        <v>0</v>
+      </c>
+      <c r="BZ3">
+        <v>0</v>
+      </c>
+      <c r="CA3">
+        <v>0</v>
+      </c>
+      <c r="CB3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="4" spans="1:80">
+      <c r="A4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B4" t="s">
+        <v>82</v>
+      </c>
+      <c r="C4" t="s">
+        <v>84</v>
+      </c>
+      <c r="D4" t="s">
+        <v>87</v>
+      </c>
+      <c r="E4" t="s">
+        <v>90</v>
+      </c>
+      <c r="F4">
+        <v>2.32</v>
+      </c>
+      <c r="G4">
+        <v>2.54</v>
+      </c>
+      <c r="H4">
+        <v>2.92</v>
+      </c>
+      <c r="I4">
+        <v>3.35</v>
+      </c>
+      <c r="J4">
+        <v>3.7</v>
+      </c>
+      <c r="K4">
+        <v>4.2</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4">
+        <v>0</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>2.26</v>
+      </c>
+      <c r="Q4">
+        <v>1.67</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>0</v>
+      </c>
+      <c r="V4">
+        <v>0</v>
+      </c>
+      <c r="W4">
+        <v>0</v>
+      </c>
+      <c r="X4">
+        <v>0</v>
+      </c>
+      <c r="Y4">
+        <v>0</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+      <c r="AA4">
+        <v>0</v>
+      </c>
+      <c r="AB4">
+        <v>0</v>
+      </c>
+      <c r="AC4">
+        <v>0</v>
+      </c>
+      <c r="AD4">
+        <v>0</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>0</v>
+      </c>
+      <c r="AG4">
+        <v>0</v>
+      </c>
+      <c r="AH4">
+        <v>0</v>
+      </c>
+      <c r="AI4">
+        <v>0</v>
+      </c>
+      <c r="AJ4">
+        <v>0</v>
+      </c>
+      <c r="AK4">
+        <v>0</v>
+      </c>
+      <c r="AL4">
+        <v>0</v>
+      </c>
+      <c r="AM4">
+        <v>0</v>
+      </c>
+      <c r="AN4">
+        <v>0</v>
+      </c>
+      <c r="AO4">
+        <v>0</v>
+      </c>
+      <c r="AP4">
+        <v>0</v>
+      </c>
+      <c r="AQ4">
+        <v>0</v>
+      </c>
+      <c r="AR4">
+        <v>0</v>
+      </c>
+      <c r="AS4">
+        <v>0</v>
+      </c>
+      <c r="AT4">
+        <v>0</v>
+      </c>
+      <c r="AU4">
+        <v>0</v>
+      </c>
+      <c r="AV4">
+        <v>0</v>
+      </c>
+      <c r="AW4">
+        <v>0</v>
+      </c>
+      <c r="AX4">
+        <v>0</v>
+      </c>
+      <c r="AY4">
+        <v>0</v>
+      </c>
+      <c r="AZ4">
+        <v>0</v>
+      </c>
+      <c r="BA4">
+        <v>0</v>
+      </c>
+      <c r="BB4">
+        <v>0</v>
+      </c>
+      <c r="BC4">
+        <v>0</v>
+      </c>
+      <c r="BD4">
+        <v>0</v>
+      </c>
+      <c r="BE4">
+        <v>0</v>
+      </c>
+      <c r="BF4">
+        <v>0</v>
+      </c>
+      <c r="BG4">
+        <v>0</v>
+      </c>
+      <c r="BH4">
+        <v>0</v>
+      </c>
+      <c r="BI4">
+        <v>0</v>
+      </c>
+      <c r="BJ4">
+        <v>0</v>
+      </c>
+      <c r="BK4">
+        <v>0</v>
+      </c>
+      <c r="BL4">
+        <v>0</v>
+      </c>
+      <c r="BM4">
+        <v>0</v>
+      </c>
+      <c r="BN4">
+        <v>0</v>
+      </c>
+      <c r="BO4">
+        <v>0</v>
+      </c>
+      <c r="BP4">
+        <v>0</v>
+      </c>
+      <c r="BQ4">
+        <v>0</v>
+      </c>
+      <c r="BR4">
+        <v>0</v>
+      </c>
+      <c r="BS4">
+        <v>0</v>
+      </c>
+      <c r="BT4">
+        <v>0</v>
+      </c>
+      <c r="BU4">
+        <v>0</v>
+      </c>
+      <c r="BV4">
+        <v>0</v>
+      </c>
+      <c r="BW4">
+        <v>0</v>
+      </c>
+      <c r="BX4">
+        <v>0</v>
+      </c>
+      <c r="BY4">
+        <v>0</v>
+      </c>
+      <c r="BZ4">
+        <v>0</v>
+      </c>
+      <c r="CA4">
+        <v>0</v>
+      </c>
+      <c r="CB4" t="s">
+        <v>91</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-28.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-28.xlsx
@@ -289,7 +289,7 @@
     <t>United IK Nordic</t>
   </si>
   <si>
-    <t>2026-07-26 01:52:46</t>
+    <t>2026-07-26 04:06:24</t>
   </si>
 </sst>
 </file>
@@ -883,16 +883,16 @@
         <v>88</v>
       </c>
       <c r="F2">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="G2">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="H2">
         <v>3.3</v>
       </c>
       <c r="I2">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="J2">
         <v>2.88</v>
@@ -904,7 +904,7 @@
         <v>1.46</v>
       </c>
       <c r="M2">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="N2">
         <v>2.58</v>
@@ -916,7 +916,7 @@
         <v>1.53</v>
       </c>
       <c r="Q2">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="R2">
         <v>1.19</v>
@@ -928,13 +928,13 @@
         <v>2.02</v>
       </c>
       <c r="U2">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="V2">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="W2">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="X2">
         <v>9.4</v>
@@ -943,7 +943,7 @@
         <v>10.5</v>
       </c>
       <c r="Z2">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AA2">
         <v>100</v>
@@ -994,13 +994,13 @@
         <v>7.6</v>
       </c>
       <c r="AQ2">
+        <v>8.4</v>
+      </c>
+      <c r="AR2">
+        <v>19.5</v>
+      </c>
+      <c r="AS2">
         <v>7.6</v>
-      </c>
-      <c r="AR2">
-        <v>17</v>
-      </c>
-      <c r="AS2">
-        <v>7.4</v>
       </c>
       <c r="AT2">
         <v>6.6</v>
@@ -1012,7 +1012,7 @@
         <v>13</v>
       </c>
       <c r="AW2">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AX2">
         <v>12.5</v>
@@ -1024,7 +1024,7 @@
         <v>18.5</v>
       </c>
       <c r="BA2">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BB2">
         <v>25</v>
@@ -1048,13 +1048,13 @@
         <v>2.84</v>
       </c>
       <c r="BI2">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="BJ2">
         <v>11.5</v>
       </c>
       <c r="BK2">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BL2">
         <v>1000</v>
@@ -1063,7 +1063,7 @@
         <v>10</v>
       </c>
       <c r="BN2">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BO2">
         <v>3.95</v>
@@ -1072,13 +1072,13 @@
         <v>23</v>
       </c>
       <c r="BQ2">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BR2">
         <v>46</v>
       </c>
       <c r="BS2">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BT2">
         <v>6.8</v>
@@ -1090,19 +1090,19 @@
         <v>36</v>
       </c>
       <c r="BW2">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX2">
         <v>60</v>
       </c>
       <c r="BY2">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BZ2">
         <v>50</v>
       </c>
       <c r="CA2">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="CB2" t="s">
         <v>91</v>
@@ -1128,10 +1128,10 @@
         <v>3.35</v>
       </c>
       <c r="G3">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="H3">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="I3">
         <v>2.24</v>
@@ -1140,7 +1140,7 @@
         <v>3.7</v>
       </c>
       <c r="K3">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L3">
         <v>0</v>
@@ -1155,10 +1155,10 @@
         <v>0</v>
       </c>
       <c r="P3">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="Q3">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="R3">
         <v>0</v>
@@ -1367,22 +1367,22 @@
         <v>90</v>
       </c>
       <c r="F4">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="G4">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="H4">
         <v>2.92</v>
       </c>
       <c r="I4">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="J4">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="K4">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L4">
         <v>0</v>
@@ -1400,7 +1400,7 @@
         <v>2.26</v>
       </c>
       <c r="Q4">
-        <v>1.67</v>
+        <v>1.59</v>
       </c>
       <c r="R4">
         <v>0</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-28.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-28.xlsx
@@ -289,7 +289,7 @@
     <t>United IK Nordic</t>
   </si>
   <si>
-    <t>2026-07-26 04:06:24</t>
+    <t>2026-07-26 06:19:41</t>
   </si>
 </sst>
 </file>
@@ -886,10 +886,10 @@
         <v>2.38</v>
       </c>
       <c r="G2">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="H2">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="I2">
         <v>3.85</v>
@@ -1370,16 +1370,16 @@
         <v>2.34</v>
       </c>
       <c r="G4">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="H4">
         <v>2.92</v>
       </c>
       <c r="I4">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="J4">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="K4">
         <v>4.1</v>
@@ -1400,7 +1400,7 @@
         <v>2.26</v>
       </c>
       <c r="Q4">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="R4">
         <v>0</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-28.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-28.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="96">
   <si>
     <t>League</t>
   </si>
@@ -259,6 +259,9 @@
     <t>Ecuadorian Serie A</t>
   </si>
   <si>
+    <t>Colombian Primera B</t>
+  </si>
+  <si>
     <t>Swedish Superettan</t>
   </si>
   <si>
@@ -268,12 +271,18 @@
     <t>00:00:00</t>
   </si>
   <si>
+    <t>00:30:00</t>
+  </si>
+  <si>
     <t>17:00:00</t>
   </si>
   <si>
     <t>Deportivo Cuenca</t>
   </si>
   <si>
+    <t>Atletico FC Cali</t>
+  </si>
+  <si>
     <t>Landskrona</t>
   </si>
   <si>
@@ -283,13 +292,16 @@
     <t>Emelec</t>
   </si>
   <si>
+    <t>Independiente Yumbo</t>
+  </si>
+  <si>
     <t>Norrkoping</t>
   </si>
   <si>
     <t>United IK Nordic</t>
   </si>
   <si>
-    <t>2026-07-26 06:19:41</t>
+    <t>2026-07-26 08:32:53</t>
   </si>
 </sst>
 </file>
@@ -621,7 +633,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB4"/>
+  <dimension ref="A1:CB5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -871,16 +883,16 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E2" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="F2">
         <v>2.38</v>
@@ -988,7 +1000,7 @@
         <v>46</v>
       </c>
       <c r="AO2">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AP2">
         <v>7.6</v>
@@ -1012,7 +1024,7 @@
         <v>13</v>
       </c>
       <c r="AW2">
-        <v>7.4</v>
+        <v>38</v>
       </c>
       <c r="AX2">
         <v>12.5</v>
@@ -1033,10 +1045,10 @@
         <v>23</v>
       </c>
       <c r="BD2">
-        <v>7.4</v>
+        <v>42</v>
       </c>
       <c r="BE2">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF2">
         <v>27</v>
@@ -1105,7 +1117,7 @@
         <v>8.6</v>
       </c>
       <c r="CB2" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1113,270 +1125,270 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D3" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E3" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="F3">
-        <v>3.35</v>
+        <v>4.6</v>
       </c>
       <c r="G3">
-        <v>3.65</v>
+        <v>5.6</v>
       </c>
       <c r="H3">
-        <v>2.12</v>
+        <v>1.88</v>
       </c>
       <c r="I3">
+        <v>2.04</v>
+      </c>
+      <c r="J3">
+        <v>3</v>
+      </c>
+      <c r="K3">
+        <v>3.45</v>
+      </c>
+      <c r="L3">
+        <v>1.45</v>
+      </c>
+      <c r="M3">
+        <v>1.1</v>
+      </c>
+      <c r="N3">
+        <v>2.82</v>
+      </c>
+      <c r="O3">
+        <v>1.46</v>
+      </c>
+      <c r="P3">
+        <v>1.62</v>
+      </c>
+      <c r="Q3">
+        <v>2.32</v>
+      </c>
+      <c r="R3">
+        <v>1.22</v>
+      </c>
+      <c r="S3">
+        <v>4.5</v>
+      </c>
+      <c r="T3">
+        <v>2.08</v>
+      </c>
+      <c r="U3">
+        <v>1.77</v>
+      </c>
+      <c r="V3">
+        <v>1.96</v>
+      </c>
+      <c r="W3">
+        <v>1.21</v>
+      </c>
+      <c r="X3">
+        <v>10.5</v>
+      </c>
+      <c r="Y3">
+        <v>7.4</v>
+      </c>
+      <c r="Z3">
+        <v>11</v>
+      </c>
+      <c r="AA3">
+        <v>24</v>
+      </c>
+      <c r="AB3">
+        <v>14.5</v>
+      </c>
+      <c r="AC3">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD3">
+        <v>11.5</v>
+      </c>
+      <c r="AE3">
+        <v>34</v>
+      </c>
+      <c r="AF3">
+        <v>44</v>
+      </c>
+      <c r="AG3">
+        <v>22</v>
+      </c>
+      <c r="AH3">
+        <v>32</v>
+      </c>
+      <c r="AI3">
+        <v>60</v>
+      </c>
+      <c r="AJ3">
+        <v>170</v>
+      </c>
+      <c r="AK3">
+        <v>110</v>
+      </c>
+      <c r="AL3">
+        <v>120</v>
+      </c>
+      <c r="AM3">
+        <v>210</v>
+      </c>
+      <c r="AN3">
+        <v>160</v>
+      </c>
+      <c r="AO3">
+        <v>21</v>
+      </c>
+      <c r="AP3">
+        <v>7.8</v>
+      </c>
+      <c r="AQ3">
+        <v>5.5</v>
+      </c>
+      <c r="AR3">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AS3">
+        <v>17</v>
+      </c>
+      <c r="AT3">
+        <v>5.4</v>
+      </c>
+      <c r="AU3">
+        <v>6.2</v>
+      </c>
+      <c r="AV3">
+        <v>8.4</v>
+      </c>
+      <c r="AW3">
+        <v>6.4</v>
+      </c>
+      <c r="AX3">
+        <v>7.2</v>
+      </c>
+      <c r="AY3">
+        <v>6.2</v>
+      </c>
+      <c r="AZ3">
+        <v>6.4</v>
+      </c>
+      <c r="BA3">
+        <v>7.6</v>
+      </c>
+      <c r="BB3">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BC3">
+        <v>8</v>
+      </c>
+      <c r="BD3">
+        <v>8</v>
+      </c>
+      <c r="BE3">
+        <v>8.4</v>
+      </c>
+      <c r="BF3">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BG3">
+        <v>6</v>
+      </c>
+      <c r="BH3">
+        <v>3</v>
+      </c>
+      <c r="BI3">
+        <v>2.6</v>
+      </c>
+      <c r="BJ3">
+        <v>12</v>
+      </c>
+      <c r="BK3">
+        <v>5.6</v>
+      </c>
+      <c r="BL3">
+        <v>1000</v>
+      </c>
+      <c r="BM3">
+        <v>2.32</v>
+      </c>
+      <c r="BN3">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BO3">
+        <v>4.8</v>
+      </c>
+      <c r="BP3">
+        <v>1000</v>
+      </c>
+      <c r="BQ3">
         <v>2.24</v>
       </c>
-      <c r="J3">
-        <v>3.7</v>
-      </c>
-      <c r="K3">
-        <v>4.1</v>
-      </c>
-      <c r="L3">
-        <v>0</v>
-      </c>
-      <c r="M3">
-        <v>0</v>
-      </c>
-      <c r="N3">
-        <v>0</v>
-      </c>
-      <c r="O3">
-        <v>0</v>
-      </c>
-      <c r="P3">
-        <v>2.18</v>
-      </c>
-      <c r="Q3">
-        <v>1.73</v>
-      </c>
-      <c r="R3">
-        <v>0</v>
-      </c>
-      <c r="S3">
-        <v>0</v>
-      </c>
-      <c r="T3">
-        <v>0</v>
-      </c>
-      <c r="U3">
-        <v>0</v>
-      </c>
-      <c r="V3">
-        <v>0</v>
-      </c>
-      <c r="W3">
-        <v>0</v>
-      </c>
-      <c r="X3">
-        <v>0</v>
-      </c>
-      <c r="Y3">
-        <v>0</v>
-      </c>
-      <c r="Z3">
-        <v>0</v>
-      </c>
-      <c r="AA3">
-        <v>0</v>
-      </c>
-      <c r="AB3">
-        <v>0</v>
-      </c>
-      <c r="AC3">
-        <v>0</v>
-      </c>
-      <c r="AD3">
-        <v>0</v>
-      </c>
-      <c r="AE3">
-        <v>0</v>
-      </c>
-      <c r="AF3">
-        <v>0</v>
-      </c>
-      <c r="AG3">
-        <v>0</v>
-      </c>
-      <c r="AH3">
-        <v>0</v>
-      </c>
-      <c r="AI3">
-        <v>0</v>
-      </c>
-      <c r="AJ3">
-        <v>0</v>
-      </c>
-      <c r="AK3">
-        <v>0</v>
-      </c>
-      <c r="AL3">
-        <v>0</v>
-      </c>
-      <c r="AM3">
-        <v>0</v>
-      </c>
-      <c r="AN3">
-        <v>0</v>
-      </c>
-      <c r="AO3">
-        <v>0</v>
-      </c>
-      <c r="AP3">
-        <v>0</v>
-      </c>
-      <c r="AQ3">
-        <v>0</v>
-      </c>
-      <c r="AR3">
-        <v>0</v>
-      </c>
-      <c r="AS3">
-        <v>0</v>
-      </c>
-      <c r="AT3">
-        <v>0</v>
-      </c>
-      <c r="AU3">
-        <v>0</v>
-      </c>
-      <c r="AV3">
-        <v>0</v>
-      </c>
-      <c r="AW3">
-        <v>0</v>
-      </c>
-      <c r="AX3">
-        <v>0</v>
-      </c>
-      <c r="AY3">
-        <v>0</v>
-      </c>
-      <c r="AZ3">
-        <v>0</v>
-      </c>
-      <c r="BA3">
-        <v>0</v>
-      </c>
-      <c r="BB3">
-        <v>0</v>
-      </c>
-      <c r="BC3">
-        <v>0</v>
-      </c>
-      <c r="BD3">
-        <v>0</v>
-      </c>
-      <c r="BE3">
-        <v>0</v>
-      </c>
-      <c r="BF3">
-        <v>0</v>
-      </c>
-      <c r="BG3">
-        <v>0</v>
-      </c>
-      <c r="BH3">
-        <v>0</v>
-      </c>
-      <c r="BI3">
-        <v>0</v>
-      </c>
-      <c r="BJ3">
-        <v>0</v>
-      </c>
-      <c r="BK3">
-        <v>0</v>
-      </c>
-      <c r="BL3">
-        <v>0</v>
-      </c>
-      <c r="BM3">
-        <v>0</v>
-      </c>
-      <c r="BN3">
-        <v>0</v>
-      </c>
-      <c r="BO3">
-        <v>0</v>
-      </c>
-      <c r="BP3">
-        <v>0</v>
-      </c>
-      <c r="BQ3">
-        <v>0</v>
-      </c>
       <c r="BR3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS3">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="BT3">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BU3">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="BV3">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="BW3">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="BX3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY3">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA3">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB3" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
     </row>
     <row r="4" spans="1:80">
       <c r="A4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C4" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D4" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E4" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="F4">
-        <v>2.34</v>
+        <v>3.35</v>
       </c>
       <c r="G4">
-        <v>2.54</v>
+        <v>3.65</v>
       </c>
       <c r="H4">
-        <v>2.92</v>
+        <v>2.12</v>
       </c>
       <c r="I4">
-        <v>3.35</v>
+        <v>2.24</v>
       </c>
       <c r="J4">
         <v>3.7</v>
@@ -1397,199 +1409,441 @@
         <v>0</v>
       </c>
       <c r="P4">
+        <v>2.18</v>
+      </c>
+      <c r="Q4">
+        <v>1.73</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>0</v>
+      </c>
+      <c r="V4">
+        <v>0</v>
+      </c>
+      <c r="W4">
+        <v>0</v>
+      </c>
+      <c r="X4">
+        <v>0</v>
+      </c>
+      <c r="Y4">
+        <v>0</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+      <c r="AA4">
+        <v>0</v>
+      </c>
+      <c r="AB4">
+        <v>0</v>
+      </c>
+      <c r="AC4">
+        <v>0</v>
+      </c>
+      <c r="AD4">
+        <v>0</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>0</v>
+      </c>
+      <c r="AG4">
+        <v>0</v>
+      </c>
+      <c r="AH4">
+        <v>0</v>
+      </c>
+      <c r="AI4">
+        <v>0</v>
+      </c>
+      <c r="AJ4">
+        <v>0</v>
+      </c>
+      <c r="AK4">
+        <v>0</v>
+      </c>
+      <c r="AL4">
+        <v>0</v>
+      </c>
+      <c r="AM4">
+        <v>0</v>
+      </c>
+      <c r="AN4">
+        <v>0</v>
+      </c>
+      <c r="AO4">
+        <v>0</v>
+      </c>
+      <c r="AP4">
+        <v>0</v>
+      </c>
+      <c r="AQ4">
+        <v>0</v>
+      </c>
+      <c r="AR4">
+        <v>0</v>
+      </c>
+      <c r="AS4">
+        <v>0</v>
+      </c>
+      <c r="AT4">
+        <v>0</v>
+      </c>
+      <c r="AU4">
+        <v>0</v>
+      </c>
+      <c r="AV4">
+        <v>0</v>
+      </c>
+      <c r="AW4">
+        <v>0</v>
+      </c>
+      <c r="AX4">
+        <v>0</v>
+      </c>
+      <c r="AY4">
+        <v>0</v>
+      </c>
+      <c r="AZ4">
+        <v>0</v>
+      </c>
+      <c r="BA4">
+        <v>0</v>
+      </c>
+      <c r="BB4">
+        <v>0</v>
+      </c>
+      <c r="BC4">
+        <v>0</v>
+      </c>
+      <c r="BD4">
+        <v>0</v>
+      </c>
+      <c r="BE4">
+        <v>0</v>
+      </c>
+      <c r="BF4">
+        <v>0</v>
+      </c>
+      <c r="BG4">
+        <v>0</v>
+      </c>
+      <c r="BH4">
+        <v>0</v>
+      </c>
+      <c r="BI4">
+        <v>0</v>
+      </c>
+      <c r="BJ4">
+        <v>0</v>
+      </c>
+      <c r="BK4">
+        <v>0</v>
+      </c>
+      <c r="BL4">
+        <v>0</v>
+      </c>
+      <c r="BM4">
+        <v>0</v>
+      </c>
+      <c r="BN4">
+        <v>0</v>
+      </c>
+      <c r="BO4">
+        <v>0</v>
+      </c>
+      <c r="BP4">
+        <v>0</v>
+      </c>
+      <c r="BQ4">
+        <v>0</v>
+      </c>
+      <c r="BR4">
+        <v>0</v>
+      </c>
+      <c r="BS4">
+        <v>0</v>
+      </c>
+      <c r="BT4">
+        <v>0</v>
+      </c>
+      <c r="BU4">
+        <v>0</v>
+      </c>
+      <c r="BV4">
+        <v>0</v>
+      </c>
+      <c r="BW4">
+        <v>0</v>
+      </c>
+      <c r="BX4">
+        <v>0</v>
+      </c>
+      <c r="BY4">
+        <v>0</v>
+      </c>
+      <c r="BZ4">
+        <v>0</v>
+      </c>
+      <c r="CA4">
+        <v>0</v>
+      </c>
+      <c r="CB4" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="5" spans="1:80">
+      <c r="A5" t="s">
+        <v>82</v>
+      </c>
+      <c r="B5" t="s">
+        <v>83</v>
+      </c>
+      <c r="C5" t="s">
+        <v>86</v>
+      </c>
+      <c r="D5" t="s">
+        <v>90</v>
+      </c>
+      <c r="E5" t="s">
+        <v>94</v>
+      </c>
+      <c r="F5">
+        <v>2.34</v>
+      </c>
+      <c r="G5">
+        <v>2.54</v>
+      </c>
+      <c r="H5">
+        <v>2.92</v>
+      </c>
+      <c r="I5">
+        <v>3.35</v>
+      </c>
+      <c r="J5">
+        <v>3.7</v>
+      </c>
+      <c r="K5">
+        <v>4.1</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
         <v>2.26</v>
       </c>
-      <c r="Q4">
+      <c r="Q5">
         <v>1.6</v>
       </c>
-      <c r="R4">
-        <v>0</v>
-      </c>
-      <c r="S4">
-        <v>0</v>
-      </c>
-      <c r="T4">
-        <v>0</v>
-      </c>
-      <c r="U4">
-        <v>0</v>
-      </c>
-      <c r="V4">
-        <v>0</v>
-      </c>
-      <c r="W4">
-        <v>0</v>
-      </c>
-      <c r="X4">
-        <v>0</v>
-      </c>
-      <c r="Y4">
-        <v>0</v>
-      </c>
-      <c r="Z4">
-        <v>0</v>
-      </c>
-      <c r="AA4">
-        <v>0</v>
-      </c>
-      <c r="AB4">
-        <v>0</v>
-      </c>
-      <c r="AC4">
-        <v>0</v>
-      </c>
-      <c r="AD4">
-        <v>0</v>
-      </c>
-      <c r="AE4">
-        <v>0</v>
-      </c>
-      <c r="AF4">
-        <v>0</v>
-      </c>
-      <c r="AG4">
-        <v>0</v>
-      </c>
-      <c r="AH4">
-        <v>0</v>
-      </c>
-      <c r="AI4">
-        <v>0</v>
-      </c>
-      <c r="AJ4">
-        <v>0</v>
-      </c>
-      <c r="AK4">
-        <v>0</v>
-      </c>
-      <c r="AL4">
-        <v>0</v>
-      </c>
-      <c r="AM4">
-        <v>0</v>
-      </c>
-      <c r="AN4">
-        <v>0</v>
-      </c>
-      <c r="AO4">
-        <v>0</v>
-      </c>
-      <c r="AP4">
-        <v>0</v>
-      </c>
-      <c r="AQ4">
-        <v>0</v>
-      </c>
-      <c r="AR4">
-        <v>0</v>
-      </c>
-      <c r="AS4">
-        <v>0</v>
-      </c>
-      <c r="AT4">
-        <v>0</v>
-      </c>
-      <c r="AU4">
-        <v>0</v>
-      </c>
-      <c r="AV4">
-        <v>0</v>
-      </c>
-      <c r="AW4">
-        <v>0</v>
-      </c>
-      <c r="AX4">
-        <v>0</v>
-      </c>
-      <c r="AY4">
-        <v>0</v>
-      </c>
-      <c r="AZ4">
-        <v>0</v>
-      </c>
-      <c r="BA4">
-        <v>0</v>
-      </c>
-      <c r="BB4">
-        <v>0</v>
-      </c>
-      <c r="BC4">
-        <v>0</v>
-      </c>
-      <c r="BD4">
-        <v>0</v>
-      </c>
-      <c r="BE4">
-        <v>0</v>
-      </c>
-      <c r="BF4">
-        <v>0</v>
-      </c>
-      <c r="BG4">
-        <v>0</v>
-      </c>
-      <c r="BH4">
-        <v>0</v>
-      </c>
-      <c r="BI4">
-        <v>0</v>
-      </c>
-      <c r="BJ4">
-        <v>0</v>
-      </c>
-      <c r="BK4">
-        <v>0</v>
-      </c>
-      <c r="BL4">
-        <v>0</v>
-      </c>
-      <c r="BM4">
-        <v>0</v>
-      </c>
-      <c r="BN4">
-        <v>0</v>
-      </c>
-      <c r="BO4">
-        <v>0</v>
-      </c>
-      <c r="BP4">
-        <v>0</v>
-      </c>
-      <c r="BQ4">
-        <v>0</v>
-      </c>
-      <c r="BR4">
-        <v>0</v>
-      </c>
-      <c r="BS4">
-        <v>0</v>
-      </c>
-      <c r="BT4">
-        <v>0</v>
-      </c>
-      <c r="BU4">
-        <v>0</v>
-      </c>
-      <c r="BV4">
-        <v>0</v>
-      </c>
-      <c r="BW4">
-        <v>0</v>
-      </c>
-      <c r="BX4">
-        <v>0</v>
-      </c>
-      <c r="BY4">
-        <v>0</v>
-      </c>
-      <c r="BZ4">
-        <v>0</v>
-      </c>
-      <c r="CA4">
-        <v>0</v>
-      </c>
-      <c r="CB4" t="s">
-        <v>91</v>
+      <c r="R5">
+        <v>0</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>0</v>
+      </c>
+      <c r="V5">
+        <v>0</v>
+      </c>
+      <c r="W5">
+        <v>0</v>
+      </c>
+      <c r="X5">
+        <v>0</v>
+      </c>
+      <c r="Y5">
+        <v>0</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+      <c r="AA5">
+        <v>0</v>
+      </c>
+      <c r="AB5">
+        <v>0</v>
+      </c>
+      <c r="AC5">
+        <v>0</v>
+      </c>
+      <c r="AD5">
+        <v>0</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
+      <c r="AF5">
+        <v>0</v>
+      </c>
+      <c r="AG5">
+        <v>0</v>
+      </c>
+      <c r="AH5">
+        <v>0</v>
+      </c>
+      <c r="AI5">
+        <v>0</v>
+      </c>
+      <c r="AJ5">
+        <v>0</v>
+      </c>
+      <c r="AK5">
+        <v>0</v>
+      </c>
+      <c r="AL5">
+        <v>0</v>
+      </c>
+      <c r="AM5">
+        <v>0</v>
+      </c>
+      <c r="AN5">
+        <v>0</v>
+      </c>
+      <c r="AO5">
+        <v>0</v>
+      </c>
+      <c r="AP5">
+        <v>0</v>
+      </c>
+      <c r="AQ5">
+        <v>0</v>
+      </c>
+      <c r="AR5">
+        <v>0</v>
+      </c>
+      <c r="AS5">
+        <v>0</v>
+      </c>
+      <c r="AT5">
+        <v>0</v>
+      </c>
+      <c r="AU5">
+        <v>0</v>
+      </c>
+      <c r="AV5">
+        <v>0</v>
+      </c>
+      <c r="AW5">
+        <v>0</v>
+      </c>
+      <c r="AX5">
+        <v>0</v>
+      </c>
+      <c r="AY5">
+        <v>0</v>
+      </c>
+      <c r="AZ5">
+        <v>0</v>
+      </c>
+      <c r="BA5">
+        <v>0</v>
+      </c>
+      <c r="BB5">
+        <v>0</v>
+      </c>
+      <c r="BC5">
+        <v>0</v>
+      </c>
+      <c r="BD5">
+        <v>0</v>
+      </c>
+      <c r="BE5">
+        <v>0</v>
+      </c>
+      <c r="BF5">
+        <v>0</v>
+      </c>
+      <c r="BG5">
+        <v>0</v>
+      </c>
+      <c r="BH5">
+        <v>0</v>
+      </c>
+      <c r="BI5">
+        <v>0</v>
+      </c>
+      <c r="BJ5">
+        <v>0</v>
+      </c>
+      <c r="BK5">
+        <v>0</v>
+      </c>
+      <c r="BL5">
+        <v>0</v>
+      </c>
+      <c r="BM5">
+        <v>0</v>
+      </c>
+      <c r="BN5">
+        <v>0</v>
+      </c>
+      <c r="BO5">
+        <v>0</v>
+      </c>
+      <c r="BP5">
+        <v>0</v>
+      </c>
+      <c r="BQ5">
+        <v>0</v>
+      </c>
+      <c r="BR5">
+        <v>0</v>
+      </c>
+      <c r="BS5">
+        <v>0</v>
+      </c>
+      <c r="BT5">
+        <v>0</v>
+      </c>
+      <c r="BU5">
+        <v>0</v>
+      </c>
+      <c r="BV5">
+        <v>0</v>
+      </c>
+      <c r="BW5">
+        <v>0</v>
+      </c>
+      <c r="BX5">
+        <v>0</v>
+      </c>
+      <c r="BY5">
+        <v>0</v>
+      </c>
+      <c r="BZ5">
+        <v>0</v>
+      </c>
+      <c r="CA5">
+        <v>0</v>
+      </c>
+      <c r="CB5" t="s">
+        <v>95</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-28.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-28.xlsx
@@ -301,7 +301,7 @@
     <t>United IK Nordic</t>
   </si>
   <si>
-    <t>2026-07-26 08:32:53</t>
+    <t>2026-07-26 10:45:17</t>
   </si>
 </sst>
 </file>
@@ -898,40 +898,40 @@
         <v>2.38</v>
       </c>
       <c r="G2">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="H2">
         <v>3.25</v>
       </c>
       <c r="I2">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="J2">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="K2">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="L2">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="M2">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="N2">
         <v>2.58</v>
       </c>
       <c r="O2">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="P2">
         <v>1.53</v>
       </c>
       <c r="Q2">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="R2">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="S2">
         <v>5</v>
@@ -940,16 +940,16 @@
         <v>2.02</v>
       </c>
       <c r="U2">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="V2">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W2">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="X2">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y2">
         <v>10.5</v>
@@ -1006,13 +1006,13 @@
         <v>7.6</v>
       </c>
       <c r="AQ2">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AR2">
         <v>19.5</v>
       </c>
       <c r="AS2">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AT2">
         <v>6.6</v>
@@ -1036,7 +1036,7 @@
         <v>18.5</v>
       </c>
       <c r="BA2">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BB2">
         <v>25</v>
@@ -1048,34 +1048,34 @@
         <v>42</v>
       </c>
       <c r="BE2">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BF2">
         <v>27</v>
       </c>
       <c r="BG2">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BH2">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="BI2">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="BJ2">
         <v>11.5</v>
       </c>
       <c r="BK2">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BN2">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BO2">
         <v>3.95</v>
@@ -1084,37 +1084,37 @@
         <v>23</v>
       </c>
       <c r="BQ2">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BR2">
         <v>46</v>
       </c>
       <c r="BS2">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="BT2">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BU2">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="BV2">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BW2">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX2">
         <v>60</v>
       </c>
       <c r="BY2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BZ2">
         <v>50</v>
       </c>
       <c r="CA2">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CB2" t="s">
         <v>95</v>
@@ -1146,10 +1146,10 @@
         <v>1.88</v>
       </c>
       <c r="I3">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="J3">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K3">
         <v>3.45</v>
@@ -1185,7 +1185,7 @@
         <v>1.77</v>
       </c>
       <c r="V3">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="W3">
         <v>1.21</v>
@@ -1215,7 +1215,7 @@
         <v>34</v>
       </c>
       <c r="AF3">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AG3">
         <v>22</v>
@@ -1257,46 +1257,46 @@
         <v>17</v>
       </c>
       <c r="AT3">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AU3">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="AV3">
         <v>8.4</v>
       </c>
       <c r="AW3">
-        <v>6.4</v>
+        <v>21</v>
       </c>
       <c r="AX3">
         <v>7.2</v>
       </c>
       <c r="AY3">
-        <v>6.2</v>
+        <v>17.5</v>
       </c>
       <c r="AZ3">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BA3">
         <v>7.6</v>
       </c>
       <c r="BB3">
+        <v>8.6</v>
+      </c>
+      <c r="BC3">
         <v>8.199999999999999</v>
       </c>
-      <c r="BC3">
-        <v>8</v>
-      </c>
       <c r="BD3">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BE3">
+        <v>8.6</v>
+      </c>
+      <c r="BF3">
         <v>8.4</v>
       </c>
-      <c r="BF3">
-        <v>8.199999999999999</v>
-      </c>
       <c r="BG3">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BH3">
         <v>3</v>
@@ -1338,7 +1338,7 @@
         <v>4.5</v>
       </c>
       <c r="BU3">
-        <v>3.15</v>
+        <v>3.75</v>
       </c>
       <c r="BV3">
         <v>15.5</v>
@@ -1654,7 +1654,7 @@
         <v>2.26</v>
       </c>
       <c r="Q5">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="R5">
         <v>0</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-28.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-28.xlsx
@@ -301,7 +301,7 @@
     <t>United IK Nordic</t>
   </si>
   <si>
-    <t>2026-07-26 10:45:17</t>
+    <t>2026-07-26 12:56:39</t>
   </si>
 </sst>
 </file>
@@ -907,7 +907,7 @@
         <v>3.8</v>
       </c>
       <c r="J2">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="K2">
         <v>3.3</v>
@@ -919,7 +919,7 @@
         <v>1.12</v>
       </c>
       <c r="N2">
-        <v>2.58</v>
+        <v>2.66</v>
       </c>
       <c r="O2">
         <v>1.5</v>
@@ -1624,16 +1624,16 @@
         <v>2.34</v>
       </c>
       <c r="G5">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="H5">
         <v>2.92</v>
       </c>
       <c r="I5">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="J5">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="K5">
         <v>4.1</v>
@@ -1654,7 +1654,7 @@
         <v>2.26</v>
       </c>
       <c r="Q5">
-        <v>1.59</v>
+        <v>1.69</v>
       </c>
       <c r="R5">
         <v>0</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-28.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-28.xlsx
@@ -301,7 +301,7 @@
     <t>United IK Nordic</t>
   </si>
   <si>
-    <t>2026-07-26 12:56:39</t>
+    <t>2026-07-26 15:07:13</t>
   </si>
 </sst>
 </file>
@@ -895,7 +895,7 @@
         <v>91</v>
       </c>
       <c r="F2">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="G2">
         <v>2.68</v>
@@ -907,7 +907,7 @@
         <v>3.8</v>
       </c>
       <c r="J2">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="K2">
         <v>3.3</v>
@@ -928,7 +928,7 @@
         <v>1.53</v>
       </c>
       <c r="Q2">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="R2">
         <v>1.21</v>
@@ -958,7 +958,7 @@
         <v>28</v>
       </c>
       <c r="AA2">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="AB2">
         <v>8.199999999999999</v>
@@ -982,7 +982,7 @@
         <v>23</v>
       </c>
       <c r="AI2">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="AJ2">
         <v>48</v>
@@ -991,7 +991,7 @@
         <v>38</v>
       </c>
       <c r="AL2">
-        <v>90</v>
+        <v>65</v>
       </c>
       <c r="AM2">
         <v>210</v>
@@ -1000,7 +1000,7 @@
         <v>46</v>
       </c>
       <c r="AO2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AP2">
         <v>7.6</v>
@@ -1039,10 +1039,10 @@
         <v>7.8</v>
       </c>
       <c r="BB2">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="BC2">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="BD2">
         <v>42</v>
@@ -1051,7 +1051,7 @@
         <v>8.4</v>
       </c>
       <c r="BF2">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="BG2">
         <v>7.8</v>
@@ -1060,7 +1060,7 @@
         <v>2.82</v>
       </c>
       <c r="BI2">
-        <v>2.48</v>
+        <v>2.28</v>
       </c>
       <c r="BJ2">
         <v>11.5</v>
@@ -1078,13 +1078,13 @@
         <v>5.3</v>
       </c>
       <c r="BO2">
-        <v>3.95</v>
+        <v>4.5</v>
       </c>
       <c r="BP2">
         <v>23</v>
       </c>
       <c r="BQ2">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BR2">
         <v>46</v>
@@ -1102,10 +1102,10 @@
         <v>34</v>
       </c>
       <c r="BW2">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BX2">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BY2">
         <v>10</v>
@@ -1140,22 +1140,22 @@
         <v>4.6</v>
       </c>
       <c r="G3">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="H3">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="I3">
         <v>2.02</v>
       </c>
       <c r="J3">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="K3">
         <v>3.45</v>
       </c>
       <c r="L3">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="M3">
         <v>1.1</v>
@@ -1212,19 +1212,19 @@
         <v>11.5</v>
       </c>
       <c r="AE3">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="AF3">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AG3">
         <v>22</v>
       </c>
       <c r="AH3">
-        <v>32</v>
+        <v>950</v>
       </c>
       <c r="AI3">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AJ3">
         <v>170</v>
@@ -1260,19 +1260,19 @@
         <v>5.5</v>
       </c>
       <c r="AU3">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="AV3">
         <v>8.4</v>
       </c>
       <c r="AW3">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="AX3">
         <v>7.2</v>
       </c>
       <c r="AY3">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="AZ3">
         <v>6.6</v>
@@ -1338,7 +1338,7 @@
         <v>4.5</v>
       </c>
       <c r="BU3">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="BV3">
         <v>15.5</v>
@@ -1394,19 +1394,19 @@
         <v>3.7</v>
       </c>
       <c r="K4">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L4">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="M4">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="P4">
         <v>2.18</v>
@@ -1415,184 +1415,184 @@
         <v>1.73</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="U4">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="V4">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="W4">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="X4">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="Y4">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="Z4">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AA4">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AB4">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AC4">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AE4">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AF4">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AG4">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AH4">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AI4">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AJ4">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AK4">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AL4">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AM4">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AN4">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AO4">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AP4">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AQ4">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AR4">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AS4">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AT4">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AU4">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AV4">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW4">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AX4">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AY4">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AZ4">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="BA4">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BB4">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="BC4">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="BD4">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="BE4">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="BF4">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BG4">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH4">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="BI4">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="BJ4">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="BK4">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="BL4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM4">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="BN4">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="BO4">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="BP4">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="BQ4">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BR4">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="BS4">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BT4">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="BU4">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BV4">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="BW4">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="BX4">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="BY4">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BZ4">
         <v>0</v>
@@ -1621,34 +1621,34 @@
         <v>94</v>
       </c>
       <c r="F5">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="G5">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="H5">
         <v>2.92</v>
       </c>
       <c r="I5">
-        <v>3.5</v>
+        <v>3.15</v>
       </c>
       <c r="J5">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="K5">
         <v>4.1</v>
       </c>
       <c r="L5">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="M5">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="P5">
         <v>2.26</v>
@@ -1657,190 +1657,190 @@
         <v>1.69</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="U5">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="V5">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W5">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="X5">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="Y5">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="Z5">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AA5">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AB5">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AC5">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AD5">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AE5">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AF5">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AG5">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AH5">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AI5">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AJ5">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AK5">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AL5">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AM5">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AN5">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AO5">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AP5">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AQ5">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AR5">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AS5">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AT5">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AU5">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AV5">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AW5">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AX5">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AY5">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ5">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="BA5">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BB5">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BC5">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="BD5">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BE5">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BF5">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="BG5">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="BH5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BI5">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="BJ5">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK5">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="BL5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM5">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="BN5">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="BO5">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BP5">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="BQ5">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR5">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="BS5">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT5">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="BU5">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="BV5">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="BW5">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY5">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BZ5">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="CA5">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="CB5" t="s">
         <v>95</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-28.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-28.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="104">
   <si>
     <t>League</t>
   </si>
@@ -265,6 +265,12 @@
     <t>Swedish Superettan</t>
   </si>
   <si>
+    <t>Paraguayan Primera Division</t>
+  </si>
+  <si>
+    <t>Icelandic 1 Deild</t>
+  </si>
+  <si>
     <t>2026-07-28</t>
   </si>
   <si>
@@ -277,6 +283,12 @@
     <t>17:00:00</t>
   </si>
   <si>
+    <t>19:00:00</t>
+  </si>
+  <si>
+    <t>19:15:00</t>
+  </si>
+  <si>
     <t>Deportivo Cuenca</t>
   </si>
   <si>
@@ -289,6 +301,12 @@
     <t>Helsingborgs</t>
   </si>
   <si>
+    <t>Rubio Nu</t>
+  </si>
+  <si>
+    <t>Aegir</t>
+  </si>
+  <si>
     <t>Emelec</t>
   </si>
   <si>
@@ -301,7 +319,13 @@
     <t>United IK Nordic</t>
   </si>
   <si>
-    <t>2026-07-26 15:07:13</t>
+    <t>Club Sportivo Ameliano</t>
+  </si>
+  <si>
+    <t>Njardvik</t>
+  </si>
+  <si>
+    <t>2026-07-26 17:16:30</t>
   </si>
 </sst>
 </file>
@@ -633,7 +657,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB5"/>
+  <dimension ref="A1:CB7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -883,16 +907,16 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D2" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="E2" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="F2">
         <v>2.4</v>
@@ -907,13 +931,13 @@
         <v>3.8</v>
       </c>
       <c r="J2">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="K2">
         <v>3.3</v>
       </c>
       <c r="L2">
-        <v>1.47</v>
+        <v>1.54</v>
       </c>
       <c r="M2">
         <v>1.12</v>
@@ -925,7 +949,7 @@
         <v>1.5</v>
       </c>
       <c r="P2">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="Q2">
         <v>2.52</v>
@@ -934,13 +958,13 @@
         <v>1.21</v>
       </c>
       <c r="S2">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="T2">
         <v>2.02</v>
       </c>
       <c r="U2">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="V2">
         <v>1.36</v>
@@ -967,7 +991,7 @@
         <v>7.4</v>
       </c>
       <c r="AD2">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AE2">
         <v>60</v>
@@ -985,7 +1009,7 @@
         <v>80</v>
       </c>
       <c r="AJ2">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AK2">
         <v>38</v>
@@ -1012,7 +1036,7 @@
         <v>19.5</v>
       </c>
       <c r="AS2">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT2">
         <v>6.6</v>
@@ -1036,7 +1060,7 @@
         <v>18.5</v>
       </c>
       <c r="BA2">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB2">
         <v>32</v>
@@ -1048,13 +1072,13 @@
         <v>42</v>
       </c>
       <c r="BE2">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF2">
         <v>30</v>
       </c>
       <c r="BG2">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH2">
         <v>2.82</v>
@@ -1078,7 +1102,7 @@
         <v>5.3</v>
       </c>
       <c r="BO2">
-        <v>4.5</v>
+        <v>3.95</v>
       </c>
       <c r="BP2">
         <v>23</v>
@@ -1096,7 +1120,7 @@
         <v>6.6</v>
       </c>
       <c r="BU2">
-        <v>5.5</v>
+        <v>4.8</v>
       </c>
       <c r="BV2">
         <v>34</v>
@@ -1117,7 +1141,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="CB2" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1125,16 +1149,16 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D3" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="E3" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="F3">
         <v>4.6</v>
@@ -1359,7 +1383,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="CB3" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1367,16 +1391,16 @@
         <v>82</v>
       </c>
       <c r="B4" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C4" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D4" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="E4" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="F4">
         <v>3.35</v>
@@ -1412,7 +1436,7 @@
         <v>2.18</v>
       </c>
       <c r="Q4">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="R4">
         <v>1.47</v>
@@ -1430,7 +1454,7 @@
         <v>1.8</v>
       </c>
       <c r="W4">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="X4">
         <v>23</v>
@@ -1601,7 +1625,7 @@
         <v>0</v>
       </c>
       <c r="CB4" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1609,22 +1633,22 @@
         <v>82</v>
       </c>
       <c r="B5" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C5" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D5" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="E5" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="F5">
         <v>2.36</v>
       </c>
       <c r="G5">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="H5">
         <v>2.92</v>
@@ -1663,16 +1687,16 @@
         <v>2.74</v>
       </c>
       <c r="T5">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="U5">
         <v>2.42</v>
       </c>
       <c r="V5">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="W5">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="X5">
         <v>24</v>
@@ -1732,16 +1756,16 @@
         <v>18</v>
       </c>
       <c r="AQ5">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="AR5">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AS5">
         <v>4.7</v>
       </c>
       <c r="AT5">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="AU5">
         <v>8</v>
@@ -1768,7 +1792,7 @@
         <v>4.5</v>
       </c>
       <c r="BC5">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BD5">
         <v>4.5</v>
@@ -1780,7 +1804,7 @@
         <v>11.5</v>
       </c>
       <c r="BG5">
-        <v>16.5</v>
+        <v>19</v>
       </c>
       <c r="BH5">
         <v>4</v>
@@ -1822,7 +1846,7 @@
         <v>6.4</v>
       </c>
       <c r="BU5">
-        <v>5.7</v>
+        <v>5</v>
       </c>
       <c r="BV5">
         <v>22</v>
@@ -1843,7 +1867,491 @@
         <v>8.6</v>
       </c>
       <c r="CB5" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="6" spans="1:80">
+      <c r="A6" t="s">
+        <v>83</v>
+      </c>
+      <c r="B6" t="s">
+        <v>85</v>
+      </c>
+      <c r="C6" t="s">
+        <v>89</v>
+      </c>
+      <c r="D6" t="s">
         <v>95</v>
+      </c>
+      <c r="E6" t="s">
+        <v>101</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>0</v>
+      </c>
+      <c r="L6">
+        <v>1.01</v>
+      </c>
+      <c r="M6">
+        <v>1.01</v>
+      </c>
+      <c r="N6">
+        <v>1.25</v>
+      </c>
+      <c r="O6">
+        <v>1.49</v>
+      </c>
+      <c r="P6">
+        <v>1.25</v>
+      </c>
+      <c r="Q6">
+        <v>1.49</v>
+      </c>
+      <c r="R6">
+        <v>1.18</v>
+      </c>
+      <c r="S6">
+        <v>1.49</v>
+      </c>
+      <c r="T6">
+        <v>1.11</v>
+      </c>
+      <c r="U6">
+        <v>1.11</v>
+      </c>
+      <c r="V6">
+        <v>1.01</v>
+      </c>
+      <c r="W6">
+        <v>1.01</v>
+      </c>
+      <c r="X6">
+        <v>1000</v>
+      </c>
+      <c r="Y6">
+        <v>1000</v>
+      </c>
+      <c r="Z6">
+        <v>1000</v>
+      </c>
+      <c r="AA6">
+        <v>1000</v>
+      </c>
+      <c r="AB6">
+        <v>1000</v>
+      </c>
+      <c r="AC6">
+        <v>1000</v>
+      </c>
+      <c r="AD6">
+        <v>1000</v>
+      </c>
+      <c r="AE6">
+        <v>1000</v>
+      </c>
+      <c r="AF6">
+        <v>1000</v>
+      </c>
+      <c r="AG6">
+        <v>1000</v>
+      </c>
+      <c r="AH6">
+        <v>1000</v>
+      </c>
+      <c r="AI6">
+        <v>1000</v>
+      </c>
+      <c r="AJ6">
+        <v>1000</v>
+      </c>
+      <c r="AK6">
+        <v>1000</v>
+      </c>
+      <c r="AL6">
+        <v>1000</v>
+      </c>
+      <c r="AM6">
+        <v>1000</v>
+      </c>
+      <c r="AN6">
+        <v>1000</v>
+      </c>
+      <c r="AO6">
+        <v>1000</v>
+      </c>
+      <c r="AP6">
+        <v>1.01</v>
+      </c>
+      <c r="AQ6">
+        <v>1.01</v>
+      </c>
+      <c r="AR6">
+        <v>1.01</v>
+      </c>
+      <c r="AS6">
+        <v>1.01</v>
+      </c>
+      <c r="AT6">
+        <v>1.01</v>
+      </c>
+      <c r="AU6">
+        <v>1.01</v>
+      </c>
+      <c r="AV6">
+        <v>1.01</v>
+      </c>
+      <c r="AW6">
+        <v>1.01</v>
+      </c>
+      <c r="AX6">
+        <v>1.01</v>
+      </c>
+      <c r="AY6">
+        <v>1.01</v>
+      </c>
+      <c r="AZ6">
+        <v>1.01</v>
+      </c>
+      <c r="BA6">
+        <v>1.01</v>
+      </c>
+      <c r="BB6">
+        <v>1.01</v>
+      </c>
+      <c r="BC6">
+        <v>1.01</v>
+      </c>
+      <c r="BD6">
+        <v>1.01</v>
+      </c>
+      <c r="BE6">
+        <v>1.01</v>
+      </c>
+      <c r="BF6">
+        <v>1.01</v>
+      </c>
+      <c r="BG6">
+        <v>1.01</v>
+      </c>
+      <c r="BH6">
+        <v>1000</v>
+      </c>
+      <c r="BI6">
+        <v>1.04</v>
+      </c>
+      <c r="BJ6">
+        <v>1000</v>
+      </c>
+      <c r="BK6">
+        <v>1.04</v>
+      </c>
+      <c r="BL6">
+        <v>1000</v>
+      </c>
+      <c r="BM6">
+        <v>1.04</v>
+      </c>
+      <c r="BN6">
+        <v>1000</v>
+      </c>
+      <c r="BO6">
+        <v>1.04</v>
+      </c>
+      <c r="BP6">
+        <v>1000</v>
+      </c>
+      <c r="BQ6">
+        <v>1.04</v>
+      </c>
+      <c r="BR6">
+        <v>1000</v>
+      </c>
+      <c r="BS6">
+        <v>1.04</v>
+      </c>
+      <c r="BT6">
+        <v>1000</v>
+      </c>
+      <c r="BU6">
+        <v>1.04</v>
+      </c>
+      <c r="BV6">
+        <v>1000</v>
+      </c>
+      <c r="BW6">
+        <v>1.04</v>
+      </c>
+      <c r="BX6">
+        <v>1000</v>
+      </c>
+      <c r="BY6">
+        <v>1.04</v>
+      </c>
+      <c r="BZ6">
+        <v>0</v>
+      </c>
+      <c r="CA6">
+        <v>0</v>
+      </c>
+      <c r="CB6" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="7" spans="1:80">
+      <c r="A7" t="s">
+        <v>84</v>
+      </c>
+      <c r="B7" t="s">
+        <v>85</v>
+      </c>
+      <c r="C7" t="s">
+        <v>90</v>
+      </c>
+      <c r="D7" t="s">
+        <v>96</v>
+      </c>
+      <c r="E7" t="s">
+        <v>102</v>
+      </c>
+      <c r="F7">
+        <v>1.04</v>
+      </c>
+      <c r="G7">
+        <v>1000</v>
+      </c>
+      <c r="H7">
+        <v>1.04</v>
+      </c>
+      <c r="I7">
+        <v>1000</v>
+      </c>
+      <c r="J7">
+        <v>1.01</v>
+      </c>
+      <c r="K7">
+        <v>1000</v>
+      </c>
+      <c r="L7">
+        <v>1.01</v>
+      </c>
+      <c r="M7">
+        <v>1.02</v>
+      </c>
+      <c r="N7">
+        <v>1.25</v>
+      </c>
+      <c r="O7">
+        <v>1.1</v>
+      </c>
+      <c r="P7">
+        <v>1.25</v>
+      </c>
+      <c r="Q7">
+        <v>1.1</v>
+      </c>
+      <c r="R7">
+        <v>1.24</v>
+      </c>
+      <c r="S7">
+        <v>1.1</v>
+      </c>
+      <c r="T7">
+        <v>1.11</v>
+      </c>
+      <c r="U7">
+        <v>1.11</v>
+      </c>
+      <c r="V7">
+        <v>1.01</v>
+      </c>
+      <c r="W7">
+        <v>1.01</v>
+      </c>
+      <c r="X7">
+        <v>1000</v>
+      </c>
+      <c r="Y7">
+        <v>1000</v>
+      </c>
+      <c r="Z7">
+        <v>1000</v>
+      </c>
+      <c r="AA7">
+        <v>1000</v>
+      </c>
+      <c r="AB7">
+        <v>1000</v>
+      </c>
+      <c r="AC7">
+        <v>1000</v>
+      </c>
+      <c r="AD7">
+        <v>1000</v>
+      </c>
+      <c r="AE7">
+        <v>1000</v>
+      </c>
+      <c r="AF7">
+        <v>1000</v>
+      </c>
+      <c r="AG7">
+        <v>1000</v>
+      </c>
+      <c r="AH7">
+        <v>1000</v>
+      </c>
+      <c r="AI7">
+        <v>1000</v>
+      </c>
+      <c r="AJ7">
+        <v>1000</v>
+      </c>
+      <c r="AK7">
+        <v>1000</v>
+      </c>
+      <c r="AL7">
+        <v>1000</v>
+      </c>
+      <c r="AM7">
+        <v>1000</v>
+      </c>
+      <c r="AN7">
+        <v>1000</v>
+      </c>
+      <c r="AO7">
+        <v>1000</v>
+      </c>
+      <c r="AP7">
+        <v>1.01</v>
+      </c>
+      <c r="AQ7">
+        <v>1.01</v>
+      </c>
+      <c r="AR7">
+        <v>1.01</v>
+      </c>
+      <c r="AS7">
+        <v>1.01</v>
+      </c>
+      <c r="AT7">
+        <v>1.01</v>
+      </c>
+      <c r="AU7">
+        <v>1.01</v>
+      </c>
+      <c r="AV7">
+        <v>1.01</v>
+      </c>
+      <c r="AW7">
+        <v>1.01</v>
+      </c>
+      <c r="AX7">
+        <v>1.01</v>
+      </c>
+      <c r="AY7">
+        <v>1.01</v>
+      </c>
+      <c r="AZ7">
+        <v>1.01</v>
+      </c>
+      <c r="BA7">
+        <v>1.01</v>
+      </c>
+      <c r="BB7">
+        <v>1.01</v>
+      </c>
+      <c r="BC7">
+        <v>1.01</v>
+      </c>
+      <c r="BD7">
+        <v>1.01</v>
+      </c>
+      <c r="BE7">
+        <v>1.01</v>
+      </c>
+      <c r="BF7">
+        <v>1.01</v>
+      </c>
+      <c r="BG7">
+        <v>1.01</v>
+      </c>
+      <c r="BH7">
+        <v>1000</v>
+      </c>
+      <c r="BI7">
+        <v>1.04</v>
+      </c>
+      <c r="BJ7">
+        <v>1000</v>
+      </c>
+      <c r="BK7">
+        <v>1.04</v>
+      </c>
+      <c r="BL7">
+        <v>1000</v>
+      </c>
+      <c r="BM7">
+        <v>1.04</v>
+      </c>
+      <c r="BN7">
+        <v>1000</v>
+      </c>
+      <c r="BO7">
+        <v>1.04</v>
+      </c>
+      <c r="BP7">
+        <v>1000</v>
+      </c>
+      <c r="BQ7">
+        <v>1.04</v>
+      </c>
+      <c r="BR7">
+        <v>1000</v>
+      </c>
+      <c r="BS7">
+        <v>1.04</v>
+      </c>
+      <c r="BT7">
+        <v>1000</v>
+      </c>
+      <c r="BU7">
+        <v>1.04</v>
+      </c>
+      <c r="BV7">
+        <v>1000</v>
+      </c>
+      <c r="BW7">
+        <v>1.04</v>
+      </c>
+      <c r="BX7">
+        <v>1000</v>
+      </c>
+      <c r="BY7">
+        <v>1.04</v>
+      </c>
+      <c r="BZ7">
+        <v>1000</v>
+      </c>
+      <c r="CA7">
+        <v>1.04</v>
+      </c>
+      <c r="CB7" t="s">
+        <v>103</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-28.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-28.xlsx
@@ -325,7 +325,7 @@
     <t>Njardvik</t>
   </si>
   <si>
-    <t>2026-07-26 17:16:30</t>
+    <t>2026-07-26 19:25:08</t>
   </si>
 </sst>
 </file>
@@ -934,7 +934,7 @@
         <v>2.98</v>
       </c>
       <c r="K2">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="L2">
         <v>1.54</v>
@@ -1090,7 +1090,7 @@
         <v>11.5</v>
       </c>
       <c r="BK2">
-        <v>5.9</v>
+        <v>8</v>
       </c>
       <c r="BL2">
         <v>1000</v>
@@ -1102,7 +1102,7 @@
         <v>5.3</v>
       </c>
       <c r="BO2">
-        <v>3.95</v>
+        <v>4.5</v>
       </c>
       <c r="BP2">
         <v>23</v>
@@ -1120,7 +1120,7 @@
         <v>6.6</v>
       </c>
       <c r="BU2">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="BV2">
         <v>34</v>
@@ -1161,7 +1161,7 @@
         <v>98</v>
       </c>
       <c r="F3">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="G3">
         <v>6</v>
@@ -1406,16 +1406,16 @@
         <v>3.35</v>
       </c>
       <c r="G4">
-        <v>3.65</v>
+        <v>3.45</v>
       </c>
       <c r="H4">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="I4">
         <v>2.24</v>
       </c>
       <c r="J4">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K4">
         <v>4</v>
@@ -1439,10 +1439,10 @@
         <v>1.74</v>
       </c>
       <c r="R4">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="S4">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="T4">
         <v>1.64</v>
@@ -1454,7 +1454,7 @@
         <v>1.8</v>
       </c>
       <c r="W4">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="X4">
         <v>23</v>
@@ -1493,7 +1493,7 @@
         <v>32</v>
       </c>
       <c r="AJ4">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AK4">
         <v>46</v>
@@ -1505,7 +1505,7 @@
         <v>75</v>
       </c>
       <c r="AN4">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="AO4">
         <v>15.5</v>
@@ -1520,7 +1520,7 @@
         <v>13.5</v>
       </c>
       <c r="AS4">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="AT4">
         <v>14</v>
@@ -1535,7 +1535,7 @@
         <v>19</v>
       </c>
       <c r="AX4">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="AY4">
         <v>13</v>
@@ -1550,13 +1550,13 @@
         <v>5.7</v>
       </c>
       <c r="BC4">
+        <v>5.4</v>
+      </c>
+      <c r="BD4">
         <v>5.5</v>
       </c>
-      <c r="BD4">
+      <c r="BE4">
         <v>5.7</v>
-      </c>
-      <c r="BE4">
-        <v>5.8</v>
       </c>
       <c r="BF4">
         <v>21</v>
@@ -1568,7 +1568,7 @@
         <v>3.85</v>
       </c>
       <c r="BI4">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="BJ4">
         <v>9</v>
@@ -1586,7 +1586,7 @@
         <v>7</v>
       </c>
       <c r="BO4">
-        <v>6</v>
+        <v>5.2</v>
       </c>
       <c r="BP4">
         <v>26</v>
@@ -1604,7 +1604,7 @@
         <v>5.2</v>
       </c>
       <c r="BU4">
-        <v>4.7</v>
+        <v>4</v>
       </c>
       <c r="BV4">
         <v>15</v>
@@ -1660,7 +1660,7 @@
         <v>3.7</v>
       </c>
       <c r="K5">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L5">
         <v>1.28</v>
@@ -1687,10 +1687,10 @@
         <v>2.74</v>
       </c>
       <c r="T5">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="U5">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="V5">
         <v>1.47</v>
@@ -2141,7 +2141,7 @@
         <v>1000</v>
       </c>
       <c r="J7">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="K7">
         <v>1000</v>
@@ -2153,19 +2153,19 @@
         <v>1.02</v>
       </c>
       <c r="N7">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="O7">
         <v>1.1</v>
       </c>
       <c r="P7">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="Q7">
         <v>1.1</v>
       </c>
       <c r="R7">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="S7">
         <v>1.1</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-28.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-28.xlsx
@@ -325,7 +325,7 @@
     <t>Njardvik</t>
   </si>
   <si>
-    <t>2026-07-26 19:25:08</t>
+    <t>2026-07-26 21:32:28</t>
   </si>
 </sst>
 </file>
@@ -919,22 +919,22 @@
         <v>97</v>
       </c>
       <c r="F2">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="G2">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="H2">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="I2">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="J2">
         <v>2.98</v>
       </c>
       <c r="K2">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="L2">
         <v>1.54</v>
@@ -943,7 +943,7 @@
         <v>1.12</v>
       </c>
       <c r="N2">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="O2">
         <v>1.5</v>
@@ -961,7 +961,7 @@
         <v>5.1</v>
       </c>
       <c r="T2">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="U2">
         <v>1.8</v>
@@ -970,7 +970,7 @@
         <v>1.36</v>
       </c>
       <c r="W2">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="X2">
         <v>9.199999999999999</v>
@@ -1009,10 +1009,10 @@
         <v>80</v>
       </c>
       <c r="AJ2">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AK2">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AL2">
         <v>65</v>
@@ -1027,7 +1027,7 @@
         <v>75</v>
       </c>
       <c r="AP2">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AQ2">
         <v>8.6</v>
@@ -1036,7 +1036,7 @@
         <v>19.5</v>
       </c>
       <c r="AS2">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AT2">
         <v>6.6</v>
@@ -1060,7 +1060,7 @@
         <v>18.5</v>
       </c>
       <c r="BA2">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BB2">
         <v>32</v>
@@ -1072,16 +1072,16 @@
         <v>42</v>
       </c>
       <c r="BE2">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BF2">
         <v>30</v>
       </c>
       <c r="BG2">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BH2">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="BI2">
         <v>2.28</v>
@@ -1096,7 +1096,7 @@
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BN2">
         <v>5.3</v>
@@ -1108,25 +1108,25 @@
         <v>23</v>
       </c>
       <c r="BQ2">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR2">
         <v>46</v>
       </c>
       <c r="BS2">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BT2">
         <v>6.6</v>
       </c>
       <c r="BU2">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BV2">
         <v>34</v>
       </c>
       <c r="BW2">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX2">
         <v>1000</v>
@@ -1138,7 +1138,7 @@
         <v>50</v>
       </c>
       <c r="CA2">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="CB2" t="s">
         <v>103</v>
@@ -1167,13 +1167,13 @@
         <v>6</v>
       </c>
       <c r="H3">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="I3">
         <v>2.02</v>
       </c>
       <c r="J3">
-        <v>3.2</v>
+        <v>2.96</v>
       </c>
       <c r="K3">
         <v>3.45</v>
@@ -1269,34 +1269,34 @@
         <v>21</v>
       </c>
       <c r="AP3">
-        <v>7.8</v>
+        <v>4.8</v>
       </c>
       <c r="AQ3">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="AR3">
-        <v>8.199999999999999</v>
+        <v>4.9</v>
       </c>
       <c r="AS3">
-        <v>17</v>
+        <v>6.4</v>
       </c>
       <c r="AT3">
         <v>5.5</v>
       </c>
       <c r="AU3">
-        <v>6.2</v>
+        <v>4.3</v>
       </c>
       <c r="AV3">
-        <v>8.4</v>
+        <v>5</v>
       </c>
       <c r="AW3">
-        <v>18.5</v>
+        <v>6.6</v>
       </c>
       <c r="AX3">
         <v>7.2</v>
       </c>
       <c r="AY3">
-        <v>15.5</v>
+        <v>6.4</v>
       </c>
       <c r="AZ3">
         <v>6.6</v>
@@ -1568,13 +1568,13 @@
         <v>3.85</v>
       </c>
       <c r="BI4">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="BJ4">
         <v>9</v>
       </c>
       <c r="BK4">
-        <v>5.8</v>
+        <v>6.8</v>
       </c>
       <c r="BL4">
         <v>1000</v>
@@ -1586,7 +1586,7 @@
         <v>7</v>
       </c>
       <c r="BO4">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="BP4">
         <v>26</v>
@@ -1604,7 +1604,7 @@
         <v>5.2</v>
       </c>
       <c r="BU4">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="BV4">
         <v>15</v>
@@ -1828,7 +1828,7 @@
         <v>5.7</v>
       </c>
       <c r="BO5">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="BP5">
         <v>17</v>
@@ -1846,7 +1846,7 @@
         <v>6.4</v>
       </c>
       <c r="BU5">
-        <v>5</v>
+        <v>5.7</v>
       </c>
       <c r="BV5">
         <v>22</v>
@@ -2141,7 +2141,7 @@
         <v>1000</v>
       </c>
       <c r="J7">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="K7">
         <v>1000</v>
@@ -2153,19 +2153,19 @@
         <v>1.02</v>
       </c>
       <c r="N7">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="O7">
         <v>1.1</v>
       </c>
       <c r="P7">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="Q7">
         <v>1.1</v>
       </c>
       <c r="R7">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="S7">
         <v>1.1</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-28.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-28.xlsx
@@ -325,7 +325,7 @@
     <t>Njardvik</t>
   </si>
   <si>
-    <t>2026-07-26 21:32:28</t>
+    <t>2026-07-26 23:40:05</t>
   </si>
 </sst>
 </file>
@@ -934,7 +934,7 @@
         <v>2.98</v>
       </c>
       <c r="K2">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="L2">
         <v>1.54</v>
@@ -949,13 +949,13 @@
         <v>1.5</v>
       </c>
       <c r="P2">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="Q2">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="R2">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="S2">
         <v>5.1</v>
@@ -964,7 +964,7 @@
         <v>2.04</v>
       </c>
       <c r="U2">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="V2">
         <v>1.36</v>
@@ -1000,7 +1000,7 @@
         <v>15.5</v>
       </c>
       <c r="AG2">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH2">
         <v>23</v>
@@ -1036,7 +1036,7 @@
         <v>19.5</v>
       </c>
       <c r="AS2">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AT2">
         <v>6.6</v>
@@ -1060,7 +1060,7 @@
         <v>18.5</v>
       </c>
       <c r="BA2">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB2">
         <v>32</v>
@@ -1072,19 +1072,19 @@
         <v>42</v>
       </c>
       <c r="BE2">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BF2">
         <v>30</v>
       </c>
       <c r="BG2">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BH2">
         <v>2.8</v>
       </c>
       <c r="BI2">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="BJ2">
         <v>11.5</v>
@@ -1096,7 +1096,7 @@
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BN2">
         <v>5.3</v>
@@ -1105,13 +1105,13 @@
         <v>4.5</v>
       </c>
       <c r="BP2">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BQ2">
         <v>8.199999999999999</v>
       </c>
       <c r="BR2">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="BS2">
         <v>10</v>
@@ -1126,19 +1126,19 @@
         <v>34</v>
       </c>
       <c r="BW2">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BX2">
         <v>1000</v>
       </c>
       <c r="BY2">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BZ2">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="CA2">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="CB2" t="s">
         <v>103</v>
@@ -1173,7 +1173,7 @@
         <v>2.02</v>
       </c>
       <c r="J3">
-        <v>2.96</v>
+        <v>3.25</v>
       </c>
       <c r="K3">
         <v>3.45</v>
@@ -1185,7 +1185,7 @@
         <v>1.1</v>
       </c>
       <c r="N3">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="O3">
         <v>1.46</v>
@@ -1212,7 +1212,7 @@
         <v>1.98</v>
       </c>
       <c r="W3">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="X3">
         <v>10.5</v>
@@ -1254,7 +1254,7 @@
         <v>170</v>
       </c>
       <c r="AK3">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AL3">
         <v>120</v>
@@ -1269,40 +1269,40 @@
         <v>21</v>
       </c>
       <c r="AP3">
-        <v>4.8</v>
+        <v>7.8</v>
       </c>
       <c r="AQ3">
-        <v>4</v>
+        <v>5.6</v>
       </c>
       <c r="AR3">
-        <v>4.9</v>
+        <v>8.6</v>
       </c>
       <c r="AS3">
-        <v>6.4</v>
+        <v>17</v>
       </c>
       <c r="AT3">
-        <v>5.5</v>
+        <v>10.5</v>
       </c>
       <c r="AU3">
-        <v>4.3</v>
+        <v>6.8</v>
       </c>
       <c r="AV3">
-        <v>5</v>
+        <v>8.4</v>
       </c>
       <c r="AW3">
-        <v>6.6</v>
+        <v>20</v>
       </c>
       <c r="AX3">
-        <v>7.2</v>
+        <v>25</v>
       </c>
       <c r="AY3">
-        <v>6.4</v>
+        <v>17.5</v>
       </c>
       <c r="AZ3">
         <v>6.6</v>
       </c>
       <c r="BA3">
-        <v>7.6</v>
+        <v>32</v>
       </c>
       <c r="BB3">
         <v>8.6</v>
@@ -1317,7 +1317,7 @@
         <v>8.6</v>
       </c>
       <c r="BF3">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BG3">
         <v>6.2</v>
@@ -1332,13 +1332,13 @@
         <v>12</v>
       </c>
       <c r="BK3">
-        <v>5.6</v>
+        <v>9</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>2.32</v>
+        <v>10</v>
       </c>
       <c r="BN3">
         <v>8.800000000000001</v>
@@ -1350,13 +1350,13 @@
         <v>1000</v>
       </c>
       <c r="BQ3">
-        <v>2.24</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR3">
         <v>1000</v>
       </c>
       <c r="BS3">
-        <v>2.26</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT3">
         <v>4.5</v>
@@ -1433,7 +1433,7 @@
         <v>1.25</v>
       </c>
       <c r="P4">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="Q4">
         <v>1.74</v>
@@ -1574,7 +1574,7 @@
         <v>9</v>
       </c>
       <c r="BK4">
-        <v>6.8</v>
+        <v>5.8</v>
       </c>
       <c r="BL4">
         <v>1000</v>
@@ -1586,7 +1586,7 @@
         <v>7</v>
       </c>
       <c r="BO4">
-        <v>6</v>
+        <v>5.3</v>
       </c>
       <c r="BP4">
         <v>26</v>
@@ -1604,7 +1604,7 @@
         <v>5.2</v>
       </c>
       <c r="BU4">
-        <v>4.7</v>
+        <v>4.1</v>
       </c>
       <c r="BV4">
         <v>15</v>
@@ -1675,13 +1675,13 @@
         <v>1.24</v>
       </c>
       <c r="P5">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="Q5">
         <v>1.69</v>
       </c>
       <c r="R5">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="S5">
         <v>2.74</v>
@@ -1810,7 +1810,7 @@
         <v>4</v>
       </c>
       <c r="BI5">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="BJ5">
         <v>8.800000000000001</v>
@@ -2141,7 +2141,7 @@
         <v>1000</v>
       </c>
       <c r="J7">
-        <v>1.1</v>
+        <v>1.19</v>
       </c>
       <c r="K7">
         <v>1000</v>
@@ -2177,10 +2177,10 @@
         <v>1.11</v>
       </c>
       <c r="V7">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W7">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X7">
         <v>1000</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-28.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-28.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="116">
   <si>
     <t>League</t>
   </si>
@@ -271,6 +271,12 @@
     <t>Icelandic 1 Deild</t>
   </si>
   <si>
+    <t>Argentinian Primera Division</t>
+  </si>
+  <si>
+    <t>Brazilian Serie B</t>
+  </si>
+  <si>
     <t>2026-07-28</t>
   </si>
   <si>
@@ -289,6 +295,12 @@
     <t>19:15:00</t>
   </si>
   <si>
+    <t>22:00:00</t>
+  </si>
+  <si>
+    <t>22:30:00</t>
+  </si>
+  <si>
     <t>Deportivo Cuenca</t>
   </si>
   <si>
@@ -307,6 +319,18 @@
     <t>Aegir</t>
   </si>
   <si>
+    <t>San Lorenzo</t>
+  </si>
+  <si>
+    <t>Banfield</t>
+  </si>
+  <si>
+    <t>Juventude</t>
+  </si>
+  <si>
+    <t>Ponte Preta</t>
+  </si>
+  <si>
     <t>Emelec</t>
   </si>
   <si>
@@ -325,7 +349,19 @@
     <t>Njardvik</t>
   </si>
   <si>
-    <t>2026-07-26 23:40:05</t>
+    <t>Gimnasia Mendoza</t>
+  </si>
+  <si>
+    <t>Sarmiento de Junin</t>
+  </si>
+  <si>
+    <t>Avai</t>
+  </si>
+  <si>
+    <t>Athletic Club</t>
+  </si>
+  <si>
+    <t>2026-07-27 01:47:59</t>
   </si>
 </sst>
 </file>
@@ -657,7 +693,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB7"/>
+  <dimension ref="A1:CB11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -907,55 +943,55 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D2" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="E2" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="F2">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="G2">
-        <v>2.66</v>
+        <v>2.54</v>
       </c>
       <c r="H2">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="I2">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="J2">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="K2">
         <v>3.25</v>
       </c>
       <c r="L2">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="M2">
         <v>1.12</v>
       </c>
       <c r="N2">
-        <v>2.68</v>
+        <v>2.78</v>
       </c>
       <c r="O2">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="P2">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="Q2">
-        <v>2.5</v>
+        <v>2.58</v>
       </c>
       <c r="R2">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="S2">
         <v>5.1</v>
@@ -964,13 +1000,13 @@
         <v>2.04</v>
       </c>
       <c r="U2">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="V2">
         <v>1.36</v>
       </c>
       <c r="W2">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="X2">
         <v>9.199999999999999</v>
@@ -985,7 +1021,7 @@
         <v>80</v>
       </c>
       <c r="AB2">
-        <v>8.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC2">
         <v>7.4</v>
@@ -997,37 +1033,37 @@
         <v>60</v>
       </c>
       <c r="AF2">
-        <v>15.5</v>
+        <v>19</v>
       </c>
       <c r="AG2">
         <v>12.5</v>
       </c>
       <c r="AH2">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI2">
         <v>80</v>
       </c>
       <c r="AJ2">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="AK2">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AL2">
         <v>65</v>
       </c>
       <c r="AM2">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="AN2">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AO2">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="AP2">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AQ2">
         <v>8.6</v>
@@ -1036,7 +1072,7 @@
         <v>19.5</v>
       </c>
       <c r="AS2">
-        <v>8.6</v>
+        <v>7.2</v>
       </c>
       <c r="AT2">
         <v>6.6</v>
@@ -1060,25 +1096,25 @@
         <v>18.5</v>
       </c>
       <c r="BA2">
-        <v>8.800000000000001</v>
+        <v>7.2</v>
       </c>
       <c r="BB2">
         <v>32</v>
       </c>
       <c r="BC2">
-        <v>29</v>
+        <v>6.4</v>
       </c>
       <c r="BD2">
         <v>42</v>
       </c>
       <c r="BE2">
-        <v>9.4</v>
+        <v>7.6</v>
       </c>
       <c r="BF2">
-        <v>30</v>
+        <v>6.6</v>
       </c>
       <c r="BG2">
-        <v>8.6</v>
+        <v>7</v>
       </c>
       <c r="BH2">
         <v>2.8</v>
@@ -1096,10 +1132,10 @@
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BN2">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BO2">
         <v>4.5</v>
@@ -1108,25 +1144,25 @@
         <v>22</v>
       </c>
       <c r="BQ2">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BR2">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BS2">
         <v>10</v>
       </c>
       <c r="BT2">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BU2">
-        <v>5.6</v>
+        <v>4.9</v>
       </c>
       <c r="BV2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BW2">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BX2">
         <v>1000</v>
@@ -1135,13 +1171,13 @@
         <v>10.5</v>
       </c>
       <c r="BZ2">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="CA2">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="CB2" t="s">
-        <v>103</v>
+        <v>115</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1149,25 +1185,25 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C3" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D3" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="E3" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="F3">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="G3">
-        <v>6</v>
+        <v>5.3</v>
       </c>
       <c r="H3">
-        <v>1.86</v>
+        <v>1.91</v>
       </c>
       <c r="I3">
         <v>2.02</v>
@@ -1179,13 +1215,13 @@
         <v>3.45</v>
       </c>
       <c r="L3">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="M3">
         <v>1.1</v>
       </c>
       <c r="N3">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="O3">
         <v>1.46</v>
@@ -1206,13 +1242,13 @@
         <v>2.08</v>
       </c>
       <c r="U3">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="V3">
         <v>1.98</v>
       </c>
       <c r="W3">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="X3">
         <v>10.5</v>
@@ -1227,7 +1263,7 @@
         <v>24</v>
       </c>
       <c r="AB3">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AC3">
         <v>8.199999999999999</v>
@@ -1242,28 +1278,28 @@
         <v>40</v>
       </c>
       <c r="AG3">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AH3">
-        <v>950</v>
+        <v>24</v>
       </c>
       <c r="AI3">
         <v>55</v>
       </c>
       <c r="AJ3">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="AK3">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="AL3">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AM3">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="AN3">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="AO3">
         <v>21</v>
@@ -1272,64 +1308,64 @@
         <v>7.8</v>
       </c>
       <c r="AQ3">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="AR3">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AS3">
         <v>17</v>
       </c>
       <c r="AT3">
-        <v>10.5</v>
+        <v>5.9</v>
       </c>
       <c r="AU3">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AV3">
         <v>8.4</v>
       </c>
       <c r="AW3">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AX3">
         <v>25</v>
       </c>
       <c r="AY3">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AZ3">
-        <v>6.6</v>
+        <v>19.5</v>
       </c>
       <c r="BA3">
         <v>32</v>
       </c>
       <c r="BB3">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="BC3">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BD3">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="BE3">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="BF3">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="BG3">
-        <v>6.2</v>
+        <v>15</v>
       </c>
       <c r="BH3">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="BI3">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="BJ3">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BK3">
         <v>9</v>
@@ -1341,16 +1377,16 @@
         <v>10</v>
       </c>
       <c r="BN3">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BO3">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="BP3">
         <v>1000</v>
       </c>
       <c r="BQ3">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BR3">
         <v>1000</v>
@@ -1359,13 +1395,13 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BT3">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BU3">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="BV3">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BW3">
         <v>6.2</v>
@@ -1383,7 +1419,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="CB3" t="s">
-        <v>103</v>
+        <v>115</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1391,34 +1427,34 @@
         <v>82</v>
       </c>
       <c r="B4" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C4" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D4" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="E4" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="F4">
         <v>3.35</v>
       </c>
       <c r="G4">
-        <v>3.45</v>
+        <v>3.75</v>
       </c>
       <c r="H4">
-        <v>2.16</v>
+        <v>2.08</v>
       </c>
       <c r="I4">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="J4">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="K4">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="L4">
         <v>1.28</v>
@@ -1430,19 +1466,19 @@
         <v>4.5</v>
       </c>
       <c r="O4">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="P4">
         <v>2.2</v>
       </c>
       <c r="Q4">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="R4">
         <v>1.48</v>
       </c>
       <c r="S4">
-        <v>2.86</v>
+        <v>2.8</v>
       </c>
       <c r="T4">
         <v>1.64</v>
@@ -1454,7 +1490,7 @@
         <v>1.8</v>
       </c>
       <c r="W4">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="X4">
         <v>23</v>
@@ -1478,10 +1514,10 @@
         <v>13.5</v>
       </c>
       <c r="AE4">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AF4">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AG4">
         <v>15</v>
@@ -1499,16 +1535,16 @@
         <v>46</v>
       </c>
       <c r="AL4">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AM4">
         <v>75</v>
       </c>
       <c r="AN4">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AO4">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AP4">
         <v>16.5</v>
@@ -1517,10 +1553,10 @@
         <v>10.5</v>
       </c>
       <c r="AR4">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AS4">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="AT4">
         <v>14</v>
@@ -1532,10 +1568,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AW4">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AX4">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="AY4">
         <v>13</v>
@@ -1547,16 +1583,16 @@
         <v>21</v>
       </c>
       <c r="BB4">
+        <v>6</v>
+      </c>
+      <c r="BC4">
         <v>5.7</v>
       </c>
-      <c r="BC4">
-        <v>5.4</v>
-      </c>
       <c r="BD4">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BE4">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BF4">
         <v>21</v>
@@ -1565,7 +1601,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BH4">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="BI4">
         <v>3.1</v>
@@ -1574,49 +1610,49 @@
         <v>9</v>
       </c>
       <c r="BK4">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="BN4">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BO4">
         <v>5.3</v>
       </c>
       <c r="BP4">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BQ4">
+        <v>9.6</v>
+      </c>
+      <c r="BR4">
+        <v>1000</v>
+      </c>
+      <c r="BS4">
         <v>10</v>
-      </c>
-      <c r="BR4">
-        <v>34</v>
-      </c>
-      <c r="BS4">
-        <v>11</v>
       </c>
       <c r="BT4">
         <v>5.2</v>
       </c>
       <c r="BU4">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="BV4">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BW4">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="BX4">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BY4">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ4">
         <v>0</v>
@@ -1625,7 +1661,7 @@
         <v>0</v>
       </c>
       <c r="CB4" t="s">
-        <v>103</v>
+        <v>115</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1633,19 +1669,19 @@
         <v>82</v>
       </c>
       <c r="B5" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C5" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D5" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="E5" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="F5">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="G5">
         <v>2.52</v>
@@ -1663,7 +1699,7 @@
         <v>4</v>
       </c>
       <c r="L5">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="M5">
         <v>1.04</v>
@@ -1672,19 +1708,19 @@
         <v>4.7</v>
       </c>
       <c r="O5">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="P5">
         <v>2.28</v>
       </c>
       <c r="Q5">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="R5">
         <v>1.51</v>
       </c>
       <c r="S5">
-        <v>2.74</v>
+        <v>2.66</v>
       </c>
       <c r="T5">
         <v>1.61</v>
@@ -1735,7 +1771,7 @@
         <v>42</v>
       </c>
       <c r="AJ5">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AK5">
         <v>28</v>
@@ -1762,7 +1798,7 @@
         <v>17</v>
       </c>
       <c r="AS5">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AT5">
         <v>10</v>
@@ -1774,7 +1810,7 @@
         <v>11.5</v>
       </c>
       <c r="AW5">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AX5">
         <v>13.5</v>
@@ -1795,10 +1831,10 @@
         <v>20</v>
       </c>
       <c r="BD5">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BE5">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BF5">
         <v>11.5</v>
@@ -1807,7 +1843,7 @@
         <v>19</v>
       </c>
       <c r="BH5">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BI5">
         <v>3.6</v>
@@ -1816,13 +1852,13 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BK5">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="BN5">
         <v>5.7</v>
@@ -1831,19 +1867,19 @@
         <v>5</v>
       </c>
       <c r="BP5">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BQ5">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="BR5">
         <v>26</v>
       </c>
       <c r="BS5">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BT5">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BU5">
         <v>5.7</v>
@@ -1852,22 +1888,22 @@
         <v>22</v>
       </c>
       <c r="BW5">
+        <v>8.4</v>
+      </c>
+      <c r="BX5">
+        <v>1000</v>
+      </c>
+      <c r="BY5">
         <v>9.199999999999999</v>
-      </c>
-      <c r="BX5">
-        <v>1000</v>
-      </c>
-      <c r="BY5">
-        <v>10</v>
       </c>
       <c r="BZ5">
         <v>19</v>
       </c>
       <c r="CA5">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="CB5" t="s">
-        <v>103</v>
+        <v>115</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -1875,16 +1911,16 @@
         <v>83</v>
       </c>
       <c r="B6" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C6" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D6" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="E6" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -1914,7 +1950,7 @@
         <v>1.25</v>
       </c>
       <c r="O6">
-        <v>1.49</v>
+        <v>1.05</v>
       </c>
       <c r="P6">
         <v>1.25</v>
@@ -2109,7 +2145,7 @@
         <v>0</v>
       </c>
       <c r="CB6" t="s">
-        <v>103</v>
+        <v>115</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2117,31 +2153,31 @@
         <v>84</v>
       </c>
       <c r="B7" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C7" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D7" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="E7" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="F7">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="G7">
         <v>1000</v>
       </c>
       <c r="H7">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="I7">
         <v>1000</v>
       </c>
       <c r="J7">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="K7">
         <v>1000</v>
@@ -2351,7 +2387,975 @@
         <v>1.04</v>
       </c>
       <c r="CB7" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="8" spans="1:80">
+      <c r="A8" t="s">
+        <v>85</v>
+      </c>
+      <c r="B8" t="s">
+        <v>87</v>
+      </c>
+      <c r="C8" t="s">
+        <v>93</v>
+      </c>
+      <c r="D8" t="s">
+        <v>101</v>
+      </c>
+      <c r="E8" t="s">
+        <v>111</v>
+      </c>
+      <c r="F8">
+        <v>2.02</v>
+      </c>
+      <c r="G8">
+        <v>2.16</v>
+      </c>
+      <c r="H8">
+        <v>3.9</v>
+      </c>
+      <c r="I8">
+        <v>5.4</v>
+      </c>
+      <c r="J8">
+        <v>2.9</v>
+      </c>
+      <c r="K8">
+        <v>3.1</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8">
+        <v>0</v>
+      </c>
+      <c r="O8">
+        <v>0</v>
+      </c>
+      <c r="P8">
+        <v>1.43</v>
+      </c>
+      <c r="Q8">
+        <v>3</v>
+      </c>
+      <c r="R8">
+        <v>0</v>
+      </c>
+      <c r="S8">
+        <v>0</v>
+      </c>
+      <c r="T8">
+        <v>0</v>
+      </c>
+      <c r="U8">
+        <v>0</v>
+      </c>
+      <c r="V8">
+        <v>0</v>
+      </c>
+      <c r="W8">
+        <v>0</v>
+      </c>
+      <c r="X8">
+        <v>0</v>
+      </c>
+      <c r="Y8">
+        <v>0</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+      <c r="AA8">
+        <v>0</v>
+      </c>
+      <c r="AB8">
+        <v>0</v>
+      </c>
+      <c r="AC8">
+        <v>0</v>
+      </c>
+      <c r="AD8">
+        <v>0</v>
+      </c>
+      <c r="AE8">
+        <v>0</v>
+      </c>
+      <c r="AF8">
+        <v>0</v>
+      </c>
+      <c r="AG8">
+        <v>0</v>
+      </c>
+      <c r="AH8">
+        <v>0</v>
+      </c>
+      <c r="AI8">
+        <v>0</v>
+      </c>
+      <c r="AJ8">
+        <v>0</v>
+      </c>
+      <c r="AK8">
+        <v>0</v>
+      </c>
+      <c r="AL8">
+        <v>0</v>
+      </c>
+      <c r="AM8">
+        <v>0</v>
+      </c>
+      <c r="AN8">
+        <v>0</v>
+      </c>
+      <c r="AO8">
+        <v>0</v>
+      </c>
+      <c r="AP8">
+        <v>0</v>
+      </c>
+      <c r="AQ8">
+        <v>0</v>
+      </c>
+      <c r="AR8">
+        <v>0</v>
+      </c>
+      <c r="AS8">
+        <v>0</v>
+      </c>
+      <c r="AT8">
+        <v>0</v>
+      </c>
+      <c r="AU8">
+        <v>0</v>
+      </c>
+      <c r="AV8">
+        <v>0</v>
+      </c>
+      <c r="AW8">
+        <v>0</v>
+      </c>
+      <c r="AX8">
+        <v>0</v>
+      </c>
+      <c r="AY8">
+        <v>0</v>
+      </c>
+      <c r="AZ8">
+        <v>0</v>
+      </c>
+      <c r="BA8">
+        <v>0</v>
+      </c>
+      <c r="BB8">
+        <v>0</v>
+      </c>
+      <c r="BC8">
+        <v>0</v>
+      </c>
+      <c r="BD8">
+        <v>0</v>
+      </c>
+      <c r="BE8">
+        <v>0</v>
+      </c>
+      <c r="BF8">
+        <v>0</v>
+      </c>
+      <c r="BG8">
+        <v>0</v>
+      </c>
+      <c r="BH8">
+        <v>0</v>
+      </c>
+      <c r="BI8">
+        <v>0</v>
+      </c>
+      <c r="BJ8">
+        <v>0</v>
+      </c>
+      <c r="BK8">
+        <v>0</v>
+      </c>
+      <c r="BL8">
+        <v>0</v>
+      </c>
+      <c r="BM8">
+        <v>0</v>
+      </c>
+      <c r="BN8">
+        <v>0</v>
+      </c>
+      <c r="BO8">
+        <v>0</v>
+      </c>
+      <c r="BP8">
+        <v>0</v>
+      </c>
+      <c r="BQ8">
+        <v>0</v>
+      </c>
+      <c r="BR8">
+        <v>0</v>
+      </c>
+      <c r="BS8">
+        <v>0</v>
+      </c>
+      <c r="BT8">
+        <v>0</v>
+      </c>
+      <c r="BU8">
+        <v>0</v>
+      </c>
+      <c r="BV8">
+        <v>0</v>
+      </c>
+      <c r="BW8">
+        <v>0</v>
+      </c>
+      <c r="BX8">
+        <v>0</v>
+      </c>
+      <c r="BY8">
+        <v>0</v>
+      </c>
+      <c r="BZ8">
+        <v>0</v>
+      </c>
+      <c r="CA8">
+        <v>0</v>
+      </c>
+      <c r="CB8" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="9" spans="1:80">
+      <c r="A9" t="s">
+        <v>85</v>
+      </c>
+      <c r="B9" t="s">
+        <v>87</v>
+      </c>
+      <c r="C9" t="s">
+        <v>93</v>
+      </c>
+      <c r="D9" t="s">
+        <v>102</v>
+      </c>
+      <c r="E9" t="s">
+        <v>112</v>
+      </c>
+      <c r="F9">
+        <v>2.08</v>
+      </c>
+      <c r="G9">
+        <v>2.2</v>
+      </c>
+      <c r="H9">
+        <v>4.3</v>
+      </c>
+      <c r="I9">
+        <v>4.9</v>
+      </c>
+      <c r="J9">
+        <v>3.1</v>
+      </c>
+      <c r="K9">
+        <v>3.25</v>
+      </c>
+      <c r="L9">
+        <v>1.59</v>
+      </c>
+      <c r="M9">
+        <v>1.14</v>
+      </c>
+      <c r="N9">
+        <v>2.34</v>
+      </c>
+      <c r="O9">
+        <v>1.63</v>
+      </c>
+      <c r="P9">
+        <v>1.47</v>
+      </c>
+      <c r="Q9">
+        <v>2.88</v>
+      </c>
+      <c r="R9">
+        <v>1.15</v>
+      </c>
+      <c r="S9">
+        <v>6.2</v>
+      </c>
+      <c r="T9">
+        <v>2.32</v>
+      </c>
+      <c r="U9">
+        <v>1.63</v>
+      </c>
+      <c r="V9">
+        <v>1.25</v>
+      </c>
+      <c r="W9">
+        <v>1.83</v>
+      </c>
+      <c r="X9">
+        <v>8.4</v>
+      </c>
+      <c r="Y9">
+        <v>11</v>
+      </c>
+      <c r="Z9">
+        <v>34</v>
+      </c>
+      <c r="AA9">
+        <v>150</v>
+      </c>
+      <c r="AB9">
+        <v>6.2</v>
+      </c>
+      <c r="AC9">
+        <v>8.4</v>
+      </c>
+      <c r="AD9">
+        <v>21</v>
+      </c>
+      <c r="AE9">
+        <v>110</v>
+      </c>
+      <c r="AF9">
+        <v>11.5</v>
+      </c>
+      <c r="AG9">
+        <v>13</v>
+      </c>
+      <c r="AH9">
+        <v>30</v>
+      </c>
+      <c r="AI9">
+        <v>140</v>
+      </c>
+      <c r="AJ9">
+        <v>29</v>
+      </c>
+      <c r="AK9">
+        <v>34</v>
+      </c>
+      <c r="AL9">
+        <v>85</v>
+      </c>
+      <c r="AM9">
+        <v>310</v>
+      </c>
+      <c r="AN9">
+        <v>34</v>
+      </c>
+      <c r="AO9">
+        <v>190</v>
+      </c>
+      <c r="AP9">
+        <v>7.2</v>
+      </c>
+      <c r="AQ9">
+        <v>9.4</v>
+      </c>
+      <c r="AR9">
+        <v>22</v>
+      </c>
+      <c r="AS9">
+        <v>9.6</v>
+      </c>
+      <c r="AT9">
+        <v>5.3</v>
+      </c>
+      <c r="AU9">
+        <v>6.8</v>
+      </c>
+      <c r="AV9">
+        <v>17.5</v>
+      </c>
+      <c r="AW9">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AX9">
+        <v>9.6</v>
+      </c>
+      <c r="AY9">
+        <v>10.5</v>
+      </c>
+      <c r="AZ9">
+        <v>7.6</v>
+      </c>
+      <c r="BA9">
+        <v>9.4</v>
+      </c>
+      <c r="BB9">
+        <v>21</v>
+      </c>
+      <c r="BC9">
+        <v>23</v>
+      </c>
+      <c r="BD9">
+        <v>9</v>
+      </c>
+      <c r="BE9">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BF9">
+        <v>7.8</v>
+      </c>
+      <c r="BG9">
+        <v>9.6</v>
+      </c>
+      <c r="BH9">
+        <v>1000</v>
+      </c>
+      <c r="BI9">
+        <v>1.69</v>
+      </c>
+      <c r="BJ9">
+        <v>17.5</v>
+      </c>
+      <c r="BK9">
+        <v>1.54</v>
+      </c>
+      <c r="BL9">
+        <v>1000</v>
+      </c>
+      <c r="BM9">
+        <v>1.69</v>
+      </c>
+      <c r="BN9">
+        <v>6</v>
+      </c>
+      <c r="BO9">
+        <v>3.2</v>
+      </c>
+      <c r="BP9">
+        <v>26</v>
+      </c>
+      <c r="BQ9">
+        <v>1.59</v>
+      </c>
+      <c r="BR9">
+        <v>1000</v>
+      </c>
+      <c r="BS9">
+        <v>1.65</v>
+      </c>
+      <c r="BT9">
+        <v>10.5</v>
+      </c>
+      <c r="BU9">
+        <v>5.1</v>
+      </c>
+      <c r="BV9">
+        <v>1000</v>
+      </c>
+      <c r="BW9">
+        <v>1.66</v>
+      </c>
+      <c r="BX9">
+        <v>1000</v>
+      </c>
+      <c r="BY9">
+        <v>1.67</v>
+      </c>
+      <c r="BZ9">
+        <v>1000</v>
+      </c>
+      <c r="CA9">
+        <v>1.66</v>
+      </c>
+      <c r="CB9" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="10" spans="1:80">
+      <c r="A10" t="s">
+        <v>86</v>
+      </c>
+      <c r="B10" t="s">
+        <v>87</v>
+      </c>
+      <c r="C10" t="s">
+        <v>94</v>
+      </c>
+      <c r="D10" t="s">
         <v>103</v>
+      </c>
+      <c r="E10" t="s">
+        <v>113</v>
+      </c>
+      <c r="F10">
+        <v>1.57</v>
+      </c>
+      <c r="G10">
+        <v>1.65</v>
+      </c>
+      <c r="H10">
+        <v>7.6</v>
+      </c>
+      <c r="I10">
+        <v>9</v>
+      </c>
+      <c r="J10">
+        <v>3.7</v>
+      </c>
+      <c r="K10">
+        <v>4.1</v>
+      </c>
+      <c r="L10">
+        <v>1.45</v>
+      </c>
+      <c r="M10">
+        <v>1.1</v>
+      </c>
+      <c r="N10">
+        <v>2.88</v>
+      </c>
+      <c r="O10">
+        <v>1.44</v>
+      </c>
+      <c r="P10">
+        <v>1.63</v>
+      </c>
+      <c r="Q10">
+        <v>2.32</v>
+      </c>
+      <c r="R10">
+        <v>1.23</v>
+      </c>
+      <c r="S10">
+        <v>4.5</v>
+      </c>
+      <c r="T10">
+        <v>2.28</v>
+      </c>
+      <c r="U10">
+        <v>1.64</v>
+      </c>
+      <c r="V10">
+        <v>1.12</v>
+      </c>
+      <c r="W10">
+        <v>2.52</v>
+      </c>
+      <c r="X10">
+        <v>1000</v>
+      </c>
+      <c r="Y10">
+        <v>1000</v>
+      </c>
+      <c r="Z10">
+        <v>1000</v>
+      </c>
+      <c r="AA10">
+        <v>1000</v>
+      </c>
+      <c r="AB10">
+        <v>1000</v>
+      </c>
+      <c r="AC10">
+        <v>1000</v>
+      </c>
+      <c r="AD10">
+        <v>1000</v>
+      </c>
+      <c r="AE10">
+        <v>1000</v>
+      </c>
+      <c r="AF10">
+        <v>1000</v>
+      </c>
+      <c r="AG10">
+        <v>1000</v>
+      </c>
+      <c r="AH10">
+        <v>1000</v>
+      </c>
+      <c r="AI10">
+        <v>1000</v>
+      </c>
+      <c r="AJ10">
+        <v>1000</v>
+      </c>
+      <c r="AK10">
+        <v>23</v>
+      </c>
+      <c r="AL10">
+        <v>1000</v>
+      </c>
+      <c r="AM10">
+        <v>1000</v>
+      </c>
+      <c r="AN10">
+        <v>1000</v>
+      </c>
+      <c r="AO10">
+        <v>1000</v>
+      </c>
+      <c r="AP10">
+        <v>1.05</v>
+      </c>
+      <c r="AQ10">
+        <v>1.05</v>
+      </c>
+      <c r="AR10">
+        <v>1.05</v>
+      </c>
+      <c r="AS10">
+        <v>1.05</v>
+      </c>
+      <c r="AT10">
+        <v>1.05</v>
+      </c>
+      <c r="AU10">
+        <v>1.05</v>
+      </c>
+      <c r="AV10">
+        <v>1.05</v>
+      </c>
+      <c r="AW10">
+        <v>1.05</v>
+      </c>
+      <c r="AX10">
+        <v>1.05</v>
+      </c>
+      <c r="AY10">
+        <v>1.05</v>
+      </c>
+      <c r="AZ10">
+        <v>1.05</v>
+      </c>
+      <c r="BA10">
+        <v>1.05</v>
+      </c>
+      <c r="BB10">
+        <v>1.05</v>
+      </c>
+      <c r="BC10">
+        <v>1.01</v>
+      </c>
+      <c r="BD10">
+        <v>1.05</v>
+      </c>
+      <c r="BE10">
+        <v>1.05</v>
+      </c>
+      <c r="BF10">
+        <v>1.05</v>
+      </c>
+      <c r="BG10">
+        <v>1.05</v>
+      </c>
+      <c r="BH10">
+        <v>1000</v>
+      </c>
+      <c r="BI10">
+        <v>1.76</v>
+      </c>
+      <c r="BJ10">
+        <v>18</v>
+      </c>
+      <c r="BK10">
+        <v>1.61</v>
+      </c>
+      <c r="BL10">
+        <v>1000</v>
+      </c>
+      <c r="BM10">
+        <v>1.76</v>
+      </c>
+      <c r="BN10">
+        <v>5</v>
+      </c>
+      <c r="BO10">
+        <v>2.7</v>
+      </c>
+      <c r="BP10">
+        <v>15.5</v>
+      </c>
+      <c r="BQ10">
+        <v>1.58</v>
+      </c>
+      <c r="BR10">
+        <v>48</v>
+      </c>
+      <c r="BS10">
+        <v>1.7</v>
+      </c>
+      <c r="BT10">
+        <v>15.5</v>
+      </c>
+      <c r="BU10">
+        <v>1.58</v>
+      </c>
+      <c r="BV10">
+        <v>1000</v>
+      </c>
+      <c r="BW10">
+        <v>1.76</v>
+      </c>
+      <c r="BX10">
+        <v>1000</v>
+      </c>
+      <c r="BY10">
+        <v>1.76</v>
+      </c>
+      <c r="BZ10">
+        <v>40</v>
+      </c>
+      <c r="CA10">
+        <v>1.69</v>
+      </c>
+      <c r="CB10" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="11" spans="1:80">
+      <c r="A11" t="s">
+        <v>86</v>
+      </c>
+      <c r="B11" t="s">
+        <v>87</v>
+      </c>
+      <c r="C11" t="s">
+        <v>94</v>
+      </c>
+      <c r="D11" t="s">
+        <v>104</v>
+      </c>
+      <c r="E11" t="s">
+        <v>114</v>
+      </c>
+      <c r="F11">
+        <v>3.9</v>
+      </c>
+      <c r="G11">
+        <v>4.9</v>
+      </c>
+      <c r="H11">
+        <v>2.02</v>
+      </c>
+      <c r="I11">
+        <v>2.2</v>
+      </c>
+      <c r="J11">
+        <v>2.96</v>
+      </c>
+      <c r="K11">
+        <v>3.5</v>
+      </c>
+      <c r="L11">
+        <v>1.45</v>
+      </c>
+      <c r="M11">
+        <v>1.1</v>
+      </c>
+      <c r="N11">
+        <v>2.72</v>
+      </c>
+      <c r="O11">
+        <v>1.46</v>
+      </c>
+      <c r="P11">
+        <v>1.57</v>
+      </c>
+      <c r="Q11">
+        <v>2.32</v>
+      </c>
+      <c r="R11">
+        <v>1.21</v>
+      </c>
+      <c r="S11">
+        <v>4.8</v>
+      </c>
+      <c r="T11">
+        <v>1.11</v>
+      </c>
+      <c r="U11">
+        <v>1.74</v>
+      </c>
+      <c r="V11">
+        <v>1.83</v>
+      </c>
+      <c r="W11">
+        <v>1.25</v>
+      </c>
+      <c r="X11">
+        <v>1000</v>
+      </c>
+      <c r="Y11">
+        <v>1000</v>
+      </c>
+      <c r="Z11">
+        <v>1000</v>
+      </c>
+      <c r="AA11">
+        <v>1000</v>
+      </c>
+      <c r="AB11">
+        <v>1000</v>
+      </c>
+      <c r="AC11">
+        <v>1000</v>
+      </c>
+      <c r="AD11">
+        <v>1000</v>
+      </c>
+      <c r="AE11">
+        <v>1000</v>
+      </c>
+      <c r="AF11">
+        <v>1000</v>
+      </c>
+      <c r="AG11">
+        <v>1000</v>
+      </c>
+      <c r="AH11">
+        <v>1000</v>
+      </c>
+      <c r="AI11">
+        <v>65</v>
+      </c>
+      <c r="AJ11">
+        <v>1000</v>
+      </c>
+      <c r="AK11">
+        <v>85</v>
+      </c>
+      <c r="AL11">
+        <v>1000</v>
+      </c>
+      <c r="AM11">
+        <v>1000</v>
+      </c>
+      <c r="AN11">
+        <v>1000</v>
+      </c>
+      <c r="AO11">
+        <v>1000</v>
+      </c>
+      <c r="AP11">
+        <v>1.03</v>
+      </c>
+      <c r="AQ11">
+        <v>1.03</v>
+      </c>
+      <c r="AR11">
+        <v>1.03</v>
+      </c>
+      <c r="AS11">
+        <v>1.03</v>
+      </c>
+      <c r="AT11">
+        <v>1.03</v>
+      </c>
+      <c r="AU11">
+        <v>1.03</v>
+      </c>
+      <c r="AV11">
+        <v>1.03</v>
+      </c>
+      <c r="AW11">
+        <v>1.03</v>
+      </c>
+      <c r="AX11">
+        <v>1.03</v>
+      </c>
+      <c r="AY11">
+        <v>1.03</v>
+      </c>
+      <c r="AZ11">
+        <v>1.03</v>
+      </c>
+      <c r="BA11">
+        <v>1.01</v>
+      </c>
+      <c r="BB11">
+        <v>1.03</v>
+      </c>
+      <c r="BC11">
+        <v>1.02</v>
+      </c>
+      <c r="BD11">
+        <v>1.03</v>
+      </c>
+      <c r="BE11">
+        <v>1.03</v>
+      </c>
+      <c r="BF11">
+        <v>1.03</v>
+      </c>
+      <c r="BG11">
+        <v>1.03</v>
+      </c>
+      <c r="BH11">
+        <v>1000</v>
+      </c>
+      <c r="BI11">
+        <v>1.04</v>
+      </c>
+      <c r="BJ11">
+        <v>1000</v>
+      </c>
+      <c r="BK11">
+        <v>1.04</v>
+      </c>
+      <c r="BL11">
+        <v>1000</v>
+      </c>
+      <c r="BM11">
+        <v>1.04</v>
+      </c>
+      <c r="BN11">
+        <v>1000</v>
+      </c>
+      <c r="BO11">
+        <v>1.04</v>
+      </c>
+      <c r="BP11">
+        <v>1000</v>
+      </c>
+      <c r="BQ11">
+        <v>1.04</v>
+      </c>
+      <c r="BR11">
+        <v>1000</v>
+      </c>
+      <c r="BS11">
+        <v>1.04</v>
+      </c>
+      <c r="BT11">
+        <v>1000</v>
+      </c>
+      <c r="BU11">
+        <v>1.04</v>
+      </c>
+      <c r="BV11">
+        <v>1000</v>
+      </c>
+      <c r="BW11">
+        <v>1.04</v>
+      </c>
+      <c r="BX11">
+        <v>1000</v>
+      </c>
+      <c r="BY11">
+        <v>1.04</v>
+      </c>
+      <c r="BZ11">
+        <v>1000</v>
+      </c>
+      <c r="CA11">
+        <v>1.04</v>
+      </c>
+      <c r="CB11" t="s">
+        <v>115</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-28.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-28.xlsx
@@ -361,7 +361,7 @@
     <t>Athletic Club</t>
   </si>
   <si>
-    <t>2026-07-27 01:47:59</t>
+    <t>2026-07-27 03:55:36</t>
   </si>
 </sst>
 </file>
@@ -958,19 +958,19 @@
         <v>2.38</v>
       </c>
       <c r="G2">
-        <v>2.54</v>
+        <v>2.48</v>
       </c>
       <c r="H2">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="I2">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="J2">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="K2">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="L2">
         <v>1.56</v>
@@ -979,16 +979,16 @@
         <v>1.12</v>
       </c>
       <c r="N2">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="O2">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="P2">
         <v>1.58</v>
       </c>
       <c r="Q2">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="R2">
         <v>1.21</v>
@@ -997,16 +997,16 @@
         <v>5.1</v>
       </c>
       <c r="T2">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="U2">
         <v>1.83</v>
       </c>
       <c r="V2">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W2">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="X2">
         <v>9.199999999999999</v>
@@ -1021,7 +1021,7 @@
         <v>80</v>
       </c>
       <c r="AB2">
-        <v>9.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="AC2">
         <v>7.4</v>
@@ -1033,10 +1033,10 @@
         <v>60</v>
       </c>
       <c r="AF2">
-        <v>19</v>
+        <v>14.5</v>
       </c>
       <c r="AG2">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH2">
         <v>22</v>
@@ -1072,7 +1072,7 @@
         <v>19.5</v>
       </c>
       <c r="AS2">
-        <v>7.2</v>
+        <v>10.5</v>
       </c>
       <c r="AT2">
         <v>6.6</v>
@@ -1096,34 +1096,34 @@
         <v>18.5</v>
       </c>
       <c r="BA2">
-        <v>7.2</v>
+        <v>10.5</v>
       </c>
       <c r="BB2">
-        <v>32</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC2">
-        <v>6.4</v>
+        <v>9</v>
       </c>
       <c r="BD2">
         <v>42</v>
       </c>
       <c r="BE2">
-        <v>7.6</v>
+        <v>11.5</v>
       </c>
       <c r="BF2">
-        <v>6.6</v>
+        <v>9.4</v>
       </c>
       <c r="BG2">
-        <v>7</v>
+        <v>10.5</v>
       </c>
       <c r="BH2">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="BI2">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="BJ2">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BK2">
         <v>8</v>
@@ -1132,49 +1132,49 @@
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>12</v>
+        <v>2.36</v>
       </c>
       <c r="BN2">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BO2">
         <v>4.5</v>
       </c>
       <c r="BP2">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BQ2">
-        <v>8</v>
+        <v>9.6</v>
       </c>
       <c r="BR2">
         <v>44</v>
       </c>
       <c r="BS2">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="BT2">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BU2">
-        <v>4.9</v>
+        <v>5.8</v>
       </c>
       <c r="BV2">
         <v>36</v>
       </c>
       <c r="BW2">
-        <v>9.4</v>
+        <v>11.5</v>
       </c>
       <c r="BX2">
         <v>1000</v>
       </c>
       <c r="BY2">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="BZ2">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="CA2">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="CB2" t="s">
         <v>115</v>
@@ -1215,7 +1215,7 @@
         <v>3.45</v>
       </c>
       <c r="L3">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="M3">
         <v>1.1</v>
@@ -1323,7 +1323,7 @@
         <v>6.6</v>
       </c>
       <c r="AV3">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW3">
         <v>21</v>
@@ -1359,13 +1359,13 @@
         <v>15</v>
       </c>
       <c r="BH3">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="BI3">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="BJ3">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BK3">
         <v>9</v>
@@ -1374,49 +1374,49 @@
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BN3">
+        <v>8.6</v>
+      </c>
+      <c r="BO3">
+        <v>4.8</v>
+      </c>
+      <c r="BP3">
+        <v>1000</v>
+      </c>
+      <c r="BQ3">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BR3">
+        <v>1000</v>
+      </c>
+      <c r="BS3">
+        <v>9.4</v>
+      </c>
+      <c r="BT3">
+        <v>4.5</v>
+      </c>
+      <c r="BU3">
+        <v>3.5</v>
+      </c>
+      <c r="BV3">
+        <v>15.5</v>
+      </c>
+      <c r="BW3">
+        <v>6.4</v>
+      </c>
+      <c r="BX3">
+        <v>1000</v>
+      </c>
+      <c r="BY3">
         <v>8.4</v>
       </c>
-      <c r="BO3">
-        <v>4.6</v>
-      </c>
-      <c r="BP3">
-        <v>1000</v>
-      </c>
-      <c r="BQ3">
-        <v>8.6</v>
-      </c>
-      <c r="BR3">
-        <v>1000</v>
-      </c>
-      <c r="BS3">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BT3">
-        <v>4.6</v>
-      </c>
-      <c r="BU3">
-        <v>3.55</v>
-      </c>
-      <c r="BV3">
-        <v>16</v>
-      </c>
-      <c r="BW3">
-        <v>6.2</v>
-      </c>
-      <c r="BX3">
-        <v>1000</v>
-      </c>
-      <c r="BY3">
-        <v>8.199999999999999</v>
-      </c>
       <c r="BZ3">
         <v>1000</v>
       </c>
       <c r="CA3">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="CB3" t="s">
         <v>115</v>
@@ -1439,7 +1439,7 @@
         <v>107</v>
       </c>
       <c r="F4">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="G4">
         <v>3.75</v>
@@ -1448,13 +1448,13 @@
         <v>2.08</v>
       </c>
       <c r="I4">
-        <v>2.26</v>
+        <v>2.18</v>
       </c>
       <c r="J4">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K4">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L4">
         <v>1.28</v>
@@ -1472,22 +1472,22 @@
         <v>2.2</v>
       </c>
       <c r="Q4">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="R4">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="S4">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="T4">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="U4">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="V4">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="W4">
         <v>1.36</v>
@@ -1499,13 +1499,13 @@
         <v>14.5</v>
       </c>
       <c r="Z4">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AA4">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="AB4">
-        <v>19.5</v>
+        <v>17</v>
       </c>
       <c r="AC4">
         <v>9</v>
@@ -1514,13 +1514,13 @@
         <v>13.5</v>
       </c>
       <c r="AE4">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AF4">
         <v>28</v>
       </c>
       <c r="AG4">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AH4">
         <v>19.5</v>
@@ -1529,16 +1529,16 @@
         <v>32</v>
       </c>
       <c r="AJ4">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AK4">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AL4">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AM4">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="AN4">
         <v>32</v>
@@ -1556,10 +1556,10 @@
         <v>13</v>
       </c>
       <c r="AS4">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AT4">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AU4">
         <v>7.8</v>
@@ -1571,40 +1571,40 @@
         <v>18</v>
       </c>
       <c r="AX4">
-        <v>5.3</v>
+        <v>20</v>
       </c>
       <c r="AY4">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AZ4">
         <v>14</v>
       </c>
       <c r="BA4">
-        <v>21</v>
+        <v>5.5</v>
       </c>
       <c r="BB4">
         <v>6</v>
       </c>
       <c r="BC4">
-        <v>5.7</v>
+        <v>32</v>
       </c>
       <c r="BD4">
-        <v>5.7</v>
+        <v>36</v>
       </c>
       <c r="BE4">
         <v>6</v>
       </c>
       <c r="BF4">
-        <v>21</v>
+        <v>5.5</v>
       </c>
       <c r="BG4">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="BH4">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="BI4">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="BJ4">
         <v>9</v>
@@ -1616,10 +1616,10 @@
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="BN4">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BO4">
         <v>5.3</v>
@@ -1628,13 +1628,13 @@
         <v>27</v>
       </c>
       <c r="BQ4">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BR4">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BS4">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BT4">
         <v>5.2</v>
@@ -1646,13 +1646,13 @@
         <v>14.5</v>
       </c>
       <c r="BW4">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BX4">
         <v>25</v>
       </c>
       <c r="BY4">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BZ4">
         <v>0</v>
@@ -1681,22 +1681,22 @@
         <v>108</v>
       </c>
       <c r="F5">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="G5">
-        <v>2.52</v>
+        <v>2.42</v>
       </c>
       <c r="H5">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="I5">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="J5">
         <v>3.7</v>
       </c>
       <c r="K5">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="L5">
         <v>1.35</v>
@@ -1714,13 +1714,13 @@
         <v>2.28</v>
       </c>
       <c r="Q5">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="R5">
         <v>1.51</v>
       </c>
       <c r="S5">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="T5">
         <v>1.61</v>
@@ -1729,13 +1729,13 @@
         <v>2.44</v>
       </c>
       <c r="V5">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="W5">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="X5">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Y5">
         <v>18</v>
@@ -1747,7 +1747,7 @@
         <v>55</v>
       </c>
       <c r="AB5">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AC5">
         <v>10.5</v>
@@ -1759,25 +1759,25 @@
         <v>32</v>
       </c>
       <c r="AF5">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AG5">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AH5">
         <v>18</v>
       </c>
       <c r="AI5">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AJ5">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AK5">
         <v>28</v>
       </c>
       <c r="AL5">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AM5">
         <v>75</v>
@@ -1798,7 +1798,7 @@
         <v>17</v>
       </c>
       <c r="AS5">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="AT5">
         <v>10</v>
@@ -1810,7 +1810,7 @@
         <v>11.5</v>
       </c>
       <c r="AW5">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="AX5">
         <v>13.5</v>
@@ -1822,19 +1822,19 @@
         <v>11.5</v>
       </c>
       <c r="BA5">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="BB5">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="BC5">
         <v>20</v>
       </c>
       <c r="BD5">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="BE5">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="BF5">
         <v>11.5</v>
@@ -1843,7 +1843,7 @@
         <v>19</v>
       </c>
       <c r="BH5">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BI5">
         <v>3.6</v>
@@ -1852,13 +1852,13 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BK5">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="BN5">
         <v>5.7</v>
@@ -1867,19 +1867,19 @@
         <v>5</v>
       </c>
       <c r="BP5">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BQ5">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR5">
         <v>26</v>
       </c>
       <c r="BS5">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT5">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BU5">
         <v>5.7</v>
@@ -1888,19 +1888,19 @@
         <v>22</v>
       </c>
       <c r="BW5">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX5">
         <v>1000</v>
       </c>
       <c r="BY5">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BZ5">
         <v>19</v>
       </c>
       <c r="CA5">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="CB5" t="s">
         <v>115</v>
@@ -2165,19 +2165,19 @@
         <v>110</v>
       </c>
       <c r="F7">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="G7">
         <v>1000</v>
       </c>
       <c r="H7">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="I7">
         <v>1000</v>
       </c>
       <c r="J7">
-        <v>1.24</v>
+        <v>1.35</v>
       </c>
       <c r="K7">
         <v>1000</v>
@@ -2213,10 +2213,10 @@
         <v>1.11</v>
       </c>
       <c r="V7">
-        <v>1.02</v>
+        <v>1.15</v>
       </c>
       <c r="W7">
-        <v>1.02</v>
+        <v>1.15</v>
       </c>
       <c r="X7">
         <v>1000</v>
@@ -2407,19 +2407,19 @@
         <v>111</v>
       </c>
       <c r="F8">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="G8">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="H8">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="I8">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="J8">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="K8">
         <v>3.1</v>
@@ -2664,16 +2664,16 @@
         <v>3.1</v>
       </c>
       <c r="K9">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="L9">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="M9">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="N9">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="O9">
         <v>1.63</v>
@@ -2685,7 +2685,7 @@
         <v>2.88</v>
       </c>
       <c r="R9">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="S9">
         <v>6.2</v>
@@ -2769,7 +2769,7 @@
         <v>9.6</v>
       </c>
       <c r="AT9">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AU9">
         <v>6.8</v>
@@ -2811,64 +2811,64 @@
         <v>9.6</v>
       </c>
       <c r="BH9">
-        <v>1000</v>
+        <v>2.64</v>
       </c>
       <c r="BI9">
-        <v>1.69</v>
+        <v>2.32</v>
       </c>
       <c r="BJ9">
-        <v>17.5</v>
+        <v>13</v>
       </c>
       <c r="BK9">
-        <v>1.54</v>
+        <v>8</v>
       </c>
       <c r="BL9">
         <v>1000</v>
       </c>
       <c r="BM9">
-        <v>1.69</v>
+        <v>11</v>
       </c>
       <c r="BN9">
-        <v>6</v>
+        <v>4.7</v>
       </c>
       <c r="BO9">
-        <v>3.2</v>
+        <v>3.95</v>
       </c>
       <c r="BP9">
-        <v>26</v>
+        <v>19.5</v>
       </c>
       <c r="BQ9">
-        <v>1.59</v>
+        <v>7.2</v>
       </c>
       <c r="BR9">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BS9">
-        <v>1.65</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT9">
-        <v>10.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU9">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="BV9">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BW9">
-        <v>1.66</v>
+        <v>9.6</v>
       </c>
       <c r="BX9">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="BY9">
-        <v>1.67</v>
+        <v>10</v>
       </c>
       <c r="BZ9">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="CA9">
-        <v>1.66</v>
+        <v>9.6</v>
       </c>
       <c r="CB9" t="s">
         <v>115</v>
@@ -2891,10 +2891,10 @@
         <v>113</v>
       </c>
       <c r="F10">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="G10">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="H10">
         <v>7.6</v>
@@ -2903,19 +2903,19 @@
         <v>9</v>
       </c>
       <c r="J10">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="K10">
         <v>4.1</v>
       </c>
       <c r="L10">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="M10">
         <v>1.1</v>
       </c>
       <c r="N10">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="O10">
         <v>1.44</v>
@@ -2942,175 +2942,175 @@
         <v>1.12</v>
       </c>
       <c r="W10">
-        <v>2.52</v>
+        <v>2.58</v>
       </c>
       <c r="X10">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="Y10">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="Z10">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AA10">
-        <v>1000</v>
+        <v>390</v>
       </c>
       <c r="AB10">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="AC10">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AD10">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AE10">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AF10">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AG10">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH10">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AI10">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AJ10">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AK10">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL10">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AM10">
-        <v>1000</v>
+        <v>300</v>
       </c>
       <c r="AN10">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AO10">
-        <v>1000</v>
+        <v>390</v>
       </c>
       <c r="AP10">
-        <v>1.05</v>
+        <v>8</v>
       </c>
       <c r="AQ10">
-        <v>1.05</v>
+        <v>14</v>
       </c>
       <c r="AR10">
-        <v>1.05</v>
+        <v>4.4</v>
       </c>
       <c r="AS10">
-        <v>1.05</v>
+        <v>4.6</v>
       </c>
       <c r="AT10">
-        <v>1.05</v>
+        <v>4.7</v>
       </c>
       <c r="AU10">
-        <v>1.05</v>
+        <v>7.8</v>
       </c>
       <c r="AV10">
-        <v>1.05</v>
+        <v>4.1</v>
       </c>
       <c r="AW10">
-        <v>1.05</v>
+        <v>4.5</v>
       </c>
       <c r="AX10">
-        <v>1.05</v>
+        <v>6</v>
       </c>
       <c r="AY10">
-        <v>1.05</v>
+        <v>7.8</v>
       </c>
       <c r="AZ10">
-        <v>1.05</v>
+        <v>4.1</v>
       </c>
       <c r="BA10">
-        <v>1.05</v>
+        <v>4.5</v>
       </c>
       <c r="BB10">
-        <v>1.05</v>
+        <v>11</v>
       </c>
       <c r="BC10">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="BD10">
-        <v>1.05</v>
+        <v>4.3</v>
       </c>
       <c r="BE10">
-        <v>1.05</v>
+        <v>4.5</v>
       </c>
       <c r="BF10">
-        <v>1.05</v>
+        <v>10</v>
       </c>
       <c r="BG10">
-        <v>1.05</v>
+        <v>4.6</v>
       </c>
       <c r="BH10">
-        <v>1000</v>
+        <v>3.1</v>
       </c>
       <c r="BI10">
-        <v>1.76</v>
+        <v>2.42</v>
       </c>
       <c r="BJ10">
-        <v>18</v>
+        <v>13.5</v>
       </c>
       <c r="BK10">
-        <v>1.61</v>
+        <v>9.6</v>
       </c>
       <c r="BL10">
         <v>1000</v>
       </c>
       <c r="BM10">
-        <v>1.76</v>
+        <v>10.5</v>
       </c>
       <c r="BN10">
-        <v>5</v>
+        <v>3.9</v>
       </c>
       <c r="BO10">
-        <v>2.7</v>
+        <v>3.05</v>
       </c>
       <c r="BP10">
-        <v>15.5</v>
+        <v>11.5</v>
       </c>
       <c r="BQ10">
-        <v>1.58</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR10">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="BS10">
-        <v>1.7</v>
+        <v>8.6</v>
       </c>
       <c r="BT10">
-        <v>15.5</v>
+        <v>11.5</v>
       </c>
       <c r="BU10">
-        <v>1.58</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BV10">
         <v>1000</v>
       </c>
       <c r="BW10">
-        <v>1.76</v>
+        <v>10</v>
       </c>
       <c r="BX10">
         <v>1000</v>
       </c>
       <c r="BY10">
-        <v>1.76</v>
+        <v>10</v>
       </c>
       <c r="BZ10">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="CA10">
-        <v>1.69</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB10" t="s">
         <v>115</v>
@@ -3133,40 +3133,40 @@
         <v>114</v>
       </c>
       <c r="F11">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="G11">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="H11">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="I11">
         <v>2.2</v>
       </c>
       <c r="J11">
-        <v>2.96</v>
+        <v>3.1</v>
       </c>
       <c r="K11">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L11">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="M11">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N11">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="O11">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="P11">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="Q11">
-        <v>2.32</v>
+        <v>2.44</v>
       </c>
       <c r="R11">
         <v>1.21</v>
@@ -3175,184 +3175,184 @@
         <v>4.8</v>
       </c>
       <c r="T11">
-        <v>1.11</v>
+        <v>2.06</v>
       </c>
       <c r="U11">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="V11">
         <v>1.83</v>
       </c>
       <c r="W11">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="X11">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="Y11">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="Z11">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AA11">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AB11">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AC11">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AD11">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AE11">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AF11">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AG11">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AH11">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AI11">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AJ11">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AK11">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AL11">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AM11">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AN11">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AO11">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AP11">
-        <v>1.03</v>
+        <v>8.4</v>
       </c>
       <c r="AQ11">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="AR11">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="AS11">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AT11">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="AU11">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="AV11">
-        <v>1.03</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW11">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AX11">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AY11">
-        <v>1.03</v>
+        <v>16</v>
       </c>
       <c r="AZ11">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="BA11">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BB11">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="BC11">
-        <v>1.02</v>
+        <v>4.2</v>
       </c>
       <c r="BD11">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="BE11">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="BF11">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="BG11">
-        <v>1.03</v>
+        <v>18</v>
       </c>
       <c r="BH11">
-        <v>1000</v>
+        <v>2.86</v>
       </c>
       <c r="BI11">
-        <v>1.04</v>
+        <v>2.4</v>
       </c>
       <c r="BJ11">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK11">
-        <v>1.04</v>
+        <v>6.4</v>
       </c>
       <c r="BL11">
         <v>1000</v>
       </c>
       <c r="BM11">
-        <v>1.04</v>
+        <v>14</v>
       </c>
       <c r="BN11">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="BO11">
-        <v>1.04</v>
+        <v>5.6</v>
       </c>
       <c r="BP11">
         <v>1000</v>
       </c>
       <c r="BQ11">
-        <v>1.04</v>
+        <v>11</v>
       </c>
       <c r="BR11">
         <v>1000</v>
       </c>
       <c r="BS11">
-        <v>1.04</v>
+        <v>12</v>
       </c>
       <c r="BT11">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="BU11">
-        <v>1.04</v>
+        <v>3.6</v>
       </c>
       <c r="BV11">
         <v>1000</v>
       </c>
       <c r="BW11">
-        <v>1.04</v>
+        <v>8</v>
       </c>
       <c r="BX11">
         <v>1000</v>
       </c>
       <c r="BY11">
-        <v>1.04</v>
+        <v>10.5</v>
       </c>
       <c r="BZ11">
         <v>1000</v>
       </c>
       <c r="CA11">
-        <v>1.04</v>
+        <v>11</v>
       </c>
       <c r="CB11" t="s">
         <v>115</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-28.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-28.xlsx
@@ -361,7 +361,7 @@
     <t>Athletic Club</t>
   </si>
   <si>
-    <t>2026-07-27 03:55:36</t>
+    <t>2026-07-27 06:02:53</t>
   </si>
 </sst>
 </file>
@@ -955,19 +955,19 @@
         <v>105</v>
       </c>
       <c r="F2">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="G2">
         <v>2.48</v>
       </c>
       <c r="H2">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="I2">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="J2">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="K2">
         <v>3.3</v>
@@ -988,7 +988,7 @@
         <v>1.58</v>
       </c>
       <c r="Q2">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="R2">
         <v>1.21</v>
@@ -1111,7 +1111,7 @@
         <v>11.5</v>
       </c>
       <c r="BF2">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BG2">
         <v>10.5</v>
@@ -1197,46 +1197,46 @@
         <v>106</v>
       </c>
       <c r="F3">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="G3">
         <v>5.3</v>
       </c>
       <c r="H3">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="I3">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="J3">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K3">
         <v>3.45</v>
       </c>
       <c r="L3">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="M3">
         <v>1.1</v>
       </c>
       <c r="N3">
-        <v>2.86</v>
+        <v>2.94</v>
       </c>
       <c r="O3">
         <v>1.46</v>
       </c>
       <c r="P3">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="Q3">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="R3">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="S3">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="T3">
         <v>2.08</v>
@@ -1245,7 +1245,7 @@
         <v>1.78</v>
       </c>
       <c r="V3">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="W3">
         <v>1.23</v>
@@ -1305,7 +1305,7 @@
         <v>21</v>
       </c>
       <c r="AP3">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AQ3">
         <v>6</v>
@@ -1448,7 +1448,7 @@
         <v>2.08</v>
       </c>
       <c r="I4">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="J4">
         <v>3.75</v>
@@ -1466,16 +1466,16 @@
         <v>4.5</v>
       </c>
       <c r="O4">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P4">
         <v>2.2</v>
       </c>
       <c r="Q4">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="R4">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="S4">
         <v>2.82</v>
@@ -1484,13 +1484,13 @@
         <v>1.65</v>
       </c>
       <c r="U4">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="V4">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="W4">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="X4">
         <v>23</v>
@@ -1505,10 +1505,10 @@
         <v>34</v>
       </c>
       <c r="AB4">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AC4">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD4">
         <v>13.5</v>
@@ -1556,7 +1556,7 @@
         <v>13</v>
       </c>
       <c r="AS4">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AT4">
         <v>14.5</v>
@@ -1580,10 +1580,10 @@
         <v>14</v>
       </c>
       <c r="BA4">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BB4">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BC4">
         <v>32</v>
@@ -1592,10 +1592,10 @@
         <v>36</v>
       </c>
       <c r="BE4">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BF4">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BG4">
         <v>11</v>
@@ -1616,10 +1616,10 @@
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BN4">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BO4">
         <v>5.3</v>
@@ -1628,13 +1628,13 @@
         <v>27</v>
       </c>
       <c r="BQ4">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BR4">
         <v>34</v>
       </c>
       <c r="BS4">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BT4">
         <v>5.2</v>
@@ -1646,13 +1646,13 @@
         <v>14.5</v>
       </c>
       <c r="BW4">
-        <v>7.6</v>
+        <v>10.5</v>
       </c>
       <c r="BX4">
         <v>25</v>
       </c>
       <c r="BY4">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BZ4">
         <v>0</v>
@@ -1684,7 +1684,7 @@
         <v>2.3</v>
       </c>
       <c r="G5">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="H5">
         <v>3</v>
@@ -1693,34 +1693,34 @@
         <v>3.25</v>
       </c>
       <c r="J5">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="K5">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L5">
         <v>1.35</v>
       </c>
       <c r="M5">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N5">
         <v>4.7</v>
       </c>
       <c r="O5">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="P5">
-        <v>2.28</v>
+        <v>2.42</v>
       </c>
       <c r="Q5">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="R5">
         <v>1.51</v>
       </c>
       <c r="S5">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="T5">
         <v>1.61</v>
@@ -1732,7 +1732,7 @@
         <v>1.44</v>
       </c>
       <c r="W5">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="X5">
         <v>23</v>
@@ -1765,7 +1765,7 @@
         <v>13</v>
       </c>
       <c r="AH5">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AI5">
         <v>38</v>
@@ -1810,7 +1810,7 @@
         <v>11.5</v>
       </c>
       <c r="AW5">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AX5">
         <v>13.5</v>
@@ -1825,16 +1825,16 @@
         <v>5.1</v>
       </c>
       <c r="BB5">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BC5">
         <v>20</v>
       </c>
       <c r="BD5">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BE5">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BF5">
         <v>11.5</v>
@@ -2165,19 +2165,19 @@
         <v>110</v>
       </c>
       <c r="F7">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="G7">
         <v>1000</v>
       </c>
       <c r="H7">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="I7">
         <v>1000</v>
       </c>
       <c r="J7">
-        <v>1.35</v>
+        <v>1.45</v>
       </c>
       <c r="K7">
         <v>1000</v>
@@ -2213,10 +2213,10 @@
         <v>1.11</v>
       </c>
       <c r="V7">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="W7">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="X7">
         <v>1000</v>
@@ -2413,7 +2413,7 @@
         <v>2.18</v>
       </c>
       <c r="H8">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="I8">
         <v>5.3</v>
@@ -2437,10 +2437,10 @@
         <v>0</v>
       </c>
       <c r="P8">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="Q8">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="R8">
         <v>0</v>
@@ -2664,7 +2664,7 @@
         <v>3.1</v>
       </c>
       <c r="K9">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="L9">
         <v>1.61</v>
@@ -2835,7 +2835,7 @@
         <v>3.95</v>
       </c>
       <c r="BP9">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BQ9">
         <v>7.2</v>
@@ -2844,7 +2844,7 @@
         <v>48</v>
       </c>
       <c r="BS9">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BT9">
         <v>8.199999999999999</v>
@@ -2891,7 +2891,7 @@
         <v>113</v>
       </c>
       <c r="F10">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="G10">
         <v>1.63</v>
@@ -2903,10 +2903,10 @@
         <v>9</v>
       </c>
       <c r="J10">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="K10">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L10">
         <v>1.47</v>
@@ -2918,10 +2918,10 @@
         <v>2.92</v>
       </c>
       <c r="O10">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="P10">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="Q10">
         <v>2.32</v>
@@ -2933,10 +2933,10 @@
         <v>4.5</v>
       </c>
       <c r="T10">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="U10">
-        <v>1.64</v>
+        <v>1.74</v>
       </c>
       <c r="V10">
         <v>1.12</v>
@@ -3044,7 +3044,7 @@
         <v>4.3</v>
       </c>
       <c r="BE10">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BF10">
         <v>10</v>
@@ -3062,7 +3062,7 @@
         <v>13.5</v>
       </c>
       <c r="BK10">
-        <v>9.6</v>
+        <v>6</v>
       </c>
       <c r="BL10">
         <v>1000</v>
@@ -3074,13 +3074,13 @@
         <v>3.9</v>
       </c>
       <c r="BO10">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="BP10">
         <v>11.5</v>
       </c>
       <c r="BQ10">
-        <v>8.199999999999999</v>
+        <v>5.7</v>
       </c>
       <c r="BR10">
         <v>1000</v>
@@ -3092,7 +3092,7 @@
         <v>11.5</v>
       </c>
       <c r="BU10">
-        <v>8.199999999999999</v>
+        <v>5.7</v>
       </c>
       <c r="BV10">
         <v>1000</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-28.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-28.xlsx
@@ -361,7 +361,7 @@
     <t>Athletic Club</t>
   </si>
   <si>
-    <t>2026-07-27 06:02:53</t>
+    <t>2026-07-27 08:10:19</t>
   </si>
 </sst>
 </file>
@@ -955,61 +955,61 @@
         <v>105</v>
       </c>
       <c r="F2">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="G2">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="H2">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="I2">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="J2">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="K2">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="L2">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="M2">
         <v>1.12</v>
       </c>
       <c r="N2">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="O2">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="P2">
         <v>1.58</v>
       </c>
       <c r="Q2">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="R2">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="S2">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="T2">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="U2">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="V2">
         <v>1.37</v>
       </c>
       <c r="W2">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="X2">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="Y2">
         <v>10.5</v>
@@ -1018,7 +1018,7 @@
         <v>28</v>
       </c>
       <c r="AA2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AB2">
         <v>7.8</v>
@@ -1027,31 +1027,31 @@
         <v>7.4</v>
       </c>
       <c r="AD2">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AE2">
+        <v>55</v>
+      </c>
+      <c r="AF2">
+        <v>15</v>
+      </c>
+      <c r="AG2">
+        <v>12.5</v>
+      </c>
+      <c r="AH2">
+        <v>23</v>
+      </c>
+      <c r="AI2">
+        <v>95</v>
+      </c>
+      <c r="AJ2">
+        <v>38</v>
+      </c>
+      <c r="AK2">
+        <v>44</v>
+      </c>
+      <c r="AL2">
         <v>60</v>
-      </c>
-      <c r="AF2">
-        <v>14.5</v>
-      </c>
-      <c r="AG2">
-        <v>12</v>
-      </c>
-      <c r="AH2">
-        <v>22</v>
-      </c>
-      <c r="AI2">
-        <v>80</v>
-      </c>
-      <c r="AJ2">
-        <v>46</v>
-      </c>
-      <c r="AK2">
-        <v>34</v>
-      </c>
-      <c r="AL2">
-        <v>65</v>
       </c>
       <c r="AM2">
         <v>200</v>
@@ -1060,31 +1060,31 @@
         <v>44</v>
       </c>
       <c r="AO2">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AP2">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ2">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AR2">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AS2">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AT2">
         <v>6.6</v>
       </c>
       <c r="AU2">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AV2">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AW2">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="AX2">
         <v>12.5</v>
@@ -1093,88 +1093,88 @@
         <v>10.5</v>
       </c>
       <c r="AZ2">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="BA2">
+        <v>24</v>
+      </c>
+      <c r="BB2">
+        <v>32</v>
+      </c>
+      <c r="BC2">
+        <v>29</v>
+      </c>
+      <c r="BD2">
+        <v>20</v>
+      </c>
+      <c r="BE2">
         <v>10.5</v>
       </c>
-      <c r="BB2">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BC2">
-        <v>9</v>
-      </c>
-      <c r="BD2">
-        <v>42</v>
-      </c>
-      <c r="BE2">
+      <c r="BF2">
+        <v>32</v>
+      </c>
+      <c r="BG2">
+        <v>19</v>
+      </c>
+      <c r="BH2">
+        <v>2.74</v>
+      </c>
+      <c r="BI2">
+        <v>2.3</v>
+      </c>
+      <c r="BJ2">
         <v>11.5</v>
       </c>
-      <c r="BF2">
-        <v>9.6</v>
-      </c>
-      <c r="BG2">
-        <v>10.5</v>
-      </c>
-      <c r="BH2">
-        <v>2.76</v>
-      </c>
-      <c r="BI2">
-        <v>2.38</v>
-      </c>
-      <c r="BJ2">
-        <v>11</v>
-      </c>
       <c r="BK2">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>2.36</v>
+        <v>13.5</v>
       </c>
       <c r="BN2">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BO2">
         <v>4.5</v>
       </c>
       <c r="BP2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BQ2">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR2">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="BS2">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="BT2">
         <v>6.6</v>
       </c>
       <c r="BU2">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BV2">
         <v>36</v>
       </c>
       <c r="BW2">
+        <v>10.5</v>
+      </c>
+      <c r="BX2">
+        <v>60</v>
+      </c>
+      <c r="BY2">
+        <v>12</v>
+      </c>
+      <c r="BZ2">
+        <v>50</v>
+      </c>
+      <c r="CA2">
         <v>11.5</v>
-      </c>
-      <c r="BX2">
-        <v>1000</v>
-      </c>
-      <c r="BY2">
-        <v>13</v>
-      </c>
-      <c r="BZ2">
-        <v>1000</v>
-      </c>
-      <c r="CA2">
-        <v>12.5</v>
       </c>
       <c r="CB2" t="s">
         <v>115</v>
@@ -1227,13 +1227,13 @@
         <v>1.46</v>
       </c>
       <c r="P3">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="Q3">
         <v>2.4</v>
       </c>
       <c r="R3">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="S3">
         <v>4.7</v>
@@ -1275,7 +1275,7 @@
         <v>26</v>
       </c>
       <c r="AF3">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AG3">
         <v>21</v>
@@ -1317,7 +1317,7 @@
         <v>17</v>
       </c>
       <c r="AT3">
-        <v>5.9</v>
+        <v>10.5</v>
       </c>
       <c r="AU3">
         <v>6.6</v>
@@ -1329,7 +1329,7 @@
         <v>21</v>
       </c>
       <c r="AX3">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="AY3">
         <v>17</v>
@@ -1338,7 +1338,7 @@
         <v>19.5</v>
       </c>
       <c r="BA3">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="BB3">
         <v>9.6</v>
@@ -1362,13 +1362,13 @@
         <v>3</v>
       </c>
       <c r="BI3">
-        <v>2.6</v>
+        <v>2.44</v>
       </c>
       <c r="BJ3">
         <v>12</v>
       </c>
       <c r="BK3">
-        <v>9</v>
+        <v>5.7</v>
       </c>
       <c r="BL3">
         <v>1000</v>
@@ -1439,22 +1439,22 @@
         <v>107</v>
       </c>
       <c r="F4">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="G4">
         <v>3.75</v>
       </c>
       <c r="H4">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="I4">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="J4">
         <v>3.75</v>
       </c>
       <c r="K4">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L4">
         <v>1.28</v>
@@ -1469,7 +1469,7 @@
         <v>1.25</v>
       </c>
       <c r="P4">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="Q4">
         <v>1.74</v>
@@ -1478,16 +1478,16 @@
         <v>1.48</v>
       </c>
       <c r="S4">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="T4">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="U4">
         <v>2.36</v>
       </c>
       <c r="V4">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="W4">
         <v>1.37</v>
@@ -1499,10 +1499,10 @@
         <v>14.5</v>
       </c>
       <c r="Z4">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AA4">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="AB4">
         <v>16.5</v>
@@ -1517,34 +1517,34 @@
         <v>25</v>
       </c>
       <c r="AF4">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AG4">
         <v>15.5</v>
       </c>
       <c r="AH4">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AI4">
         <v>32</v>
       </c>
       <c r="AJ4">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="AK4">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AL4">
         <v>55</v>
       </c>
       <c r="AM4">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="AN4">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AO4">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AP4">
         <v>16.5</v>
@@ -1556,7 +1556,7 @@
         <v>13</v>
       </c>
       <c r="AS4">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="AT4">
         <v>14.5</v>
@@ -1580,22 +1580,22 @@
         <v>14</v>
       </c>
       <c r="BA4">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BB4">
+        <v>6.4</v>
+      </c>
+      <c r="BC4">
+        <v>6</v>
+      </c>
+      <c r="BD4">
         <v>6.2</v>
       </c>
-      <c r="BC4">
-        <v>32</v>
-      </c>
-      <c r="BD4">
-        <v>36</v>
-      </c>
       <c r="BE4">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BF4">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BG4">
         <v>11</v>
@@ -1604,37 +1604,37 @@
         <v>3.9</v>
       </c>
       <c r="BI4">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="BJ4">
         <v>9</v>
       </c>
       <c r="BK4">
-        <v>6.6</v>
+        <v>5.9</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BN4">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BO4">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BP4">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BQ4">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BR4">
         <v>34</v>
       </c>
       <c r="BS4">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BT4">
         <v>5.2</v>
@@ -1652,7 +1652,7 @@
         <v>25</v>
       </c>
       <c r="BY4">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BZ4">
         <v>0</v>
@@ -1681,10 +1681,10 @@
         <v>108</v>
       </c>
       <c r="F5">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="G5">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="H5">
         <v>3</v>
@@ -1705,28 +1705,28 @@
         <v>1.05</v>
       </c>
       <c r="N5">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="O5">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="P5">
         <v>2.42</v>
       </c>
       <c r="Q5">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="R5">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="S5">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="T5">
         <v>1.61</v>
       </c>
       <c r="U5">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="V5">
         <v>1.44</v>
@@ -1774,7 +1774,7 @@
         <v>32</v>
       </c>
       <c r="AK5">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AL5">
         <v>32</v>
@@ -1783,10 +1783,10 @@
         <v>75</v>
       </c>
       <c r="AN5">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AO5">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AP5">
         <v>18</v>
@@ -1795,10 +1795,10 @@
         <v>11.5</v>
       </c>
       <c r="AR5">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="AS5">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="AT5">
         <v>10</v>
@@ -1810,7 +1810,7 @@
         <v>11.5</v>
       </c>
       <c r="AW5">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="AX5">
         <v>13.5</v>
@@ -1822,19 +1822,19 @@
         <v>11.5</v>
       </c>
       <c r="BA5">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BB5">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BC5">
         <v>20</v>
       </c>
       <c r="BD5">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BE5">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BF5">
         <v>11.5</v>
@@ -1891,7 +1891,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BX5">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BY5">
         <v>10</v>
@@ -1950,19 +1950,19 @@
         <v>1.25</v>
       </c>
       <c r="O6">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="P6">
         <v>1.25</v>
       </c>
       <c r="Q6">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="R6">
         <v>1.18</v>
       </c>
       <c r="S6">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="T6">
         <v>1.11</v>
@@ -2165,19 +2165,19 @@
         <v>110</v>
       </c>
       <c r="F7">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="G7">
         <v>1000</v>
       </c>
       <c r="H7">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="I7">
         <v>1000</v>
       </c>
       <c r="J7">
-        <v>1.45</v>
+        <v>1.27</v>
       </c>
       <c r="K7">
         <v>1000</v>
@@ -2189,22 +2189,22 @@
         <v>1.02</v>
       </c>
       <c r="N7">
-        <v>1.32</v>
+        <v>3.15</v>
       </c>
       <c r="O7">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="P7">
-        <v>1.32</v>
+        <v>3.15</v>
       </c>
       <c r="Q7">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="R7">
-        <v>1.32</v>
+        <v>1.73</v>
       </c>
       <c r="S7">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="T7">
         <v>1.11</v>
@@ -2213,10 +2213,10 @@
         <v>1.11</v>
       </c>
       <c r="V7">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="W7">
-        <v>1.18</v>
+        <v>1.05</v>
       </c>
       <c r="X7">
         <v>1000</v>
@@ -2667,22 +2667,22 @@
         <v>3.25</v>
       </c>
       <c r="L9">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="M9">
         <v>1.13</v>
       </c>
       <c r="N9">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="O9">
         <v>1.63</v>
       </c>
       <c r="P9">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="Q9">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="R9">
         <v>1.16</v>
@@ -2718,7 +2718,7 @@
         <v>6.2</v>
       </c>
       <c r="AC9">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD9">
         <v>21</v>
@@ -2745,7 +2745,7 @@
         <v>34</v>
       </c>
       <c r="AL9">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="AM9">
         <v>310</v>
@@ -2763,13 +2763,13 @@
         <v>9.4</v>
       </c>
       <c r="AR9">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="AS9">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT9">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="AU9">
         <v>6.8</v>
@@ -2778,7 +2778,7 @@
         <v>17.5</v>
       </c>
       <c r="AW9">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AX9">
         <v>9.6</v>
@@ -2787,28 +2787,28 @@
         <v>10.5</v>
       </c>
       <c r="AZ9">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BA9">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB9">
-        <v>21</v>
+        <v>7.8</v>
       </c>
       <c r="BC9">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="BD9">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE9">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BF9">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BG9">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BH9">
         <v>2.64</v>
@@ -2820,7 +2820,7 @@
         <v>13</v>
       </c>
       <c r="BK9">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BL9">
         <v>1000</v>
@@ -2853,19 +2853,19 @@
         <v>5.5</v>
       </c>
       <c r="BV9">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BW9">
         <v>9.6</v>
       </c>
       <c r="BX9">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="BY9">
         <v>10</v>
       </c>
       <c r="BZ9">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="CA9">
         <v>9.6</v>
@@ -2894,7 +2894,7 @@
         <v>1.57</v>
       </c>
       <c r="G10">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="H10">
         <v>7.6</v>
@@ -2903,13 +2903,13 @@
         <v>9</v>
       </c>
       <c r="J10">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="K10">
         <v>4</v>
       </c>
       <c r="L10">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="M10">
         <v>1.1</v>
@@ -2918,37 +2918,37 @@
         <v>2.92</v>
       </c>
       <c r="O10">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="P10">
         <v>1.65</v>
       </c>
       <c r="Q10">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="R10">
         <v>1.23</v>
       </c>
       <c r="S10">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="T10">
         <v>2.32</v>
       </c>
       <c r="U10">
-        <v>1.74</v>
+        <v>1.66</v>
       </c>
       <c r="V10">
         <v>1.12</v>
       </c>
       <c r="W10">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
       <c r="X10">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Y10">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Z10">
         <v>85</v>
@@ -2957,7 +2957,7 @@
         <v>390</v>
       </c>
       <c r="AB10">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="AC10">
         <v>11</v>
@@ -2981,7 +2981,7 @@
         <v>200</v>
       </c>
       <c r="AJ10">
-        <v>18.5</v>
+        <v>16</v>
       </c>
       <c r="AK10">
         <v>22</v>
@@ -2993,7 +2993,7 @@
         <v>300</v>
       </c>
       <c r="AN10">
-        <v>16.5</v>
+        <v>14</v>
       </c>
       <c r="AO10">
         <v>390</v>
@@ -3005,34 +3005,34 @@
         <v>14</v>
       </c>
       <c r="AR10">
-        <v>4.4</v>
+        <v>5.2</v>
       </c>
       <c r="AS10">
-        <v>4.6</v>
+        <v>5.5</v>
       </c>
       <c r="AT10">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="AU10">
         <v>7.8</v>
       </c>
       <c r="AV10">
-        <v>4.1</v>
+        <v>4.9</v>
       </c>
       <c r="AW10">
-        <v>4.5</v>
+        <v>5.4</v>
       </c>
       <c r="AX10">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="AY10">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AZ10">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="BA10">
-        <v>4.5</v>
+        <v>5.4</v>
       </c>
       <c r="BB10">
         <v>11</v>
@@ -3041,16 +3041,16 @@
         <v>15.5</v>
       </c>
       <c r="BD10">
-        <v>4.3</v>
+        <v>5.1</v>
       </c>
       <c r="BE10">
-        <v>4.6</v>
+        <v>5.5</v>
       </c>
       <c r="BF10">
         <v>10</v>
       </c>
       <c r="BG10">
-        <v>4.6</v>
+        <v>5.5</v>
       </c>
       <c r="BH10">
         <v>3.1</v>
@@ -3074,22 +3074,22 @@
         <v>3.9</v>
       </c>
       <c r="BO10">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="BP10">
         <v>11.5</v>
       </c>
       <c r="BQ10">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BR10">
         <v>1000</v>
       </c>
       <c r="BS10">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BT10">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BU10">
         <v>5.7</v>
@@ -3098,19 +3098,19 @@
         <v>1000</v>
       </c>
       <c r="BW10">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BX10">
         <v>1000</v>
       </c>
       <c r="BY10">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ10">
         <v>1000</v>
       </c>
       <c r="CA10">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="CB10" t="s">
         <v>115</v>
@@ -3139,7 +3139,7 @@
         <v>4.7</v>
       </c>
       <c r="H11">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="I11">
         <v>2.2</v>
@@ -3148,7 +3148,7 @@
         <v>3.1</v>
       </c>
       <c r="K11">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L11">
         <v>1.53</v>
@@ -3157,22 +3157,22 @@
         <v>1.11</v>
       </c>
       <c r="N11">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="O11">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="P11">
         <v>1.59</v>
       </c>
       <c r="Q11">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="R11">
         <v>1.21</v>
       </c>
       <c r="S11">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="T11">
         <v>2.06</v>
@@ -3187,10 +3187,10 @@
         <v>1.27</v>
       </c>
       <c r="X11">
-        <v>11.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y11">
-        <v>8.6</v>
+        <v>7.4</v>
       </c>
       <c r="Z11">
         <v>14.5</v>
@@ -3250,7 +3250,7 @@
         <v>10.5</v>
       </c>
       <c r="AS11">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="AT11">
         <v>10.5</v>
@@ -3262,34 +3262,34 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AW11">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="AX11">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="AY11">
         <v>16</v>
       </c>
       <c r="AZ11">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="BA11">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="BB11">
-        <v>4.3</v>
+        <v>5.1</v>
       </c>
       <c r="BC11">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="BD11">
-        <v>4.3</v>
+        <v>5.1</v>
       </c>
       <c r="BE11">
-        <v>4.4</v>
+        <v>5.2</v>
       </c>
       <c r="BF11">
-        <v>4.3</v>
+        <v>5.1</v>
       </c>
       <c r="BG11">
         <v>18</v>
@@ -3304,7 +3304,7 @@
         <v>11.5</v>
       </c>
       <c r="BK11">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BL11">
         <v>1000</v>
@@ -3346,7 +3346,7 @@
         <v>1000</v>
       </c>
       <c r="BY11">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BZ11">
         <v>1000</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-28.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-28.xlsx
@@ -361,7 +361,7 @@
     <t>Athletic Club</t>
   </si>
   <si>
-    <t>2026-07-27 08:10:19</t>
+    <t>2026-07-27 08:59:28</t>
   </si>
 </sst>
 </file>
@@ -964,10 +964,10 @@
         <v>3.45</v>
       </c>
       <c r="I2">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="J2">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="K2">
         <v>3.25</v>
@@ -982,25 +982,25 @@
         <v>2.78</v>
       </c>
       <c r="O2">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="P2">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="Q2">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="R2">
         <v>1.2</v>
       </c>
       <c r="S2">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="T2">
-        <v>2.08</v>
+        <v>1.57</v>
       </c>
       <c r="U2">
-        <v>1.8</v>
+        <v>1.49</v>
       </c>
       <c r="V2">
         <v>1.37</v>
@@ -1009,172 +1009,172 @@
         <v>1.65</v>
       </c>
       <c r="X2">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="Y2">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="Z2">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AA2">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AB2">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="AC2">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="AD2">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AE2">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AF2">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AG2">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AH2">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AI2">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AJ2">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AK2">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AL2">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AM2">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="AN2">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AO2">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AP2">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AQ2">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AR2">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="AS2">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="AT2">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AU2">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV2">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW2">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="AX2">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY2">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AZ2">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA2">
-        <v>24</v>
+        <v>1.01</v>
       </c>
       <c r="BB2">
-        <v>32</v>
+        <v>1.01</v>
       </c>
       <c r="BC2">
-        <v>29</v>
+        <v>1.01</v>
       </c>
       <c r="BD2">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BE2">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BF2">
-        <v>32</v>
+        <v>1.01</v>
       </c>
       <c r="BG2">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="BH2">
-        <v>2.74</v>
+        <v>1000</v>
       </c>
       <c r="BI2">
-        <v>2.3</v>
+        <v>1.04</v>
       </c>
       <c r="BJ2">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BK2">
-        <v>8.4</v>
+        <v>1.04</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>13.5</v>
+        <v>1.04</v>
       </c>
       <c r="BN2">
-        <v>5.2</v>
+        <v>1000</v>
       </c>
       <c r="BO2">
-        <v>4.5</v>
+        <v>1.04</v>
       </c>
       <c r="BP2">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="BQ2">
-        <v>8.800000000000001</v>
+        <v>1.04</v>
       </c>
       <c r="BR2">
         <v>1000</v>
       </c>
       <c r="BS2">
-        <v>11</v>
+        <v>1.04</v>
       </c>
       <c r="BT2">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="BU2">
-        <v>5.7</v>
+        <v>1.04</v>
       </c>
       <c r="BV2">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BW2">
-        <v>10.5</v>
+        <v>1.04</v>
       </c>
       <c r="BX2">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BY2">
-        <v>12</v>
+        <v>1.04</v>
       </c>
       <c r="BZ2">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="CA2">
-        <v>11.5</v>
+        <v>1.04</v>
       </c>
       <c r="CB2" t="s">
         <v>115</v>
@@ -1200,16 +1200,16 @@
         <v>4.7</v>
       </c>
       <c r="G3">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="H3">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="I3">
         <v>2</v>
       </c>
       <c r="J3">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="K3">
         <v>3.45</v>
@@ -1239,184 +1239,184 @@
         <v>4.7</v>
       </c>
       <c r="T3">
-        <v>2.08</v>
+        <v>1.11</v>
       </c>
       <c r="U3">
-        <v>1.78</v>
+        <v>1.11</v>
       </c>
       <c r="V3">
         <v>2</v>
       </c>
       <c r="W3">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="X3">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="Y3">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="Z3">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AA3">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AB3">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AC3">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AD3">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AE3">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AF3">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AG3">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AH3">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AI3">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AJ3">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AK3">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AL3">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AM3">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="AN3">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AO3">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AP3">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="AQ3">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="AR3">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="AS3">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="AT3">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AU3">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AV3">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AW3">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="AX3">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="AY3">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="AZ3">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA3">
-        <v>42</v>
+        <v>1.01</v>
       </c>
       <c r="BB3">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="BC3">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="BD3">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="BE3">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="BF3">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="BG3">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="BH3">
-        <v>3</v>
+        <v>1000</v>
       </c>
       <c r="BI3">
-        <v>2.44</v>
+        <v>1.04</v>
       </c>
       <c r="BJ3">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BK3">
-        <v>5.7</v>
+        <v>1.04</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>10.5</v>
+        <v>1.04</v>
       </c>
       <c r="BN3">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="BO3">
-        <v>4.8</v>
+        <v>1.04</v>
       </c>
       <c r="BP3">
         <v>1000</v>
       </c>
       <c r="BQ3">
-        <v>9.199999999999999</v>
+        <v>1.04</v>
       </c>
       <c r="BR3">
         <v>1000</v>
       </c>
       <c r="BS3">
-        <v>9.4</v>
+        <v>1.04</v>
       </c>
       <c r="BT3">
-        <v>4.5</v>
+        <v>1000</v>
       </c>
       <c r="BU3">
-        <v>3.5</v>
+        <v>1.04</v>
       </c>
       <c r="BV3">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="BW3">
-        <v>6.4</v>
+        <v>1.04</v>
       </c>
       <c r="BX3">
         <v>1000</v>
       </c>
       <c r="BY3">
-        <v>8.4</v>
+        <v>1.04</v>
       </c>
       <c r="BZ3">
         <v>1000</v>
       </c>
       <c r="CA3">
-        <v>8.4</v>
+        <v>1.04</v>
       </c>
       <c r="CB3" t="s">
         <v>115</v>
@@ -1439,220 +1439,220 @@
         <v>107</v>
       </c>
       <c r="F4">
-        <v>3.45</v>
+        <v>2.2</v>
       </c>
       <c r="G4">
-        <v>3.75</v>
+        <v>1000</v>
       </c>
       <c r="H4">
-        <v>2.12</v>
+        <v>1.04</v>
       </c>
       <c r="I4">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="J4">
-        <v>3.75</v>
+        <v>1.02</v>
       </c>
       <c r="K4">
-        <v>3.95</v>
+        <v>1000</v>
       </c>
       <c r="L4">
-        <v>1.28</v>
+        <v>1.01</v>
       </c>
       <c r="M4">
         <v>1.05</v>
       </c>
       <c r="N4">
-        <v>4.5</v>
+        <v>1.1</v>
       </c>
       <c r="O4">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="P4">
-        <v>2.22</v>
+        <v>1.82</v>
       </c>
       <c r="Q4">
         <v>1.74</v>
       </c>
       <c r="R4">
-        <v>1.48</v>
+        <v>1.25</v>
       </c>
       <c r="S4">
-        <v>2.84</v>
+        <v>2.1</v>
       </c>
       <c r="T4">
-        <v>1.64</v>
+        <v>1.11</v>
       </c>
       <c r="U4">
-        <v>2.36</v>
+        <v>1.11</v>
       </c>
       <c r="V4">
-        <v>1.81</v>
+        <v>1.76</v>
       </c>
       <c r="W4">
-        <v>1.37</v>
+        <v>1.15</v>
       </c>
       <c r="X4">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="Y4">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="Z4">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AA4">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AB4">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AC4">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AD4">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AE4">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AF4">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AG4">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AH4">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AI4">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AJ4">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AK4">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AL4">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AM4">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AN4">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AO4">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AP4">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ4">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR4">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="AS4">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="AT4">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="AU4">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AV4">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AW4">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="AX4">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="AY4">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="AZ4">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="BA4">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="BB4">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BC4">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BD4">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BE4">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BF4">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="BG4">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BH4">
-        <v>3.9</v>
+        <v>1000</v>
       </c>
       <c r="BI4">
-        <v>3.55</v>
+        <v>1.04</v>
       </c>
       <c r="BJ4">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="BK4">
-        <v>5.9</v>
+        <v>1.04</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>14</v>
+        <v>1.04</v>
       </c>
       <c r="BN4">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="BO4">
-        <v>5.2</v>
+        <v>1.04</v>
       </c>
       <c r="BP4">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="BQ4">
-        <v>10</v>
+        <v>1.04</v>
       </c>
       <c r="BR4">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BS4">
-        <v>11</v>
+        <v>1.04</v>
       </c>
       <c r="BT4">
-        <v>5.2</v>
+        <v>1000</v>
       </c>
       <c r="BU4">
-        <v>4.6</v>
+        <v>1.04</v>
       </c>
       <c r="BV4">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="BW4">
-        <v>10.5</v>
+        <v>1.04</v>
       </c>
       <c r="BX4">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="BY4">
-        <v>10</v>
+        <v>1.04</v>
       </c>
       <c r="BZ4">
         <v>0</v>
@@ -1681,22 +1681,22 @@
         <v>108</v>
       </c>
       <c r="F5">
-        <v>2.32</v>
+        <v>1.71</v>
       </c>
       <c r="G5">
         <v>2.44</v>
       </c>
       <c r="H5">
-        <v>3</v>
+        <v>1.77</v>
       </c>
       <c r="I5">
-        <v>3.25</v>
+        <v>5.4</v>
       </c>
       <c r="J5">
-        <v>3.8</v>
+        <v>1.02</v>
       </c>
       <c r="K5">
-        <v>4</v>
+        <v>1000</v>
       </c>
       <c r="L5">
         <v>1.35</v>
@@ -1705,202 +1705,202 @@
         <v>1.05</v>
       </c>
       <c r="N5">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="O5">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="P5">
         <v>2.42</v>
       </c>
       <c r="Q5">
-        <v>1.68</v>
+        <v>1.23</v>
       </c>
       <c r="R5">
-        <v>1.52</v>
+        <v>1.25</v>
       </c>
       <c r="S5">
-        <v>2.72</v>
+        <v>1.23</v>
       </c>
       <c r="T5">
-        <v>1.61</v>
+        <v>1.35</v>
       </c>
       <c r="U5">
-        <v>2.46</v>
+        <v>1.87</v>
       </c>
       <c r="V5">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="W5">
         <v>1.69</v>
       </c>
       <c r="X5">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="Y5">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="Z5">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AA5">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AB5">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AC5">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AD5">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AE5">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AF5">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AG5">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AH5">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AI5">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AJ5">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AK5">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AL5">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AM5">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AN5">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AO5">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AP5">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="AQ5">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR5">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="AS5">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="AT5">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AU5">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="AV5">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW5">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="AX5">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY5">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AZ5">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA5">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="BB5">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="BC5">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BD5">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="BE5">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="BF5">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG5">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="BH5">
-        <v>4</v>
+        <v>1000</v>
       </c>
       <c r="BI5">
-        <v>3.6</v>
+        <v>1.04</v>
       </c>
       <c r="BJ5">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BK5">
-        <v>5.6</v>
+        <v>1.04</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>13</v>
+        <v>1.04</v>
       </c>
       <c r="BN5">
-        <v>5.7</v>
+        <v>1000</v>
       </c>
       <c r="BO5">
-        <v>5</v>
+        <v>1.04</v>
       </c>
       <c r="BP5">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="BQ5">
-        <v>8.199999999999999</v>
+        <v>1.04</v>
       </c>
       <c r="BR5">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="BS5">
-        <v>9.800000000000001</v>
+        <v>1.04</v>
       </c>
       <c r="BT5">
-        <v>6.4</v>
+        <v>1000</v>
       </c>
       <c r="BU5">
-        <v>5.7</v>
+        <v>1.04</v>
       </c>
       <c r="BV5">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="BW5">
-        <v>9.199999999999999</v>
+        <v>1.04</v>
       </c>
       <c r="BX5">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="BY5">
-        <v>10</v>
+        <v>1.04</v>
       </c>
       <c r="BZ5">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="CA5">
-        <v>8.6</v>
+        <v>1.04</v>
       </c>
       <c r="CB5" t="s">
         <v>115</v>
@@ -2171,13 +2171,13 @@
         <v>1000</v>
       </c>
       <c r="H7">
-        <v>1.23</v>
+        <v>1.04</v>
       </c>
       <c r="I7">
         <v>1000</v>
       </c>
       <c r="J7">
-        <v>1.27</v>
+        <v>1.03</v>
       </c>
       <c r="K7">
         <v>1000</v>
@@ -2189,22 +2189,22 @@
         <v>1.02</v>
       </c>
       <c r="N7">
-        <v>3.15</v>
+        <v>2.16</v>
       </c>
       <c r="O7">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="P7">
-        <v>3.15</v>
+        <v>2.16</v>
       </c>
       <c r="Q7">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="R7">
-        <v>1.73</v>
+        <v>2.16</v>
       </c>
       <c r="S7">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="T7">
         <v>1.11</v>
@@ -2213,10 +2213,10 @@
         <v>1.11</v>
       </c>
       <c r="V7">
-        <v>1.21</v>
+        <v>1.05</v>
       </c>
       <c r="W7">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="X7">
         <v>1000</v>
@@ -2407,22 +2407,22 @@
         <v>111</v>
       </c>
       <c r="F8">
-        <v>2.04</v>
+        <v>1.47</v>
       </c>
       <c r="G8">
-        <v>2.18</v>
+        <v>1000</v>
       </c>
       <c r="H8">
-        <v>4.7</v>
+        <v>1.47</v>
       </c>
       <c r="I8">
-        <v>5.3</v>
+        <v>1000</v>
       </c>
       <c r="J8">
-        <v>2.94</v>
+        <v>1.01</v>
       </c>
       <c r="K8">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="L8">
         <v>0</v>
@@ -2437,10 +2437,10 @@
         <v>0</v>
       </c>
       <c r="P8">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="Q8">
-        <v>2.96</v>
+        <v>1.01</v>
       </c>
       <c r="R8">
         <v>0</v>
@@ -2649,226 +2649,226 @@
         <v>112</v>
       </c>
       <c r="F9">
-        <v>2.08</v>
+        <v>1.45</v>
       </c>
       <c r="G9">
-        <v>2.2</v>
+        <v>24</v>
       </c>
       <c r="H9">
-        <v>4.3</v>
+        <v>3.5</v>
       </c>
       <c r="I9">
-        <v>4.9</v>
+        <v>110</v>
       </c>
       <c r="J9">
-        <v>3.1</v>
+        <v>1.11</v>
       </c>
       <c r="K9">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="L9">
-        <v>1.62</v>
+        <v>1.33</v>
       </c>
       <c r="M9">
         <v>1.13</v>
       </c>
       <c r="N9">
-        <v>2.44</v>
+        <v>2.2</v>
       </c>
       <c r="O9">
-        <v>1.63</v>
+        <v>1.14</v>
       </c>
       <c r="P9">
-        <v>1.46</v>
+        <v>1.26</v>
       </c>
       <c r="Q9">
-        <v>2.9</v>
+        <v>1.6</v>
       </c>
       <c r="R9">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="S9">
-        <v>6.2</v>
+        <v>1.05</v>
       </c>
       <c r="T9">
-        <v>2.32</v>
+        <v>1.11</v>
       </c>
       <c r="U9">
-        <v>1.63</v>
+        <v>1.11</v>
       </c>
       <c r="V9">
         <v>1.25</v>
       </c>
       <c r="W9">
-        <v>1.83</v>
+        <v>1.04</v>
       </c>
       <c r="X9">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="Y9">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="Z9">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AA9">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AB9">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="AC9">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AD9">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AE9">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AF9">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AG9">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AH9">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AI9">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AJ9">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AK9">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AL9">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AM9">
-        <v>310</v>
+        <v>1000</v>
       </c>
       <c r="AN9">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AO9">
-        <v>190</v>
+        <v>1000</v>
       </c>
       <c r="AP9">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AQ9">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AR9">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="AS9">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AT9">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="AU9">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="AV9">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW9">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="AX9">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="AY9">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AZ9">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="BA9">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BB9">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="BC9">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="BD9">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BE9">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BF9">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="BG9">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BH9">
-        <v>2.64</v>
+        <v>1000</v>
       </c>
       <c r="BI9">
-        <v>2.32</v>
+        <v>1.04</v>
       </c>
       <c r="BJ9">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="BK9">
-        <v>6</v>
+        <v>1.04</v>
       </c>
       <c r="BL9">
         <v>1000</v>
       </c>
       <c r="BM9">
-        <v>11</v>
+        <v>1.04</v>
       </c>
       <c r="BN9">
-        <v>4.7</v>
+        <v>1000</v>
       </c>
       <c r="BO9">
-        <v>3.95</v>
+        <v>1.04</v>
       </c>
       <c r="BP9">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="BQ9">
-        <v>7.2</v>
+        <v>1.04</v>
       </c>
       <c r="BR9">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="BS9">
-        <v>9.4</v>
+        <v>1.04</v>
       </c>
       <c r="BT9">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="BU9">
-        <v>5.5</v>
+        <v>1.04</v>
       </c>
       <c r="BV9">
         <v>1000</v>
       </c>
       <c r="BW9">
-        <v>9.6</v>
+        <v>1.04</v>
       </c>
       <c r="BX9">
         <v>1000</v>
       </c>
       <c r="BY9">
-        <v>10</v>
+        <v>1.04</v>
       </c>
       <c r="BZ9">
         <v>1000</v>
       </c>
       <c r="CA9">
-        <v>9.6</v>
+        <v>1.04</v>
       </c>
       <c r="CB9" t="s">
         <v>115</v>
@@ -2891,226 +2891,226 @@
         <v>113</v>
       </c>
       <c r="F10">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="G10">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="H10">
-        <v>7.6</v>
+        <v>6.2</v>
       </c>
       <c r="I10">
-        <v>9</v>
+        <v>15.5</v>
       </c>
       <c r="J10">
         <v>3.7</v>
       </c>
       <c r="K10">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L10">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="M10">
         <v>1.1</v>
       </c>
       <c r="N10">
-        <v>2.92</v>
+        <v>1.1</v>
       </c>
       <c r="O10">
-        <v>1.46</v>
+        <v>1.1</v>
       </c>
       <c r="P10">
-        <v>1.65</v>
+        <v>1.33</v>
       </c>
       <c r="Q10">
-        <v>2.34</v>
+        <v>1.9</v>
       </c>
       <c r="R10">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="S10">
-        <v>4.7</v>
+        <v>1.9</v>
       </c>
       <c r="T10">
-        <v>2.32</v>
+        <v>1.75</v>
       </c>
       <c r="U10">
-        <v>1.66</v>
+        <v>1.35</v>
       </c>
       <c r="V10">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="W10">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="X10">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="Y10">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="Z10">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AA10">
-        <v>390</v>
+        <v>1000</v>
       </c>
       <c r="AB10">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="AC10">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AD10">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AE10">
-        <v>210</v>
+        <v>1000</v>
       </c>
       <c r="AF10">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="AG10">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AH10">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AI10">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="AJ10">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AK10">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AL10">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AM10">
-        <v>300</v>
+        <v>1000</v>
       </c>
       <c r="AN10">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AO10">
-        <v>390</v>
+        <v>1000</v>
       </c>
       <c r="AP10">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="AQ10">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="AR10">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="AS10">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="AT10">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="AU10">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AV10">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="AW10">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="AX10">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="AY10">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="AZ10">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BA10">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="BB10">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BC10">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD10">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BE10">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="BF10">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BG10">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="BH10">
-        <v>3.1</v>
+        <v>1000</v>
       </c>
       <c r="BI10">
-        <v>2.42</v>
+        <v>1.04</v>
       </c>
       <c r="BJ10">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="BK10">
-        <v>6</v>
+        <v>1.04</v>
       </c>
       <c r="BL10">
         <v>1000</v>
       </c>
       <c r="BM10">
-        <v>10.5</v>
+        <v>1.04</v>
       </c>
       <c r="BN10">
-        <v>3.9</v>
+        <v>1000</v>
       </c>
       <c r="BO10">
-        <v>2.98</v>
+        <v>1.04</v>
       </c>
       <c r="BP10">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ10">
-        <v>5.6</v>
+        <v>1.04</v>
       </c>
       <c r="BR10">
         <v>1000</v>
       </c>
       <c r="BS10">
-        <v>8.4</v>
+        <v>1.04</v>
       </c>
       <c r="BT10">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BU10">
-        <v>5.7</v>
+        <v>1.04</v>
       </c>
       <c r="BV10">
         <v>1000</v>
       </c>
       <c r="BW10">
-        <v>9.800000000000001</v>
+        <v>1.04</v>
       </c>
       <c r="BX10">
         <v>1000</v>
       </c>
       <c r="BY10">
-        <v>9.800000000000001</v>
+        <v>1.04</v>
       </c>
       <c r="BZ10">
         <v>1000</v>
       </c>
       <c r="CA10">
-        <v>7.8</v>
+        <v>1.04</v>
       </c>
       <c r="CB10" t="s">
         <v>115</v>
@@ -3136,223 +3136,223 @@
         <v>4.3</v>
       </c>
       <c r="G11">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="H11">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="I11">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="J11">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="K11">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="L11">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="M11">
+        <v>1.04</v>
+      </c>
+      <c r="N11">
+        <v>2.06</v>
+      </c>
+      <c r="O11">
+        <v>1.24</v>
+      </c>
+      <c r="P11">
+        <v>1.25</v>
+      </c>
+      <c r="Q11">
+        <v>1.47</v>
+      </c>
+      <c r="R11">
+        <v>1.17</v>
+      </c>
+      <c r="S11">
+        <v>1.47</v>
+      </c>
+      <c r="T11">
         <v>1.11</v>
       </c>
-      <c r="N11">
-        <v>2.78</v>
-      </c>
-      <c r="O11">
-        <v>1.48</v>
-      </c>
-      <c r="P11">
-        <v>1.59</v>
-      </c>
-      <c r="Q11">
-        <v>2.42</v>
-      </c>
-      <c r="R11">
-        <v>1.21</v>
-      </c>
-      <c r="S11">
-        <v>4.9</v>
-      </c>
-      <c r="T11">
-        <v>2.06</v>
-      </c>
       <c r="U11">
-        <v>1.8</v>
+        <v>1.11</v>
       </c>
       <c r="V11">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="W11">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="X11">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="Y11">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="Z11">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AA11">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AB11">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AC11">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="AD11">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AE11">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AF11">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AG11">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AH11">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AI11">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AJ11">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AK11">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AL11">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AM11">
-        <v>210</v>
+        <v>1000</v>
       </c>
       <c r="AN11">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AO11">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AP11">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="AQ11">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AR11">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS11">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="AT11">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AU11">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AV11">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AW11">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="AX11">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="AY11">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="AZ11">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA11">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BB11">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BC11">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="BD11">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BE11">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="BF11">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BG11">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="BH11">
-        <v>2.86</v>
+        <v>1000</v>
       </c>
       <c r="BI11">
-        <v>2.4</v>
+        <v>1.04</v>
       </c>
       <c r="BJ11">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BK11">
-        <v>6.6</v>
+        <v>1.04</v>
       </c>
       <c r="BL11">
         <v>1000</v>
       </c>
       <c r="BM11">
-        <v>14</v>
+        <v>1.04</v>
       </c>
       <c r="BN11">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="BO11">
-        <v>5.6</v>
+        <v>1.04</v>
       </c>
       <c r="BP11">
         <v>1000</v>
       </c>
       <c r="BQ11">
-        <v>11</v>
+        <v>1.04</v>
       </c>
       <c r="BR11">
         <v>1000</v>
       </c>
       <c r="BS11">
-        <v>12</v>
+        <v>1.04</v>
       </c>
       <c r="BT11">
-        <v>4.7</v>
+        <v>1000</v>
       </c>
       <c r="BU11">
-        <v>3.6</v>
+        <v>1.04</v>
       </c>
       <c r="BV11">
         <v>1000</v>
       </c>
       <c r="BW11">
-        <v>8</v>
+        <v>1.04</v>
       </c>
       <c r="BX11">
         <v>1000</v>
       </c>
       <c r="BY11">
-        <v>11</v>
+        <v>1.04</v>
       </c>
       <c r="BZ11">
         <v>1000</v>
       </c>
       <c r="CA11">
-        <v>11</v>
+        <v>1.04</v>
       </c>
       <c r="CB11" t="s">
         <v>115</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-28.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-28.xlsx
@@ -361,7 +361,7 @@
     <t>Athletic Club</t>
   </si>
   <si>
-    <t>2026-07-27 08:59:28</t>
+    <t>2026-07-27 11:06:49</t>
   </si>
 </sst>
 </file>
@@ -955,13 +955,13 @@
         <v>105</v>
       </c>
       <c r="F2">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="G2">
         <v>2.52</v>
       </c>
       <c r="H2">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="I2">
         <v>3.7</v>
@@ -973,7 +973,7 @@
         <v>3.25</v>
       </c>
       <c r="L2">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="M2">
         <v>1.12</v>
@@ -982,25 +982,25 @@
         <v>2.78</v>
       </c>
       <c r="O2">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="P2">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="Q2">
         <v>2.64</v>
       </c>
       <c r="R2">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="S2">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="T2">
-        <v>1.57</v>
+        <v>2.08</v>
       </c>
       <c r="U2">
-        <v>1.49</v>
+        <v>1.81</v>
       </c>
       <c r="V2">
         <v>1.37</v>
@@ -1009,172 +1009,172 @@
         <v>1.65</v>
       </c>
       <c r="X2">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y2">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="Z2">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AA2">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AB2">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="AC2">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="AD2">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AE2">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AF2">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AG2">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH2">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI2">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AJ2">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AK2">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AL2">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AM2">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AN2">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AO2">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AP2">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AQ2">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AR2">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="AS2">
-        <v>1.01</v>
+        <v>55</v>
       </c>
       <c r="AT2">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AU2">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AV2">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AW2">
-        <v>1.01</v>
+        <v>34</v>
       </c>
       <c r="AX2">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AY2">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AZ2">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="BA2">
-        <v>1.01</v>
+        <v>50</v>
       </c>
       <c r="BB2">
-        <v>1.01</v>
+        <v>28</v>
       </c>
       <c r="BC2">
-        <v>1.01</v>
+        <v>26</v>
       </c>
       <c r="BD2">
-        <v>1.01</v>
+        <v>44</v>
       </c>
       <c r="BE2">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BF2">
-        <v>1.01</v>
+        <v>27</v>
       </c>
       <c r="BG2">
-        <v>1.01</v>
+        <v>50</v>
       </c>
       <c r="BH2">
-        <v>1000</v>
+        <v>2.74</v>
       </c>
       <c r="BI2">
-        <v>1.04</v>
+        <v>2.34</v>
       </c>
       <c r="BJ2">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK2">
-        <v>1.04</v>
+        <v>6.6</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>1.04</v>
+        <v>2.32</v>
       </c>
       <c r="BN2">
-        <v>1000</v>
+        <v>5.1</v>
       </c>
       <c r="BO2">
-        <v>1.04</v>
+        <v>3.9</v>
       </c>
       <c r="BP2">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="BQ2">
-        <v>1.04</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BR2">
         <v>1000</v>
       </c>
       <c r="BS2">
-        <v>1.04</v>
+        <v>11.5</v>
       </c>
       <c r="BT2">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="BU2">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="BV2">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BW2">
-        <v>1.04</v>
+        <v>11</v>
       </c>
       <c r="BX2">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BY2">
-        <v>1.04</v>
+        <v>12.5</v>
       </c>
       <c r="BZ2">
         <v>1000</v>
       </c>
       <c r="CA2">
-        <v>1.04</v>
+        <v>12</v>
       </c>
       <c r="CB2" t="s">
         <v>115</v>
@@ -1197,22 +1197,22 @@
         <v>106</v>
       </c>
       <c r="F3">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="G3">
-        <v>5.7</v>
+        <v>5.4</v>
       </c>
       <c r="H3">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="I3">
         <v>2</v>
       </c>
       <c r="J3">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K3">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L3">
         <v>1.52</v>
@@ -1227,10 +1227,10 @@
         <v>1.46</v>
       </c>
       <c r="P3">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="Q3">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="R3">
         <v>1.23</v>
@@ -1239,184 +1239,184 @@
         <v>4.7</v>
       </c>
       <c r="T3">
-        <v>1.11</v>
+        <v>2.08</v>
       </c>
       <c r="U3">
-        <v>1.11</v>
+        <v>1.79</v>
       </c>
       <c r="V3">
         <v>2</v>
       </c>
       <c r="W3">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="X3">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="Y3">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="Z3">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AA3">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AB3">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AC3">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD3">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AE3">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AF3">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AG3">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AH3">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AI3">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AJ3">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AK3">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AL3">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AM3">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AN3">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AO3">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AP3">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AQ3">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="AR3">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS3">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="AT3">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AU3">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AV3">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW3">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="AX3">
-        <v>1.01</v>
+        <v>28</v>
       </c>
       <c r="AY3">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="AZ3">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="BA3">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BB3">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BC3">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BD3">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BE3">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BF3">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BG3">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="BH3">
-        <v>1000</v>
+        <v>3</v>
       </c>
       <c r="BI3">
-        <v>1.04</v>
+        <v>2.44</v>
       </c>
       <c r="BJ3">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BK3">
-        <v>1.04</v>
+        <v>5.7</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>1.04</v>
+        <v>10.5</v>
       </c>
       <c r="BN3">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="BO3">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="BP3">
         <v>1000</v>
       </c>
       <c r="BQ3">
-        <v>1.04</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BR3">
         <v>1000</v>
       </c>
       <c r="BS3">
-        <v>1.04</v>
+        <v>9.4</v>
       </c>
       <c r="BT3">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="BU3">
-        <v>1.04</v>
+        <v>3.5</v>
       </c>
       <c r="BV3">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="BW3">
-        <v>1.04</v>
+        <v>6.4</v>
       </c>
       <c r="BX3">
         <v>1000</v>
       </c>
       <c r="BY3">
-        <v>1.04</v>
+        <v>8.4</v>
       </c>
       <c r="BZ3">
         <v>1000</v>
       </c>
       <c r="CA3">
-        <v>1.04</v>
+        <v>8.4</v>
       </c>
       <c r="CB3" t="s">
         <v>115</v>
@@ -1439,220 +1439,220 @@
         <v>107</v>
       </c>
       <c r="F4">
-        <v>2.2</v>
+        <v>3.4</v>
       </c>
       <c r="G4">
-        <v>1000</v>
+        <v>3.65</v>
       </c>
       <c r="H4">
-        <v>1.04</v>
+        <v>2.12</v>
       </c>
       <c r="I4">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="J4">
-        <v>1.02</v>
+        <v>3.75</v>
       </c>
       <c r="K4">
-        <v>1000</v>
+        <v>3.95</v>
       </c>
       <c r="L4">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="M4">
         <v>1.05</v>
       </c>
       <c r="N4">
-        <v>1.1</v>
+        <v>4.5</v>
       </c>
       <c r="O4">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="P4">
-        <v>1.82</v>
+        <v>2.2</v>
       </c>
       <c r="Q4">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="R4">
-        <v>1.25</v>
+        <v>1.48</v>
       </c>
       <c r="S4">
-        <v>2.1</v>
+        <v>2.82</v>
       </c>
       <c r="T4">
-        <v>1.11</v>
+        <v>1.64</v>
       </c>
       <c r="U4">
-        <v>1.11</v>
+        <v>2.36</v>
       </c>
       <c r="V4">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="W4">
-        <v>1.15</v>
+        <v>1.37</v>
       </c>
       <c r="X4">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="Y4">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="Z4">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AA4">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AB4">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AC4">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD4">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AE4">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AF4">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AG4">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AH4">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AI4">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AJ4">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AK4">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AL4">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM4">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AN4">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AO4">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AP4">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="AQ4">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AR4">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="AS4">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AT4">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="AU4">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AV4">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AW4">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="AX4">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AY4">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AZ4">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BA4">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BB4">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BC4">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BD4">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BE4">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BF4">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BG4">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="BH4">
-        <v>1000</v>
+        <v>3.9</v>
       </c>
       <c r="BI4">
-        <v>1.04</v>
+        <v>3.55</v>
       </c>
       <c r="BJ4">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="BK4">
-        <v>1.04</v>
+        <v>5.7</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>1.04</v>
+        <v>13</v>
       </c>
       <c r="BN4">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="BO4">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="BP4">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BQ4">
-        <v>1.04</v>
+        <v>9.6</v>
       </c>
       <c r="BR4">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BS4">
-        <v>1.04</v>
+        <v>10.5</v>
       </c>
       <c r="BT4">
-        <v>1000</v>
+        <v>5.3</v>
       </c>
       <c r="BU4">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="BV4">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="BW4">
-        <v>1.04</v>
+        <v>7.6</v>
       </c>
       <c r="BX4">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BY4">
-        <v>1.04</v>
+        <v>9.6</v>
       </c>
       <c r="BZ4">
         <v>0</v>
@@ -1681,22 +1681,22 @@
         <v>108</v>
       </c>
       <c r="F5">
-        <v>1.71</v>
+        <v>2.3</v>
       </c>
       <c r="G5">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="H5">
-        <v>1.77</v>
+        <v>2.98</v>
       </c>
       <c r="I5">
-        <v>5.4</v>
+        <v>3.25</v>
       </c>
       <c r="J5">
-        <v>1.02</v>
+        <v>3.8</v>
       </c>
       <c r="K5">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="L5">
         <v>1.35</v>
@@ -1705,202 +1705,202 @@
         <v>1.05</v>
       </c>
       <c r="N5">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="O5">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="P5">
         <v>2.42</v>
       </c>
       <c r="Q5">
-        <v>1.23</v>
+        <v>1.68</v>
       </c>
       <c r="R5">
-        <v>1.25</v>
+        <v>1.52</v>
       </c>
       <c r="S5">
-        <v>1.23</v>
+        <v>2.72</v>
       </c>
       <c r="T5">
-        <v>1.35</v>
+        <v>1.6</v>
       </c>
       <c r="U5">
-        <v>1.87</v>
+        <v>2.46</v>
       </c>
       <c r="V5">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="W5">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="X5">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="Y5">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="Z5">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AA5">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AB5">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AC5">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AD5">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AE5">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AF5">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AG5">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH5">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AI5">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AJ5">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AK5">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AL5">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AM5">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AN5">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AO5">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AP5">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="AQ5">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AR5">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="AS5">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT5">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AU5">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AV5">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AW5">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX5">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="AY5">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AZ5">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BA5">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB5">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC5">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BD5">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE5">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BF5">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BG5">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="BH5">
-        <v>1000</v>
+        <v>4</v>
       </c>
       <c r="BI5">
-        <v>1.04</v>
+        <v>3.6</v>
       </c>
       <c r="BJ5">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK5">
-        <v>1.04</v>
+        <v>5.6</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>1.04</v>
+        <v>13</v>
       </c>
       <c r="BN5">
-        <v>1000</v>
+        <v>5.7</v>
       </c>
       <c r="BO5">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="BP5">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="BQ5">
-        <v>1.04</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR5">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BS5">
-        <v>1.04</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT5">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BU5">
-        <v>1.04</v>
+        <v>5.7</v>
       </c>
       <c r="BV5">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="BW5">
-        <v>1.04</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX5">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BY5">
-        <v>1.04</v>
+        <v>10</v>
       </c>
       <c r="BZ5">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="CA5">
-        <v>1.04</v>
+        <v>8.6</v>
       </c>
       <c r="CB5" t="s">
         <v>115</v>
@@ -2165,226 +2165,226 @@
         <v>110</v>
       </c>
       <c r="F7">
-        <v>1.23</v>
+        <v>6.8</v>
       </c>
       <c r="G7">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="H7">
-        <v>1.04</v>
+        <v>1.41</v>
       </c>
       <c r="I7">
-        <v>1000</v>
+        <v>1.47</v>
       </c>
       <c r="J7">
-        <v>1.03</v>
+        <v>5.7</v>
       </c>
       <c r="K7">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="L7">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="M7">
         <v>1.02</v>
       </c>
       <c r="N7">
-        <v>2.16</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O7">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="P7">
-        <v>2.16</v>
+        <v>3.55</v>
       </c>
       <c r="Q7">
-        <v>1.07</v>
+        <v>1.34</v>
       </c>
       <c r="R7">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="S7">
-        <v>1.07</v>
+        <v>1.81</v>
       </c>
       <c r="T7">
-        <v>1.11</v>
+        <v>1.56</v>
       </c>
       <c r="U7">
-        <v>1.11</v>
+        <v>2.58</v>
       </c>
       <c r="V7">
-        <v>1.05</v>
+        <v>3.1</v>
       </c>
       <c r="W7">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="X7">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Y7">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z7">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AA7">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AB7">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AC7">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AD7">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AE7">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AF7">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AG7">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AH7">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI7">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AJ7">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AK7">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AL7">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AM7">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AN7">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AO7">
-        <v>1000</v>
+        <v>3.85</v>
       </c>
       <c r="AP7">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AQ7">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AR7">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AS7">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AT7">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AU7">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AV7">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="AW7">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AX7">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AY7">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ7">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BA7">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BB7">
-        <v>1.01</v>
+        <v>2.9</v>
       </c>
       <c r="BC7">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BD7">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BE7">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BF7">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BG7">
-        <v>1.01</v>
+        <v>2.92</v>
       </c>
       <c r="BH7">
-        <v>1000</v>
+        <v>5.9</v>
       </c>
       <c r="BI7">
-        <v>1.04</v>
+        <v>4.1</v>
       </c>
       <c r="BJ7">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="BK7">
-        <v>1.04</v>
+        <v>5.5</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>1.04</v>
+        <v>11</v>
       </c>
       <c r="BN7">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BO7">
-        <v>1.04</v>
+        <v>6.2</v>
       </c>
       <c r="BP7">
         <v>1000</v>
       </c>
       <c r="BQ7">
-        <v>1.04</v>
+        <v>10</v>
       </c>
       <c r="BR7">
         <v>1000</v>
       </c>
       <c r="BS7">
-        <v>1.04</v>
+        <v>10</v>
       </c>
       <c r="BT7">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="BU7">
-        <v>1.04</v>
+        <v>3.9</v>
       </c>
       <c r="BV7">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="BW7">
-        <v>1.04</v>
+        <v>5.2</v>
       </c>
       <c r="BX7">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="BY7">
-        <v>1.04</v>
+        <v>7.4</v>
       </c>
       <c r="BZ7">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="CA7">
-        <v>1.04</v>
+        <v>5.2</v>
       </c>
       <c r="CB7" t="s">
         <v>115</v>
@@ -2407,22 +2407,22 @@
         <v>111</v>
       </c>
       <c r="F8">
-        <v>1.47</v>
+        <v>2.04</v>
       </c>
       <c r="G8">
-        <v>1000</v>
+        <v>2.18</v>
       </c>
       <c r="H8">
-        <v>1.47</v>
+        <v>4.7</v>
       </c>
       <c r="I8">
-        <v>1000</v>
+        <v>5.3</v>
       </c>
       <c r="J8">
-        <v>1.01</v>
+        <v>2.98</v>
       </c>
       <c r="K8">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="L8">
         <v>0</v>
@@ -2437,10 +2437,10 @@
         <v>0</v>
       </c>
       <c r="P8">
-        <v>1.25</v>
+        <v>1.45</v>
       </c>
       <c r="Q8">
-        <v>1.01</v>
+        <v>2.96</v>
       </c>
       <c r="R8">
         <v>0</v>
@@ -2649,226 +2649,226 @@
         <v>112</v>
       </c>
       <c r="F9">
-        <v>1.45</v>
+        <v>2.08</v>
       </c>
       <c r="G9">
-        <v>24</v>
+        <v>2.2</v>
       </c>
       <c r="H9">
-        <v>3.5</v>
+        <v>4.3</v>
       </c>
       <c r="I9">
-        <v>110</v>
+        <v>4.9</v>
       </c>
       <c r="J9">
-        <v>1.11</v>
+        <v>3.05</v>
       </c>
       <c r="K9">
         <v>3.3</v>
       </c>
       <c r="L9">
-        <v>1.33</v>
+        <v>1.63</v>
       </c>
       <c r="M9">
         <v>1.13</v>
       </c>
       <c r="N9">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="O9">
-        <v>1.14</v>
+        <v>1.62</v>
       </c>
       <c r="P9">
-        <v>1.26</v>
+        <v>1.45</v>
       </c>
       <c r="Q9">
-        <v>1.6</v>
+        <v>2.9</v>
       </c>
       <c r="R9">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="S9">
-        <v>1.05</v>
+        <v>6.2</v>
       </c>
       <c r="T9">
-        <v>1.11</v>
+        <v>2.36</v>
       </c>
       <c r="U9">
-        <v>1.11</v>
+        <v>1.63</v>
       </c>
       <c r="V9">
         <v>1.25</v>
       </c>
       <c r="W9">
-        <v>1.04</v>
+        <v>1.83</v>
       </c>
       <c r="X9">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="Y9">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="Z9">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AA9">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AB9">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="AC9">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="AD9">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AE9">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AF9">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AG9">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH9">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AI9">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AJ9">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AK9">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AL9">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AM9">
-        <v>1000</v>
+        <v>320</v>
       </c>
       <c r="AN9">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AO9">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AP9">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AQ9">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR9">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AS9">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT9">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="AU9">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AV9">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="AW9">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AX9">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY9">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AZ9">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BA9">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BB9">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BC9">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BD9">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BE9">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="BF9">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BG9">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH9">
-        <v>1000</v>
+        <v>2.62</v>
       </c>
       <c r="BI9">
-        <v>1.04</v>
+        <v>2.3</v>
       </c>
       <c r="BJ9">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BK9">
-        <v>1.04</v>
+        <v>6.2</v>
       </c>
       <c r="BL9">
         <v>1000</v>
       </c>
       <c r="BM9">
-        <v>1.04</v>
+        <v>11</v>
       </c>
       <c r="BN9">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="BO9">
-        <v>1.04</v>
+        <v>3.95</v>
       </c>
       <c r="BP9">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="BQ9">
-        <v>1.04</v>
+        <v>7.4</v>
       </c>
       <c r="BR9">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BS9">
-        <v>1.04</v>
+        <v>9.6</v>
       </c>
       <c r="BT9">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU9">
-        <v>1.04</v>
+        <v>5.5</v>
       </c>
       <c r="BV9">
         <v>1000</v>
       </c>
       <c r="BW9">
-        <v>1.04</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BX9">
         <v>1000</v>
       </c>
       <c r="BY9">
-        <v>1.04</v>
+        <v>10</v>
       </c>
       <c r="BZ9">
         <v>1000</v>
       </c>
       <c r="CA9">
-        <v>1.04</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CB9" t="s">
         <v>115</v>
@@ -2891,226 +2891,226 @@
         <v>113</v>
       </c>
       <c r="F10">
-        <v>1.38</v>
+        <v>1.58</v>
       </c>
       <c r="G10">
         <v>1.64</v>
       </c>
       <c r="H10">
+        <v>7.6</v>
+      </c>
+      <c r="I10">
+        <v>8.6</v>
+      </c>
+      <c r="J10">
+        <v>3.85</v>
+      </c>
+      <c r="K10">
+        <v>4</v>
+      </c>
+      <c r="L10">
+        <v>1.51</v>
+      </c>
+      <c r="M10">
+        <v>1.11</v>
+      </c>
+      <c r="N10">
+        <v>2.88</v>
+      </c>
+      <c r="O10">
+        <v>1.47</v>
+      </c>
+      <c r="P10">
+        <v>1.59</v>
+      </c>
+      <c r="Q10">
+        <v>2.4</v>
+      </c>
+      <c r="R10">
+        <v>1.21</v>
+      </c>
+      <c r="S10">
+        <v>4.8</v>
+      </c>
+      <c r="T10">
+        <v>2.3</v>
+      </c>
+      <c r="U10">
+        <v>1.63</v>
+      </c>
+      <c r="V10">
+        <v>1.13</v>
+      </c>
+      <c r="W10">
+        <v>2.56</v>
+      </c>
+      <c r="X10">
+        <v>12</v>
+      </c>
+      <c r="Y10">
+        <v>23</v>
+      </c>
+      <c r="Z10">
+        <v>85</v>
+      </c>
+      <c r="AA10">
+        <v>420</v>
+      </c>
+      <c r="AB10">
+        <v>6.4</v>
+      </c>
+      <c r="AC10">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD10">
+        <v>40</v>
+      </c>
+      <c r="AE10">
+        <v>220</v>
+      </c>
+      <c r="AF10">
+        <v>8.4</v>
+      </c>
+      <c r="AG10">
+        <v>13</v>
+      </c>
+      <c r="AH10">
+        <v>38</v>
+      </c>
+      <c r="AI10">
+        <v>210</v>
+      </c>
+      <c r="AJ10">
+        <v>16</v>
+      </c>
+      <c r="AK10">
+        <v>23</v>
+      </c>
+      <c r="AL10">
+        <v>70</v>
+      </c>
+      <c r="AM10">
+        <v>310</v>
+      </c>
+      <c r="AN10">
+        <v>14.5</v>
+      </c>
+      <c r="AO10">
+        <v>420</v>
+      </c>
+      <c r="AP10">
+        <v>7.6</v>
+      </c>
+      <c r="AQ10">
+        <v>14</v>
+      </c>
+      <c r="AR10">
+        <v>6.4</v>
+      </c>
+      <c r="AS10">
+        <v>6.8</v>
+      </c>
+      <c r="AT10">
+        <v>4.7</v>
+      </c>
+      <c r="AU10">
+        <v>7.8</v>
+      </c>
+      <c r="AV10">
+        <v>5.9</v>
+      </c>
+      <c r="AW10">
+        <v>6.6</v>
+      </c>
+      <c r="AX10">
+        <v>7</v>
+      </c>
+      <c r="AY10">
+        <v>8</v>
+      </c>
+      <c r="AZ10">
+        <v>5.9</v>
+      </c>
+      <c r="BA10">
+        <v>6.6</v>
+      </c>
+      <c r="BB10">
+        <v>11</v>
+      </c>
+      <c r="BC10">
+        <v>15.5</v>
+      </c>
+      <c r="BD10">
         <v>6.2</v>
       </c>
-      <c r="I10">
-        <v>15.5</v>
-      </c>
-      <c r="J10">
-        <v>3.7</v>
-      </c>
-      <c r="K10">
-        <v>7</v>
-      </c>
-      <c r="L10">
-        <v>1.47</v>
-      </c>
-      <c r="M10">
-        <v>1.1</v>
-      </c>
-      <c r="N10">
-        <v>1.1</v>
-      </c>
-      <c r="O10">
-        <v>1.1</v>
-      </c>
-      <c r="P10">
-        <v>1.33</v>
-      </c>
-      <c r="Q10">
-        <v>1.9</v>
-      </c>
-      <c r="R10">
-        <v>1.18</v>
-      </c>
-      <c r="S10">
-        <v>1.9</v>
-      </c>
-      <c r="T10">
-        <v>1.75</v>
-      </c>
-      <c r="U10">
-        <v>1.35</v>
-      </c>
-      <c r="V10">
-        <v>1.07</v>
-      </c>
-      <c r="W10">
-        <v>2.52</v>
-      </c>
-      <c r="X10">
-        <v>1000</v>
-      </c>
-      <c r="Y10">
-        <v>1000</v>
-      </c>
-      <c r="Z10">
-        <v>1000</v>
-      </c>
-      <c r="AA10">
-        <v>1000</v>
-      </c>
-      <c r="AB10">
-        <v>1000</v>
-      </c>
-      <c r="AC10">
-        <v>1000</v>
-      </c>
-      <c r="AD10">
-        <v>1000</v>
-      </c>
-      <c r="AE10">
-        <v>1000</v>
-      </c>
-      <c r="AF10">
-        <v>1000</v>
-      </c>
-      <c r="AG10">
-        <v>1000</v>
-      </c>
-      <c r="AH10">
-        <v>1000</v>
-      </c>
-      <c r="AI10">
-        <v>1000</v>
-      </c>
-      <c r="AJ10">
-        <v>1000</v>
-      </c>
-      <c r="AK10">
-        <v>1000</v>
-      </c>
-      <c r="AL10">
-        <v>1000</v>
-      </c>
-      <c r="AM10">
-        <v>1000</v>
-      </c>
-      <c r="AN10">
-        <v>1000</v>
-      </c>
-      <c r="AO10">
-        <v>1000</v>
-      </c>
-      <c r="AP10">
-        <v>1.01</v>
-      </c>
-      <c r="AQ10">
-        <v>1.01</v>
-      </c>
-      <c r="AR10">
-        <v>1.01</v>
-      </c>
-      <c r="AS10">
-        <v>1.01</v>
-      </c>
-      <c r="AT10">
-        <v>1.01</v>
-      </c>
-      <c r="AU10">
-        <v>1.01</v>
-      </c>
-      <c r="AV10">
-        <v>1.01</v>
-      </c>
-      <c r="AW10">
-        <v>1.01</v>
-      </c>
-      <c r="AX10">
-        <v>1.01</v>
-      </c>
-      <c r="AY10">
-        <v>1.01</v>
-      </c>
-      <c r="AZ10">
-        <v>1.01</v>
-      </c>
-      <c r="BA10">
-        <v>1.01</v>
-      </c>
-      <c r="BB10">
-        <v>1.01</v>
-      </c>
-      <c r="BC10">
-        <v>1.01</v>
-      </c>
-      <c r="BD10">
-        <v>1.01</v>
-      </c>
       <c r="BE10">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BF10">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BG10">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BH10">
-        <v>1000</v>
+        <v>3.05</v>
       </c>
       <c r="BI10">
-        <v>1.04</v>
+        <v>2.38</v>
       </c>
       <c r="BJ10">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BK10">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="BL10">
         <v>1000</v>
       </c>
       <c r="BM10">
-        <v>1.04</v>
+        <v>10</v>
       </c>
       <c r="BN10">
-        <v>1000</v>
+        <v>3.9</v>
       </c>
       <c r="BO10">
-        <v>1.04</v>
+        <v>2.98</v>
       </c>
       <c r="BP10">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BQ10">
-        <v>1.04</v>
+        <v>5.6</v>
       </c>
       <c r="BR10">
         <v>1000</v>
       </c>
       <c r="BS10">
-        <v>1.04</v>
+        <v>8.4</v>
       </c>
       <c r="BT10">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BU10">
-        <v>1.04</v>
+        <v>5.6</v>
       </c>
       <c r="BV10">
         <v>1000</v>
       </c>
       <c r="BW10">
-        <v>1.04</v>
+        <v>9.6</v>
       </c>
       <c r="BX10">
         <v>1000</v>
       </c>
       <c r="BY10">
-        <v>1.04</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ10">
         <v>1000</v>
       </c>
       <c r="CA10">
-        <v>1.04</v>
+        <v>7.8</v>
       </c>
       <c r="CB10" t="s">
         <v>115</v>
@@ -3136,223 +3136,223 @@
         <v>4.3</v>
       </c>
       <c r="G11">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="H11">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="I11">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="J11">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="K11">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="L11">
+        <v>1.52</v>
+      </c>
+      <c r="M11">
+        <v>1.11</v>
+      </c>
+      <c r="N11">
+        <v>2.82</v>
+      </c>
+      <c r="O11">
         <v>1.47</v>
       </c>
-      <c r="M11">
-        <v>1.04</v>
-      </c>
-      <c r="N11">
+      <c r="P11">
+        <v>1.62</v>
+      </c>
+      <c r="Q11">
+        <v>2.4</v>
+      </c>
+      <c r="R11">
+        <v>1.22</v>
+      </c>
+      <c r="S11">
+        <v>4.8</v>
+      </c>
+      <c r="T11">
         <v>2.06</v>
       </c>
-      <c r="O11">
-        <v>1.24</v>
-      </c>
-      <c r="P11">
-        <v>1.25</v>
-      </c>
-      <c r="Q11">
-        <v>1.47</v>
-      </c>
-      <c r="R11">
-        <v>1.17</v>
-      </c>
-      <c r="S11">
-        <v>1.47</v>
-      </c>
-      <c r="T11">
-        <v>1.11</v>
-      </c>
       <c r="U11">
-        <v>1.11</v>
+        <v>1.8</v>
       </c>
       <c r="V11">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="W11">
         <v>1.26</v>
       </c>
       <c r="X11">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="Y11">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="Z11">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AA11">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AB11">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AC11">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AD11">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AE11">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AF11">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AG11">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AH11">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI11">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AJ11">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AK11">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AL11">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AM11">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AN11">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AO11">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AP11">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AQ11">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AR11">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AS11">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AT11">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AU11">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AV11">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW11">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AX11">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AY11">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="AZ11">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BA11">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BB11">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BC11">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BD11">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BE11">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BF11">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BG11">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="BH11">
-        <v>1000</v>
+        <v>2.86</v>
       </c>
       <c r="BI11">
-        <v>1.04</v>
+        <v>2.42</v>
       </c>
       <c r="BJ11">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK11">
-        <v>1.04</v>
+        <v>6.6</v>
       </c>
       <c r="BL11">
         <v>1000</v>
       </c>
       <c r="BM11">
-        <v>1.04</v>
+        <v>2.38</v>
       </c>
       <c r="BN11">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="BO11">
-        <v>1.04</v>
+        <v>5.7</v>
       </c>
       <c r="BP11">
         <v>1000</v>
       </c>
       <c r="BQ11">
-        <v>1.04</v>
+        <v>11.5</v>
       </c>
       <c r="BR11">
         <v>1000</v>
       </c>
       <c r="BS11">
-        <v>1.04</v>
+        <v>12.5</v>
       </c>
       <c r="BT11">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="BU11">
-        <v>1.04</v>
+        <v>3.55</v>
       </c>
       <c r="BV11">
         <v>1000</v>
       </c>
       <c r="BW11">
-        <v>1.04</v>
+        <v>8</v>
       </c>
       <c r="BX11">
         <v>1000</v>
       </c>
       <c r="BY11">
-        <v>1.04</v>
+        <v>11</v>
       </c>
       <c r="BZ11">
         <v>1000</v>
       </c>
       <c r="CA11">
-        <v>1.04</v>
+        <v>11</v>
       </c>
       <c r="CB11" t="s">
         <v>115</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-28.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-28.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="119">
   <si>
     <t>League</t>
   </si>
@@ -295,6 +295,9 @@
     <t>19:15:00</t>
   </si>
   <si>
+    <t>21:30:00</t>
+  </si>
+  <si>
     <t>22:00:00</t>
   </si>
   <si>
@@ -319,6 +322,9 @@
     <t>Aegir</t>
   </si>
   <si>
+    <t>2 Mayo de PJC</t>
+  </si>
+  <si>
     <t>San Lorenzo</t>
   </si>
   <si>
@@ -349,6 +355,9 @@
     <t>Njardvik</t>
   </si>
   <si>
+    <t>Cerro Porteno</t>
+  </si>
+  <si>
     <t>Gimnasia Mendoza</t>
   </si>
   <si>
@@ -361,7 +370,7 @@
     <t>Athletic Club</t>
   </si>
   <si>
-    <t>2026-07-27 11:06:49</t>
+    <t>2026-07-27 13:13:42</t>
   </si>
 </sst>
 </file>
@@ -693,7 +702,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB11"/>
+  <dimension ref="A1:CB12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -949,25 +958,25 @@
         <v>88</v>
       </c>
       <c r="D2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F2">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="G2">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="H2">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="I2">
         <v>3.7</v>
       </c>
       <c r="J2">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="K2">
         <v>3.25</v>
@@ -985,10 +994,10 @@
         <v>1.53</v>
       </c>
       <c r="P2">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="Q2">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="R2">
         <v>1.21</v>
@@ -997,31 +1006,31 @@
         <v>5.3</v>
       </c>
       <c r="T2">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="U2">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="V2">
         <v>1.37</v>
       </c>
       <c r="W2">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="X2">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="Y2">
         <v>10.5</v>
       </c>
       <c r="Z2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AA2">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AB2">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AC2">
         <v>7.2</v>
@@ -1030,25 +1039,25 @@
         <v>16</v>
       </c>
       <c r="AE2">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AF2">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AG2">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH2">
         <v>23</v>
       </c>
       <c r="AI2">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AJ2">
         <v>38</v>
       </c>
       <c r="AK2">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="AL2">
         <v>80</v>
@@ -1057,7 +1066,7 @@
         <v>220</v>
       </c>
       <c r="AN2">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="AO2">
         <v>95</v>
@@ -1084,7 +1093,7 @@
         <v>14</v>
       </c>
       <c r="AW2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AX2">
         <v>12.5</v>
@@ -1099,7 +1108,7 @@
         <v>50</v>
       </c>
       <c r="BB2">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BC2">
         <v>26</v>
@@ -1108,10 +1117,10 @@
         <v>44</v>
       </c>
       <c r="BE2">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="BF2">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="BG2">
         <v>50</v>
@@ -1120,64 +1129,64 @@
         <v>2.74</v>
       </c>
       <c r="BI2">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="BJ2">
         <v>11.5</v>
       </c>
       <c r="BK2">
-        <v>6.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>2.32</v>
+        <v>14</v>
       </c>
       <c r="BN2">
         <v>5.1</v>
       </c>
       <c r="BO2">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="BP2">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BQ2">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR2">
         <v>1000</v>
       </c>
       <c r="BS2">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BT2">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BU2">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BV2">
         <v>36</v>
       </c>
       <c r="BW2">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BX2">
         <v>60</v>
       </c>
       <c r="BY2">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BZ2">
         <v>1000</v>
       </c>
       <c r="CA2">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="CB2" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1191,10 +1200,10 @@
         <v>89</v>
       </c>
       <c r="D3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E3" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="F3">
         <v>4.8</v>
@@ -1221,7 +1230,7 @@
         <v>1.1</v>
       </c>
       <c r="N3">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="O3">
         <v>1.46</v>
@@ -1251,10 +1260,10 @@
         <v>1.23</v>
       </c>
       <c r="X3">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Y3">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="Z3">
         <v>11.5</v>
@@ -1266,7 +1275,7 @@
         <v>14.5</v>
       </c>
       <c r="AC3">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD3">
         <v>11.5</v>
@@ -1299,64 +1308,64 @@
         <v>210</v>
       </c>
       <c r="AN3">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AO3">
         <v>21</v>
       </c>
       <c r="AP3">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="AQ3">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="AR3">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS3">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="AT3">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AU3">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="AV3">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AW3">
         <v>21</v>
       </c>
       <c r="AX3">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AY3">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AZ3">
         <v>19.5</v>
       </c>
       <c r="BA3">
-        <v>7</v>
+        <v>42</v>
       </c>
       <c r="BB3">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="BC3">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BD3">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="BE3">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="BF3">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="BG3">
-        <v>16.5</v>
+        <v>6.2</v>
       </c>
       <c r="BH3">
         <v>3</v>
@@ -1419,7 +1428,7 @@
         <v>8.4</v>
       </c>
       <c r="CB3" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1433,25 +1442,25 @@
         <v>90</v>
       </c>
       <c r="D4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E4" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="F4">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="G4">
+        <v>3.6</v>
+      </c>
+      <c r="H4">
+        <v>2.16</v>
+      </c>
+      <c r="I4">
+        <v>2.3</v>
+      </c>
+      <c r="J4">
         <v>3.65</v>
-      </c>
-      <c r="H4">
-        <v>2.12</v>
-      </c>
-      <c r="I4">
-        <v>2.24</v>
-      </c>
-      <c r="J4">
-        <v>3.75</v>
       </c>
       <c r="K4">
         <v>3.95</v>
@@ -1466,175 +1475,175 @@
         <v>4.5</v>
       </c>
       <c r="O4">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P4">
         <v>2.2</v>
       </c>
       <c r="Q4">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="R4">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="S4">
-        <v>2.82</v>
+        <v>2.86</v>
       </c>
       <c r="T4">
         <v>1.64</v>
       </c>
       <c r="U4">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="V4">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="W4">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="X4">
         <v>23</v>
       </c>
       <c r="Y4">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="Z4">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="AA4">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="AB4">
-        <v>16.5</v>
+        <v>19.5</v>
       </c>
       <c r="AC4">
         <v>8.800000000000001</v>
       </c>
       <c r="AD4">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AE4">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AF4">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="AG4">
-        <v>15.5</v>
+        <v>18</v>
       </c>
       <c r="AH4">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AI4">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="AJ4">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="AK4">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AL4">
         <v>55</v>
       </c>
       <c r="AM4">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="AN4">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="AO4">
-        <v>13.5</v>
+        <v>17</v>
       </c>
       <c r="AP4">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AQ4">
         <v>10.5</v>
       </c>
       <c r="AR4">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="AS4">
-        <v>6.2</v>
+        <v>20</v>
       </c>
       <c r="AT4">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AU4">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AV4">
         <v>10</v>
       </c>
       <c r="AW4">
-        <v>18.5</v>
+        <v>16</v>
       </c>
       <c r="AX4">
-        <v>6.2</v>
+        <v>4</v>
       </c>
       <c r="AY4">
-        <v>13</v>
+        <v>10.5</v>
       </c>
       <c r="AZ4">
         <v>13.5</v>
       </c>
       <c r="BA4">
-        <v>6.4</v>
+        <v>4.1</v>
       </c>
       <c r="BB4">
-        <v>7</v>
+        <v>4.3</v>
       </c>
       <c r="BC4">
-        <v>6.8</v>
+        <v>4.1</v>
       </c>
       <c r="BD4">
-        <v>7</v>
+        <v>4.2</v>
       </c>
       <c r="BE4">
-        <v>7.2</v>
+        <v>4.3</v>
       </c>
       <c r="BF4">
         <v>21</v>
       </c>
       <c r="BG4">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BH4">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="BI4">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="BJ4">
         <v>9</v>
       </c>
       <c r="BK4">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BN4">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BO4">
         <v>6</v>
       </c>
       <c r="BP4">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BQ4">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BR4">
         <v>34</v>
       </c>
       <c r="BS4">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BT4">
         <v>5.3</v>
@@ -1643,16 +1652,16 @@
         <v>4.7</v>
       </c>
       <c r="BV4">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BW4">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BX4">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BY4">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BZ4">
         <v>0</v>
@@ -1661,7 +1670,7 @@
         <v>0</v>
       </c>
       <c r="CB4" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1675,13 +1684,13 @@
         <v>90</v>
       </c>
       <c r="D5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E5" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="F5">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="G5">
         <v>2.46</v>
@@ -1690,13 +1699,13 @@
         <v>2.98</v>
       </c>
       <c r="I5">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="J5">
         <v>3.8</v>
       </c>
       <c r="K5">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="L5">
         <v>1.35</v>
@@ -1708,13 +1717,13 @@
         <v>4.8</v>
       </c>
       <c r="O5">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="P5">
         <v>2.42</v>
       </c>
       <c r="Q5">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="R5">
         <v>1.52</v>
@@ -1726,10 +1735,10 @@
         <v>1.6</v>
       </c>
       <c r="U5">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="V5">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="W5">
         <v>1.68</v>
@@ -1738,43 +1747,43 @@
         <v>23</v>
       </c>
       <c r="Y5">
+        <v>18.5</v>
+      </c>
+      <c r="Z5">
+        <v>28</v>
+      </c>
+      <c r="AA5">
+        <v>60</v>
+      </c>
+      <c r="AB5">
+        <v>15.5</v>
+      </c>
+      <c r="AC5">
+        <v>10</v>
+      </c>
+      <c r="AD5">
         <v>16</v>
-      </c>
-      <c r="Z5">
-        <v>24</v>
-      </c>
-      <c r="AA5">
-        <v>48</v>
-      </c>
-      <c r="AB5">
-        <v>13.5</v>
-      </c>
-      <c r="AC5">
-        <v>9</v>
-      </c>
-      <c r="AD5">
-        <v>14</v>
       </c>
       <c r="AE5">
         <v>32</v>
       </c>
       <c r="AF5">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AG5">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AH5">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="AI5">
         <v>38</v>
       </c>
       <c r="AJ5">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="AK5">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AL5">
         <v>32</v>
@@ -1783,10 +1792,10 @@
         <v>65</v>
       </c>
       <c r="AN5">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="AO5">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AP5">
         <v>17.5</v>
@@ -1795,52 +1804,52 @@
         <v>14</v>
       </c>
       <c r="AR5">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AS5">
-        <v>9.800000000000001</v>
+        <v>5.5</v>
       </c>
       <c r="AT5">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="AU5">
         <v>8</v>
       </c>
       <c r="AV5">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AW5">
-        <v>8.800000000000001</v>
+        <v>5.1</v>
       </c>
       <c r="AX5">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AY5">
         <v>10</v>
       </c>
       <c r="AZ5">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="BA5">
-        <v>9.199999999999999</v>
+        <v>28</v>
       </c>
       <c r="BB5">
-        <v>8.800000000000001</v>
+        <v>24</v>
       </c>
       <c r="BC5">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="BD5">
-        <v>8.800000000000001</v>
+        <v>5.1</v>
       </c>
       <c r="BE5">
-        <v>10</v>
+        <v>5.6</v>
       </c>
       <c r="BF5">
         <v>13</v>
       </c>
       <c r="BG5">
-        <v>19.5</v>
+        <v>17</v>
       </c>
       <c r="BH5">
         <v>4</v>
@@ -1903,7 +1912,7 @@
         <v>8.6</v>
       </c>
       <c r="CB5" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -1917,10 +1926,10 @@
         <v>91</v>
       </c>
       <c r="D6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E6" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -2145,7 +2154,7 @@
         <v>0</v>
       </c>
       <c r="CB6" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2159,19 +2168,19 @@
         <v>92</v>
       </c>
       <c r="D7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E7" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="F7">
         <v>6.8</v>
       </c>
       <c r="G7">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="H7">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="I7">
         <v>1.47</v>
@@ -2192,13 +2201,13 @@
         <v>8.800000000000001</v>
       </c>
       <c r="O7">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="P7">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="Q7">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="R7">
         <v>2.2</v>
@@ -2207,7 +2216,7 @@
         <v>1.81</v>
       </c>
       <c r="T7">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="U7">
         <v>2.58</v>
@@ -2216,115 +2225,115 @@
         <v>3.1</v>
       </c>
       <c r="W7">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="X7">
         <v>950</v>
       </c>
       <c r="Y7">
-        <v>970</v>
+        <v>20</v>
       </c>
       <c r="Z7">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AA7">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="AB7">
         <v>55</v>
       </c>
       <c r="AC7">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="AD7">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AE7">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="AF7">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AG7">
         <v>950</v>
       </c>
       <c r="AH7">
-        <v>950</v>
+        <v>23</v>
       </c>
       <c r="AI7">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AJ7">
         <v>200</v>
       </c>
       <c r="AK7">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AL7">
         <v>70</v>
       </c>
       <c r="AM7">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AN7">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AO7">
-        <v>3.85</v>
+        <v>4.3</v>
       </c>
       <c r="AP7">
+        <v>5.2</v>
+      </c>
+      <c r="AQ7">
+        <v>15</v>
+      </c>
+      <c r="AR7">
+        <v>10.5</v>
+      </c>
+      <c r="AS7">
+        <v>13</v>
+      </c>
+      <c r="AT7">
+        <v>5.2</v>
+      </c>
+      <c r="AU7">
+        <v>12</v>
+      </c>
+      <c r="AV7">
         <v>10</v>
       </c>
-      <c r="AQ7">
-        <v>7.2</v>
-      </c>
-      <c r="AR7">
-        <v>6.4</v>
-      </c>
-      <c r="AS7">
-        <v>6.8</v>
-      </c>
-      <c r="AT7">
-        <v>10</v>
-      </c>
-      <c r="AU7">
-        <v>6.8</v>
-      </c>
-      <c r="AV7">
-        <v>5.9</v>
-      </c>
       <c r="AW7">
-        <v>6.4</v>
+        <v>11.5</v>
       </c>
       <c r="AX7">
-        <v>10.5</v>
+        <v>5.4</v>
       </c>
       <c r="AY7">
-        <v>8.800000000000001</v>
+        <v>4.9</v>
       </c>
       <c r="AZ7">
-        <v>7.4</v>
+        <v>14.5</v>
       </c>
       <c r="BA7">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="BB7">
-        <v>2.9</v>
+        <v>5.6</v>
       </c>
       <c r="BC7">
-        <v>10.5</v>
+        <v>5.4</v>
       </c>
       <c r="BD7">
-        <v>10.5</v>
+        <v>5.3</v>
       </c>
       <c r="BE7">
-        <v>10</v>
+        <v>5.3</v>
       </c>
       <c r="BF7">
-        <v>10</v>
+        <v>5.2</v>
       </c>
       <c r="BG7">
-        <v>2.92</v>
+        <v>3.45</v>
       </c>
       <c r="BH7">
         <v>5.9</v>
@@ -2387,12 +2396,12 @@
         <v>5.2</v>
       </c>
       <c r="CB7" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="8" spans="1:80">
       <c r="A8" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B8" t="s">
         <v>87</v>
@@ -2401,235 +2410,235 @@
         <v>93</v>
       </c>
       <c r="D8" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E8" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="F8">
-        <v>2.04</v>
+        <v>1.04</v>
       </c>
       <c r="G8">
-        <v>2.18</v>
+        <v>1000</v>
       </c>
       <c r="H8">
-        <v>4.7</v>
+        <v>1.04</v>
       </c>
       <c r="I8">
-        <v>5.3</v>
+        <v>1000</v>
       </c>
       <c r="J8">
-        <v>2.98</v>
+        <v>1.01</v>
       </c>
       <c r="K8">
-        <v>3.25</v>
+        <v>1000</v>
       </c>
       <c r="L8">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="M8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P8">
-        <v>1.45</v>
+        <v>1.24</v>
       </c>
       <c r="Q8">
-        <v>2.96</v>
+        <v>1.02</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP8">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AQ8">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AR8">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS8">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AT8">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AU8">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AV8">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW8">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AX8">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AY8">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AZ8">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="BA8">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BB8">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BC8">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BD8">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BE8">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BF8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB8" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="9" spans="1:80">
@@ -2640,243 +2649,243 @@
         <v>87</v>
       </c>
       <c r="C9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E9" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F9">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="G9">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="H9">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="I9">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="J9">
         <v>3.05</v>
       </c>
       <c r="K9">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="L9">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="M9">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="N9">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="O9">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="P9">
         <v>1.45</v>
       </c>
       <c r="Q9">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="R9">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="S9">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="T9">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="U9">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="V9">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W9">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="X9">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="Y9">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="Z9">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="AA9">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="AB9">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="AC9">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AD9">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="AE9">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="AF9">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AG9">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AH9">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AI9">
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="AJ9">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="AK9">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="AL9">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="AM9">
-        <v>320</v>
+        <v>0</v>
       </c>
       <c r="AN9">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="AO9">
-        <v>190</v>
+        <v>0</v>
       </c>
       <c r="AP9">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AQ9">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AR9">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="AS9">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AT9">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="AU9">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="AV9">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="AW9">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AX9">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AY9">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AZ9">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="BA9">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="BB9">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="BC9">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="BD9">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="BE9">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="BF9">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="BG9">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="BH9">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="BI9">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="BJ9">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="BK9">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="BL9">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM9">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="BN9">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="BO9">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="BP9">
-        <v>19.5</v>
+        <v>0</v>
       </c>
       <c r="BQ9">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="BR9">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="BS9">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="BT9">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="BU9">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="BV9">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BW9">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="BX9">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY9">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="BZ9">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA9">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="CB9" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="10" spans="1:80">
       <c r="A10" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B10" t="s">
         <v>87</v>
@@ -2885,235 +2894,235 @@
         <v>94</v>
       </c>
       <c r="D10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E10" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="F10">
-        <v>1.58</v>
+        <v>2.08</v>
       </c>
       <c r="G10">
-        <v>1.64</v>
+        <v>2.2</v>
       </c>
       <c r="H10">
-        <v>7.6</v>
+        <v>4.4</v>
       </c>
       <c r="I10">
-        <v>8.6</v>
+        <v>4.9</v>
       </c>
       <c r="J10">
-        <v>3.85</v>
+        <v>3.05</v>
       </c>
       <c r="K10">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="L10">
-        <v>1.51</v>
+        <v>1.63</v>
       </c>
       <c r="M10">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="N10">
-        <v>2.88</v>
+        <v>2.38</v>
       </c>
       <c r="O10">
-        <v>1.47</v>
+        <v>1.63</v>
       </c>
       <c r="P10">
-        <v>1.59</v>
+        <v>1.43</v>
       </c>
       <c r="Q10">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
       <c r="R10">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="S10">
-        <v>4.8</v>
+        <v>6.2</v>
       </c>
       <c r="T10">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="U10">
         <v>1.63</v>
       </c>
       <c r="V10">
-        <v>1.13</v>
+        <v>1.26</v>
       </c>
       <c r="W10">
-        <v>2.56</v>
+        <v>1.84</v>
       </c>
       <c r="X10">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="Y10">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="Z10">
-        <v>85</v>
+        <v>34</v>
       </c>
       <c r="AA10">
-        <v>420</v>
+        <v>160</v>
       </c>
       <c r="AB10">
         <v>6.4</v>
       </c>
       <c r="AC10">
-        <v>9.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD10">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="AE10">
-        <v>220</v>
+        <v>110</v>
       </c>
       <c r="AF10">
+        <v>12</v>
+      </c>
+      <c r="AG10">
+        <v>13.5</v>
+      </c>
+      <c r="AH10">
+        <v>32</v>
+      </c>
+      <c r="AI10">
+        <v>140</v>
+      </c>
+      <c r="AJ10">
+        <v>30</v>
+      </c>
+      <c r="AK10">
+        <v>34</v>
+      </c>
+      <c r="AL10">
+        <v>75</v>
+      </c>
+      <c r="AM10">
+        <v>320</v>
+      </c>
+      <c r="AN10">
+        <v>34</v>
+      </c>
+      <c r="AO10">
+        <v>200</v>
+      </c>
+      <c r="AP10">
+        <v>6.8</v>
+      </c>
+      <c r="AQ10">
+        <v>9</v>
+      </c>
+      <c r="AR10">
+        <v>6.8</v>
+      </c>
+      <c r="AS10">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AT10">
+        <v>5.5</v>
+      </c>
+      <c r="AU10">
+        <v>6.6</v>
+      </c>
+      <c r="AV10">
+        <v>17</v>
+      </c>
+      <c r="AW10">
+        <v>8</v>
+      </c>
+      <c r="AX10">
+        <v>9.4</v>
+      </c>
+      <c r="AY10">
+        <v>10.5</v>
+      </c>
+      <c r="AZ10">
+        <v>6.8</v>
+      </c>
+      <c r="BA10">
+        <v>8</v>
+      </c>
+      <c r="BB10">
+        <v>6.6</v>
+      </c>
+      <c r="BC10">
+        <v>6.8</v>
+      </c>
+      <c r="BD10">
+        <v>7.6</v>
+      </c>
+      <c r="BE10">
         <v>8.4</v>
       </c>
-      <c r="AG10">
+      <c r="BF10">
+        <v>6.8</v>
+      </c>
+      <c r="BG10">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BH10">
+        <v>2.62</v>
+      </c>
+      <c r="BI10">
+        <v>2.3</v>
+      </c>
+      <c r="BJ10">
         <v>13</v>
       </c>
-      <c r="AH10">
-        <v>38</v>
-      </c>
-      <c r="AI10">
-        <v>210</v>
-      </c>
-      <c r="AJ10">
-        <v>16</v>
-      </c>
-      <c r="AK10">
-        <v>23</v>
-      </c>
-      <c r="AL10">
-        <v>70</v>
-      </c>
-      <c r="AM10">
-        <v>310</v>
-      </c>
-      <c r="AN10">
+      <c r="BK10">
+        <v>6.2</v>
+      </c>
+      <c r="BL10">
+        <v>1000</v>
+      </c>
+      <c r="BM10">
+        <v>11</v>
+      </c>
+      <c r="BN10">
+        <v>4.7</v>
+      </c>
+      <c r="BO10">
+        <v>3.95</v>
+      </c>
+      <c r="BP10">
+        <v>19.5</v>
+      </c>
+      <c r="BQ10">
         <v>14.5</v>
       </c>
-      <c r="AO10">
-        <v>420</v>
-      </c>
-      <c r="AP10">
-        <v>7.6</v>
-      </c>
-      <c r="AQ10">
-        <v>14</v>
-      </c>
-      <c r="AR10">
-        <v>6.4</v>
-      </c>
-      <c r="AS10">
-        <v>6.8</v>
-      </c>
-      <c r="AT10">
-        <v>4.7</v>
-      </c>
-      <c r="AU10">
-        <v>7.8</v>
-      </c>
-      <c r="AV10">
-        <v>5.9</v>
-      </c>
-      <c r="AW10">
-        <v>6.6</v>
-      </c>
-      <c r="AX10">
-        <v>7</v>
-      </c>
-      <c r="AY10">
-        <v>8</v>
-      </c>
-      <c r="AZ10">
-        <v>5.9</v>
-      </c>
-      <c r="BA10">
-        <v>6.6</v>
-      </c>
-      <c r="BB10">
-        <v>11</v>
-      </c>
-      <c r="BC10">
-        <v>15.5</v>
-      </c>
-      <c r="BD10">
-        <v>6.2</v>
-      </c>
-      <c r="BE10">
-        <v>6.8</v>
-      </c>
-      <c r="BF10">
-        <v>10.5</v>
-      </c>
-      <c r="BG10">
-        <v>6.8</v>
-      </c>
-      <c r="BH10">
-        <v>3.05</v>
-      </c>
-      <c r="BI10">
-        <v>2.38</v>
-      </c>
-      <c r="BJ10">
-        <v>13.5</v>
-      </c>
-      <c r="BK10">
-        <v>6</v>
-      </c>
-      <c r="BL10">
-        <v>1000</v>
-      </c>
-      <c r="BM10">
+      <c r="BR10">
+        <v>50</v>
+      </c>
+      <c r="BS10">
+        <v>9.6</v>
+      </c>
+      <c r="BT10">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BU10">
+        <v>5.5</v>
+      </c>
+      <c r="BV10">
+        <v>1000</v>
+      </c>
+      <c r="BW10">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BX10">
+        <v>1000</v>
+      </c>
+      <c r="BY10">
         <v>10</v>
       </c>
-      <c r="BN10">
-        <v>3.9</v>
-      </c>
-      <c r="BO10">
-        <v>2.98</v>
-      </c>
-      <c r="BP10">
-        <v>12</v>
-      </c>
-      <c r="BQ10">
-        <v>5.6</v>
-      </c>
-      <c r="BR10">
-        <v>1000</v>
-      </c>
-      <c r="BS10">
-        <v>8.4</v>
-      </c>
-      <c r="BT10">
-        <v>12</v>
-      </c>
-      <c r="BU10">
-        <v>5.6</v>
-      </c>
-      <c r="BV10">
-        <v>1000</v>
-      </c>
-      <c r="BW10">
-        <v>9.6</v>
-      </c>
-      <c r="BX10">
-        <v>1000</v>
-      </c>
-      <c r="BY10">
+      <c r="BZ10">
+        <v>1000</v>
+      </c>
+      <c r="CA10">
         <v>9.800000000000001</v>
       </c>
-      <c r="BZ10">
-        <v>1000</v>
-      </c>
-      <c r="CA10">
-        <v>7.8</v>
-      </c>
       <c r="CB10" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="11" spans="1:80">
@@ -3124,238 +3133,480 @@
         <v>87</v>
       </c>
       <c r="C11" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D11" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E11" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F11">
-        <v>4.3</v>
+        <v>1.58</v>
       </c>
       <c r="G11">
-        <v>4.8</v>
+        <v>1.61</v>
       </c>
       <c r="H11">
-        <v>2</v>
+        <v>7.6</v>
       </c>
       <c r="I11">
-        <v>2.14</v>
+        <v>8.6</v>
       </c>
       <c r="J11">
-        <v>3.2</v>
+        <v>3.85</v>
       </c>
       <c r="K11">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="L11">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="M11">
         <v>1.11</v>
       </c>
       <c r="N11">
-        <v>2.82</v>
+        <v>2.88</v>
       </c>
       <c r="O11">
         <v>1.47</v>
       </c>
       <c r="P11">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="Q11">
         <v>2.4</v>
       </c>
       <c r="R11">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="S11">
         <v>4.8</v>
       </c>
       <c r="T11">
-        <v>2.06</v>
+        <v>2.3</v>
       </c>
       <c r="U11">
+        <v>1.63</v>
+      </c>
+      <c r="V11">
+        <v>1.13</v>
+      </c>
+      <c r="W11">
+        <v>2.62</v>
+      </c>
+      <c r="X11">
+        <v>12.5</v>
+      </c>
+      <c r="Y11">
+        <v>23</v>
+      </c>
+      <c r="Z11">
+        <v>85</v>
+      </c>
+      <c r="AA11">
+        <v>430</v>
+      </c>
+      <c r="AB11">
+        <v>7.2</v>
+      </c>
+      <c r="AC11">
+        <v>11</v>
+      </c>
+      <c r="AD11">
+        <v>40</v>
+      </c>
+      <c r="AE11">
+        <v>220</v>
+      </c>
+      <c r="AF11">
+        <v>8.6</v>
+      </c>
+      <c r="AG11">
+        <v>13</v>
+      </c>
+      <c r="AH11">
+        <v>38</v>
+      </c>
+      <c r="AI11">
+        <v>220</v>
+      </c>
+      <c r="AJ11">
+        <v>19</v>
+      </c>
+      <c r="AK11">
+        <v>27</v>
+      </c>
+      <c r="AL11">
+        <v>75</v>
+      </c>
+      <c r="AM11">
+        <v>320</v>
+      </c>
+      <c r="AN11">
+        <v>17</v>
+      </c>
+      <c r="AO11">
+        <v>440</v>
+      </c>
+      <c r="AP11">
+        <v>7.4</v>
+      </c>
+      <c r="AQ11">
+        <v>16</v>
+      </c>
+      <c r="AR11">
+        <v>4.4</v>
+      </c>
+      <c r="AS11">
+        <v>4.6</v>
+      </c>
+      <c r="AT11">
+        <v>4.6</v>
+      </c>
+      <c r="AU11">
+        <v>7.8</v>
+      </c>
+      <c r="AV11">
+        <v>4.2</v>
+      </c>
+      <c r="AW11">
+        <v>4.6</v>
+      </c>
+      <c r="AX11">
+        <v>6</v>
+      </c>
+      <c r="AY11">
+        <v>8</v>
+      </c>
+      <c r="AZ11">
+        <v>4.1</v>
+      </c>
+      <c r="BA11">
+        <v>4.6</v>
+      </c>
+      <c r="BB11">
+        <v>11</v>
+      </c>
+      <c r="BC11">
+        <v>15.5</v>
+      </c>
+      <c r="BD11">
+        <v>4.4</v>
+      </c>
+      <c r="BE11">
+        <v>4.6</v>
+      </c>
+      <c r="BF11">
+        <v>10</v>
+      </c>
+      <c r="BG11">
+        <v>4.6</v>
+      </c>
+      <c r="BH11">
+        <v>3.05</v>
+      </c>
+      <c r="BI11">
+        <v>2.38</v>
+      </c>
+      <c r="BJ11">
+        <v>13.5</v>
+      </c>
+      <c r="BK11">
+        <v>6</v>
+      </c>
+      <c r="BL11">
+        <v>1000</v>
+      </c>
+      <c r="BM11">
+        <v>10</v>
+      </c>
+      <c r="BN11">
+        <v>3.9</v>
+      </c>
+      <c r="BO11">
+        <v>2.98</v>
+      </c>
+      <c r="BP11">
+        <v>12</v>
+      </c>
+      <c r="BQ11">
+        <v>5.6</v>
+      </c>
+      <c r="BR11">
+        <v>1000</v>
+      </c>
+      <c r="BS11">
+        <v>8.4</v>
+      </c>
+      <c r="BT11">
+        <v>12</v>
+      </c>
+      <c r="BU11">
+        <v>5.6</v>
+      </c>
+      <c r="BV11">
+        <v>1000</v>
+      </c>
+      <c r="BW11">
+        <v>9.6</v>
+      </c>
+      <c r="BX11">
+        <v>1000</v>
+      </c>
+      <c r="BY11">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BZ11">
+        <v>1000</v>
+      </c>
+      <c r="CA11">
+        <v>7.8</v>
+      </c>
+      <c r="CB11" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="12" spans="1:80">
+      <c r="A12" t="s">
+        <v>86</v>
+      </c>
+      <c r="B12" t="s">
+        <v>87</v>
+      </c>
+      <c r="C12" t="s">
+        <v>95</v>
+      </c>
+      <c r="D12" t="s">
+        <v>106</v>
+      </c>
+      <c r="E12" t="s">
+        <v>117</v>
+      </c>
+      <c r="F12">
+        <v>4.4</v>
+      </c>
+      <c r="G12">
+        <v>5</v>
+      </c>
+      <c r="H12">
+        <v>2.02</v>
+      </c>
+      <c r="I12">
+        <v>2.1</v>
+      </c>
+      <c r="J12">
+        <v>3.2</v>
+      </c>
+      <c r="K12">
+        <v>3.45</v>
+      </c>
+      <c r="L12">
+        <v>1.52</v>
+      </c>
+      <c r="M12">
+        <v>1.11</v>
+      </c>
+      <c r="N12">
+        <v>2.82</v>
+      </c>
+      <c r="O12">
+        <v>1.47</v>
+      </c>
+      <c r="P12">
+        <v>1.6</v>
+      </c>
+      <c r="Q12">
+        <v>2.4</v>
+      </c>
+      <c r="R12">
+        <v>1.22</v>
+      </c>
+      <c r="S12">
+        <v>4.8</v>
+      </c>
+      <c r="T12">
+        <v>2.08</v>
+      </c>
+      <c r="U12">
         <v>1.8</v>
       </c>
-      <c r="V11">
-        <v>1.87</v>
-      </c>
-      <c r="W11">
-        <v>1.26</v>
-      </c>
-      <c r="X11">
+      <c r="V12">
+        <v>1.9</v>
+      </c>
+      <c r="W12">
+        <v>1.25</v>
+      </c>
+      <c r="X12">
         <v>12</v>
       </c>
-      <c r="Y11">
+      <c r="Y12">
+        <v>8.4</v>
+      </c>
+      <c r="Z12">
+        <v>14</v>
+      </c>
+      <c r="AA12">
+        <v>32</v>
+      </c>
+      <c r="AB12">
+        <v>15.5</v>
+      </c>
+      <c r="AC12">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD12">
+        <v>13.5</v>
+      </c>
+      <c r="AE12">
+        <v>34</v>
+      </c>
+      <c r="AF12">
+        <v>42</v>
+      </c>
+      <c r="AG12">
+        <v>24</v>
+      </c>
+      <c r="AH12">
+        <v>28</v>
+      </c>
+      <c r="AI12">
+        <v>65</v>
+      </c>
+      <c r="AJ12">
+        <v>150</v>
+      </c>
+      <c r="AK12">
+        <v>95</v>
+      </c>
+      <c r="AL12">
+        <v>120</v>
+      </c>
+      <c r="AM12">
+        <v>210</v>
+      </c>
+      <c r="AN12">
+        <v>150</v>
+      </c>
+      <c r="AO12">
+        <v>28</v>
+      </c>
+      <c r="AP12">
         <v>8.6</v>
       </c>
-      <c r="Z11">
+      <c r="AQ12">
+        <v>6.2</v>
+      </c>
+      <c r="AR12">
+        <v>10</v>
+      </c>
+      <c r="AS12">
+        <v>3.8</v>
+      </c>
+      <c r="AT12">
+        <v>9.4</v>
+      </c>
+      <c r="AU12">
+        <v>6.8</v>
+      </c>
+      <c r="AV12">
+        <v>9.6</v>
+      </c>
+      <c r="AW12">
+        <v>3.85</v>
+      </c>
+      <c r="AX12">
+        <v>3.95</v>
+      </c>
+      <c r="AY12">
+        <v>14</v>
+      </c>
+      <c r="AZ12">
+        <v>3.75</v>
+      </c>
+      <c r="BA12">
+        <v>4</v>
+      </c>
+      <c r="BB12">
+        <v>4.2</v>
+      </c>
+      <c r="BC12">
+        <v>4.1</v>
+      </c>
+      <c r="BD12">
+        <v>4.2</v>
+      </c>
+      <c r="BE12">
+        <v>4.2</v>
+      </c>
+      <c r="BF12">
+        <v>4.2</v>
+      </c>
+      <c r="BG12">
+        <v>16.5</v>
+      </c>
+      <c r="BH12">
+        <v>2.86</v>
+      </c>
+      <c r="BI12">
+        <v>2.44</v>
+      </c>
+      <c r="BJ12">
+        <v>11.5</v>
+      </c>
+      <c r="BK12">
+        <v>6.8</v>
+      </c>
+      <c r="BL12">
+        <v>1000</v>
+      </c>
+      <c r="BM12">
+        <v>16</v>
+      </c>
+      <c r="BN12">
+        <v>7.8</v>
+      </c>
+      <c r="BO12">
+        <v>5.3</v>
+      </c>
+      <c r="BP12">
+        <v>1000</v>
+      </c>
+      <c r="BQ12">
+        <v>12.5</v>
+      </c>
+      <c r="BR12">
+        <v>1000</v>
+      </c>
+      <c r="BS12">
+        <v>13.5</v>
+      </c>
+      <c r="BT12">
+        <v>4.5</v>
+      </c>
+      <c r="BU12">
+        <v>4</v>
+      </c>
+      <c r="BV12">
+        <v>1000</v>
+      </c>
+      <c r="BW12">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BX12">
+        <v>1000</v>
+      </c>
+      <c r="BY12">
+        <v>11.5</v>
+      </c>
+      <c r="BZ12">
+        <v>1000</v>
+      </c>
+      <c r="CA12">
         <v>12</v>
       </c>
-      <c r="AA11">
-        <v>32</v>
-      </c>
-      <c r="AB11">
-        <v>15.5</v>
-      </c>
-      <c r="AC11">
-        <v>9</v>
-      </c>
-      <c r="AD11">
-        <v>11.5</v>
-      </c>
-      <c r="AE11">
-        <v>32</v>
-      </c>
-      <c r="AF11">
-        <v>40</v>
-      </c>
-      <c r="AG11">
-        <v>24</v>
-      </c>
-      <c r="AH11">
-        <v>950</v>
-      </c>
-      <c r="AI11">
-        <v>55</v>
-      </c>
-      <c r="AJ11">
-        <v>150</v>
-      </c>
-      <c r="AK11">
-        <v>95</v>
-      </c>
-      <c r="AL11">
-        <v>110</v>
-      </c>
-      <c r="AM11">
-        <v>200</v>
-      </c>
-      <c r="AN11">
-        <v>140</v>
-      </c>
-      <c r="AO11">
-        <v>28</v>
-      </c>
-      <c r="AP11">
-        <v>8.6</v>
-      </c>
-      <c r="AQ11">
-        <v>6.2</v>
-      </c>
-      <c r="AR11">
-        <v>10</v>
-      </c>
-      <c r="AS11">
-        <v>4.5</v>
-      </c>
-      <c r="AT11">
-        <v>11</v>
-      </c>
-      <c r="AU11">
-        <v>6.6</v>
-      </c>
-      <c r="AV11">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AW11">
-        <v>4.5</v>
-      </c>
-      <c r="AX11">
-        <v>4.6</v>
-      </c>
-      <c r="AY11">
-        <v>16.5</v>
-      </c>
-      <c r="AZ11">
-        <v>4.2</v>
-      </c>
-      <c r="BA11">
-        <v>4.8</v>
-      </c>
-      <c r="BB11">
-        <v>5</v>
-      </c>
-      <c r="BC11">
-        <v>4.9</v>
-      </c>
-      <c r="BD11">
-        <v>5</v>
-      </c>
-      <c r="BE11">
-        <v>5.1</v>
-      </c>
-      <c r="BF11">
-        <v>5</v>
-      </c>
-      <c r="BG11">
-        <v>17</v>
-      </c>
-      <c r="BH11">
-        <v>2.86</v>
-      </c>
-      <c r="BI11">
-        <v>2.42</v>
-      </c>
-      <c r="BJ11">
-        <v>11.5</v>
-      </c>
-      <c r="BK11">
-        <v>6.6</v>
-      </c>
-      <c r="BL11">
-        <v>1000</v>
-      </c>
-      <c r="BM11">
-        <v>2.38</v>
-      </c>
-      <c r="BN11">
-        <v>7.8</v>
-      </c>
-      <c r="BO11">
-        <v>5.7</v>
-      </c>
-      <c r="BP11">
-        <v>1000</v>
-      </c>
-      <c r="BQ11">
-        <v>11.5</v>
-      </c>
-      <c r="BR11">
-        <v>1000</v>
-      </c>
-      <c r="BS11">
-        <v>12.5</v>
-      </c>
-      <c r="BT11">
-        <v>4.6</v>
-      </c>
-      <c r="BU11">
-        <v>3.55</v>
-      </c>
-      <c r="BV11">
-        <v>1000</v>
-      </c>
-      <c r="BW11">
-        <v>8</v>
-      </c>
-      <c r="BX11">
-        <v>1000</v>
-      </c>
-      <c r="BY11">
-        <v>11</v>
-      </c>
-      <c r="BZ11">
-        <v>1000</v>
-      </c>
-      <c r="CA11">
-        <v>11</v>
-      </c>
-      <c r="CB11" t="s">
-        <v>115</v>
+      <c r="CB12" t="s">
+        <v>118</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-28.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-28.xlsx
@@ -370,7 +370,7 @@
     <t>Athletic Club</t>
   </si>
   <si>
-    <t>2026-07-27 13:13:42</t>
+    <t>2026-07-27 15:21:31</t>
   </si>
 </sst>
 </file>
@@ -964,25 +964,25 @@
         <v>107</v>
       </c>
       <c r="F2">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="G2">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="H2">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="I2">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="J2">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="K2">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="L2">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="M2">
         <v>1.12</v>
@@ -997,28 +997,28 @@
         <v>1.58</v>
       </c>
       <c r="Q2">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="R2">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="S2">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="T2">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="U2">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
       <c r="V2">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="W2">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="X2">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y2">
         <v>10.5</v>
@@ -1027,19 +1027,19 @@
         <v>25</v>
       </c>
       <c r="AA2">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="AB2">
+        <v>7.4</v>
+      </c>
+      <c r="AC2">
         <v>7.6</v>
       </c>
-      <c r="AC2">
-        <v>7.2</v>
-      </c>
       <c r="AD2">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AE2">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="AF2">
         <v>14</v>
@@ -1048,22 +1048,22 @@
         <v>12</v>
       </c>
       <c r="AH2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AI2">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="AJ2">
         <v>38</v>
       </c>
       <c r="AK2">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AL2">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="AM2">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="AN2">
         <v>46</v>
@@ -1072,7 +1072,7 @@
         <v>95</v>
       </c>
       <c r="AP2">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AQ2">
         <v>9</v>
@@ -1084,10 +1084,10 @@
         <v>55</v>
       </c>
       <c r="AT2">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AU2">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV2">
         <v>14</v>
@@ -1096,7 +1096,7 @@
         <v>36</v>
       </c>
       <c r="AX2">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AY2">
         <v>10.5</v>
@@ -1117,7 +1117,7 @@
         <v>44</v>
       </c>
       <c r="BE2">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BF2">
         <v>30</v>
@@ -1156,7 +1156,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BR2">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BS2">
         <v>11</v>
@@ -1165,7 +1165,7 @@
         <v>6.8</v>
       </c>
       <c r="BU2">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="BV2">
         <v>36</v>
@@ -1180,7 +1180,7 @@
         <v>12</v>
       </c>
       <c r="BZ2">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="CA2">
         <v>11.5</v>
@@ -1206,22 +1206,22 @@
         <v>108</v>
       </c>
       <c r="F3">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="G3">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="H3">
         <v>1.93</v>
       </c>
       <c r="I3">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="J3">
         <v>3.3</v>
       </c>
       <c r="K3">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="L3">
         <v>1.52</v>
@@ -1230,7 +1230,7 @@
         <v>1.1</v>
       </c>
       <c r="N3">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="O3">
         <v>1.46</v>
@@ -1239,13 +1239,13 @@
         <v>1.64</v>
       </c>
       <c r="Q3">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="R3">
         <v>1.23</v>
       </c>
       <c r="S3">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="T3">
         <v>2.08</v>
@@ -1254,13 +1254,13 @@
         <v>1.79</v>
       </c>
       <c r="V3">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="W3">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="X3">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Y3">
         <v>7.2</v>
@@ -1272,7 +1272,7 @@
         <v>24</v>
       </c>
       <c r="AB3">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AC3">
         <v>8</v>
@@ -1281,13 +1281,13 @@
         <v>11.5</v>
       </c>
       <c r="AE3">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="AF3">
         <v>40</v>
       </c>
       <c r="AG3">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AH3">
         <v>25</v>
@@ -1296,19 +1296,19 @@
         <v>55</v>
       </c>
       <c r="AJ3">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AK3">
-        <v>90</v>
+        <v>140</v>
       </c>
       <c r="AL3">
-        <v>120</v>
+        <v>160</v>
       </c>
       <c r="AM3">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="AN3">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AO3">
         <v>21</v>
@@ -1326,7 +1326,7 @@
         <v>19</v>
       </c>
       <c r="AT3">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AU3">
         <v>6.8</v>
@@ -1350,82 +1350,82 @@
         <v>42</v>
       </c>
       <c r="BB3">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC3">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BD3">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="BE3">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="BF3">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG3">
-        <v>6.2</v>
+        <v>17.5</v>
       </c>
       <c r="BH3">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="BI3">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="BJ3">
         <v>12</v>
       </c>
       <c r="BK3">
-        <v>5.7</v>
+        <v>5.4</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="BN3">
         <v>8.6</v>
       </c>
       <c r="BO3">
-        <v>4.8</v>
+        <v>6.6</v>
       </c>
       <c r="BP3">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BQ3">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BR3">
         <v>1000</v>
       </c>
       <c r="BS3">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT3">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BU3">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="BV3">
         <v>15.5</v>
       </c>
       <c r="BW3">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="BX3">
         <v>1000</v>
       </c>
       <c r="BY3">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="BZ3">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="CA3">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="CB3" t="s">
         <v>118</v>
@@ -1451,16 +1451,16 @@
         <v>3.3</v>
       </c>
       <c r="G4">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="H4">
         <v>2.16</v>
       </c>
       <c r="I4">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="J4">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="K4">
         <v>3.95</v>
@@ -1484,7 +1484,7 @@
         <v>1.74</v>
       </c>
       <c r="R4">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="S4">
         <v>2.86</v>
@@ -1493,10 +1493,10 @@
         <v>1.64</v>
       </c>
       <c r="U4">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="V4">
-        <v>1.76</v>
+        <v>1.81</v>
       </c>
       <c r="W4">
         <v>1.39</v>
@@ -1553,7 +1553,7 @@
         <v>36</v>
       </c>
       <c r="AO4">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AP4">
         <v>16</v>
@@ -1610,7 +1610,7 @@
         <v>10</v>
       </c>
       <c r="BH4">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="BI4">
         <v>3.5</v>
@@ -1619,13 +1619,13 @@
         <v>9</v>
       </c>
       <c r="BK4">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BN4">
         <v>6.8</v>
@@ -1637,13 +1637,13 @@
         <v>25</v>
       </c>
       <c r="BQ4">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BR4">
         <v>34</v>
       </c>
       <c r="BS4">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BT4">
         <v>5.3</v>
@@ -1655,13 +1655,13 @@
         <v>15.5</v>
       </c>
       <c r="BW4">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BX4">
         <v>26</v>
       </c>
       <c r="BY4">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ4">
         <v>0</v>
@@ -1702,7 +1702,7 @@
         <v>3.2</v>
       </c>
       <c r="J5">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="K5">
         <v>3.95</v>
@@ -1723,22 +1723,22 @@
         <v>2.42</v>
       </c>
       <c r="Q5">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="R5">
         <v>1.52</v>
       </c>
       <c r="S5">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="T5">
         <v>1.6</v>
       </c>
       <c r="U5">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="V5">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="W5">
         <v>1.68</v>
@@ -1780,7 +1780,7 @@
         <v>38</v>
       </c>
       <c r="AJ5">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AK5">
         <v>26</v>
@@ -1861,13 +1861,13 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BK5">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BN5">
         <v>5.7</v>
@@ -1885,7 +1885,7 @@
         <v>26</v>
       </c>
       <c r="BS5">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BT5">
         <v>6.4</v>
@@ -1894,7 +1894,7 @@
         <v>5.7</v>
       </c>
       <c r="BV5">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BW5">
         <v>9.199999999999999</v>
@@ -1909,7 +1909,7 @@
         <v>19</v>
       </c>
       <c r="CA5">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB5" t="s">
         <v>118</v>
@@ -2252,7 +2252,7 @@
         <v>15.5</v>
       </c>
       <c r="AF7">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AG7">
         <v>950</v>
@@ -2267,7 +2267,7 @@
         <v>200</v>
       </c>
       <c r="AK7">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AL7">
         <v>70</v>
@@ -2276,25 +2276,25 @@
         <v>70</v>
       </c>
       <c r="AN7">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AO7">
-        <v>4.3</v>
+        <v>3.85</v>
       </c>
       <c r="AP7">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="AQ7">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AR7">
         <v>10.5</v>
       </c>
       <c r="AS7">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AT7">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="AU7">
         <v>12</v>
@@ -2303,13 +2303,13 @@
         <v>10</v>
       </c>
       <c r="AW7">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="AX7">
-        <v>5.4</v>
+        <v>6.4</v>
       </c>
       <c r="AY7">
-        <v>4.9</v>
+        <v>5.7</v>
       </c>
       <c r="AZ7">
         <v>14.5</v>
@@ -2318,19 +2318,19 @@
         <v>17</v>
       </c>
       <c r="BB7">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="BC7">
-        <v>5.4</v>
+        <v>6.4</v>
       </c>
       <c r="BD7">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="BE7">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="BF7">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="BG7">
         <v>3.45</v>
@@ -2339,7 +2339,7 @@
         <v>5.9</v>
       </c>
       <c r="BI7">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="BJ7">
         <v>9.4</v>
@@ -2360,7 +2360,7 @@
         <v>6.2</v>
       </c>
       <c r="BP7">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BQ7">
         <v>10</v>
@@ -2416,52 +2416,52 @@
         <v>113</v>
       </c>
       <c r="F8">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="G8">
         <v>1000</v>
       </c>
       <c r="H8">
-        <v>1.04</v>
+        <v>1.72</v>
       </c>
       <c r="I8">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="J8">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="K8">
         <v>1000</v>
       </c>
       <c r="L8">
-        <v>1.54</v>
+        <v>1.01</v>
       </c>
       <c r="M8">
         <v>1.01</v>
       </c>
       <c r="N8">
-        <v>1.24</v>
+        <v>1.97</v>
       </c>
       <c r="O8">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P8">
-        <v>1.24</v>
+        <v>1.48</v>
       </c>
       <c r="Q8">
-        <v>1.02</v>
+        <v>1.82</v>
       </c>
       <c r="R8">
         <v>1.18</v>
       </c>
       <c r="S8">
-        <v>1.02</v>
+        <v>1.82</v>
       </c>
       <c r="T8">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U8">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V8">
         <v>1.01</v>
@@ -2524,52 +2524,52 @@
         <v>1000</v>
       </c>
       <c r="AP8">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="AQ8">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="AR8">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AS8">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="AT8">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AU8">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="AV8">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AW8">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="AX8">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="AY8">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="AZ8">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="BA8">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BB8">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BC8">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BD8">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BE8">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BF8">
         <v>1.01</v>
@@ -2658,22 +2658,22 @@
         <v>114</v>
       </c>
       <c r="F9">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="G9">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="H9">
         <v>4.7</v>
       </c>
       <c r="I9">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="J9">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="K9">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="L9">
         <v>0</v>
@@ -2688,10 +2688,10 @@
         <v>0</v>
       </c>
       <c r="P9">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="Q9">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="R9">
         <v>0</v>
@@ -2900,7 +2900,7 @@
         <v>115</v>
       </c>
       <c r="F10">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="G10">
         <v>2.2</v>
@@ -2915,13 +2915,13 @@
         <v>3.05</v>
       </c>
       <c r="K10">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="L10">
         <v>1.63</v>
       </c>
       <c r="M10">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="N10">
         <v>2.38</v>
@@ -2930,7 +2930,7 @@
         <v>1.63</v>
       </c>
       <c r="P10">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="Q10">
         <v>2.9</v>
@@ -2939,10 +2939,10 @@
         <v>1.16</v>
       </c>
       <c r="S10">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="T10">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="U10">
         <v>1.63</v>
@@ -2951,7 +2951,7 @@
         <v>1.26</v>
       </c>
       <c r="W10">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="X10">
         <v>9</v>
@@ -2963,7 +2963,7 @@
         <v>34</v>
       </c>
       <c r="AA10">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AB10">
         <v>6.4</v>
@@ -2978,7 +2978,7 @@
         <v>110</v>
       </c>
       <c r="AF10">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AG10">
         <v>13.5</v>
@@ -2990,7 +2990,7 @@
         <v>140</v>
       </c>
       <c r="AJ10">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AK10">
         <v>34</v>
@@ -3005,7 +3005,7 @@
         <v>34</v>
       </c>
       <c r="AO10">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="AP10">
         <v>6.8</v>
@@ -3014,10 +3014,10 @@
         <v>9</v>
       </c>
       <c r="AR10">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AS10">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AT10">
         <v>5.5</v>
@@ -3029,7 +3029,7 @@
         <v>17</v>
       </c>
       <c r="AW10">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AX10">
         <v>9.4</v>
@@ -3038,31 +3038,31 @@
         <v>10.5</v>
       </c>
       <c r="AZ10">
+        <v>7</v>
+      </c>
+      <c r="BA10">
+        <v>8.4</v>
+      </c>
+      <c r="BB10">
         <v>6.8</v>
       </c>
-      <c r="BA10">
+      <c r="BC10">
+        <v>7</v>
+      </c>
+      <c r="BD10">
         <v>8</v>
       </c>
-      <c r="BB10">
-        <v>6.6</v>
-      </c>
-      <c r="BC10">
-        <v>6.8</v>
-      </c>
-      <c r="BD10">
-        <v>7.6</v>
-      </c>
       <c r="BE10">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF10">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BG10">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BH10">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="BI10">
         <v>2.3</v>
@@ -3077,46 +3077,46 @@
         <v>1000</v>
       </c>
       <c r="BM10">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BN10">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BO10">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="BP10">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="BQ10">
-        <v>14.5</v>
+        <v>7.2</v>
       </c>
       <c r="BR10">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BS10">
         <v>9.6</v>
       </c>
       <c r="BT10">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BU10">
         <v>5.5</v>
       </c>
       <c r="BV10">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BW10">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BX10">
         <v>1000</v>
       </c>
       <c r="BY10">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BZ10">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="CA10">
         <v>9.800000000000001</v>
@@ -3142,19 +3142,19 @@
         <v>116</v>
       </c>
       <c r="F11">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="G11">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="H11">
         <v>7.6</v>
       </c>
       <c r="I11">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="J11">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="K11">
         <v>4</v>
@@ -3178,7 +3178,7 @@
         <v>2.4</v>
       </c>
       <c r="R11">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="S11">
         <v>4.8</v>
@@ -3187,16 +3187,16 @@
         <v>2.3</v>
       </c>
       <c r="U11">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="V11">
         <v>1.13</v>
       </c>
       <c r="W11">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="X11">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Y11">
         <v>23</v>
@@ -3205,10 +3205,10 @@
         <v>85</v>
       </c>
       <c r="AA11">
-        <v>430</v>
+        <v>410</v>
       </c>
       <c r="AB11">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AC11">
         <v>11</v>
@@ -3229,10 +3229,10 @@
         <v>38</v>
       </c>
       <c r="AI11">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="AJ11">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AK11">
         <v>27</v>
@@ -3247,31 +3247,31 @@
         <v>17</v>
       </c>
       <c r="AO11">
-        <v>440</v>
+        <v>420</v>
       </c>
       <c r="AP11">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AQ11">
         <v>16</v>
       </c>
       <c r="AR11">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AS11">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="AT11">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="AU11">
         <v>7.8</v>
       </c>
       <c r="AV11">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AW11">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="AX11">
         <v>6</v>
@@ -3280,10 +3280,10 @@
         <v>8</v>
       </c>
       <c r="AZ11">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BA11">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BB11">
         <v>11</v>
@@ -3292,22 +3292,22 @@
         <v>15.5</v>
       </c>
       <c r="BD11">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BE11">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BF11">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BG11">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BH11">
         <v>3.05</v>
       </c>
       <c r="BI11">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="BJ11">
         <v>13.5</v>
@@ -3319,49 +3319,49 @@
         <v>1000</v>
       </c>
       <c r="BM11">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BN11">
         <v>3.9</v>
       </c>
       <c r="BO11">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="BP11">
         <v>12</v>
       </c>
       <c r="BQ11">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BR11">
         <v>1000</v>
       </c>
       <c r="BS11">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BT11">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BU11">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BV11">
         <v>1000</v>
       </c>
       <c r="BW11">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BX11">
         <v>1000</v>
       </c>
       <c r="BY11">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BZ11">
         <v>1000</v>
       </c>
       <c r="CA11">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB11" t="s">
         <v>118</v>
@@ -3387,19 +3387,19 @@
         <v>4.4</v>
       </c>
       <c r="G12">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="H12">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="I12">
         <v>2.1</v>
       </c>
       <c r="J12">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="K12">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L12">
         <v>1.52</v>
@@ -3414,16 +3414,16 @@
         <v>1.47</v>
       </c>
       <c r="P12">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="Q12">
         <v>2.4</v>
       </c>
       <c r="R12">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="S12">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="T12">
         <v>2.08</v>
@@ -3432,10 +3432,10 @@
         <v>1.8</v>
       </c>
       <c r="V12">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="W12">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="X12">
         <v>12</v>
@@ -3453,13 +3453,13 @@
         <v>15.5</v>
       </c>
       <c r="AC12">
-        <v>9.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="AD12">
         <v>13.5</v>
       </c>
       <c r="AE12">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AF12">
         <v>42</v>
@@ -3480,13 +3480,13 @@
         <v>95</v>
       </c>
       <c r="AL12">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AM12">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="AN12">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AO12">
         <v>28</v>
@@ -3501,7 +3501,7 @@
         <v>10</v>
       </c>
       <c r="AS12">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="AT12">
         <v>9.4</v>
@@ -3513,34 +3513,34 @@
         <v>9.6</v>
       </c>
       <c r="AW12">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="AX12">
-        <v>3.95</v>
+        <v>4.4</v>
       </c>
       <c r="AY12">
         <v>14</v>
       </c>
       <c r="AZ12">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="BA12">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="BB12">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="BC12">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="BD12">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="BE12">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="BF12">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="BG12">
         <v>16.5</v>
@@ -3567,7 +3567,7 @@
         <v>7.8</v>
       </c>
       <c r="BO12">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="BP12">
         <v>1000</v>
@@ -3585,7 +3585,7 @@
         <v>4.5</v>
       </c>
       <c r="BU12">
-        <v>4</v>
+        <v>3.55</v>
       </c>
       <c r="BV12">
         <v>1000</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-28.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-28.xlsx
@@ -370,7 +370,7 @@
     <t>Athletic Club</t>
   </si>
   <si>
-    <t>2026-07-27 15:21:31</t>
+    <t>2026-07-27 17:28:26</t>
   </si>
 </sst>
 </file>
@@ -964,19 +964,19 @@
         <v>107</v>
       </c>
       <c r="F2">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="G2">
         <v>2.44</v>
       </c>
       <c r="H2">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="I2">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="J2">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="K2">
         <v>3.3</v>
@@ -997,7 +997,7 @@
         <v>1.58</v>
       </c>
       <c r="Q2">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="R2">
         <v>1.2</v>
@@ -1006,34 +1006,34 @@
         <v>5.4</v>
       </c>
       <c r="T2">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="U2">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="V2">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W2">
         <v>1.69</v>
       </c>
       <c r="X2">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="Y2">
         <v>10.5</v>
       </c>
       <c r="Z2">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AA2">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AB2">
+        <v>7.6</v>
+      </c>
+      <c r="AC2">
         <v>7.4</v>
-      </c>
-      <c r="AC2">
-        <v>7.6</v>
       </c>
       <c r="AD2">
         <v>16.5</v>
@@ -1048,22 +1048,22 @@
         <v>12</v>
       </c>
       <c r="AH2">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI2">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AJ2">
         <v>38</v>
       </c>
       <c r="AK2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AL2">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AM2">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="AN2">
         <v>46</v>
@@ -1075,13 +1075,13 @@
         <v>7.8</v>
       </c>
       <c r="AQ2">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR2">
         <v>21</v>
       </c>
       <c r="AS2">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AT2">
         <v>6.6</v>
@@ -1090,10 +1090,10 @@
         <v>6.6</v>
       </c>
       <c r="AV2">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AW2">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AX2">
         <v>12</v>
@@ -1105,31 +1105,31 @@
         <v>19.5</v>
       </c>
       <c r="BA2">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BB2">
         <v>27</v>
       </c>
       <c r="BC2">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BD2">
         <v>44</v>
       </c>
       <c r="BE2">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="BF2">
         <v>30</v>
       </c>
       <c r="BG2">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BH2">
         <v>2.74</v>
       </c>
       <c r="BI2">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="BJ2">
         <v>11.5</v>
@@ -1141,7 +1141,7 @@
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BN2">
         <v>5.1</v>
@@ -1153,16 +1153,16 @@
         <v>21</v>
       </c>
       <c r="BQ2">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BR2">
         <v>44</v>
       </c>
       <c r="BS2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BT2">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BU2">
         <v>5</v>
@@ -1171,19 +1171,19 @@
         <v>36</v>
       </c>
       <c r="BW2">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BX2">
         <v>60</v>
       </c>
       <c r="BY2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BZ2">
         <v>48</v>
       </c>
       <c r="CA2">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="CB2" t="s">
         <v>118</v>
@@ -1206,193 +1206,193 @@
         <v>108</v>
       </c>
       <c r="F3">
-        <v>4.7</v>
+        <v>3.75</v>
       </c>
       <c r="G3">
-        <v>5.3</v>
+        <v>4.3</v>
       </c>
       <c r="H3">
-        <v>1.93</v>
+        <v>2.24</v>
       </c>
       <c r="I3">
+        <v>2.42</v>
+      </c>
+      <c r="J3">
+        <v>3</v>
+      </c>
+      <c r="K3">
+        <v>3.25</v>
+      </c>
+      <c r="L3">
+        <v>1.54</v>
+      </c>
+      <c r="M3">
+        <v>1.11</v>
+      </c>
+      <c r="N3">
+        <v>2.78</v>
+      </c>
+      <c r="O3">
+        <v>1.52</v>
+      </c>
+      <c r="P3">
+        <v>1.57</v>
+      </c>
+      <c r="Q3">
+        <v>2.52</v>
+      </c>
+      <c r="R3">
+        <v>1.2</v>
+      </c>
+      <c r="S3">
+        <v>5.1</v>
+      </c>
+      <c r="T3">
         <v>2.02</v>
       </c>
-      <c r="J3">
-        <v>3.3</v>
-      </c>
-      <c r="K3">
-        <v>3.6</v>
-      </c>
-      <c r="L3">
-        <v>1.52</v>
-      </c>
-      <c r="M3">
-        <v>1.1</v>
-      </c>
-      <c r="N3">
-        <v>2.94</v>
-      </c>
-      <c r="O3">
-        <v>1.46</v>
-      </c>
-      <c r="P3">
-        <v>1.64</v>
-      </c>
-      <c r="Q3">
-        <v>2.42</v>
-      </c>
-      <c r="R3">
-        <v>1.23</v>
-      </c>
-      <c r="S3">
-        <v>4.8</v>
-      </c>
-      <c r="T3">
-        <v>2.08</v>
-      </c>
       <c r="U3">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="V3">
-        <v>1.99</v>
+        <v>1.73</v>
       </c>
       <c r="W3">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="X3">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="Y3">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="Z3">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="AA3">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="AB3">
+        <v>12</v>
+      </c>
+      <c r="AC3">
+        <v>7.8</v>
+      </c>
+      <c r="AD3">
+        <v>12.5</v>
+      </c>
+      <c r="AE3">
+        <v>36</v>
+      </c>
+      <c r="AF3">
+        <v>36</v>
+      </c>
+      <c r="AG3">
+        <v>18</v>
+      </c>
+      <c r="AH3">
+        <v>30</v>
+      </c>
+      <c r="AI3">
+        <v>70</v>
+      </c>
+      <c r="AJ3">
+        <v>100</v>
+      </c>
+      <c r="AK3">
+        <v>65</v>
+      </c>
+      <c r="AL3">
+        <v>100</v>
+      </c>
+      <c r="AM3">
+        <v>180</v>
+      </c>
+      <c r="AN3">
+        <v>95</v>
+      </c>
+      <c r="AO3">
+        <v>32</v>
+      </c>
+      <c r="AP3">
+        <v>8</v>
+      </c>
+      <c r="AQ3">
+        <v>6.4</v>
+      </c>
+      <c r="AR3">
+        <v>11</v>
+      </c>
+      <c r="AS3">
+        <v>23</v>
+      </c>
+      <c r="AT3">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AU3">
+        <v>6.2</v>
+      </c>
+      <c r="AV3">
+        <v>10</v>
+      </c>
+      <c r="AW3">
+        <v>23</v>
+      </c>
+      <c r="AX3">
+        <v>19.5</v>
+      </c>
+      <c r="AY3">
         <v>14</v>
       </c>
-      <c r="AC3">
-        <v>8</v>
-      </c>
-      <c r="AD3">
-        <v>11.5</v>
-      </c>
-      <c r="AE3">
-        <v>38</v>
-      </c>
-      <c r="AF3">
-        <v>40</v>
-      </c>
-      <c r="AG3">
-        <v>21</v>
-      </c>
-      <c r="AH3">
-        <v>25</v>
-      </c>
-      <c r="AI3">
-        <v>55</v>
-      </c>
-      <c r="AJ3">
-        <v>160</v>
-      </c>
-      <c r="AK3">
-        <v>140</v>
-      </c>
-      <c r="AL3">
-        <v>160</v>
-      </c>
-      <c r="AM3">
-        <v>200</v>
-      </c>
-      <c r="AN3">
-        <v>140</v>
-      </c>
-      <c r="AO3">
-        <v>21</v>
-      </c>
-      <c r="AP3">
-        <v>9</v>
-      </c>
-      <c r="AQ3">
-        <v>6.2</v>
-      </c>
-      <c r="AR3">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AS3">
+      <c r="AZ3">
         <v>19</v>
-      </c>
-      <c r="AT3">
-        <v>11.5</v>
-      </c>
-      <c r="AU3">
-        <v>6.8</v>
-      </c>
-      <c r="AV3">
-        <v>9.4</v>
-      </c>
-      <c r="AW3">
-        <v>21</v>
-      </c>
-      <c r="AX3">
-        <v>30</v>
-      </c>
-      <c r="AY3">
-        <v>17.5</v>
-      </c>
-      <c r="AZ3">
-        <v>19.5</v>
       </c>
       <c r="BA3">
         <v>42</v>
       </c>
       <c r="BB3">
-        <v>9.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="BC3">
-        <v>9.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="BD3">
-        <v>9.6</v>
+        <v>7.6</v>
       </c>
       <c r="BE3">
+        <v>8</v>
+      </c>
+      <c r="BF3">
+        <v>7.8</v>
+      </c>
+      <c r="BG3">
+        <v>8</v>
+      </c>
+      <c r="BH3">
+        <v>2.88</v>
+      </c>
+      <c r="BI3">
+        <v>2.36</v>
+      </c>
+      <c r="BJ3">
+        <v>11.5</v>
+      </c>
+      <c r="BK3">
+        <v>8.4</v>
+      </c>
+      <c r="BL3">
+        <v>1000</v>
+      </c>
+      <c r="BM3">
         <v>10</v>
       </c>
-      <c r="BF3">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BG3">
-        <v>17.5</v>
-      </c>
-      <c r="BH3">
-        <v>3.05</v>
-      </c>
-      <c r="BI3">
-        <v>2.46</v>
-      </c>
-      <c r="BJ3">
-        <v>12</v>
-      </c>
-      <c r="BK3">
-        <v>5.4</v>
-      </c>
-      <c r="BL3">
-        <v>1000</v>
-      </c>
-      <c r="BM3">
-        <v>9.6</v>
-      </c>
       <c r="BN3">
-        <v>8.6</v>
+        <v>7.2</v>
       </c>
       <c r="BO3">
-        <v>6.6</v>
+        <v>5.7</v>
       </c>
       <c r="BP3">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BQ3">
         <v>8.4</v>
@@ -1401,31 +1401,31 @@
         <v>1000</v>
       </c>
       <c r="BS3">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BT3">
+        <v>5.1</v>
+      </c>
+      <c r="BU3">
+        <v>3.95</v>
+      </c>
+      <c r="BV3">
+        <v>21</v>
+      </c>
+      <c r="BW3">
+        <v>7.2</v>
+      </c>
+      <c r="BX3">
+        <v>1000</v>
+      </c>
+      <c r="BY3">
         <v>8.800000000000001</v>
       </c>
-      <c r="BT3">
-        <v>4.6</v>
-      </c>
-      <c r="BU3">
-        <v>3.8</v>
-      </c>
-      <c r="BV3">
-        <v>15.5</v>
-      </c>
-      <c r="BW3">
-        <v>6</v>
-      </c>
-      <c r="BX3">
-        <v>1000</v>
-      </c>
-      <c r="BY3">
-        <v>7.8</v>
-      </c>
       <c r="BZ3">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="CA3">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB3" t="s">
         <v>118</v>
@@ -1457,7 +1457,7 @@
         <v>2.16</v>
       </c>
       <c r="I4">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="J4">
         <v>3.75</v>
@@ -1481,31 +1481,31 @@
         <v>2.2</v>
       </c>
       <c r="Q4">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="R4">
         <v>1.48</v>
       </c>
       <c r="S4">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="T4">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="U4">
         <v>2.36</v>
       </c>
       <c r="V4">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="W4">
         <v>1.39</v>
       </c>
       <c r="X4">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Y4">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="Z4">
         <v>19</v>
@@ -1514,16 +1514,16 @@
         <v>34</v>
       </c>
       <c r="AB4">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AC4">
         <v>8.800000000000001</v>
       </c>
       <c r="AD4">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AE4">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AF4">
         <v>32</v>
@@ -1538,7 +1538,7 @@
         <v>40</v>
       </c>
       <c r="AJ4">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AK4">
         <v>44</v>
@@ -1580,7 +1580,7 @@
         <v>16</v>
       </c>
       <c r="AX4">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="AY4">
         <v>10.5</v>
@@ -1589,19 +1589,19 @@
         <v>13.5</v>
       </c>
       <c r="BA4">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="BB4">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BC4">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="BD4">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="BE4">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="BF4">
         <v>21</v>
@@ -1610,7 +1610,7 @@
         <v>10</v>
       </c>
       <c r="BH4">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="BI4">
         <v>3.5</v>
@@ -1625,7 +1625,7 @@
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BN4">
         <v>6.8</v>
@@ -1690,22 +1690,22 @@
         <v>110</v>
       </c>
       <c r="F5">
-        <v>2.32</v>
+        <v>2.26</v>
       </c>
       <c r="G5">
-        <v>2.46</v>
+        <v>2.38</v>
       </c>
       <c r="H5">
-        <v>2.98</v>
+        <v>3.1</v>
       </c>
       <c r="I5">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="J5">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="K5">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L5">
         <v>1.35</v>
@@ -1720,46 +1720,46 @@
         <v>1.23</v>
       </c>
       <c r="P5">
-        <v>2.42</v>
+        <v>2.32</v>
       </c>
       <c r="Q5">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="R5">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="S5">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="T5">
         <v>1.6</v>
       </c>
       <c r="U5">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="V5">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="W5">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="X5">
         <v>23</v>
       </c>
       <c r="Y5">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="Z5">
         <v>28</v>
       </c>
       <c r="AA5">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AB5">
         <v>15.5</v>
       </c>
       <c r="AC5">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AD5">
         <v>16</v>
@@ -1780,19 +1780,19 @@
         <v>38</v>
       </c>
       <c r="AJ5">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AK5">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AL5">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AM5">
         <v>65</v>
       </c>
       <c r="AN5">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AO5">
         <v>25</v>
@@ -1807,7 +1807,7 @@
         <v>18</v>
       </c>
       <c r="AS5">
-        <v>5.5</v>
+        <v>36</v>
       </c>
       <c r="AT5">
         <v>10</v>
@@ -1819,7 +1819,7 @@
         <v>10.5</v>
       </c>
       <c r="AW5">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="AX5">
         <v>13.5</v>
@@ -1834,82 +1834,82 @@
         <v>28</v>
       </c>
       <c r="BB5">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="BC5">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="BD5">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="BE5">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BF5">
-        <v>13</v>
+        <v>10.5</v>
       </c>
       <c r="BG5">
         <v>17</v>
       </c>
       <c r="BH5">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BI5">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="BJ5">
         <v>8.800000000000001</v>
       </c>
       <c r="BK5">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="BN5">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BO5">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BP5">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BQ5">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BR5">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BS5">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="BT5">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BU5">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BV5">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BW5">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BX5">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BY5">
         <v>10</v>
       </c>
       <c r="BZ5">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="CA5">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB5" t="s">
         <v>118</v>
@@ -1932,58 +1932,58 @@
         <v>111</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="K6">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="L6">
-        <v>1.01</v>
+        <v>1.54</v>
       </c>
       <c r="M6">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="N6">
-        <v>1.25</v>
+        <v>2.14</v>
       </c>
       <c r="O6">
-        <v>1.02</v>
+        <v>1.51</v>
       </c>
       <c r="P6">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="Q6">
-        <v>1.51</v>
+        <v>2.42</v>
       </c>
       <c r="R6">
         <v>1.18</v>
       </c>
       <c r="S6">
-        <v>1.51</v>
+        <v>4.7</v>
       </c>
       <c r="T6">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="U6">
-        <v>1.11</v>
+        <v>1.56</v>
       </c>
       <c r="V6">
-        <v>1.01</v>
+        <v>1.6</v>
       </c>
       <c r="W6">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="X6">
         <v>1000</v>
@@ -2097,55 +2097,55 @@
         <v>1000</v>
       </c>
       <c r="BI6">
-        <v>1.04</v>
+        <v>1.78</v>
       </c>
       <c r="BJ6">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="BK6">
-        <v>1.04</v>
+        <v>1.6</v>
       </c>
       <c r="BL6">
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>1.04</v>
+        <v>1.78</v>
       </c>
       <c r="BN6">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="BO6">
-        <v>1.04</v>
+        <v>4.6</v>
       </c>
       <c r="BP6">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BQ6">
-        <v>1.04</v>
+        <v>1.72</v>
       </c>
       <c r="BR6">
         <v>1000</v>
       </c>
       <c r="BS6">
-        <v>1.04</v>
+        <v>1.75</v>
       </c>
       <c r="BT6">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BU6">
-        <v>1.04</v>
+        <v>3.55</v>
       </c>
       <c r="BV6">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BW6">
-        <v>1.04</v>
+        <v>1.68</v>
       </c>
       <c r="BX6">
         <v>1000</v>
       </c>
       <c r="BY6">
-        <v>1.04</v>
+        <v>1.73</v>
       </c>
       <c r="BZ6">
         <v>0</v>
@@ -2174,22 +2174,22 @@
         <v>112</v>
       </c>
       <c r="F7">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="G7">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="H7">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="I7">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="J7">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="K7">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="L7">
         <v>1.17</v>
@@ -2204,43 +2204,43 @@
         <v>1.1</v>
       </c>
       <c r="P7">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="Q7">
         <v>1.33</v>
       </c>
       <c r="R7">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="S7">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="T7">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="U7">
-        <v>2.58</v>
+        <v>2.7</v>
       </c>
       <c r="V7">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="W7">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="X7">
         <v>950</v>
       </c>
       <c r="Y7">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Z7">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA7">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AB7">
-        <v>55</v>
+        <v>950</v>
       </c>
       <c r="AC7">
         <v>18.5</v>
@@ -2258,94 +2258,94 @@
         <v>950</v>
       </c>
       <c r="AH7">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI7">
         <v>26</v>
       </c>
       <c r="AJ7">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="AK7">
         <v>85</v>
       </c>
       <c r="AL7">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AM7">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AN7">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AO7">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="AP7">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="AQ7">
+        <v>15.5</v>
+      </c>
+      <c r="AR7">
+        <v>12.5</v>
+      </c>
+      <c r="AS7">
         <v>13.5</v>
       </c>
-      <c r="AR7">
-        <v>10.5</v>
-      </c>
-      <c r="AS7">
+      <c r="AT7">
+        <v>29</v>
+      </c>
+      <c r="AU7">
         <v>11.5</v>
-      </c>
-      <c r="AT7">
-        <v>6</v>
-      </c>
-      <c r="AU7">
-        <v>12</v>
       </c>
       <c r="AV7">
         <v>10</v>
       </c>
       <c r="AW7">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AX7">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AY7">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="AZ7">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BA7">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="BB7">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="BC7">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BD7">
-        <v>6.2</v>
+        <v>38</v>
       </c>
       <c r="BE7">
-        <v>6.2</v>
+        <v>36</v>
       </c>
       <c r="BF7">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="BG7">
         <v>3.45</v>
       </c>
       <c r="BH7">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BI7">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="BJ7">
         <v>9.4</v>
       </c>
       <c r="BK7">
-        <v>5.5</v>
+        <v>7.2</v>
       </c>
       <c r="BL7">
         <v>1000</v>
@@ -2354,13 +2354,13 @@
         <v>11</v>
       </c>
       <c r="BN7">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BO7">
-        <v>6.2</v>
+        <v>8.4</v>
       </c>
       <c r="BP7">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BQ7">
         <v>10</v>
@@ -2369,19 +2369,19 @@
         <v>1000</v>
       </c>
       <c r="BS7">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT7">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BU7">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="BV7">
         <v>8.6</v>
       </c>
       <c r="BW7">
-        <v>5.2</v>
+        <v>6.8</v>
       </c>
       <c r="BX7">
         <v>16.5</v>
@@ -2393,7 +2393,7 @@
         <v>8.4</v>
       </c>
       <c r="CA7">
-        <v>5.2</v>
+        <v>6.6</v>
       </c>
       <c r="CB7" t="s">
         <v>118</v>
@@ -2416,7 +2416,7 @@
         <v>113</v>
       </c>
       <c r="F8">
-        <v>1.05</v>
+        <v>1.47</v>
       </c>
       <c r="G8">
         <v>1000</v>
@@ -2431,7 +2431,7 @@
         <v>1.1</v>
       </c>
       <c r="K8">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L8">
         <v>1.01</v>
@@ -2581,61 +2581,61 @@
         <v>1000</v>
       </c>
       <c r="BI8">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ8">
         <v>1000</v>
       </c>
       <c r="BK8">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL8">
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN8">
         <v>1000</v>
       </c>
       <c r="BO8">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP8">
         <v>1000</v>
       </c>
       <c r="BQ8">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR8">
         <v>1000</v>
       </c>
       <c r="BS8">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT8">
         <v>1000</v>
       </c>
       <c r="BU8">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV8">
         <v>1000</v>
       </c>
       <c r="BW8">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX8">
         <v>1000</v>
       </c>
       <c r="BY8">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ8">
         <v>1000</v>
       </c>
       <c r="CA8">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB8" t="s">
         <v>118</v>
@@ -2658,10 +2658,10 @@
         <v>114</v>
       </c>
       <c r="F9">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="G9">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="H9">
         <v>4.7</v>
@@ -2670,214 +2670,214 @@
         <v>5.3</v>
       </c>
       <c r="J9">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="K9">
         <v>3.3</v>
       </c>
       <c r="L9">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M9">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="N9">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="P9">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="Q9">
         <v>2.96</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="T9">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="U9">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="V9">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="W9">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="X9">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="Y9">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Z9">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AA9">
-        <v>0</v>
+        <v>190</v>
       </c>
       <c r="AB9">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AC9">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD9">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AE9">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="AF9">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AG9">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AH9">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AI9">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="AJ9">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AK9">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AL9">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="AM9">
-        <v>0</v>
+        <v>380</v>
       </c>
       <c r="AN9">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AO9">
-        <v>0</v>
+        <v>260</v>
       </c>
       <c r="AP9">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AQ9">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR9">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AS9">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AT9">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AU9">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AV9">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AW9">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AX9">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AY9">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AZ9">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BA9">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="BB9">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BC9">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BD9">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BE9">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="BF9">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BG9">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="BH9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ9">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="BK9">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="BL9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM9">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BN9">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="BO9">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="BP9">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="BQ9">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="BR9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS9">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BT9">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BU9">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="BV9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW9">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BX9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY9">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BZ9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA9">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="CB9" t="s">
         <v>118</v>
@@ -2900,16 +2900,16 @@
         <v>115</v>
       </c>
       <c r="F10">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="G10">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="H10">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="I10">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="J10">
         <v>3.05</v>
@@ -2921,76 +2921,76 @@
         <v>1.63</v>
       </c>
       <c r="M10">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="N10">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="O10">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="P10">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="Q10">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="R10">
         <v>1.16</v>
       </c>
       <c r="S10">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="T10">
         <v>2.38</v>
       </c>
       <c r="U10">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="V10">
         <v>1.26</v>
       </c>
       <c r="W10">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="X10">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y10">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="Z10">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AA10">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AB10">
         <v>6.4</v>
       </c>
       <c r="AC10">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AD10">
         <v>21</v>
       </c>
       <c r="AE10">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AF10">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AG10">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH10">
         <v>32</v>
       </c>
       <c r="AI10">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AJ10">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AK10">
         <v>34</v>
@@ -3002,67 +3002,67 @@
         <v>320</v>
       </c>
       <c r="AN10">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AO10">
-        <v>190</v>
+        <v>1000</v>
       </c>
       <c r="AP10">
+        <v>7.2</v>
+      </c>
+      <c r="AQ10">
+        <v>9.4</v>
+      </c>
+      <c r="AR10">
+        <v>18.5</v>
+      </c>
+      <c r="AS10">
+        <v>38</v>
+      </c>
+      <c r="AT10">
+        <v>5.7</v>
+      </c>
+      <c r="AU10">
         <v>6.8</v>
       </c>
-      <c r="AQ10">
-        <v>9</v>
-      </c>
-      <c r="AR10">
-        <v>7</v>
-      </c>
-      <c r="AS10">
-        <v>8.6</v>
-      </c>
-      <c r="AT10">
-        <v>5.5</v>
-      </c>
-      <c r="AU10">
-        <v>6.6</v>
-      </c>
       <c r="AV10">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AW10">
-        <v>8.4</v>
+        <v>36</v>
       </c>
       <c r="AX10">
         <v>9.4</v>
       </c>
       <c r="AY10">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AZ10">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="BA10">
-        <v>8.4</v>
+        <v>42</v>
       </c>
       <c r="BB10">
-        <v>6.8</v>
+        <v>18</v>
       </c>
       <c r="BC10">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="BD10">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="BE10">
-        <v>8.800000000000001</v>
+        <v>95</v>
       </c>
       <c r="BF10">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="BG10">
-        <v>8.6</v>
+        <v>42</v>
       </c>
       <c r="BH10">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="BI10">
         <v>2.3</v>
@@ -3071,22 +3071,22 @@
         <v>13</v>
       </c>
       <c r="BK10">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BL10">
         <v>1000</v>
       </c>
       <c r="BM10">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BN10">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BO10">
         <v>3.9</v>
       </c>
       <c r="BP10">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BQ10">
         <v>7.2</v>
@@ -3095,7 +3095,7 @@
         <v>1000</v>
       </c>
       <c r="BS10">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT10">
         <v>8.4</v>
@@ -3107,19 +3107,19 @@
         <v>60</v>
       </c>
       <c r="BW10">
+        <v>9.6</v>
+      </c>
+      <c r="BX10">
+        <v>1000</v>
+      </c>
+      <c r="BY10">
         <v>10</v>
-      </c>
-      <c r="BX10">
-        <v>1000</v>
-      </c>
-      <c r="BY10">
-        <v>10.5</v>
       </c>
       <c r="BZ10">
         <v>60</v>
       </c>
       <c r="CA10">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="CB10" t="s">
         <v>118</v>
@@ -3142,10 +3142,10 @@
         <v>116</v>
       </c>
       <c r="F11">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="G11">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="H11">
         <v>7.6</v>
@@ -3154,10 +3154,10 @@
         <v>8.4</v>
       </c>
       <c r="J11">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="K11">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="L11">
         <v>1.51</v>
@@ -3166,13 +3166,13 @@
         <v>1.11</v>
       </c>
       <c r="N11">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="O11">
         <v>1.47</v>
       </c>
       <c r="P11">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="Q11">
         <v>2.4</v>
@@ -3184,22 +3184,22 @@
         <v>4.8</v>
       </c>
       <c r="T11">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="U11">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="V11">
         <v>1.13</v>
       </c>
       <c r="W11">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="X11">
         <v>12</v>
       </c>
       <c r="Y11">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="Z11">
         <v>85</v>
@@ -3208,19 +3208,19 @@
         <v>410</v>
       </c>
       <c r="AB11">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="AC11">
         <v>11</v>
       </c>
       <c r="AD11">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AE11">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="AF11">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG11">
         <v>13</v>
@@ -3256,34 +3256,34 @@
         <v>16</v>
       </c>
       <c r="AR11">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="AS11">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="AT11">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="AU11">
         <v>7.8</v>
       </c>
       <c r="AV11">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="AW11">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AX11">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AY11">
         <v>8</v>
       </c>
       <c r="AZ11">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BA11">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BB11">
         <v>11</v>
@@ -3292,19 +3292,19 @@
         <v>15.5</v>
       </c>
       <c r="BD11">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BE11">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="BF11">
         <v>10.5</v>
       </c>
       <c r="BG11">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="BH11">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="BI11">
         <v>2.4</v>
@@ -3313,13 +3313,13 @@
         <v>13.5</v>
       </c>
       <c r="BK11">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BL11">
         <v>1000</v>
       </c>
       <c r="BM11">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BN11">
         <v>3.9</v>
@@ -3331,37 +3331,37 @@
         <v>12</v>
       </c>
       <c r="BQ11">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BR11">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BS11">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT11">
         <v>11.5</v>
       </c>
       <c r="BU11">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BV11">
         <v>1000</v>
       </c>
       <c r="BW11">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BX11">
         <v>1000</v>
       </c>
       <c r="BY11">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BZ11">
         <v>1000</v>
       </c>
       <c r="CA11">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="CB11" t="s">
         <v>118</v>
@@ -3387,16 +3387,16 @@
         <v>4.4</v>
       </c>
       <c r="G12">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="H12">
         <v>2.06</v>
       </c>
       <c r="I12">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="J12">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="K12">
         <v>3.4</v>
@@ -3408,34 +3408,34 @@
         <v>1.11</v>
       </c>
       <c r="N12">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="O12">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="P12">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="Q12">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="R12">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="S12">
         <v>4.9</v>
       </c>
       <c r="T12">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="U12">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="V12">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="W12">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="X12">
         <v>12</v>
@@ -3462,10 +3462,10 @@
         <v>32</v>
       </c>
       <c r="AF12">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AG12">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AH12">
         <v>28</v>
@@ -3477,7 +3477,7 @@
         <v>150</v>
       </c>
       <c r="AK12">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AL12">
         <v>110</v>
@@ -3486,7 +3486,7 @@
         <v>200</v>
       </c>
       <c r="AN12">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AO12">
         <v>28</v>
@@ -3501,7 +3501,7 @@
         <v>10</v>
       </c>
       <c r="AS12">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AT12">
         <v>9.4</v>
@@ -3513,34 +3513,34 @@
         <v>9.6</v>
       </c>
       <c r="AW12">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AX12">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AY12">
         <v>14</v>
       </c>
       <c r="AZ12">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="BA12">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="BB12">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="BC12">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="BD12">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="BE12">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="BF12">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="BG12">
         <v>16.5</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-28.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-28.xlsx
@@ -370,7 +370,7 @@
     <t>Athletic Club</t>
   </si>
   <si>
-    <t>2026-07-27 17:28:26</t>
+    <t>2026-07-27 19:35:21</t>
   </si>
 </sst>
 </file>
@@ -964,61 +964,61 @@
         <v>107</v>
       </c>
       <c r="F2">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="G2">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="H2">
         <v>3.55</v>
       </c>
       <c r="I2">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="J2">
         <v>3.15</v>
       </c>
       <c r="K2">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="L2">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="M2">
         <v>1.12</v>
       </c>
       <c r="N2">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="O2">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="P2">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="Q2">
         <v>2.66</v>
       </c>
       <c r="R2">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="S2">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="T2">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="U2">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="V2">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W2">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="X2">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y2">
         <v>10.5</v>
@@ -1027,7 +1027,7 @@
         <v>24</v>
       </c>
       <c r="AA2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AB2">
         <v>7.6</v>
@@ -1039,7 +1039,7 @@
         <v>16.5</v>
       </c>
       <c r="AE2">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="AF2">
         <v>14</v>
@@ -1051,7 +1051,7 @@
         <v>23</v>
       </c>
       <c r="AI2">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="AJ2">
         <v>38</v>
@@ -1066,58 +1066,58 @@
         <v>220</v>
       </c>
       <c r="AN2">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="AO2">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="AP2">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ2">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AR2">
         <v>21</v>
       </c>
       <c r="AS2">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AT2">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AU2">
         <v>6.6</v>
       </c>
       <c r="AV2">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AW2">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="AX2">
         <v>12</v>
       </c>
       <c r="AY2">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AZ2">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BA2">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BB2">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="BC2">
         <v>27</v>
       </c>
       <c r="BD2">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="BE2">
-        <v>13.5</v>
+        <v>18</v>
       </c>
       <c r="BF2">
         <v>30</v>
@@ -1129,10 +1129,10 @@
         <v>2.74</v>
       </c>
       <c r="BI2">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="BJ2">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BK2">
         <v>8.199999999999999</v>
@@ -1141,7 +1141,7 @@
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="BN2">
         <v>5.1</v>
@@ -1153,13 +1153,13 @@
         <v>21</v>
       </c>
       <c r="BQ2">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BR2">
         <v>44</v>
       </c>
       <c r="BS2">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BT2">
         <v>6.6</v>
@@ -1171,19 +1171,19 @@
         <v>36</v>
       </c>
       <c r="BW2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BX2">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="BY2">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BZ2">
         <v>48</v>
       </c>
       <c r="CA2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="CB2" t="s">
         <v>118</v>
@@ -1206,22 +1206,22 @@
         <v>108</v>
       </c>
       <c r="F3">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="G3">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="H3">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="I3">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="J3">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="K3">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="L3">
         <v>1.54</v>
@@ -1230,76 +1230,76 @@
         <v>1.11</v>
       </c>
       <c r="N3">
-        <v>2.78</v>
+        <v>2.86</v>
       </c>
       <c r="O3">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="P3">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="Q3">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="R3">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="S3">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="T3">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="U3">
-        <v>1.78</v>
+        <v>1.86</v>
       </c>
       <c r="V3">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="W3">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="X3">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y3">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="Z3">
         <v>14</v>
       </c>
       <c r="AA3">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="AB3">
+        <v>11.5</v>
+      </c>
+      <c r="AC3">
+        <v>7.6</v>
+      </c>
+      <c r="AD3">
         <v>12</v>
       </c>
-      <c r="AC3">
-        <v>7.8</v>
-      </c>
-      <c r="AD3">
-        <v>12.5</v>
-      </c>
       <c r="AE3">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AF3">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="AG3">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AH3">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="AI3">
         <v>70</v>
       </c>
       <c r="AJ3">
-        <v>100</v>
+        <v>170</v>
       </c>
       <c r="AK3">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="AL3">
         <v>100</v>
@@ -1308,28 +1308,28 @@
         <v>180</v>
       </c>
       <c r="AN3">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AO3">
         <v>32</v>
       </c>
       <c r="AP3">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ3">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="AR3">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AS3">
         <v>23</v>
       </c>
       <c r="AT3">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU3">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AV3">
         <v>10</v>
@@ -1338,40 +1338,40 @@
         <v>23</v>
       </c>
       <c r="AX3">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="AY3">
         <v>14</v>
       </c>
       <c r="AZ3">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BA3">
         <v>42</v>
       </c>
       <c r="BB3">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="BC3">
-        <v>7.6</v>
+        <v>34</v>
       </c>
       <c r="BD3">
-        <v>7.6</v>
+        <v>9.6</v>
       </c>
       <c r="BE3">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="BF3">
-        <v>7.8</v>
+        <v>42</v>
       </c>
       <c r="BG3">
-        <v>8</v>
+        <v>9.4</v>
       </c>
       <c r="BH3">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="BI3">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="BJ3">
         <v>11.5</v>
@@ -1383,49 +1383,49 @@
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="BN3">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BO3">
         <v>5.7</v>
       </c>
       <c r="BP3">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BQ3">
-        <v>8.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BR3">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="BS3">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="BT3">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BU3">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="BV3">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="BW3">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BX3">
         <v>1000</v>
       </c>
       <c r="BY3">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BZ3">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="CA3">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="CB3" t="s">
         <v>118</v>
@@ -1451,19 +1451,19 @@
         <v>3.3</v>
       </c>
       <c r="G4">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="H4">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="I4">
         <v>2.3</v>
       </c>
       <c r="J4">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="K4">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L4">
         <v>1.28</v>
@@ -1472,22 +1472,22 @@
         <v>1.05</v>
       </c>
       <c r="N4">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="O4">
         <v>1.25</v>
       </c>
       <c r="P4">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="Q4">
         <v>1.75</v>
       </c>
       <c r="R4">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="S4">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="T4">
         <v>1.65</v>
@@ -1496,7 +1496,7 @@
         <v>2.36</v>
       </c>
       <c r="V4">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="W4">
         <v>1.39</v>
@@ -1538,7 +1538,7 @@
         <v>40</v>
       </c>
       <c r="AJ4">
-        <v>70</v>
+        <v>130</v>
       </c>
       <c r="AK4">
         <v>44</v>
@@ -1547,7 +1547,7 @@
         <v>55</v>
       </c>
       <c r="AM4">
-        <v>85</v>
+        <v>580</v>
       </c>
       <c r="AN4">
         <v>36</v>
@@ -1571,16 +1571,16 @@
         <v>14</v>
       </c>
       <c r="AU4">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AV4">
         <v>10</v>
       </c>
       <c r="AW4">
-        <v>16</v>
+        <v>19.5</v>
       </c>
       <c r="AX4">
-        <v>4.3</v>
+        <v>11.5</v>
       </c>
       <c r="AY4">
         <v>10.5</v>
@@ -1589,19 +1589,19 @@
         <v>13.5</v>
       </c>
       <c r="BA4">
-        <v>4.5</v>
+        <v>16</v>
       </c>
       <c r="BB4">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="BC4">
-        <v>4.5</v>
+        <v>16</v>
       </c>
       <c r="BD4">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="BE4">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BF4">
         <v>21</v>
@@ -1690,22 +1690,22 @@
         <v>110</v>
       </c>
       <c r="F5">
-        <v>2.26</v>
+        <v>2.44</v>
       </c>
       <c r="G5">
-        <v>2.38</v>
+        <v>2.7</v>
       </c>
       <c r="H5">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="I5">
-        <v>3.35</v>
+        <v>3.05</v>
       </c>
       <c r="J5">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="K5">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L5">
         <v>1.35</v>
@@ -1714,118 +1714,118 @@
         <v>1.05</v>
       </c>
       <c r="N5">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="O5">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="P5">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="Q5">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="R5">
         <v>1.53</v>
       </c>
       <c r="S5">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="T5">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="U5">
-        <v>2.48</v>
+        <v>2.54</v>
       </c>
       <c r="V5">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="W5">
-        <v>1.72</v>
+        <v>1.59</v>
       </c>
       <c r="X5">
+        <v>22</v>
+      </c>
+      <c r="Y5">
+        <v>16</v>
+      </c>
+      <c r="Z5">
         <v>23</v>
       </c>
-      <c r="Y5">
-        <v>18</v>
-      </c>
-      <c r="Z5">
-        <v>28</v>
-      </c>
       <c r="AA5">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AB5">
         <v>15.5</v>
       </c>
       <c r="AC5">
-        <v>10.5</v>
+        <v>8.6</v>
       </c>
       <c r="AD5">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AE5">
+        <v>29</v>
+      </c>
+      <c r="AF5">
+        <v>21</v>
+      </c>
+      <c r="AG5">
+        <v>13.5</v>
+      </c>
+      <c r="AH5">
+        <v>14.5</v>
+      </c>
+      <c r="AI5">
+        <v>34</v>
+      </c>
+      <c r="AJ5">
+        <v>44</v>
+      </c>
+      <c r="AK5">
         <v>32</v>
       </c>
-      <c r="AF5">
-        <v>20</v>
-      </c>
-      <c r="AG5">
-        <v>13</v>
-      </c>
-      <c r="AH5">
+      <c r="AL5">
+        <v>36</v>
+      </c>
+      <c r="AM5">
+        <v>60</v>
+      </c>
+      <c r="AN5">
+        <v>15.5</v>
+      </c>
+      <c r="AO5">
+        <v>21</v>
+      </c>
+      <c r="AP5">
         <v>17</v>
       </c>
-      <c r="AI5">
-        <v>38</v>
-      </c>
-      <c r="AJ5">
-        <v>30</v>
-      </c>
-      <c r="AK5">
-        <v>23</v>
-      </c>
-      <c r="AL5">
-        <v>30</v>
-      </c>
-      <c r="AM5">
-        <v>65</v>
-      </c>
-      <c r="AN5">
-        <v>16</v>
-      </c>
-      <c r="AO5">
-        <v>25</v>
-      </c>
-      <c r="AP5">
-        <v>17.5</v>
-      </c>
       <c r="AQ5">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AR5">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="AS5">
         <v>36</v>
       </c>
       <c r="AT5">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AU5">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AV5">
         <v>10.5</v>
       </c>
       <c r="AW5">
-        <v>5.5</v>
+        <v>14.5</v>
       </c>
       <c r="AX5">
-        <v>13.5</v>
+        <v>17.5</v>
       </c>
       <c r="AY5">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AZ5">
         <v>11.5</v>
@@ -1834,82 +1834,82 @@
         <v>28</v>
       </c>
       <c r="BB5">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="BC5">
-        <v>19.5</v>
+        <v>11.5</v>
       </c>
       <c r="BD5">
-        <v>6</v>
+        <v>14.5</v>
       </c>
       <c r="BE5">
-        <v>6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF5">
-        <v>10.5</v>
+        <v>13.5</v>
       </c>
       <c r="BG5">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BH5">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BI5">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="BJ5">
         <v>8.800000000000001</v>
       </c>
       <c r="BK5">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BN5">
         <v>5.6</v>
       </c>
       <c r="BO5">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BP5">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BQ5">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BR5">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BS5">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT5">
         <v>6.6</v>
       </c>
       <c r="BU5">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BV5">
         <v>22</v>
       </c>
       <c r="BW5">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX5">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="BY5">
         <v>10</v>
       </c>
       <c r="BZ5">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="CA5">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="CB5" t="s">
         <v>118</v>
@@ -1932,13 +1932,13 @@
         <v>111</v>
       </c>
       <c r="F6">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="G6">
         <v>4.6</v>
       </c>
       <c r="H6">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="I6">
         <v>2.66</v>
@@ -1947,16 +1947,16 @@
         <v>2.7</v>
       </c>
       <c r="K6">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="L6">
-        <v>1.54</v>
+        <v>1.01</v>
       </c>
       <c r="M6">
         <v>1.13</v>
       </c>
       <c r="N6">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="O6">
         <v>1.51</v>
@@ -1974,10 +1974,10 @@
         <v>4.7</v>
       </c>
       <c r="T6">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="U6">
-        <v>1.56</v>
+        <v>1.64</v>
       </c>
       <c r="V6">
         <v>1.6</v>
@@ -1986,49 +1986,49 @@
         <v>1.28</v>
       </c>
       <c r="X6">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Y6">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Z6">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AA6">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB6">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AC6">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AD6">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AE6">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AF6">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AG6">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH6">
         <v>1000</v>
       </c>
       <c r="AI6">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AJ6">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK6">
-        <v>1000</v>
+        <v>300</v>
       </c>
       <c r="AL6">
-        <v>1000</v>
+        <v>420</v>
       </c>
       <c r="AM6">
         <v>1000</v>
@@ -2040,58 +2040,58 @@
         <v>1000</v>
       </c>
       <c r="AP6">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AQ6">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="AR6">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="AS6">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="AT6">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="AU6">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AV6">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="AW6">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="AX6">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="AY6">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="AZ6">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="BA6">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="BB6">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="BC6">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="BD6">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="BE6">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="BF6">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BG6">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BH6">
         <v>1000</v>
@@ -2177,16 +2177,16 @@
         <v>6.2</v>
       </c>
       <c r="G7">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="H7">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="I7">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="J7">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="K7">
         <v>6.2</v>
@@ -2201,7 +2201,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="O7">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="P7">
         <v>3.65</v>
@@ -2222,13 +2222,13 @@
         <v>2.7</v>
       </c>
       <c r="V7">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="W7">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="X7">
-        <v>950</v>
+        <v>120</v>
       </c>
       <c r="Y7">
         <v>21</v>
@@ -2252,7 +2252,7 @@
         <v>15.5</v>
       </c>
       <c r="AF7">
-        <v>80</v>
+        <v>450</v>
       </c>
       <c r="AG7">
         <v>950</v>
@@ -2267,22 +2267,22 @@
         <v>180</v>
       </c>
       <c r="AK7">
-        <v>85</v>
+        <v>400</v>
       </c>
       <c r="AL7">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="AM7">
-        <v>65</v>
+        <v>160</v>
       </c>
       <c r="AN7">
         <v>46</v>
       </c>
       <c r="AO7">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="AP7">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="AQ7">
         <v>15.5</v>
@@ -2306,10 +2306,10 @@
         <v>11.5</v>
       </c>
       <c r="AX7">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AY7">
-        <v>6.2</v>
+        <v>13</v>
       </c>
       <c r="AZ7">
         <v>14</v>
@@ -2318,10 +2318,10 @@
         <v>19</v>
       </c>
       <c r="BB7">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BC7">
-        <v>6.8</v>
+        <v>28</v>
       </c>
       <c r="BD7">
         <v>38</v>
@@ -2342,7 +2342,7 @@
         <v>5.2</v>
       </c>
       <c r="BJ7">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK7">
         <v>7.2</v>
@@ -2378,7 +2378,7 @@
         <v>4.4</v>
       </c>
       <c r="BV7">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BW7">
         <v>6.8</v>
@@ -2393,7 +2393,7 @@
         <v>8.4</v>
       </c>
       <c r="CA7">
-        <v>6.6</v>
+        <v>5.2</v>
       </c>
       <c r="CB7" t="s">
         <v>118</v>
@@ -2416,22 +2416,22 @@
         <v>113</v>
       </c>
       <c r="F8">
-        <v>1.47</v>
+        <v>3.2</v>
       </c>
       <c r="G8">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="H8">
         <v>1.72</v>
       </c>
       <c r="I8">
-        <v>90</v>
+        <v>2.92</v>
       </c>
       <c r="J8">
-        <v>1.1</v>
+        <v>2.72</v>
       </c>
       <c r="K8">
-        <v>950</v>
+        <v>7</v>
       </c>
       <c r="L8">
         <v>1.01</v>
@@ -2470,52 +2470,52 @@
         <v>1.01</v>
       </c>
       <c r="X8">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Y8">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Z8">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AA8">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB8">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AC8">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AD8">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AE8">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AF8">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AG8">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AH8">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI8">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="AJ8">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK8">
-        <v>1000</v>
+        <v>260</v>
       </c>
       <c r="AL8">
-        <v>1000</v>
+        <v>350</v>
       </c>
       <c r="AM8">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN8">
         <v>1000</v>
@@ -2524,58 +2524,58 @@
         <v>1000</v>
       </c>
       <c r="AP8">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AQ8">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="AR8">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="AS8">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="AT8">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="AU8">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AV8">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="AW8">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="AX8">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="AY8">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="AZ8">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="BA8">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="BB8">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="BC8">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="BD8">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="BE8">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="BF8">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BG8">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BH8">
         <v>1000</v>
@@ -2661,124 +2661,124 @@
         <v>2.04</v>
       </c>
       <c r="G9">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="H9">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="I9">
         <v>5.3</v>
       </c>
       <c r="J9">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="K9">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="L9">
-        <v>1.65</v>
+        <v>1.01</v>
       </c>
       <c r="M9">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="N9">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="O9">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="P9">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="Q9">
-        <v>2.96</v>
+        <v>3.15</v>
       </c>
       <c r="R9">
         <v>1.14</v>
       </c>
       <c r="S9">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="T9">
         <v>2.52</v>
       </c>
       <c r="U9">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="V9">
         <v>1.23</v>
       </c>
       <c r="W9">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="X9">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="Y9">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Z9">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="AA9">
-        <v>190</v>
+        <v>690</v>
       </c>
       <c r="AB9">
-        <v>6.6</v>
+        <v>5.8</v>
       </c>
       <c r="AC9">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="AD9">
+        <v>26</v>
+      </c>
+      <c r="AE9">
+        <v>690</v>
+      </c>
+      <c r="AF9">
+        <v>10.5</v>
+      </c>
+      <c r="AG9">
+        <v>13.5</v>
+      </c>
+      <c r="AH9">
+        <v>36</v>
+      </c>
+      <c r="AI9">
+        <v>690</v>
+      </c>
+      <c r="AJ9">
         <v>27</v>
       </c>
-      <c r="AE9">
-        <v>130</v>
-      </c>
-      <c r="AF9">
-        <v>12.5</v>
-      </c>
-      <c r="AG9">
-        <v>14.5</v>
-      </c>
-      <c r="AH9">
-        <v>38</v>
-      </c>
-      <c r="AI9">
-        <v>180</v>
-      </c>
-      <c r="AJ9">
-        <v>34</v>
-      </c>
       <c r="AK9">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AL9">
         <v>95</v>
       </c>
       <c r="AM9">
-        <v>380</v>
+        <v>500</v>
       </c>
       <c r="AN9">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="AO9">
-        <v>260</v>
+        <v>690</v>
       </c>
       <c r="AP9">
         <v>6.4</v>
       </c>
       <c r="AQ9">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AR9">
-        <v>4.6</v>
+        <v>21</v>
       </c>
       <c r="AS9">
-        <v>5.1</v>
+        <v>42</v>
       </c>
       <c r="AT9">
-        <v>2.92</v>
+        <v>5.3</v>
       </c>
       <c r="AU9">
         <v>6.8</v>
@@ -2787,76 +2787,76 @@
         <v>20</v>
       </c>
       <c r="AW9">
-        <v>5</v>
+        <v>38</v>
       </c>
       <c r="AX9">
         <v>9.4</v>
       </c>
       <c r="AY9">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AZ9">
-        <v>4.6</v>
+        <v>21</v>
       </c>
       <c r="BA9">
-        <v>5.1</v>
+        <v>44</v>
       </c>
       <c r="BB9">
-        <v>4.5</v>
+        <v>17</v>
       </c>
       <c r="BC9">
-        <v>4.6</v>
+        <v>22</v>
       </c>
       <c r="BD9">
-        <v>5</v>
+        <v>36</v>
       </c>
       <c r="BE9">
-        <v>5.2</v>
+        <v>100</v>
       </c>
       <c r="BF9">
-        <v>4.6</v>
+        <v>19.5</v>
       </c>
       <c r="BG9">
-        <v>5.1</v>
+        <v>48</v>
       </c>
       <c r="BH9">
         <v>1000</v>
       </c>
       <c r="BI9">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="BJ9">
         <v>18</v>
       </c>
       <c r="BK9">
-        <v>8.4</v>
+        <v>1.33</v>
       </c>
       <c r="BL9">
         <v>1000</v>
       </c>
       <c r="BM9">
-        <v>21</v>
+        <v>1.44</v>
       </c>
       <c r="BN9">
         <v>5.9</v>
       </c>
       <c r="BO9">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="BP9">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BQ9">
-        <v>12</v>
+        <v>1.36</v>
       </c>
       <c r="BR9">
         <v>1000</v>
       </c>
       <c r="BS9">
-        <v>21</v>
+        <v>1.41</v>
       </c>
       <c r="BT9">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BU9">
         <v>5.4</v>
@@ -2865,19 +2865,19 @@
         <v>1000</v>
       </c>
       <c r="BW9">
-        <v>21</v>
+        <v>1.41</v>
       </c>
       <c r="BX9">
         <v>1000</v>
       </c>
       <c r="BY9">
-        <v>21</v>
+        <v>1.44</v>
       </c>
       <c r="BZ9">
         <v>1000</v>
       </c>
       <c r="CA9">
-        <v>21</v>
+        <v>1.41</v>
       </c>
       <c r="CB9" t="s">
         <v>118</v>
@@ -2900,16 +2900,16 @@
         <v>115</v>
       </c>
       <c r="F10">
-        <v>2.14</v>
+        <v>2.08</v>
       </c>
       <c r="G10">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="H10">
         <v>4.6</v>
       </c>
       <c r="I10">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="J10">
         <v>3.05</v>
@@ -2924,10 +2924,10 @@
         <v>1.15</v>
       </c>
       <c r="N10">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="O10">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="P10">
         <v>1.47</v>
@@ -2942,25 +2942,25 @@
         <v>6.2</v>
       </c>
       <c r="T10">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="U10">
         <v>1.66</v>
       </c>
       <c r="V10">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="W10">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="X10">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="Y10">
         <v>11.5</v>
       </c>
       <c r="Z10">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AA10">
         <v>1000</v>
@@ -2972,10 +2972,10 @@
         <v>7.6</v>
       </c>
       <c r="AD10">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AE10">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AF10">
         <v>11</v>
@@ -2984,7 +2984,7 @@
         <v>13</v>
       </c>
       <c r="AH10">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AI10">
         <v>1000</v>
@@ -2999,7 +2999,7 @@
         <v>75</v>
       </c>
       <c r="AM10">
-        <v>320</v>
+        <v>500</v>
       </c>
       <c r="AN10">
         <v>32</v>
@@ -3008,16 +3008,16 @@
         <v>1000</v>
       </c>
       <c r="AP10">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="AQ10">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AR10">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="AS10">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AT10">
         <v>5.7</v>
@@ -3026,43 +3026,43 @@
         <v>6.8</v>
       </c>
       <c r="AV10">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AW10">
         <v>36</v>
       </c>
       <c r="AX10">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AY10">
         <v>11</v>
       </c>
       <c r="AZ10">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="BA10">
         <v>42</v>
       </c>
       <c r="BB10">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="BC10">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BD10">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BE10">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="BF10">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="BG10">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BH10">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="BI10">
         <v>2.3</v>
@@ -3080,16 +3080,16 @@
         <v>11</v>
       </c>
       <c r="BN10">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BO10">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="BP10">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BQ10">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BR10">
         <v>1000</v>
@@ -3098,7 +3098,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BT10">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BU10">
         <v>5.5</v>
@@ -3110,7 +3110,7 @@
         <v>9.6</v>
       </c>
       <c r="BX10">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="BY10">
         <v>10</v>
@@ -3142,7 +3142,7 @@
         <v>116</v>
       </c>
       <c r="F11">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="G11">
         <v>1.66</v>
@@ -3166,16 +3166,16 @@
         <v>1.11</v>
       </c>
       <c r="N11">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="O11">
         <v>1.47</v>
       </c>
       <c r="P11">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="Q11">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="R11">
         <v>1.22</v>
@@ -3187,7 +3187,7 @@
         <v>2.36</v>
       </c>
       <c r="U11">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="V11">
         <v>1.13</v>
@@ -3196,13 +3196,13 @@
         <v>2.5</v>
       </c>
       <c r="X11">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="Y11">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="Z11">
-        <v>85</v>
+        <v>400</v>
       </c>
       <c r="AA11">
         <v>410</v>
@@ -3214,16 +3214,16 @@
         <v>11</v>
       </c>
       <c r="AD11">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AE11">
         <v>210</v>
       </c>
       <c r="AF11">
-        <v>9.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AG11">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AH11">
         <v>38</v>
@@ -3238,10 +3238,10 @@
         <v>27</v>
       </c>
       <c r="AL11">
-        <v>75</v>
+        <v>290</v>
       </c>
       <c r="AM11">
-        <v>320</v>
+        <v>700</v>
       </c>
       <c r="AN11">
         <v>17</v>
@@ -3253,25 +3253,25 @@
         <v>7.6</v>
       </c>
       <c r="AQ11">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AR11">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="AS11">
-        <v>5.1</v>
+        <v>6.4</v>
       </c>
       <c r="AT11">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="AU11">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AV11">
-        <v>4.5</v>
+        <v>14.5</v>
       </c>
       <c r="AW11">
-        <v>5</v>
+        <v>6.2</v>
       </c>
       <c r="AX11">
         <v>6.2</v>
@@ -3280,10 +3280,10 @@
         <v>8</v>
       </c>
       <c r="AZ11">
-        <v>4.5</v>
+        <v>14.5</v>
       </c>
       <c r="BA11">
-        <v>5</v>
+        <v>6.2</v>
       </c>
       <c r="BB11">
         <v>11</v>
@@ -3292,16 +3292,16 @@
         <v>15.5</v>
       </c>
       <c r="BD11">
-        <v>4.8</v>
+        <v>5.9</v>
       </c>
       <c r="BE11">
-        <v>5.1</v>
+        <v>6.4</v>
       </c>
       <c r="BF11">
         <v>10.5</v>
       </c>
       <c r="BG11">
-        <v>5.1</v>
+        <v>6.4</v>
       </c>
       <c r="BH11">
         <v>2.98</v>
@@ -3387,16 +3387,16 @@
         <v>4.4</v>
       </c>
       <c r="G12">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="H12">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="I12">
         <v>2.12</v>
       </c>
       <c r="J12">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K12">
         <v>3.4</v>
@@ -3408,7 +3408,7 @@
         <v>1.11</v>
       </c>
       <c r="N12">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="O12">
         <v>1.48</v>
@@ -3423,7 +3423,7 @@
         <v>1.22</v>
       </c>
       <c r="S12">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="T12">
         <v>2.1</v>
@@ -3435,13 +3435,13 @@
         <v>1.89</v>
       </c>
       <c r="W12">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="X12">
         <v>12</v>
       </c>
       <c r="Y12">
-        <v>8.4</v>
+        <v>7.2</v>
       </c>
       <c r="Z12">
         <v>14</v>
@@ -3456,7 +3456,7 @@
         <v>7.6</v>
       </c>
       <c r="AD12">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AE12">
         <v>32</v>
@@ -3471,25 +3471,25 @@
         <v>28</v>
       </c>
       <c r="AI12">
-        <v>65</v>
+        <v>290</v>
       </c>
       <c r="AJ12">
-        <v>150</v>
+        <v>900</v>
       </c>
       <c r="AK12">
-        <v>90</v>
+        <v>200</v>
       </c>
       <c r="AL12">
-        <v>110</v>
+        <v>380</v>
       </c>
       <c r="AM12">
-        <v>200</v>
+        <v>580</v>
       </c>
       <c r="AN12">
-        <v>130</v>
+        <v>500</v>
       </c>
       <c r="AO12">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AP12">
         <v>8.6</v>
@@ -3501,7 +3501,7 @@
         <v>10</v>
       </c>
       <c r="AS12">
-        <v>4.5</v>
+        <v>11.5</v>
       </c>
       <c r="AT12">
         <v>9.4</v>
@@ -3513,34 +3513,34 @@
         <v>9.6</v>
       </c>
       <c r="AW12">
-        <v>4.5</v>
+        <v>13</v>
       </c>
       <c r="AX12">
-        <v>4.6</v>
+        <v>14.5</v>
       </c>
       <c r="AY12">
-        <v>14</v>
+        <v>10.5</v>
       </c>
       <c r="AZ12">
-        <v>4.4</v>
+        <v>11.5</v>
       </c>
       <c r="BA12">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="BB12">
-        <v>5</v>
+        <v>5.9</v>
       </c>
       <c r="BC12">
-        <v>4.9</v>
+        <v>5.7</v>
       </c>
       <c r="BD12">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="BE12">
-        <v>5.1</v>
+        <v>5.9</v>
       </c>
       <c r="BF12">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="BG12">
         <v>16.5</v>
@@ -3549,19 +3549,19 @@
         <v>2.86</v>
       </c>
       <c r="BI12">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="BJ12">
         <v>11.5</v>
       </c>
       <c r="BK12">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BL12">
         <v>1000</v>
       </c>
       <c r="BM12">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="BN12">
         <v>7.8</v>
@@ -3573,37 +3573,37 @@
         <v>1000</v>
       </c>
       <c r="BQ12">
+        <v>11.5</v>
+      </c>
+      <c r="BR12">
+        <v>1000</v>
+      </c>
+      <c r="BS12">
         <v>12.5</v>
       </c>
-      <c r="BR12">
-        <v>1000</v>
-      </c>
-      <c r="BS12">
-        <v>13.5</v>
-      </c>
       <c r="BT12">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BU12">
         <v>3.55</v>
       </c>
       <c r="BV12">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="BW12">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BX12">
         <v>1000</v>
       </c>
       <c r="BY12">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BZ12">
         <v>1000</v>
       </c>
       <c r="CA12">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="CB12" t="s">
         <v>118</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-28.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-28.xlsx
@@ -370,7 +370,7 @@
     <t>Athletic Club</t>
   </si>
   <si>
-    <t>2026-07-27 19:35:21</t>
+    <t>2026-07-27 21:42:38</t>
   </si>
 </sst>
 </file>
@@ -964,226 +964,226 @@
         <v>107</v>
       </c>
       <c r="F2">
-        <v>2.4</v>
+        <v>1.37</v>
       </c>
       <c r="G2">
-        <v>2.48</v>
+        <v>1.4</v>
       </c>
       <c r="H2">
-        <v>3.55</v>
+        <v>14</v>
       </c>
       <c r="I2">
-        <v>3.7</v>
+        <v>15.5</v>
       </c>
       <c r="J2">
-        <v>3.15</v>
+        <v>4.6</v>
       </c>
       <c r="K2">
-        <v>3.25</v>
+        <v>4.9</v>
       </c>
       <c r="L2">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="M2">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="N2">
-        <v>2.8</v>
+        <v>4.4</v>
       </c>
       <c r="O2">
-        <v>1.54</v>
+        <v>1.27</v>
       </c>
       <c r="P2">
-        <v>1.59</v>
+        <v>1.74</v>
       </c>
       <c r="Q2">
-        <v>2.66</v>
+        <v>2.26</v>
       </c>
       <c r="R2">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="S2">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="T2">
-        <v>2.08</v>
+        <v>1.96</v>
       </c>
       <c r="U2">
-        <v>1.81</v>
+        <v>1.9</v>
       </c>
       <c r="V2">
-        <v>1.37</v>
+        <v>1.07</v>
       </c>
       <c r="W2">
-        <v>1.68</v>
+        <v>3.5</v>
       </c>
       <c r="X2">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="Y2">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="Z2">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AA2">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AB2">
-        <v>7.6</v>
+        <v>4.5</v>
       </c>
       <c r="AC2">
-        <v>7.4</v>
+        <v>6.2</v>
       </c>
       <c r="AD2">
-        <v>16.5</v>
+        <v>23</v>
       </c>
       <c r="AE2">
+        <v>170</v>
+      </c>
+      <c r="AF2">
+        <v>5.6</v>
+      </c>
+      <c r="AG2">
+        <v>8.6</v>
+      </c>
+      <c r="AH2">
+        <v>30</v>
+      </c>
+      <c r="AI2">
+        <v>170</v>
+      </c>
+      <c r="AJ2">
+        <v>15</v>
+      </c>
+      <c r="AK2">
+        <v>22</v>
+      </c>
+      <c r="AL2">
+        <v>90</v>
+      </c>
+      <c r="AM2">
+        <v>400</v>
+      </c>
+      <c r="AN2">
+        <v>29</v>
+      </c>
+      <c r="AO2">
+        <v>510</v>
+      </c>
+      <c r="AP2">
+        <v>15.5</v>
+      </c>
+      <c r="AQ2">
+        <v>15.5</v>
+      </c>
+      <c r="AR2">
+        <v>15.5</v>
+      </c>
+      <c r="AS2">
+        <v>15.5</v>
+      </c>
+      <c r="AT2">
+        <v>4</v>
+      </c>
+      <c r="AU2">
+        <v>5.8</v>
+      </c>
+      <c r="AV2">
+        <v>19</v>
+      </c>
+      <c r="AW2">
+        <v>95</v>
+      </c>
+      <c r="AX2">
+        <v>5.2</v>
+      </c>
+      <c r="AY2">
+        <v>7.8</v>
+      </c>
+      <c r="AZ2">
+        <v>21</v>
+      </c>
+      <c r="BA2">
+        <v>110</v>
+      </c>
+      <c r="BB2">
+        <v>12.5</v>
+      </c>
+      <c r="BC2">
+        <v>18.5</v>
+      </c>
+      <c r="BD2">
         <v>60</v>
       </c>
-      <c r="AF2">
-        <v>14</v>
-      </c>
-      <c r="AG2">
-        <v>12</v>
-      </c>
-      <c r="AH2">
-        <v>23</v>
-      </c>
-      <c r="AI2">
-        <v>80</v>
-      </c>
-      <c r="AJ2">
-        <v>38</v>
-      </c>
-      <c r="AK2">
-        <v>34</v>
-      </c>
-      <c r="AL2">
-        <v>75</v>
-      </c>
-      <c r="AM2">
+      <c r="BE2">
         <v>220</v>
       </c>
-      <c r="AN2">
-        <v>36</v>
-      </c>
-      <c r="AO2">
-        <v>80</v>
-      </c>
-      <c r="AP2">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AQ2">
-        <v>9.4</v>
-      </c>
-      <c r="AR2">
-        <v>21</v>
-      </c>
-      <c r="AS2">
-        <v>65</v>
-      </c>
-      <c r="AT2">
-        <v>7</v>
-      </c>
-      <c r="AU2">
-        <v>6.6</v>
-      </c>
-      <c r="AV2">
-        <v>14</v>
-      </c>
-      <c r="AW2">
-        <v>50</v>
-      </c>
-      <c r="AX2">
-        <v>12</v>
-      </c>
-      <c r="AY2">
-        <v>11</v>
-      </c>
-      <c r="AZ2">
-        <v>20</v>
-      </c>
-      <c r="BA2">
-        <v>60</v>
-      </c>
-      <c r="BB2">
-        <v>30</v>
-      </c>
-      <c r="BC2">
-        <v>27</v>
-      </c>
-      <c r="BD2">
-        <v>50</v>
-      </c>
-      <c r="BE2">
-        <v>18</v>
-      </c>
       <c r="BF2">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="BG2">
-        <v>55</v>
+        <v>180</v>
       </c>
       <c r="BH2">
-        <v>2.74</v>
+        <v>1000</v>
       </c>
       <c r="BI2">
-        <v>2.38</v>
+        <v>1.25</v>
       </c>
       <c r="BJ2">
-        <v>11</v>
+        <v>970</v>
       </c>
       <c r="BK2">
-        <v>8.199999999999999</v>
+        <v>1.25</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>16.5</v>
+        <v>1.25</v>
       </c>
       <c r="BN2">
-        <v>5.1</v>
+        <v>1.23</v>
       </c>
       <c r="BO2">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="BP2">
-        <v>21</v>
+        <v>880</v>
       </c>
       <c r="BQ2">
-        <v>9.800000000000001</v>
+        <v>2.02</v>
       </c>
       <c r="BR2">
-        <v>44</v>
+        <v>910</v>
       </c>
       <c r="BS2">
-        <v>12.5</v>
+        <v>1.25</v>
       </c>
       <c r="BT2">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="BU2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="BV2">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BW2">
-        <v>12</v>
+        <v>1.25</v>
       </c>
       <c r="BX2">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BY2">
-        <v>13.5</v>
+        <v>1.25</v>
       </c>
       <c r="BZ2">
-        <v>48</v>
+        <v>830</v>
       </c>
       <c r="CA2">
-        <v>13</v>
+        <v>1.25</v>
       </c>
       <c r="CB2" t="s">
         <v>118</v>
@@ -1206,226 +1206,226 @@
         <v>108</v>
       </c>
       <c r="F3">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="G3">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="H3">
-        <v>2.3</v>
+        <v>2.16</v>
       </c>
       <c r="I3">
-        <v>2.4</v>
+        <v>2.26</v>
       </c>
       <c r="J3">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="K3">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="L3">
-        <v>1.54</v>
+        <v>1.84</v>
       </c>
       <c r="M3">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="N3">
-        <v>2.86</v>
+        <v>2.52</v>
       </c>
       <c r="O3">
+        <v>1.62</v>
+      </c>
+      <c r="P3">
         <v>1.5</v>
       </c>
-      <c r="P3">
-        <v>1.62</v>
-      </c>
       <c r="Q3">
-        <v>2.48</v>
+        <v>2.88</v>
       </c>
       <c r="R3">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="S3">
-        <v>5</v>
+        <v>6.2</v>
       </c>
       <c r="T3">
-        <v>1.98</v>
+        <v>2.24</v>
       </c>
       <c r="U3">
-        <v>1.86</v>
+        <v>1.7</v>
       </c>
       <c r="V3">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="W3">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="X3">
-        <v>9.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="Y3">
-        <v>8.4</v>
+        <v>6.8</v>
       </c>
       <c r="Z3">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AA3">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AB3">
         <v>11.5</v>
       </c>
       <c r="AC3">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AD3">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AE3">
+        <v>34</v>
+      </c>
+      <c r="AF3">
         <v>32</v>
       </c>
-      <c r="AF3">
-        <v>27</v>
-      </c>
       <c r="AG3">
-        <v>16.5</v>
+        <v>20</v>
       </c>
       <c r="AH3">
+        <v>28</v>
+      </c>
+      <c r="AI3">
+        <v>75</v>
+      </c>
+      <c r="AJ3">
+        <v>130</v>
+      </c>
+      <c r="AK3">
+        <v>85</v>
+      </c>
+      <c r="AL3">
+        <v>120</v>
+      </c>
+      <c r="AM3">
+        <v>250</v>
+      </c>
+      <c r="AN3">
+        <v>150</v>
+      </c>
+      <c r="AO3">
+        <v>38</v>
+      </c>
+      <c r="AP3">
+        <v>7.2</v>
+      </c>
+      <c r="AQ3">
+        <v>6.2</v>
+      </c>
+      <c r="AR3">
+        <v>10</v>
+      </c>
+      <c r="AS3">
         <v>22</v>
       </c>
-      <c r="AI3">
-        <v>70</v>
-      </c>
-      <c r="AJ3">
-        <v>170</v>
-      </c>
-      <c r="AK3">
-        <v>80</v>
-      </c>
-      <c r="AL3">
-        <v>100</v>
-      </c>
-      <c r="AM3">
-        <v>180</v>
-      </c>
-      <c r="AN3">
-        <v>100</v>
-      </c>
-      <c r="AO3">
-        <v>32</v>
-      </c>
-      <c r="AP3">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AQ3">
-        <v>7.2</v>
-      </c>
-      <c r="AR3">
-        <v>12</v>
-      </c>
-      <c r="AS3">
-        <v>23</v>
-      </c>
       <c r="AT3">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AU3">
         <v>6.4</v>
       </c>
       <c r="AV3">
+        <v>10.5</v>
+      </c>
+      <c r="AW3">
+        <v>24</v>
+      </c>
+      <c r="AX3">
+        <v>23</v>
+      </c>
+      <c r="AY3">
+        <v>13.5</v>
+      </c>
+      <c r="AZ3">
+        <v>23</v>
+      </c>
+      <c r="BA3">
         <v>10</v>
       </c>
-      <c r="AW3">
-        <v>23</v>
-      </c>
-      <c r="AX3">
-        <v>22</v>
-      </c>
-      <c r="AY3">
+      <c r="BB3">
+        <v>11</v>
+      </c>
+      <c r="BC3">
+        <v>10.5</v>
+      </c>
+      <c r="BD3">
+        <v>10.5</v>
+      </c>
+      <c r="BE3">
+        <v>11</v>
+      </c>
+      <c r="BF3">
+        <v>11</v>
+      </c>
+      <c r="BG3">
+        <v>21</v>
+      </c>
+      <c r="BH3">
+        <v>2.24</v>
+      </c>
+      <c r="BI3">
+        <v>2.12</v>
+      </c>
+      <c r="BJ3">
+        <v>16</v>
+      </c>
+      <c r="BK3">
+        <v>13.5</v>
+      </c>
+      <c r="BL3">
+        <v>960</v>
+      </c>
+      <c r="BM3">
         <v>14</v>
       </c>
-      <c r="AZ3">
-        <v>18</v>
-      </c>
-      <c r="BA3">
-        <v>42</v>
-      </c>
-      <c r="BB3">
-        <v>26</v>
-      </c>
-      <c r="BC3">
-        <v>34</v>
-      </c>
-      <c r="BD3">
-        <v>9.6</v>
-      </c>
-      <c r="BE3">
-        <v>10</v>
-      </c>
-      <c r="BF3">
-        <v>42</v>
-      </c>
-      <c r="BG3">
-        <v>9.4</v>
-      </c>
-      <c r="BH3">
-        <v>2.86</v>
-      </c>
-      <c r="BI3">
-        <v>2.38</v>
-      </c>
-      <c r="BJ3">
-        <v>11.5</v>
-      </c>
-      <c r="BK3">
-        <v>8.4</v>
-      </c>
-      <c r="BL3">
-        <v>1000</v>
-      </c>
-      <c r="BM3">
-        <v>12.5</v>
-      </c>
       <c r="BN3">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="BO3">
-        <v>5.7</v>
+        <v>6.8</v>
       </c>
       <c r="BP3">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BQ3">
-        <v>9.800000000000001</v>
+        <v>30</v>
       </c>
       <c r="BR3">
-        <v>75</v>
+        <v>910</v>
       </c>
       <c r="BS3">
-        <v>10.5</v>
+        <v>80</v>
       </c>
       <c r="BT3">
         <v>5</v>
       </c>
       <c r="BU3">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BV3">
-        <v>19.5</v>
+        <v>23</v>
       </c>
       <c r="BW3">
-        <v>7.8</v>
+        <v>19</v>
       </c>
       <c r="BX3">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BY3">
-        <v>10</v>
+        <v>55</v>
       </c>
       <c r="BZ3">
-        <v>1000</v>
+        <v>860</v>
       </c>
       <c r="CA3">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="CB3" t="s">
         <v>118</v>
@@ -1493,7 +1493,7 @@
         <v>1.65</v>
       </c>
       <c r="U4">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="V4">
         <v>1.76</v>
@@ -1610,13 +1610,13 @@
         <v>10</v>
       </c>
       <c r="BH4">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="BI4">
         <v>3.5</v>
       </c>
       <c r="BJ4">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK4">
         <v>5.7</v>
@@ -1625,7 +1625,7 @@
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BN4">
         <v>6.8</v>
@@ -1637,13 +1637,13 @@
         <v>25</v>
       </c>
       <c r="BQ4">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BR4">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BS4">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BT4">
         <v>5.3</v>
@@ -1652,7 +1652,7 @@
         <v>4.7</v>
       </c>
       <c r="BV4">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BW4">
         <v>7.8</v>
@@ -1661,7 +1661,7 @@
         <v>26</v>
       </c>
       <c r="BY4">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BZ4">
         <v>0</v>
@@ -1693,16 +1693,16 @@
         <v>2.44</v>
       </c>
       <c r="G5">
-        <v>2.7</v>
+        <v>2.58</v>
       </c>
       <c r="H5">
-        <v>2.9</v>
+        <v>2.98</v>
       </c>
       <c r="I5">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="J5">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="K5">
         <v>3.85</v>
@@ -1714,7 +1714,7 @@
         <v>1.05</v>
       </c>
       <c r="N5">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="O5">
         <v>1.22</v>
@@ -1729,7 +1729,7 @@
         <v>1.53</v>
       </c>
       <c r="S5">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="T5">
         <v>1.58</v>
@@ -1738,13 +1738,13 @@
         <v>2.54</v>
       </c>
       <c r="V5">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="W5">
-        <v>1.59</v>
+        <v>1.63</v>
       </c>
       <c r="X5">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="Y5">
         <v>16</v>
@@ -1753,7 +1753,7 @@
         <v>23</v>
       </c>
       <c r="AA5">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="AB5">
         <v>15.5</v>
@@ -1762,10 +1762,10 @@
         <v>8.6</v>
       </c>
       <c r="AD5">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AE5">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="AF5">
         <v>21</v>
@@ -1777,7 +1777,7 @@
         <v>14.5</v>
       </c>
       <c r="AI5">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AJ5">
         <v>44</v>
@@ -1786,13 +1786,13 @@
         <v>32</v>
       </c>
       <c r="AL5">
-        <v>36</v>
+        <v>80</v>
       </c>
       <c r="AM5">
-        <v>60</v>
+        <v>200</v>
       </c>
       <c r="AN5">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AO5">
         <v>21</v>
@@ -1801,10 +1801,10 @@
         <v>17</v>
       </c>
       <c r="AQ5">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AR5">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AS5">
         <v>36</v>
@@ -1813,7 +1813,7 @@
         <v>13</v>
       </c>
       <c r="AU5">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AV5">
         <v>10.5</v>
@@ -1822,34 +1822,34 @@
         <v>14.5</v>
       </c>
       <c r="AX5">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AY5">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AZ5">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BA5">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="BB5">
         <v>16</v>
       </c>
       <c r="BC5">
-        <v>11.5</v>
+        <v>21</v>
       </c>
       <c r="BD5">
         <v>14.5</v>
       </c>
       <c r="BE5">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF5">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BG5">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BH5">
         <v>4</v>
@@ -1941,16 +1941,16 @@
         <v>2.36</v>
       </c>
       <c r="I6">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="J6">
-        <v>2.7</v>
+        <v>2.84</v>
       </c>
       <c r="K6">
         <v>3.15</v>
       </c>
       <c r="L6">
-        <v>1.01</v>
+        <v>1.56</v>
       </c>
       <c r="M6">
         <v>1.13</v>
@@ -1983,7 +1983,7 @@
         <v>1.6</v>
       </c>
       <c r="W6">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="X6">
         <v>970</v>
@@ -1992,7 +1992,7 @@
         <v>950</v>
       </c>
       <c r="Z6">
-        <v>160</v>
+        <v>500</v>
       </c>
       <c r="AA6">
         <v>900</v>
@@ -2007,85 +2007,85 @@
         <v>970</v>
       </c>
       <c r="AE6">
-        <v>180</v>
+        <v>500</v>
       </c>
       <c r="AF6">
-        <v>130</v>
+        <v>500</v>
       </c>
       <c r="AG6">
         <v>970</v>
       </c>
       <c r="AH6">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI6">
-        <v>230</v>
+        <v>500</v>
       </c>
       <c r="AJ6">
         <v>900</v>
       </c>
       <c r="AK6">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="AL6">
-        <v>420</v>
+        <v>500</v>
       </c>
       <c r="AM6">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN6">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AO6">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AP6">
         <v>4.9</v>
       </c>
       <c r="AQ6">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AR6">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AS6">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AT6">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AU6">
         <v>4.2</v>
       </c>
       <c r="AV6">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AW6">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AX6">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AY6">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AZ6">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="BA6">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="BB6">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="BC6">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="BD6">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="BE6">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="BF6">
         <v>1.55</v>
@@ -2416,22 +2416,22 @@
         <v>113</v>
       </c>
       <c r="F8">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="G8">
         <v>80</v>
       </c>
       <c r="H8">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="I8">
-        <v>2.92</v>
+        <v>2.74</v>
       </c>
       <c r="J8">
-        <v>2.72</v>
+        <v>2.9</v>
       </c>
       <c r="K8">
-        <v>7</v>
+        <v>3.95</v>
       </c>
       <c r="L8">
         <v>1.01</v>
@@ -2476,7 +2476,7 @@
         <v>950</v>
       </c>
       <c r="Z8">
-        <v>160</v>
+        <v>500</v>
       </c>
       <c r="AA8">
         <v>900</v>
@@ -2491,10 +2491,10 @@
         <v>950</v>
       </c>
       <c r="AE8">
-        <v>180</v>
+        <v>500</v>
       </c>
       <c r="AF8">
-        <v>160</v>
+        <v>500</v>
       </c>
       <c r="AG8">
         <v>950</v>
@@ -2503,25 +2503,25 @@
         <v>950</v>
       </c>
       <c r="AI8">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="AJ8">
         <v>900</v>
       </c>
       <c r="AK8">
-        <v>260</v>
+        <v>500</v>
       </c>
       <c r="AL8">
-        <v>350</v>
+        <v>500</v>
       </c>
       <c r="AM8">
         <v>580</v>
       </c>
       <c r="AN8">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AO8">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AP8">
         <v>4.9</v>
@@ -2530,31 +2530,31 @@
         <v>1.31</v>
       </c>
       <c r="AR8">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AS8">
+        <v>1.34</v>
+      </c>
+      <c r="AT8">
         <v>1.33</v>
-      </c>
-      <c r="AT8">
-        <v>1.32</v>
       </c>
       <c r="AU8">
         <v>4.4</v>
       </c>
       <c r="AV8">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AW8">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AX8">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AY8">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AZ8">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="BA8">
         <v>1.34</v>
@@ -2566,10 +2566,10 @@
         <v>1.34</v>
       </c>
       <c r="BD8">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="BE8">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="BF8">
         <v>1.55</v>
@@ -2658,16 +2658,16 @@
         <v>114</v>
       </c>
       <c r="F9">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="G9">
         <v>2.14</v>
       </c>
       <c r="H9">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="I9">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J9">
         <v>3</v>
@@ -2682,58 +2682,58 @@
         <v>1.16</v>
       </c>
       <c r="N9">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="O9">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="P9">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="Q9">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="R9">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="S9">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="T9">
-        <v>2.52</v>
+        <v>2.44</v>
       </c>
       <c r="U9">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="V9">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="W9">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="X9">
         <v>7.6</v>
       </c>
       <c r="Y9">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="Z9">
-        <v>60</v>
+        <v>34</v>
       </c>
       <c r="AA9">
         <v>690</v>
       </c>
       <c r="AB9">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AC9">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AD9">
         <v>26</v>
       </c>
       <c r="AE9">
-        <v>690</v>
+        <v>250</v>
       </c>
       <c r="AF9">
         <v>10.5</v>
@@ -2742,16 +2742,16 @@
         <v>13.5</v>
       </c>
       <c r="AH9">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AI9">
         <v>690</v>
       </c>
       <c r="AJ9">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="AK9">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AL9">
         <v>95</v>
@@ -2760,7 +2760,7 @@
         <v>500</v>
       </c>
       <c r="AN9">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="AO9">
         <v>690</v>
@@ -2772,28 +2772,28 @@
         <v>10</v>
       </c>
       <c r="AR9">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AS9">
         <v>42</v>
       </c>
       <c r="AT9">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="AU9">
         <v>6.8</v>
       </c>
       <c r="AV9">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AW9">
         <v>38</v>
       </c>
       <c r="AX9">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY9">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AZ9">
         <v>21</v>
@@ -2817,25 +2817,25 @@
         <v>19.5</v>
       </c>
       <c r="BG9">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="BH9">
         <v>1000</v>
       </c>
       <c r="BI9">
-        <v>1.44</v>
+        <v>1.65</v>
       </c>
       <c r="BJ9">
         <v>18</v>
       </c>
       <c r="BK9">
-        <v>1.33</v>
+        <v>1.51</v>
       </c>
       <c r="BL9">
         <v>1000</v>
       </c>
       <c r="BM9">
-        <v>1.44</v>
+        <v>1.65</v>
       </c>
       <c r="BN9">
         <v>5.9</v>
@@ -2847,16 +2847,16 @@
         <v>25</v>
       </c>
       <c r="BQ9">
-        <v>1.36</v>
+        <v>1.55</v>
       </c>
       <c r="BR9">
         <v>1000</v>
       </c>
       <c r="BS9">
-        <v>1.41</v>
+        <v>1.61</v>
       </c>
       <c r="BT9">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BU9">
         <v>5.4</v>
@@ -2865,19 +2865,19 @@
         <v>1000</v>
       </c>
       <c r="BW9">
-        <v>1.41</v>
+        <v>1.62</v>
       </c>
       <c r="BX9">
         <v>1000</v>
       </c>
       <c r="BY9">
-        <v>1.44</v>
+        <v>1.65</v>
       </c>
       <c r="BZ9">
         <v>1000</v>
       </c>
       <c r="CA9">
-        <v>1.41</v>
+        <v>1.62</v>
       </c>
       <c r="CB9" t="s">
         <v>118</v>
@@ -2900,19 +2900,19 @@
         <v>115</v>
       </c>
       <c r="F10">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="G10">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="H10">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="I10">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="J10">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="K10">
         <v>3.15</v>
@@ -2927,10 +2927,10 @@
         <v>2.46</v>
       </c>
       <c r="O10">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="P10">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="Q10">
         <v>2.88</v>
@@ -2942,40 +2942,40 @@
         <v>6.2</v>
       </c>
       <c r="T10">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="U10">
         <v>1.66</v>
       </c>
       <c r="V10">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="W10">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="X10">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y10">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Z10">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AA10">
-        <v>1000</v>
+        <v>690</v>
       </c>
       <c r="AB10">
         <v>6.4</v>
       </c>
       <c r="AC10">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD10">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AE10">
-        <v>700</v>
+        <v>220</v>
       </c>
       <c r="AF10">
         <v>11</v>
@@ -2987,43 +2987,43 @@
         <v>30</v>
       </c>
       <c r="AI10">
-        <v>1000</v>
+        <v>530</v>
       </c>
       <c r="AJ10">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AK10">
         <v>34</v>
       </c>
       <c r="AL10">
-        <v>75</v>
+        <v>150</v>
       </c>
       <c r="AM10">
         <v>500</v>
       </c>
       <c r="AN10">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AO10">
-        <v>1000</v>
+        <v>690</v>
       </c>
       <c r="AP10">
         <v>6.8</v>
       </c>
       <c r="AQ10">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AR10">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AS10">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AT10">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AU10">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AV10">
         <v>18</v>
@@ -3032,7 +3032,7 @@
         <v>36</v>
       </c>
       <c r="AX10">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AY10">
         <v>11</v>
@@ -3047,7 +3047,7 @@
         <v>22</v>
       </c>
       <c r="BC10">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BD10">
         <v>34</v>
@@ -3056,13 +3056,13 @@
         <v>100</v>
       </c>
       <c r="BF10">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="BG10">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BH10">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="BI10">
         <v>2.3</v>
@@ -3080,37 +3080,37 @@
         <v>11</v>
       </c>
       <c r="BN10">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BO10">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="BP10">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BQ10">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BR10">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BS10">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BT10">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BU10">
         <v>5.5</v>
       </c>
       <c r="BV10">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BW10">
         <v>9.6</v>
       </c>
       <c r="BX10">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="BY10">
         <v>10</v>
@@ -3142,19 +3142,19 @@
         <v>116</v>
       </c>
       <c r="F11">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="G11">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="H11">
         <v>7.6</v>
       </c>
       <c r="I11">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J11">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K11">
         <v>3.9</v>
@@ -3166,16 +3166,16 @@
         <v>1.11</v>
       </c>
       <c r="N11">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="O11">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="P11">
         <v>1.63</v>
       </c>
       <c r="Q11">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="R11">
         <v>1.22</v>
@@ -3184,31 +3184,31 @@
         <v>4.8</v>
       </c>
       <c r="T11">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="U11">
         <v>1.66</v>
       </c>
       <c r="V11">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="W11">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="X11">
         <v>10.5</v>
       </c>
       <c r="Y11">
-        <v>19.5</v>
+        <v>970</v>
       </c>
       <c r="Z11">
         <v>400</v>
       </c>
       <c r="AA11">
-        <v>410</v>
+        <v>400</v>
       </c>
       <c r="AB11">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AC11">
         <v>11</v>
@@ -3253,16 +3253,16 @@
         <v>7.6</v>
       </c>
       <c r="AQ11">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AR11">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="AS11">
         <v>6.4</v>
       </c>
       <c r="AT11">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="AU11">
         <v>7.6</v>
@@ -3274,7 +3274,7 @@
         <v>6.2</v>
       </c>
       <c r="AX11">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="AY11">
         <v>8</v>
@@ -3390,7 +3390,7 @@
         <v>4.8</v>
       </c>
       <c r="H12">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="I12">
         <v>2.12</v>
@@ -3423,7 +3423,7 @@
         <v>1.22</v>
       </c>
       <c r="S12">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="T12">
         <v>2.1</v>
@@ -3441,7 +3441,7 @@
         <v>12</v>
       </c>
       <c r="Y12">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="Z12">
         <v>14</v>
@@ -3456,13 +3456,13 @@
         <v>7.6</v>
       </c>
       <c r="AD12">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AE12">
         <v>32</v>
       </c>
       <c r="AF12">
-        <v>40</v>
+        <v>85</v>
       </c>
       <c r="AG12">
         <v>23</v>
@@ -3489,7 +3489,7 @@
         <v>500</v>
       </c>
       <c r="AO12">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AP12">
         <v>8.6</v>
@@ -3519,91 +3519,91 @@
         <v>14.5</v>
       </c>
       <c r="AY12">
-        <v>10.5</v>
+        <v>16.5</v>
       </c>
       <c r="AZ12">
         <v>11.5</v>
       </c>
       <c r="BA12">
-        <v>5.5</v>
+        <v>4.9</v>
       </c>
       <c r="BB12">
-        <v>5.9</v>
+        <v>5.2</v>
       </c>
       <c r="BC12">
-        <v>5.7</v>
+        <v>5.1</v>
       </c>
       <c r="BD12">
-        <v>5.8</v>
+        <v>5.2</v>
       </c>
       <c r="BE12">
-        <v>5.9</v>
+        <v>5.3</v>
       </c>
       <c r="BF12">
-        <v>5.8</v>
+        <v>5.2</v>
       </c>
       <c r="BG12">
-        <v>16.5</v>
+        <v>5.2</v>
       </c>
       <c r="BH12">
         <v>2.86</v>
       </c>
       <c r="BI12">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="BJ12">
         <v>11.5</v>
       </c>
       <c r="BK12">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BL12">
         <v>1000</v>
       </c>
       <c r="BM12">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="BN12">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BO12">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BP12">
         <v>1000</v>
       </c>
       <c r="BQ12">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BR12">
         <v>1000</v>
       </c>
       <c r="BS12">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BT12">
         <v>4.6</v>
       </c>
       <c r="BU12">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="BV12">
         <v>16.5</v>
       </c>
       <c r="BW12">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX12">
         <v>1000</v>
       </c>
       <c r="BY12">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BZ12">
         <v>1000</v>
       </c>
       <c r="CA12">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="CB12" t="s">
         <v>118</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-28.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-28.xlsx
@@ -346,7 +346,7 @@
     <t>Athletic Club</t>
   </si>
   <si>
-    <t>2026-07-27 23:49:23</t>
+    <t>2026-07-28 01:56:17</t>
   </si>
 </sst>
 </file>
@@ -943,55 +943,55 @@
         <v>3.35</v>
       </c>
       <c r="G2">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="H2">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="I2">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="J2">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K2">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L2">
-        <v>1.28</v>
+        <v>1.37</v>
       </c>
       <c r="M2">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N2">
         <v>4.4</v>
       </c>
       <c r="O2">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="P2">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="Q2">
-        <v>1.76</v>
+        <v>1.81</v>
       </c>
       <c r="R2">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="S2">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="T2">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="U2">
         <v>2.38</v>
       </c>
       <c r="V2">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="W2">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="X2">
         <v>22</v>
@@ -1003,22 +1003,22 @@
         <v>19</v>
       </c>
       <c r="AA2">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AB2">
         <v>19</v>
       </c>
       <c r="AC2">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AD2">
         <v>12</v>
       </c>
       <c r="AE2">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AF2">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="AG2">
         <v>15.5</v>
@@ -1039,31 +1039,31 @@
         <v>55</v>
       </c>
       <c r="AM2">
-        <v>580</v>
+        <v>200</v>
       </c>
       <c r="AN2">
         <v>36</v>
       </c>
       <c r="AO2">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="AP2">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AQ2">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AR2">
         <v>11.5</v>
       </c>
       <c r="AS2">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AT2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AU2">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AV2">
         <v>10</v>
@@ -1072,52 +1072,52 @@
         <v>19.5</v>
       </c>
       <c r="AX2">
-        <v>11.5</v>
+        <v>21</v>
       </c>
       <c r="AY2">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="AZ2">
         <v>13.5</v>
       </c>
       <c r="BA2">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="BB2">
-        <v>6.2</v>
+        <v>30</v>
       </c>
       <c r="BC2">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="BD2">
         <v>34</v>
       </c>
       <c r="BE2">
-        <v>6.2</v>
+        <v>50</v>
       </c>
       <c r="BF2">
         <v>21</v>
       </c>
       <c r="BG2">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="BH2">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="BI2">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="BJ2">
         <v>8.800000000000001</v>
       </c>
       <c r="BK2">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="BN2">
         <v>6.8</v>
@@ -1129,13 +1129,13 @@
         <v>25</v>
       </c>
       <c r="BQ2">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BR2">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BS2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BT2">
         <v>5.3</v>
@@ -1144,16 +1144,16 @@
         <v>4.7</v>
       </c>
       <c r="BV2">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BW2">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BX2">
         <v>26</v>
       </c>
       <c r="BY2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BZ2">
         <v>0</v>
@@ -1185,109 +1185,109 @@
         <v>2.46</v>
       </c>
       <c r="G3">
-        <v>2.58</v>
+        <v>2.52</v>
       </c>
       <c r="H3">
         <v>2.98</v>
       </c>
       <c r="I3">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="J3">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="K3">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L3">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="M3">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N3">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="O3">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="P3">
-        <v>2.32</v>
+        <v>2.42</v>
       </c>
       <c r="Q3">
         <v>1.67</v>
       </c>
       <c r="R3">
-        <v>1.54</v>
+        <v>1.58</v>
       </c>
       <c r="S3">
         <v>2.66</v>
       </c>
       <c r="T3">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="U3">
-        <v>2.56</v>
+        <v>2.68</v>
       </c>
       <c r="V3">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="W3">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="X3">
         <v>24</v>
       </c>
       <c r="Y3">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="Z3">
         <v>23</v>
       </c>
       <c r="AA3">
-        <v>100</v>
+        <v>280</v>
       </c>
       <c r="AB3">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AC3">
         <v>8.6</v>
       </c>
       <c r="AD3">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AE3">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="AF3">
         <v>21</v>
       </c>
       <c r="AG3">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH3">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AI3">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AJ3">
-        <v>44</v>
+        <v>95</v>
       </c>
       <c r="AK3">
         <v>32</v>
       </c>
       <c r="AL3">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="AM3">
-        <v>200</v>
+        <v>55</v>
       </c>
       <c r="AN3">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AO3">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AP3">
         <v>17</v>
@@ -1305,13 +1305,13 @@
         <v>13</v>
       </c>
       <c r="AU3">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AV3">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AW3">
-        <v>14.5</v>
+        <v>24</v>
       </c>
       <c r="AX3">
         <v>16.5</v>
@@ -1323,58 +1323,58 @@
         <v>12</v>
       </c>
       <c r="BA3">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="BB3">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="BC3">
         <v>21</v>
       </c>
       <c r="BD3">
-        <v>14.5</v>
+        <v>25</v>
       </c>
       <c r="BE3">
-        <v>8.6</v>
+        <v>23</v>
       </c>
       <c r="BF3">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BG3">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="BH3">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="BI3">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="BJ3">
         <v>8.800000000000001</v>
       </c>
       <c r="BK3">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BN3">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BO3">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BP3">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="BQ3">
-        <v>12.5</v>
+        <v>8</v>
       </c>
       <c r="BR3">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="BS3">
         <v>9.800000000000001</v>
@@ -1383,10 +1383,10 @@
         <v>6.6</v>
       </c>
       <c r="BU3">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BV3">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BW3">
         <v>9.199999999999999</v>
@@ -1398,10 +1398,10 @@
         <v>10</v>
       </c>
       <c r="BZ3">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="CA3">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="CB3" t="s">
         <v>110</v>
@@ -1424,58 +1424,58 @@
         <v>103</v>
       </c>
       <c r="F4">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="G4">
-        <v>4.6</v>
+        <v>3.95</v>
       </c>
       <c r="H4">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="I4">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="J4">
-        <v>2.84</v>
+        <v>2.92</v>
       </c>
       <c r="K4">
         <v>3.15</v>
       </c>
       <c r="L4">
-        <v>1.01</v>
+        <v>1.59</v>
       </c>
       <c r="M4">
         <v>1.13</v>
       </c>
       <c r="N4">
-        <v>2.24</v>
+        <v>2.62</v>
       </c>
       <c r="O4">
-        <v>1.51</v>
+        <v>1.55</v>
       </c>
       <c r="P4">
-        <v>1.51</v>
+        <v>1.55</v>
       </c>
       <c r="Q4">
-        <v>2.6</v>
+        <v>2.72</v>
       </c>
       <c r="R4">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="S4">
-        <v>4.7</v>
+        <v>5.5</v>
       </c>
       <c r="T4">
-        <v>1.11</v>
+        <v>1.94</v>
       </c>
       <c r="U4">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="V4">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="W4">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="X4">
         <v>8.6</v>
@@ -1487,7 +1487,7 @@
         <v>15</v>
       </c>
       <c r="AA4">
-        <v>85</v>
+        <v>40</v>
       </c>
       <c r="AB4">
         <v>10.5</v>
@@ -1499,7 +1499,7 @@
         <v>13</v>
       </c>
       <c r="AE4">
-        <v>85</v>
+        <v>38</v>
       </c>
       <c r="AF4">
         <v>42</v>
@@ -1517,10 +1517,10 @@
         <v>900</v>
       </c>
       <c r="AK4">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="AL4">
-        <v>500</v>
+        <v>420</v>
       </c>
       <c r="AM4">
         <v>500</v>
@@ -1532,7 +1532,7 @@
         <v>44</v>
       </c>
       <c r="AP4">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AQ4">
         <v>6.4</v>
@@ -1541,7 +1541,7 @@
         <v>12</v>
       </c>
       <c r="AS4">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AT4">
         <v>8.6</v>
@@ -1553,10 +1553,10 @@
         <v>10.5</v>
       </c>
       <c r="AW4">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AX4">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AY4">
         <v>14</v>
@@ -1565,25 +1565,25 @@
         <v>17.5</v>
       </c>
       <c r="BA4">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB4">
+        <v>9</v>
+      </c>
+      <c r="BC4">
         <v>8.800000000000001</v>
       </c>
-      <c r="BC4">
-        <v>8.6</v>
-      </c>
       <c r="BD4">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE4">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BF4">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG4">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="BH4">
         <v>1000</v>
@@ -1669,10 +1669,10 @@
         <v>6.2</v>
       </c>
       <c r="G5">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="H5">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="I5">
         <v>1.51</v>
@@ -1681,10 +1681,10 @@
         <v>5.4</v>
       </c>
       <c r="K5">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="L5">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="M5">
         <v>1.02</v>
@@ -1696,22 +1696,22 @@
         <v>1.11</v>
       </c>
       <c r="P5">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="Q5">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="R5">
         <v>2.08</v>
       </c>
       <c r="S5">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="T5">
         <v>1.52</v>
       </c>
       <c r="U5">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="V5">
         <v>2.96</v>
@@ -1720,10 +1720,10 @@
         <v>1.17</v>
       </c>
       <c r="X5">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="Y5">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Z5">
         <v>17</v>
@@ -1747,7 +1747,7 @@
         <v>450</v>
       </c>
       <c r="AG5">
-        <v>950</v>
+        <v>32</v>
       </c>
       <c r="AH5">
         <v>22</v>
@@ -1756,13 +1756,13 @@
         <v>26</v>
       </c>
       <c r="AJ5">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AK5">
         <v>400</v>
       </c>
       <c r="AL5">
-        <v>120</v>
+        <v>200</v>
       </c>
       <c r="AM5">
         <v>160</v>
@@ -1771,7 +1771,7 @@
         <v>46</v>
       </c>
       <c r="AO5">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AP5">
         <v>7.2</v>
@@ -1786,43 +1786,43 @@
         <v>14.5</v>
       </c>
       <c r="AT5">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="AU5">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="AV5">
         <v>10</v>
       </c>
       <c r="AW5">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AX5">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AY5">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="AZ5">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="BA5">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BB5">
         <v>8</v>
       </c>
       <c r="BC5">
-        <v>28</v>
+        <v>7.4</v>
       </c>
       <c r="BD5">
-        <v>38</v>
+        <v>7.2</v>
       </c>
       <c r="BE5">
-        <v>36</v>
+        <v>7.4</v>
       </c>
       <c r="BF5">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BG5">
         <v>3.55</v>
@@ -1834,10 +1834,10 @@
         <v>5.2</v>
       </c>
       <c r="BJ5">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BK5">
-        <v>7.2</v>
+        <v>5.5</v>
       </c>
       <c r="BL5">
         <v>1000</v>
@@ -1849,7 +1849,7 @@
         <v>11</v>
       </c>
       <c r="BO5">
-        <v>8.4</v>
+        <v>6</v>
       </c>
       <c r="BP5">
         <v>1000</v>
@@ -1861,7 +1861,7 @@
         <v>1000</v>
       </c>
       <c r="BS5">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BT5">
         <v>5</v>
@@ -1879,13 +1879,13 @@
         <v>16.5</v>
       </c>
       <c r="BY5">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BZ5">
         <v>8.4</v>
       </c>
       <c r="CA5">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="CB5" t="s">
         <v>110</v>
@@ -1908,16 +1908,16 @@
         <v>105</v>
       </c>
       <c r="F6">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="G6">
-        <v>18</v>
+        <v>80</v>
       </c>
       <c r="H6">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="I6">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="J6">
         <v>2.9</v>
@@ -1935,7 +1935,7 @@
         <v>1.97</v>
       </c>
       <c r="O6">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="P6">
         <v>1.48</v>
@@ -2019,49 +2019,49 @@
         <v>4.9</v>
       </c>
       <c r="AQ6">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AR6">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AS6">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AT6">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AU6">
         <v>4.4</v>
       </c>
       <c r="AV6">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="AW6">
         <v>1.34</v>
       </c>
       <c r="AX6">
+        <v>1.36</v>
+      </c>
+      <c r="AY6">
+        <v>1.35</v>
+      </c>
+      <c r="AZ6">
         <v>1.34</v>
       </c>
-      <c r="AY6">
-        <v>1.34</v>
-      </c>
-      <c r="AZ6">
-        <v>1.32</v>
-      </c>
       <c r="BA6">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="BB6">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="BC6">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="BD6">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="BE6">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="BF6">
         <v>1.55</v>
@@ -2153,58 +2153,58 @@
         <v>2.08</v>
       </c>
       <c r="G7">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="H7">
         <v>4.7</v>
       </c>
       <c r="I7">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="J7">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="K7">
         <v>3.15</v>
       </c>
       <c r="L7">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="M7">
+        <v>1.15</v>
+      </c>
+      <c r="N7">
+        <v>2.46</v>
+      </c>
+      <c r="O7">
+        <v>1.66</v>
+      </c>
+      <c r="P7">
+        <v>1.47</v>
+      </c>
+      <c r="Q7">
+        <v>3.05</v>
+      </c>
+      <c r="R7">
         <v>1.16</v>
       </c>
-      <c r="N7">
-        <v>2.4</v>
-      </c>
-      <c r="O7">
+      <c r="S7">
+        <v>6.8</v>
+      </c>
+      <c r="T7">
+        <v>2.42</v>
+      </c>
+      <c r="U7">
         <v>1.65</v>
       </c>
-      <c r="P7">
-        <v>1.44</v>
-      </c>
-      <c r="Q7">
-        <v>3</v>
-      </c>
-      <c r="R7">
-        <v>1.15</v>
-      </c>
-      <c r="S7">
-        <v>6.6</v>
-      </c>
-      <c r="T7">
-        <v>2.44</v>
-      </c>
-      <c r="U7">
-        <v>1.62</v>
-      </c>
       <c r="V7">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="W7">
         <v>1.87</v>
       </c>
       <c r="X7">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="Y7">
         <v>11.5</v>
@@ -2219,7 +2219,7 @@
         <v>6.2</v>
       </c>
       <c r="AC7">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AD7">
         <v>22</v>
@@ -2231,10 +2231,10 @@
         <v>10.5</v>
       </c>
       <c r="AG7">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH7">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="AI7">
         <v>690</v>
@@ -2243,7 +2243,7 @@
         <v>30</v>
       </c>
       <c r="AK7">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="AL7">
         <v>200</v>
@@ -2258,7 +2258,7 @@
         <v>690</v>
       </c>
       <c r="AP7">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AQ7">
         <v>10</v>
@@ -2276,7 +2276,7 @@
         <v>6.8</v>
       </c>
       <c r="AV7">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AW7">
         <v>38</v>
@@ -2306,19 +2306,19 @@
         <v>100</v>
       </c>
       <c r="BF7">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BG7">
         <v>46</v>
       </c>
       <c r="BH7">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="BI7">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="BJ7">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BK7">
         <v>7.6</v>
@@ -2327,7 +2327,7 @@
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="BN7">
         <v>4.5</v>
@@ -2336,10 +2336,10 @@
         <v>4</v>
       </c>
       <c r="BP7">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BQ7">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BR7">
         <v>1000</v>
@@ -2357,7 +2357,7 @@
         <v>1000</v>
       </c>
       <c r="BW7">
-        <v>2.14</v>
+        <v>14</v>
       </c>
       <c r="BX7">
         <v>1000</v>
@@ -2369,7 +2369,7 @@
         <v>1000</v>
       </c>
       <c r="CA7">
-        <v>2.12</v>
+        <v>14</v>
       </c>
       <c r="CB7" t="s">
         <v>110</v>
@@ -2395,58 +2395,58 @@
         <v>2.12</v>
       </c>
       <c r="G8">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="H8">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="I8">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J8">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="K8">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="L8">
         <v>1.63</v>
       </c>
       <c r="M8">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="N8">
-        <v>2.46</v>
+        <v>2.58</v>
       </c>
       <c r="O8">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="P8">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="Q8">
         <v>2.88</v>
       </c>
       <c r="R8">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="S8">
         <v>6.2</v>
       </c>
       <c r="T8">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="U8">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="V8">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="W8">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="X8">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y8">
         <v>11</v>
@@ -2455,28 +2455,28 @@
         <v>32</v>
       </c>
       <c r="AA8">
-        <v>690</v>
+        <v>130</v>
       </c>
       <c r="AB8">
         <v>6.4</v>
       </c>
       <c r="AC8">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AD8">
         <v>22</v>
       </c>
       <c r="AE8">
-        <v>220</v>
+        <v>95</v>
       </c>
       <c r="AF8">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AG8">
         <v>13</v>
       </c>
       <c r="AH8">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AI8">
         <v>530</v>
@@ -2485,7 +2485,7 @@
         <v>29</v>
       </c>
       <c r="AK8">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AL8">
         <v>75</v>
@@ -2494,25 +2494,25 @@
         <v>500</v>
       </c>
       <c r="AN8">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AO8">
-        <v>690</v>
+        <v>180</v>
       </c>
       <c r="AP8">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AQ8">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AR8">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AS8">
         <v>38</v>
       </c>
       <c r="AT8">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="AU8">
         <v>6.6</v>
@@ -2530,19 +2530,19 @@
         <v>11</v>
       </c>
       <c r="AZ8">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BA8">
-        <v>42</v>
+        <v>75</v>
       </c>
       <c r="BB8">
         <v>22</v>
       </c>
       <c r="BC8">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="BD8">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="BE8">
         <v>100</v>
@@ -2554,22 +2554,22 @@
         <v>42</v>
       </c>
       <c r="BH8">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="BI8">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="BJ8">
+        <v>12.5</v>
+      </c>
+      <c r="BK8">
+        <v>6.4</v>
+      </c>
+      <c r="BL8">
+        <v>1000</v>
+      </c>
+      <c r="BM8">
         <v>13</v>
-      </c>
-      <c r="BK8">
-        <v>6</v>
-      </c>
-      <c r="BL8">
-        <v>1000</v>
-      </c>
-      <c r="BM8">
-        <v>11</v>
       </c>
       <c r="BN8">
         <v>4.7</v>
@@ -2578,16 +2578,16 @@
         <v>3.95</v>
       </c>
       <c r="BP8">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="BQ8">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BR8">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="BS8">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="BT8">
         <v>8.199999999999999</v>
@@ -2596,22 +2596,22 @@
         <v>5.5</v>
       </c>
       <c r="BV8">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BW8">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="BX8">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="BY8">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BZ8">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="CA8">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="CB8" t="s">
         <v>110</v>
@@ -2634,10 +2634,10 @@
         <v>108</v>
       </c>
       <c r="F9">
+        <v>1.6</v>
+      </c>
+      <c r="G9">
         <v>1.62</v>
-      </c>
-      <c r="G9">
-        <v>1.65</v>
       </c>
       <c r="H9">
         <v>7.6</v>
@@ -2646,154 +2646,154 @@
         <v>8.199999999999999</v>
       </c>
       <c r="J9">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="K9">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="L9">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="M9">
         <v>1.11</v>
       </c>
       <c r="N9">
-        <v>2.88</v>
+        <v>2.96</v>
       </c>
       <c r="O9">
         <v>1.48</v>
       </c>
       <c r="P9">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="Q9">
         <v>2.46</v>
       </c>
       <c r="R9">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="S9">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="T9">
         <v>2.42</v>
       </c>
       <c r="U9">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="V9">
         <v>1.14</v>
       </c>
       <c r="W9">
-        <v>2.52</v>
+        <v>2.6</v>
       </c>
       <c r="X9">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="Y9">
-        <v>970</v>
+        <v>19</v>
       </c>
       <c r="Z9">
         <v>400</v>
       </c>
       <c r="AA9">
-        <v>400</v>
+        <v>330</v>
       </c>
       <c r="AB9">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="AC9">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AD9">
         <v>34</v>
       </c>
       <c r="AE9">
-        <v>210</v>
+        <v>180</v>
       </c>
       <c r="AF9">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="AG9">
+        <v>11</v>
+      </c>
+      <c r="AH9">
+        <v>34</v>
+      </c>
+      <c r="AI9">
+        <v>200</v>
+      </c>
+      <c r="AJ9">
+        <v>15.5</v>
+      </c>
+      <c r="AK9">
+        <v>22</v>
+      </c>
+      <c r="AL9">
+        <v>65</v>
+      </c>
+      <c r="AM9">
+        <v>580</v>
+      </c>
+      <c r="AN9">
+        <v>14.5</v>
+      </c>
+      <c r="AO9">
+        <v>360</v>
+      </c>
+      <c r="AP9">
+        <v>9</v>
+      </c>
+      <c r="AQ9">
+        <v>17</v>
+      </c>
+      <c r="AR9">
+        <v>55</v>
+      </c>
+      <c r="AS9">
         <v>11.5</v>
       </c>
-      <c r="AH9">
-        <v>38</v>
-      </c>
-      <c r="AI9">
-        <v>210</v>
-      </c>
-      <c r="AJ9">
-        <v>16.5</v>
-      </c>
-      <c r="AK9">
-        <v>23</v>
-      </c>
-      <c r="AL9">
-        <v>290</v>
-      </c>
-      <c r="AM9">
-        <v>700</v>
-      </c>
-      <c r="AN9">
-        <v>17</v>
-      </c>
-      <c r="AO9">
-        <v>420</v>
-      </c>
-      <c r="AP9">
-        <v>7.6</v>
-      </c>
-      <c r="AQ9">
-        <v>9</v>
-      </c>
-      <c r="AR9">
-        <v>6</v>
-      </c>
-      <c r="AS9">
-        <v>6.6</v>
-      </c>
       <c r="AT9">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="AU9">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV9">
-        <v>14.5</v>
+        <v>29</v>
       </c>
       <c r="AW9">
-        <v>6.4</v>
+        <v>11</v>
       </c>
       <c r="AX9">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AY9">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="AZ9">
-        <v>14.5</v>
+        <v>30</v>
       </c>
       <c r="BA9">
-        <v>6.4</v>
+        <v>11.5</v>
       </c>
       <c r="BB9">
-        <v>11</v>
+        <v>13.5</v>
       </c>
       <c r="BC9">
-        <v>15.5</v>
+        <v>19.5</v>
       </c>
       <c r="BD9">
-        <v>6</v>
+        <v>50</v>
       </c>
       <c r="BE9">
-        <v>6.6</v>
+        <v>11.5</v>
       </c>
       <c r="BF9">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="BG9">
-        <v>6.6</v>
+        <v>11.5</v>
       </c>
       <c r="BH9">
         <v>2.98</v>
@@ -2876,43 +2876,43 @@
         <v>109</v>
       </c>
       <c r="F10">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="G10">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="H10">
+        <v>2.02</v>
+      </c>
+      <c r="I10">
         <v>2.06</v>
-      </c>
-      <c r="I10">
-        <v>2.12</v>
       </c>
       <c r="J10">
         <v>3.3</v>
       </c>
       <c r="K10">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="L10">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="M10">
         <v>1.11</v>
       </c>
       <c r="N10">
-        <v>2.86</v>
+        <v>2.96</v>
       </c>
       <c r="O10">
         <v>1.49</v>
       </c>
       <c r="P10">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="Q10">
         <v>2.48</v>
       </c>
       <c r="R10">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="S10">
         <v>5</v>
@@ -2921,127 +2921,127 @@
         <v>2.1</v>
       </c>
       <c r="U10">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="V10">
-        <v>1.89</v>
+        <v>1.95</v>
       </c>
       <c r="W10">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="X10">
+        <v>10.5</v>
+      </c>
+      <c r="Y10">
+        <v>7</v>
+      </c>
+      <c r="Z10">
         <v>12</v>
       </c>
-      <c r="Y10">
-        <v>7.6</v>
-      </c>
-      <c r="Z10">
-        <v>14</v>
-      </c>
       <c r="AA10">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AB10">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AC10">
         <v>9.199999999999999</v>
       </c>
       <c r="AD10">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AE10">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AF10">
+        <v>34</v>
+      </c>
+      <c r="AG10">
+        <v>22</v>
+      </c>
+      <c r="AH10">
+        <v>27</v>
+      </c>
+      <c r="AI10">
+        <v>55</v>
+      </c>
+      <c r="AJ10">
+        <v>130</v>
+      </c>
+      <c r="AK10">
         <v>85</v>
       </c>
-      <c r="AG10">
-        <v>23</v>
-      </c>
-      <c r="AH10">
-        <v>28</v>
-      </c>
-      <c r="AI10">
-        <v>150</v>
-      </c>
-      <c r="AJ10">
-        <v>900</v>
-      </c>
-      <c r="AK10">
-        <v>200</v>
-      </c>
       <c r="AL10">
-        <v>380</v>
+        <v>110</v>
       </c>
       <c r="AM10">
-        <v>580</v>
+        <v>190</v>
       </c>
       <c r="AN10">
-        <v>500</v>
+        <v>120</v>
       </c>
       <c r="AO10">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AP10">
         <v>8.6</v>
       </c>
       <c r="AQ10">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AR10">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AS10">
-        <v>11.5</v>
+        <v>21</v>
       </c>
       <c r="AT10">
-        <v>9.4</v>
+        <v>12</v>
       </c>
       <c r="AU10">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AV10">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW10">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="AX10">
-        <v>4.7</v>
+        <v>30</v>
       </c>
       <c r="AY10">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AZ10">
-        <v>11.5</v>
+        <v>22</v>
       </c>
       <c r="BA10">
-        <v>4.5</v>
+        <v>44</v>
       </c>
       <c r="BB10">
-        <v>4.7</v>
+        <v>7.6</v>
       </c>
       <c r="BC10">
-        <v>4.6</v>
+        <v>7.4</v>
       </c>
       <c r="BD10">
-        <v>4.7</v>
+        <v>7.6</v>
       </c>
       <c r="BE10">
-        <v>4.8</v>
+        <v>7.8</v>
       </c>
       <c r="BF10">
-        <v>5.3</v>
+        <v>7.6</v>
       </c>
       <c r="BG10">
-        <v>5.2</v>
+        <v>18.5</v>
       </c>
       <c r="BH10">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="BI10">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="BJ10">
         <v>11.5</v>
@@ -3053,13 +3053,13 @@
         <v>1000</v>
       </c>
       <c r="BM10">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BN10">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BO10">
-        <v>5.7</v>
+        <v>5.3</v>
       </c>
       <c r="BP10">
         <v>1000</v>
@@ -3071,19 +3071,19 @@
         <v>1000</v>
       </c>
       <c r="BS10">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BT10">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BU10">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="BV10">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="BW10">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BX10">
         <v>1000</v>
@@ -3095,7 +3095,7 @@
         <v>1000</v>
       </c>
       <c r="CA10">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="CB10" t="s">
         <v>110</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-28.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-28.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="115">
   <si>
     <t>League</t>
   </si>
@@ -259,6 +259,9 @@
     <t>Swedish Superettan</t>
   </si>
   <si>
+    <t>Argentinian Primera C</t>
+  </si>
+  <si>
     <t>Paraguayan Primera Division</t>
   </si>
   <si>
@@ -277,6 +280,9 @@
     <t>17:00:00</t>
   </si>
   <si>
+    <t>18:00:00</t>
+  </si>
+  <si>
     <t>19:00:00</t>
   </si>
   <si>
@@ -298,13 +304,16 @@
     <t>Helsingborgs</t>
   </si>
   <si>
+    <t>Sportivo Barracas</t>
+  </si>
+  <si>
     <t>Rubio Nu</t>
   </si>
   <si>
     <t>Aegir</t>
   </si>
   <si>
-    <t>2 Mayo de PJC</t>
+    <t>Club 2 de Mayo de Pedro Juan Cab</t>
   </si>
   <si>
     <t>San Lorenzo</t>
@@ -325,6 +334,9 @@
     <t>United IK Nordic</t>
   </si>
   <si>
+    <t>Club El Porvenir</t>
+  </si>
+  <si>
     <t>Club Sportivo Ameliano</t>
   </si>
   <si>
@@ -346,7 +358,7 @@
     <t>Athletic Club</t>
   </si>
   <si>
-    <t>2026-07-28 01:56:17</t>
+    <t>2026-07-28 03:58:18</t>
   </si>
 </sst>
 </file>
@@ -678,7 +690,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB10"/>
+  <dimension ref="A1:CB11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -928,16 +940,16 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E2" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="F2">
         <v>3.35</v>
@@ -946,7 +958,7 @@
         <v>3.5</v>
       </c>
       <c r="H2">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="I2">
         <v>2.28</v>
@@ -958,34 +970,34 @@
         <v>3.85</v>
       </c>
       <c r="L2">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="M2">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N2">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="O2">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="P2">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="Q2">
-        <v>1.81</v>
+        <v>1.76</v>
       </c>
       <c r="R2">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="S2">
-        <v>3.05</v>
+        <v>2.94</v>
       </c>
       <c r="T2">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="U2">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="V2">
         <v>1.78</v>
@@ -994,73 +1006,73 @@
         <v>1.4</v>
       </c>
       <c r="X2">
-        <v>22</v>
+        <v>18.5</v>
       </c>
       <c r="Y2">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Z2">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="AA2">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AB2">
-        <v>19</v>
+        <v>15.5</v>
       </c>
       <c r="AC2">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AD2">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AE2">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AF2">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AG2">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AH2">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AI2">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AJ2">
-        <v>130</v>
+        <v>65</v>
       </c>
       <c r="AK2">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AL2">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AM2">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="AN2">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AO2">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AP2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AR2">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="AS2">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AT2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AU2">
         <v>7.6</v>
@@ -1069,55 +1081,55 @@
         <v>10</v>
       </c>
       <c r="AW2">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AX2">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AY2">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AZ2">
         <v>13.5</v>
       </c>
       <c r="BA2">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="BB2">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="BC2">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="BD2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BE2">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BF2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BG2">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BH2">
-        <v>3.7</v>
+        <v>3.95</v>
       </c>
       <c r="BI2">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="BJ2">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BK2">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BN2">
         <v>6.8</v>
@@ -1126,13 +1138,13 @@
         <v>6</v>
       </c>
       <c r="BP2">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BQ2">
         <v>10.5</v>
       </c>
       <c r="BR2">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BS2">
         <v>12</v>
@@ -1144,16 +1156,16 @@
         <v>4.7</v>
       </c>
       <c r="BV2">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BW2">
         <v>8.4</v>
       </c>
       <c r="BX2">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="BY2">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BZ2">
         <v>0</v>
@@ -1162,7 +1174,7 @@
         <v>0</v>
       </c>
       <c r="CB2" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1170,133 +1182,133 @@
         <v>80</v>
       </c>
       <c r="B3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D3" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E3" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="F3">
-        <v>2.46</v>
+        <v>2.36</v>
       </c>
       <c r="G3">
-        <v>2.52</v>
+        <v>2.42</v>
       </c>
       <c r="H3">
-        <v>2.98</v>
+        <v>3.15</v>
       </c>
       <c r="I3">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="J3">
         <v>3.65</v>
       </c>
       <c r="K3">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L3">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="M3">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N3">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="O3">
         <v>1.21</v>
       </c>
       <c r="P3">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="Q3">
         <v>1.67</v>
       </c>
       <c r="R3">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="S3">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="T3">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="U3">
-        <v>2.68</v>
+        <v>2.62</v>
       </c>
       <c r="V3">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="W3">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="X3">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Y3">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="Z3">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AA3">
         <v>280</v>
       </c>
       <c r="AB3">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AC3">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AD3">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AE3">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="AF3">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AG3">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH3">
         <v>14</v>
       </c>
       <c r="AI3">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="AJ3">
-        <v>95</v>
+        <v>32</v>
       </c>
       <c r="AK3">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="AL3">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="AM3">
         <v>55</v>
       </c>
       <c r="AN3">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AO3">
+        <v>21</v>
+      </c>
+      <c r="AP3">
         <v>19.5</v>
       </c>
-      <c r="AP3">
-        <v>17</v>
-      </c>
       <c r="AQ3">
-        <v>13.5</v>
+        <v>16</v>
       </c>
       <c r="AR3">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AS3">
         <v>36</v>
@@ -1308,76 +1320,76 @@
         <v>7.6</v>
       </c>
       <c r="AV3">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AW3">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AX3">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AY3">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ3">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BA3">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="BB3">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="BC3">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="BD3">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BE3">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="BF3">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BG3">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="BH3">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="BI3">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="BJ3">
         <v>8.800000000000001</v>
       </c>
       <c r="BK3">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BL3">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="BM3">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BN3">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BO3">
         <v>4.9</v>
       </c>
       <c r="BP3">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BQ3">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BR3">
         <v>24</v>
       </c>
       <c r="BS3">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BT3">
         <v>6.6</v>
@@ -1389,22 +1401,22 @@
         <v>21</v>
       </c>
       <c r="BW3">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BX3">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BY3">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BZ3">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="CA3">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB3" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1412,178 +1424,178 @@
         <v>81</v>
       </c>
       <c r="B4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D4" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E4" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="F4">
-        <v>3.45</v>
+        <v>2.74</v>
       </c>
       <c r="G4">
-        <v>3.95</v>
+        <v>3.15</v>
       </c>
       <c r="H4">
-        <v>2.38</v>
+        <v>3.25</v>
       </c>
       <c r="I4">
-        <v>2.6</v>
+        <v>3.8</v>
       </c>
       <c r="J4">
-        <v>2.92</v>
+        <v>2.48</v>
       </c>
       <c r="K4">
-        <v>3.15</v>
+        <v>2.72</v>
       </c>
       <c r="L4">
-        <v>1.59</v>
+        <v>1.01</v>
       </c>
       <c r="M4">
-        <v>1.13</v>
+        <v>1.01</v>
       </c>
       <c r="N4">
-        <v>2.62</v>
+        <v>1.1</v>
       </c>
       <c r="O4">
-        <v>1.55</v>
+        <v>1.01</v>
       </c>
       <c r="P4">
-        <v>1.55</v>
+        <v>1.15</v>
       </c>
       <c r="Q4">
-        <v>2.72</v>
+        <v>1.01</v>
       </c>
       <c r="R4">
-        <v>1.19</v>
+        <v>1.08</v>
       </c>
       <c r="S4">
-        <v>5.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="T4">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="U4">
-        <v>1.64</v>
+        <v>1.35</v>
       </c>
       <c r="V4">
-        <v>1.62</v>
+        <v>1.01</v>
       </c>
       <c r="W4">
-        <v>1.35</v>
+        <v>1.01</v>
       </c>
       <c r="X4">
-        <v>8.6</v>
+        <v>970</v>
       </c>
       <c r="Y4">
-        <v>7.6</v>
+        <v>10.5</v>
       </c>
       <c r="Z4">
-        <v>15</v>
+        <v>970</v>
       </c>
       <c r="AA4">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AB4">
-        <v>10.5</v>
+        <v>8.4</v>
       </c>
       <c r="AC4">
-        <v>7.4</v>
+        <v>970</v>
       </c>
       <c r="AD4">
-        <v>13</v>
+        <v>970</v>
       </c>
       <c r="AE4">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AF4">
-        <v>42</v>
+        <v>970</v>
       </c>
       <c r="AG4">
-        <v>17</v>
+        <v>970</v>
       </c>
       <c r="AH4">
-        <v>27</v>
+        <v>950</v>
       </c>
       <c r="AI4">
-        <v>500</v>
+        <v>180</v>
       </c>
       <c r="AJ4">
-        <v>900</v>
+        <v>80</v>
       </c>
       <c r="AK4">
-        <v>150</v>
+        <v>80</v>
       </c>
       <c r="AL4">
-        <v>420</v>
+        <v>170</v>
       </c>
       <c r="AM4">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AN4">
-        <v>500</v>
+        <v>110</v>
       </c>
       <c r="AO4">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AP4">
-        <v>7.2</v>
+        <v>5.2</v>
       </c>
       <c r="AQ4">
-        <v>6.4</v>
+        <v>2.32</v>
       </c>
       <c r="AR4">
-        <v>12</v>
+        <v>1.86</v>
       </c>
       <c r="AS4">
-        <v>8</v>
+        <v>2.02</v>
       </c>
       <c r="AT4">
-        <v>8.6</v>
+        <v>5.4</v>
       </c>
       <c r="AU4">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="AV4">
-        <v>10.5</v>
+        <v>1.84</v>
       </c>
       <c r="AW4">
-        <v>8</v>
+        <v>2.02</v>
       </c>
       <c r="AX4">
-        <v>7.2</v>
+        <v>1.79</v>
       </c>
       <c r="AY4">
-        <v>14</v>
+        <v>2.5</v>
       </c>
       <c r="AZ4">
-        <v>17.5</v>
+        <v>1.91</v>
       </c>
       <c r="BA4">
-        <v>8.800000000000001</v>
+        <v>2</v>
       </c>
       <c r="BB4">
-        <v>9</v>
+        <v>1.97</v>
       </c>
       <c r="BC4">
-        <v>8.800000000000001</v>
+        <v>1.97</v>
       </c>
       <c r="BD4">
-        <v>9.199999999999999</v>
+        <v>1.99</v>
       </c>
       <c r="BE4">
-        <v>9.6</v>
+        <v>2.02</v>
       </c>
       <c r="BF4">
-        <v>9.199999999999999</v>
+        <v>1.98</v>
       </c>
       <c r="BG4">
-        <v>32</v>
+        <v>2.02</v>
       </c>
       <c r="BH4">
         <v>1000</v>
@@ -1640,13 +1652,13 @@
         <v>1.04</v>
       </c>
       <c r="BZ4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA4">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="CB4" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1654,202 +1666,202 @@
         <v>82</v>
       </c>
       <c r="B5" t="s">
+        <v>86</v>
+      </c>
+      <c r="C5" t="s">
+        <v>89</v>
+      </c>
+      <c r="D5" t="s">
+        <v>97</v>
+      </c>
+      <c r="E5" t="s">
+        <v>107</v>
+      </c>
+      <c r="F5">
+        <v>3.5</v>
+      </c>
+      <c r="G5">
+        <v>3.95</v>
+      </c>
+      <c r="H5">
+        <v>2.42</v>
+      </c>
+      <c r="I5">
+        <v>2.6</v>
+      </c>
+      <c r="J5">
+        <v>3</v>
+      </c>
+      <c r="K5">
+        <v>3.1</v>
+      </c>
+      <c r="L5">
+        <v>1.62</v>
+      </c>
+      <c r="M5">
+        <v>1.14</v>
+      </c>
+      <c r="N5">
+        <v>2.5</v>
+      </c>
+      <c r="O5">
+        <v>1.58</v>
+      </c>
+      <c r="P5">
+        <v>1.47</v>
+      </c>
+      <c r="Q5">
+        <v>2.82</v>
+      </c>
+      <c r="R5">
+        <v>1.18</v>
+      </c>
+      <c r="S5">
+        <v>5.8</v>
+      </c>
+      <c r="T5">
+        <v>2.16</v>
+      </c>
+      <c r="U5">
+        <v>1.72</v>
+      </c>
+      <c r="V5">
+        <v>1.63</v>
+      </c>
+      <c r="W5">
+        <v>1.35</v>
+      </c>
+      <c r="X5">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="Y5">
+        <v>7.4</v>
+      </c>
+      <c r="Z5">
+        <v>14.5</v>
+      </c>
+      <c r="AA5">
         <v>85</v>
       </c>
-      <c r="C5" t="s">
-        <v>88</v>
-      </c>
-      <c r="D5" t="s">
-        <v>95</v>
-      </c>
-      <c r="E5" t="s">
-        <v>104</v>
-      </c>
-      <c r="F5">
-        <v>6.2</v>
-      </c>
-      <c r="G5">
+      <c r="AB5">
+        <v>10</v>
+      </c>
+      <c r="AC5">
         <v>7.2</v>
-      </c>
-      <c r="H5">
-        <v>1.48</v>
-      </c>
-      <c r="I5">
-        <v>1.51</v>
-      </c>
-      <c r="J5">
-        <v>5.4</v>
-      </c>
-      <c r="K5">
-        <v>6</v>
-      </c>
-      <c r="L5">
-        <v>1.2</v>
-      </c>
-      <c r="M5">
-        <v>1.02</v>
-      </c>
-      <c r="N5">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="O5">
-        <v>1.11</v>
-      </c>
-      <c r="P5">
-        <v>3.6</v>
-      </c>
-      <c r="Q5">
-        <v>1.35</v>
-      </c>
-      <c r="R5">
-        <v>2.08</v>
-      </c>
-      <c r="S5">
-        <v>1.87</v>
-      </c>
-      <c r="T5">
-        <v>1.52</v>
-      </c>
-      <c r="U5">
-        <v>2.68</v>
-      </c>
-      <c r="V5">
-        <v>2.96</v>
-      </c>
-      <c r="W5">
-        <v>1.17</v>
-      </c>
-      <c r="X5">
-        <v>130</v>
-      </c>
-      <c r="Y5">
-        <v>20</v>
-      </c>
-      <c r="Z5">
-        <v>17</v>
-      </c>
-      <c r="AA5">
-        <v>19</v>
-      </c>
-      <c r="AB5">
-        <v>950</v>
-      </c>
-      <c r="AC5">
-        <v>17</v>
       </c>
       <c r="AD5">
         <v>13</v>
       </c>
       <c r="AE5">
-        <v>15</v>
+        <v>85</v>
       </c>
       <c r="AF5">
-        <v>450</v>
+        <v>42</v>
       </c>
       <c r="AG5">
+        <v>17</v>
+      </c>
+      <c r="AH5">
+        <v>25</v>
+      </c>
+      <c r="AI5">
+        <v>230</v>
+      </c>
+      <c r="AJ5">
+        <v>500</v>
+      </c>
+      <c r="AK5">
+        <v>150</v>
+      </c>
+      <c r="AL5">
+        <v>500</v>
+      </c>
+      <c r="AM5">
+        <v>500</v>
+      </c>
+      <c r="AN5">
+        <v>500</v>
+      </c>
+      <c r="AO5">
+        <v>44</v>
+      </c>
+      <c r="AP5">
+        <v>6.8</v>
+      </c>
+      <c r="AQ5">
+        <v>6.4</v>
+      </c>
+      <c r="AR5">
+        <v>12</v>
+      </c>
+      <c r="AS5">
+        <v>9.4</v>
+      </c>
+      <c r="AT5">
+        <v>8.6</v>
+      </c>
+      <c r="AU5">
+        <v>6</v>
+      </c>
+      <c r="AV5">
+        <v>10.5</v>
+      </c>
+      <c r="AW5">
+        <v>28</v>
+      </c>
+      <c r="AX5">
+        <v>9.4</v>
+      </c>
+      <c r="AY5">
+        <v>14</v>
+      </c>
+      <c r="AZ5">
+        <v>18.5</v>
+      </c>
+      <c r="BA5">
         <v>32</v>
       </c>
-      <c r="AH5">
-        <v>22</v>
-      </c>
-      <c r="AI5">
-        <v>26</v>
-      </c>
-      <c r="AJ5">
-        <v>170</v>
-      </c>
-      <c r="AK5">
-        <v>400</v>
-      </c>
-      <c r="AL5">
-        <v>200</v>
-      </c>
-      <c r="AM5">
-        <v>160</v>
-      </c>
-      <c r="AN5">
-        <v>46</v>
-      </c>
-      <c r="AO5">
-        <v>4</v>
-      </c>
-      <c r="AP5">
-        <v>7.2</v>
-      </c>
-      <c r="AQ5">
-        <v>15.5</v>
-      </c>
-      <c r="AR5">
-        <v>12.5</v>
-      </c>
-      <c r="AS5">
-        <v>14.5</v>
-      </c>
-      <c r="AT5">
-        <v>36</v>
-      </c>
-      <c r="AU5">
-        <v>13.5</v>
-      </c>
-      <c r="AV5">
-        <v>10</v>
-      </c>
-      <c r="AW5">
+      <c r="BB5">
+        <v>11</v>
+      </c>
+      <c r="BC5">
+        <v>30</v>
+      </c>
+      <c r="BD5">
+        <v>11</v>
+      </c>
+      <c r="BE5">
+        <v>11.5</v>
+      </c>
+      <c r="BF5">
+        <v>11</v>
+      </c>
+      <c r="BG5">
+        <v>32</v>
+      </c>
+      <c r="BH5">
+        <v>2.66</v>
+      </c>
+      <c r="BI5">
+        <v>2.42</v>
+      </c>
+      <c r="BJ5">
         <v>12</v>
       </c>
-      <c r="AX5">
-        <v>7.6</v>
-      </c>
-      <c r="AY5">
-        <v>23</v>
-      </c>
-      <c r="AZ5">
-        <v>15.5</v>
-      </c>
-      <c r="BA5">
-        <v>18.5</v>
-      </c>
-      <c r="BB5">
-        <v>8</v>
-      </c>
-      <c r="BC5">
-        <v>7.4</v>
-      </c>
-      <c r="BD5">
-        <v>7.2</v>
-      </c>
-      <c r="BE5">
-        <v>7.4</v>
-      </c>
-      <c r="BF5">
-        <v>7.2</v>
-      </c>
-      <c r="BG5">
-        <v>3.55</v>
-      </c>
-      <c r="BH5">
-        <v>6</v>
-      </c>
-      <c r="BI5">
-        <v>5.2</v>
-      </c>
-      <c r="BJ5">
-        <v>9.4</v>
-      </c>
       <c r="BK5">
-        <v>5.5</v>
+        <v>9</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BN5">
-        <v>11</v>
+        <v>6.8</v>
       </c>
       <c r="BO5">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="BP5">
         <v>1000</v>
@@ -1861,643 +1873,643 @@
         <v>1000</v>
       </c>
       <c r="BS5">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="BT5">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BU5">
         <v>4.4</v>
       </c>
       <c r="BV5">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BW5">
-        <v>6.8</v>
+        <v>8.6</v>
       </c>
       <c r="BX5">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="BY5">
-        <v>7.2</v>
+        <v>10.5</v>
       </c>
       <c r="BZ5">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="CA5">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="CB5" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
     </row>
     <row r="6" spans="1:80">
       <c r="A6" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D6" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E6" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="F6">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="G6">
-        <v>80</v>
+        <v>6.8</v>
       </c>
       <c r="H6">
-        <v>1.72</v>
+        <v>1.48</v>
       </c>
       <c r="I6">
+        <v>1.52</v>
+      </c>
+      <c r="J6">
+        <v>5.3</v>
+      </c>
+      <c r="K6">
+        <v>6</v>
+      </c>
+      <c r="L6">
+        <v>1.2</v>
+      </c>
+      <c r="M6">
+        <v>1.02</v>
+      </c>
+      <c r="N6">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="O6">
+        <v>1.1</v>
+      </c>
+      <c r="P6">
+        <v>3.65</v>
+      </c>
+      <c r="Q6">
+        <v>1.34</v>
+      </c>
+      <c r="R6">
+        <v>2.08</v>
+      </c>
+      <c r="S6">
+        <v>1.86</v>
+      </c>
+      <c r="T6">
+        <v>1.5</v>
+      </c>
+      <c r="U6">
         <v>2.72</v>
       </c>
-      <c r="J6">
-        <v>2.9</v>
-      </c>
-      <c r="K6">
-        <v>3.95</v>
-      </c>
-      <c r="L6">
-        <v>1.01</v>
-      </c>
-      <c r="M6">
-        <v>1.01</v>
-      </c>
-      <c r="N6">
-        <v>1.97</v>
-      </c>
-      <c r="O6">
-        <v>1.05</v>
-      </c>
-      <c r="P6">
-        <v>1.48</v>
-      </c>
-      <c r="Q6">
-        <v>1.82</v>
-      </c>
-      <c r="R6">
-        <v>1.18</v>
-      </c>
-      <c r="S6">
-        <v>1.82</v>
-      </c>
-      <c r="T6">
-        <v>1.11</v>
-      </c>
-      <c r="U6">
-        <v>1.83</v>
-      </c>
       <c r="V6">
-        <v>1.01</v>
+        <v>2.92</v>
       </c>
       <c r="W6">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="X6">
-        <v>970</v>
+        <v>950</v>
       </c>
       <c r="Y6">
-        <v>950</v>
+        <v>21</v>
       </c>
       <c r="Z6">
-        <v>500</v>
+        <v>17</v>
       </c>
       <c r="AA6">
-        <v>900</v>
+        <v>19</v>
       </c>
       <c r="AB6">
         <v>950</v>
       </c>
       <c r="AC6">
+        <v>17</v>
+      </c>
+      <c r="AD6">
+        <v>13</v>
+      </c>
+      <c r="AE6">
+        <v>15</v>
+      </c>
+      <c r="AF6">
+        <v>450</v>
+      </c>
+      <c r="AG6">
+        <v>32</v>
+      </c>
+      <c r="AH6">
+        <v>22</v>
+      </c>
+      <c r="AI6">
+        <v>22</v>
+      </c>
+      <c r="AJ6">
+        <v>160</v>
+      </c>
+      <c r="AK6">
+        <v>400</v>
+      </c>
+      <c r="AL6">
+        <v>200</v>
+      </c>
+      <c r="AM6">
+        <v>160</v>
+      </c>
+      <c r="AN6">
+        <v>50</v>
+      </c>
+      <c r="AO6">
+        <v>4</v>
+      </c>
+      <c r="AP6">
+        <v>18</v>
+      </c>
+      <c r="AQ6">
+        <v>14</v>
+      </c>
+      <c r="AR6">
+        <v>12.5</v>
+      </c>
+      <c r="AS6">
+        <v>13</v>
+      </c>
+      <c r="AT6">
+        <v>18</v>
+      </c>
+      <c r="AU6">
+        <v>13.5</v>
+      </c>
+      <c r="AV6">
+        <v>10</v>
+      </c>
+      <c r="AW6">
+        <v>12</v>
+      </c>
+      <c r="AX6">
+        <v>46</v>
+      </c>
+      <c r="AY6">
+        <v>18.5</v>
+      </c>
+      <c r="AZ6">
+        <v>13.5</v>
+      </c>
+      <c r="BA6">
+        <v>16</v>
+      </c>
+      <c r="BB6">
+        <v>9</v>
+      </c>
+      <c r="BC6">
         <v>42</v>
       </c>
-      <c r="AD6">
-        <v>950</v>
-      </c>
-      <c r="AE6">
-        <v>500</v>
-      </c>
-      <c r="AF6">
-        <v>500</v>
-      </c>
-      <c r="AG6">
-        <v>950</v>
-      </c>
-      <c r="AH6">
-        <v>950</v>
-      </c>
-      <c r="AI6">
-        <v>500</v>
-      </c>
-      <c r="AJ6">
-        <v>900</v>
-      </c>
-      <c r="AK6">
-        <v>500</v>
-      </c>
-      <c r="AL6">
-        <v>500</v>
-      </c>
-      <c r="AM6">
-        <v>580</v>
-      </c>
-      <c r="AN6">
-        <v>500</v>
-      </c>
-      <c r="AO6">
-        <v>500</v>
-      </c>
-      <c r="AP6">
-        <v>4.9</v>
-      </c>
-      <c r="AQ6">
-        <v>1.33</v>
-      </c>
-      <c r="AR6">
-        <v>1.34</v>
-      </c>
-      <c r="AS6">
-        <v>1.36</v>
-      </c>
-      <c r="AT6">
-        <v>1.35</v>
-      </c>
-      <c r="AU6">
+      <c r="BD6">
+        <v>23</v>
+      </c>
+      <c r="BE6">
+        <v>36</v>
+      </c>
+      <c r="BF6">
+        <v>7.6</v>
+      </c>
+      <c r="BG6">
+        <v>3.65</v>
+      </c>
+      <c r="BH6">
+        <v>6</v>
+      </c>
+      <c r="BI6">
+        <v>5.2</v>
+      </c>
+      <c r="BJ6">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BK6">
+        <v>5.4</v>
+      </c>
+      <c r="BL6">
+        <v>1000</v>
+      </c>
+      <c r="BM6">
+        <v>11</v>
+      </c>
+      <c r="BN6">
+        <v>11</v>
+      </c>
+      <c r="BO6">
+        <v>6</v>
+      </c>
+      <c r="BP6">
+        <v>1000</v>
+      </c>
+      <c r="BQ6">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BR6">
+        <v>1000</v>
+      </c>
+      <c r="BS6">
+        <v>9.6</v>
+      </c>
+      <c r="BT6">
+        <v>5</v>
+      </c>
+      <c r="BU6">
         <v>4.4</v>
       </c>
-      <c r="AV6">
-        <v>1.34</v>
-      </c>
-      <c r="AW6">
-        <v>1.34</v>
-      </c>
-      <c r="AX6">
-        <v>1.36</v>
-      </c>
-      <c r="AY6">
-        <v>1.35</v>
-      </c>
-      <c r="AZ6">
-        <v>1.34</v>
-      </c>
-      <c r="BA6">
-        <v>1.36</v>
-      </c>
-      <c r="BB6">
-        <v>1.36</v>
-      </c>
-      <c r="BC6">
-        <v>1.36</v>
-      </c>
-      <c r="BD6">
-        <v>1.36</v>
-      </c>
-      <c r="BE6">
-        <v>1.37</v>
-      </c>
-      <c r="BF6">
-        <v>1.55</v>
-      </c>
-      <c r="BG6">
-        <v>1.55</v>
-      </c>
-      <c r="BH6">
-        <v>1000</v>
-      </c>
-      <c r="BI6">
-        <v>1.04</v>
-      </c>
-      <c r="BJ6">
-        <v>1000</v>
-      </c>
-      <c r="BK6">
-        <v>1.04</v>
-      </c>
-      <c r="BL6">
-        <v>1000</v>
-      </c>
-      <c r="BM6">
-        <v>1.04</v>
-      </c>
-      <c r="BN6">
-        <v>1000</v>
-      </c>
-      <c r="BO6">
-        <v>1.04</v>
-      </c>
-      <c r="BP6">
-        <v>1000</v>
-      </c>
-      <c r="BQ6">
-        <v>1.04</v>
-      </c>
-      <c r="BR6">
-        <v>1000</v>
-      </c>
-      <c r="BS6">
-        <v>1.04</v>
-      </c>
-      <c r="BT6">
-        <v>1000</v>
-      </c>
-      <c r="BU6">
-        <v>1.04</v>
-      </c>
       <c r="BV6">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="BW6">
-        <v>1.04</v>
+        <v>5.3</v>
       </c>
       <c r="BX6">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="BY6">
-        <v>1.04</v>
+        <v>7.2</v>
       </c>
       <c r="BZ6">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="CA6">
-        <v>1.04</v>
+        <v>5.2</v>
       </c>
       <c r="CB6" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
     </row>
     <row r="7" spans="1:80">
       <c r="A7" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C7" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D7" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E7" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="F7">
-        <v>2.08</v>
+        <v>3.7</v>
       </c>
       <c r="G7">
-        <v>2.14</v>
+        <v>5.2</v>
       </c>
       <c r="H7">
-        <v>4.7</v>
+        <v>2.06</v>
       </c>
       <c r="I7">
+        <v>2.2</v>
+      </c>
+      <c r="J7">
+        <v>3.2</v>
+      </c>
+      <c r="K7">
+        <v>3.65</v>
+      </c>
+      <c r="L7">
+        <v>1.55</v>
+      </c>
+      <c r="M7">
+        <v>1.11</v>
+      </c>
+      <c r="N7">
+        <v>2.78</v>
+      </c>
+      <c r="O7">
+        <v>1.51</v>
+      </c>
+      <c r="P7">
+        <v>1.57</v>
+      </c>
+      <c r="Q7">
+        <v>2.56</v>
+      </c>
+      <c r="R7">
+        <v>1.2</v>
+      </c>
+      <c r="S7">
+        <v>5.1</v>
+      </c>
+      <c r="T7">
+        <v>1.11</v>
+      </c>
+      <c r="U7">
+        <v>1.83</v>
+      </c>
+      <c r="V7">
+        <v>1.01</v>
+      </c>
+      <c r="W7">
+        <v>1.01</v>
+      </c>
+      <c r="X7">
+        <v>970</v>
+      </c>
+      <c r="Y7">
+        <v>950</v>
+      </c>
+      <c r="Z7">
+        <v>500</v>
+      </c>
+      <c r="AA7">
+        <v>900</v>
+      </c>
+      <c r="AB7">
+        <v>950</v>
+      </c>
+      <c r="AC7">
+        <v>42</v>
+      </c>
+      <c r="AD7">
+        <v>500</v>
+      </c>
+      <c r="AE7">
+        <v>500</v>
+      </c>
+      <c r="AF7">
+        <v>500</v>
+      </c>
+      <c r="AG7">
+        <v>950</v>
+      </c>
+      <c r="AH7">
+        <v>950</v>
+      </c>
+      <c r="AI7">
+        <v>500</v>
+      </c>
+      <c r="AJ7">
+        <v>900</v>
+      </c>
+      <c r="AK7">
+        <v>500</v>
+      </c>
+      <c r="AL7">
+        <v>500</v>
+      </c>
+      <c r="AM7">
+        <v>580</v>
+      </c>
+      <c r="AN7">
+        <v>500</v>
+      </c>
+      <c r="AO7">
+        <v>500</v>
+      </c>
+      <c r="AP7">
         <v>4.9</v>
       </c>
-      <c r="J7">
-        <v>3.1</v>
-      </c>
-      <c r="K7">
-        <v>3.15</v>
-      </c>
-      <c r="L7">
-        <v>1.66</v>
-      </c>
-      <c r="M7">
-        <v>1.15</v>
-      </c>
-      <c r="N7">
-        <v>2.46</v>
-      </c>
-      <c r="O7">
-        <v>1.66</v>
-      </c>
-      <c r="P7">
-        <v>1.47</v>
-      </c>
-      <c r="Q7">
-        <v>3.05</v>
-      </c>
-      <c r="R7">
-        <v>1.16</v>
-      </c>
-      <c r="S7">
-        <v>6.8</v>
-      </c>
-      <c r="T7">
-        <v>2.42</v>
-      </c>
-      <c r="U7">
-        <v>1.65</v>
-      </c>
-      <c r="V7">
-        <v>1.25</v>
-      </c>
-      <c r="W7">
-        <v>1.87</v>
-      </c>
-      <c r="X7">
-        <v>7.8</v>
-      </c>
-      <c r="Y7">
-        <v>11.5</v>
-      </c>
-      <c r="Z7">
-        <v>34</v>
-      </c>
-      <c r="AA7">
-        <v>690</v>
-      </c>
-      <c r="AB7">
-        <v>6.2</v>
-      </c>
-      <c r="AC7">
-        <v>7.8</v>
-      </c>
-      <c r="AD7">
-        <v>22</v>
-      </c>
-      <c r="AE7">
-        <v>250</v>
-      </c>
-      <c r="AF7">
-        <v>10.5</v>
-      </c>
-      <c r="AG7">
-        <v>12</v>
-      </c>
-      <c r="AH7">
-        <v>60</v>
-      </c>
-      <c r="AI7">
-        <v>690</v>
-      </c>
-      <c r="AJ7">
-        <v>30</v>
-      </c>
-      <c r="AK7">
-        <v>60</v>
-      </c>
-      <c r="AL7">
-        <v>200</v>
-      </c>
-      <c r="AM7">
-        <v>500</v>
-      </c>
-      <c r="AN7">
-        <v>50</v>
-      </c>
-      <c r="AO7">
-        <v>690</v>
-      </c>
-      <c r="AP7">
-        <v>7</v>
-      </c>
       <c r="AQ7">
-        <v>10</v>
+        <v>1.36</v>
       </c>
       <c r="AR7">
-        <v>20</v>
+        <v>1.37</v>
       </c>
       <c r="AS7">
-        <v>42</v>
+        <v>1.38</v>
       </c>
       <c r="AT7">
-        <v>5.5</v>
+        <v>1.37</v>
       </c>
       <c r="AU7">
-        <v>6.8</v>
+        <v>4.4</v>
       </c>
       <c r="AV7">
-        <v>19</v>
+        <v>1.34</v>
       </c>
       <c r="AW7">
-        <v>38</v>
+        <v>1.36</v>
       </c>
       <c r="AX7">
-        <v>9.199999999999999</v>
+        <v>1.38</v>
       </c>
       <c r="AY7">
-        <v>11</v>
+        <v>1.38</v>
       </c>
       <c r="AZ7">
-        <v>26</v>
+        <v>1.36</v>
       </c>
       <c r="BA7">
-        <v>44</v>
+        <v>1.39</v>
       </c>
       <c r="BB7">
-        <v>17</v>
+        <v>1.39</v>
       </c>
       <c r="BC7">
-        <v>22</v>
+        <v>1.39</v>
       </c>
       <c r="BD7">
-        <v>36</v>
+        <v>1.39</v>
       </c>
       <c r="BE7">
-        <v>100</v>
+        <v>1.39</v>
       </c>
       <c r="BF7">
-        <v>19</v>
+        <v>1.55</v>
       </c>
       <c r="BG7">
-        <v>46</v>
+        <v>1.55</v>
       </c>
       <c r="BH7">
-        <v>2.54</v>
+        <v>1000</v>
       </c>
       <c r="BI7">
-        <v>2.36</v>
+        <v>1.04</v>
       </c>
       <c r="BJ7">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BK7">
-        <v>7.6</v>
+        <v>1.04</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>2.22</v>
+        <v>1.04</v>
       </c>
       <c r="BN7">
-        <v>4.5</v>
+        <v>1000</v>
       </c>
       <c r="BO7">
-        <v>4</v>
+        <v>1.04</v>
       </c>
       <c r="BP7">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="BQ7">
-        <v>9.199999999999999</v>
+        <v>1.04</v>
       </c>
       <c r="BR7">
         <v>1000</v>
       </c>
       <c r="BS7">
-        <v>13.5</v>
+        <v>1.04</v>
       </c>
       <c r="BT7">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="BU7">
-        <v>5.6</v>
+        <v>1.04</v>
       </c>
       <c r="BV7">
         <v>1000</v>
       </c>
       <c r="BW7">
-        <v>14</v>
+        <v>1.04</v>
       </c>
       <c r="BX7">
         <v>1000</v>
       </c>
       <c r="BY7">
-        <v>15.5</v>
+        <v>1.04</v>
       </c>
       <c r="BZ7">
         <v>1000</v>
       </c>
       <c r="CA7">
-        <v>14</v>
+        <v>1.04</v>
       </c>
       <c r="CB7" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
     </row>
     <row r="8" spans="1:80">
       <c r="A8" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B8" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C8" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D8" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E8" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="F8">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="G8">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="H8">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="I8">
         <v>4.8</v>
       </c>
       <c r="J8">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="K8">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="L8">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="M8">
         <v>1.14</v>
       </c>
       <c r="N8">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="O8">
         <v>1.61</v>
       </c>
       <c r="P8">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="Q8">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="R8">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="S8">
         <v>6.2</v>
       </c>
       <c r="T8">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="U8">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="V8">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="W8">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="X8">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="Y8">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="Z8">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="AA8">
-        <v>130</v>
+        <v>320</v>
       </c>
       <c r="AB8">
         <v>6.4</v>
       </c>
       <c r="AC8">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AD8">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AE8">
-        <v>95</v>
+        <v>250</v>
       </c>
       <c r="AF8">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AG8">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AH8">
-        <v>28</v>
+        <v>55</v>
       </c>
       <c r="AI8">
-        <v>530</v>
+        <v>690</v>
       </c>
       <c r="AJ8">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AK8">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="AL8">
-        <v>75</v>
+        <v>200</v>
       </c>
       <c r="AM8">
         <v>500</v>
       </c>
       <c r="AN8">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="AO8">
-        <v>180</v>
+        <v>690</v>
       </c>
       <c r="AP8">
         <v>7.2</v>
@@ -2506,10 +2518,10 @@
         <v>10</v>
       </c>
       <c r="AR8">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AS8">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AT8">
         <v>5.8</v>
@@ -2524,97 +2536,97 @@
         <v>36</v>
       </c>
       <c r="AX8">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AY8">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AZ8">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="BA8">
-        <v>75</v>
+        <v>42</v>
       </c>
       <c r="BB8">
-        <v>22</v>
+        <v>16.5</v>
       </c>
       <c r="BC8">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="BD8">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="BE8">
         <v>100</v>
       </c>
       <c r="BF8">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="BG8">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="BH8">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="BI8">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="BJ8">
         <v>12.5</v>
       </c>
       <c r="BK8">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="BL8">
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>13</v>
+        <v>2.24</v>
       </c>
       <c r="BN8">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="BO8">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BP8">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BQ8">
-        <v>7.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BR8">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="BS8">
-        <v>10.5</v>
+        <v>13.5</v>
       </c>
       <c r="BT8">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BU8">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="BV8">
         <v>1000</v>
       </c>
       <c r="BW8">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="BX8">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="BY8">
-        <v>11.5</v>
+        <v>15</v>
       </c>
       <c r="BZ8">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="CA8">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="CB8" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
     </row>
     <row r="9" spans="1:80">
@@ -2622,276 +2634,276 @@
         <v>84</v>
       </c>
       <c r="B9" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C9" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D9" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E9" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="F9">
+        <v>2.14</v>
+      </c>
+      <c r="G9">
+        <v>2.16</v>
+      </c>
+      <c r="H9">
+        <v>4.4</v>
+      </c>
+      <c r="I9">
+        <v>4.7</v>
+      </c>
+      <c r="J9">
+        <v>3.1</v>
+      </c>
+      <c r="K9">
+        <v>3.2</v>
+      </c>
+      <c r="L9">
+        <v>1.64</v>
+      </c>
+      <c r="M9">
+        <v>1.14</v>
+      </c>
+      <c r="N9">
+        <v>2.6</v>
+      </c>
+      <c r="O9">
         <v>1.6</v>
       </c>
-      <c r="G9">
-        <v>1.62</v>
-      </c>
-      <c r="H9">
-        <v>7.6</v>
-      </c>
-      <c r="I9">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="J9">
-        <v>3.85</v>
-      </c>
-      <c r="K9">
-        <v>4</v>
-      </c>
-      <c r="L9">
-        <v>1.53</v>
-      </c>
-      <c r="M9">
-        <v>1.11</v>
-      </c>
-      <c r="N9">
-        <v>2.96</v>
-      </c>
-      <c r="O9">
-        <v>1.48</v>
-      </c>
       <c r="P9">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="Q9">
-        <v>2.46</v>
+        <v>2.88</v>
       </c>
       <c r="R9">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="S9">
-        <v>5</v>
+        <v>6.2</v>
       </c>
       <c r="T9">
-        <v>2.42</v>
+        <v>2.28</v>
       </c>
       <c r="U9">
-        <v>1.64</v>
+        <v>1.7</v>
       </c>
       <c r="V9">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="W9">
-        <v>2.6</v>
+        <v>1.86</v>
       </c>
       <c r="X9">
+        <v>8.4</v>
+      </c>
+      <c r="Y9">
+        <v>11.5</v>
+      </c>
+      <c r="Z9">
+        <v>32</v>
+      </c>
+      <c r="AA9">
+        <v>130</v>
+      </c>
+      <c r="AB9">
+        <v>6.6</v>
+      </c>
+      <c r="AC9">
+        <v>7.2</v>
+      </c>
+      <c r="AD9">
+        <v>22</v>
+      </c>
+      <c r="AE9">
+        <v>95</v>
+      </c>
+      <c r="AF9">
+        <v>11.5</v>
+      </c>
+      <c r="AG9">
+        <v>13</v>
+      </c>
+      <c r="AH9">
+        <v>28</v>
+      </c>
+      <c r="AI9">
+        <v>530</v>
+      </c>
+      <c r="AJ9">
+        <v>29</v>
+      </c>
+      <c r="AK9">
+        <v>32</v>
+      </c>
+      <c r="AL9">
+        <v>75</v>
+      </c>
+      <c r="AM9">
+        <v>1000</v>
+      </c>
+      <c r="AN9">
+        <v>32</v>
+      </c>
+      <c r="AO9">
+        <v>180</v>
+      </c>
+      <c r="AP9">
+        <v>7.4</v>
+      </c>
+      <c r="AQ9">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AR9">
+        <v>24</v>
+      </c>
+      <c r="AS9">
+        <v>38</v>
+      </c>
+      <c r="AT9">
+        <v>6</v>
+      </c>
+      <c r="AU9">
+        <v>6.6</v>
+      </c>
+      <c r="AV9">
+        <v>18</v>
+      </c>
+      <c r="AW9">
+        <v>65</v>
+      </c>
+      <c r="AX9">
         <v>10</v>
       </c>
-      <c r="Y9">
-        <v>19</v>
-      </c>
-      <c r="Z9">
-        <v>400</v>
-      </c>
-      <c r="AA9">
-        <v>330</v>
-      </c>
-      <c r="AB9">
-        <v>6.2</v>
-      </c>
-      <c r="AC9">
-        <v>10.5</v>
-      </c>
-      <c r="AD9">
-        <v>34</v>
-      </c>
-      <c r="AE9">
-        <v>180</v>
-      </c>
-      <c r="AF9">
-        <v>8</v>
-      </c>
-      <c r="AG9">
+      <c r="AY9">
         <v>11</v>
       </c>
-      <c r="AH9">
-        <v>34</v>
-      </c>
-      <c r="AI9">
-        <v>200</v>
-      </c>
-      <c r="AJ9">
-        <v>15.5</v>
-      </c>
-      <c r="AK9">
+      <c r="AZ9">
+        <v>23</v>
+      </c>
+      <c r="BA9">
+        <v>75</v>
+      </c>
+      <c r="BB9">
         <v>22</v>
       </c>
-      <c r="AL9">
-        <v>65</v>
-      </c>
-      <c r="AM9">
-        <v>580</v>
-      </c>
-      <c r="AN9">
-        <v>14.5</v>
-      </c>
-      <c r="AO9">
-        <v>360</v>
-      </c>
-      <c r="AP9">
-        <v>9</v>
-      </c>
-      <c r="AQ9">
-        <v>17</v>
-      </c>
-      <c r="AR9">
-        <v>55</v>
-      </c>
-      <c r="AS9">
-        <v>11.5</v>
-      </c>
-      <c r="AT9">
-        <v>5.4</v>
-      </c>
-      <c r="AU9">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AV9">
-        <v>29</v>
-      </c>
-      <c r="AW9">
-        <v>11</v>
-      </c>
-      <c r="AX9">
-        <v>7.2</v>
-      </c>
-      <c r="AY9">
-        <v>9.6</v>
-      </c>
-      <c r="AZ9">
-        <v>30</v>
-      </c>
-      <c r="BA9">
-        <v>11.5</v>
-      </c>
-      <c r="BB9">
-        <v>13.5</v>
-      </c>
       <c r="BC9">
-        <v>19.5</v>
+        <v>24</v>
       </c>
       <c r="BD9">
         <v>50</v>
       </c>
       <c r="BE9">
-        <v>11.5</v>
+        <v>100</v>
       </c>
       <c r="BF9">
+        <v>25</v>
+      </c>
+      <c r="BG9">
+        <v>42</v>
+      </c>
+      <c r="BH9">
+        <v>2.72</v>
+      </c>
+      <c r="BI9">
+        <v>2.38</v>
+      </c>
+      <c r="BJ9">
         <v>12.5</v>
       </c>
-      <c r="BG9">
-        <v>11.5</v>
-      </c>
-      <c r="BH9">
-        <v>2.98</v>
-      </c>
-      <c r="BI9">
-        <v>2.42</v>
-      </c>
-      <c r="BJ9">
-        <v>13.5</v>
-      </c>
       <c r="BK9">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="BL9">
         <v>1000</v>
       </c>
       <c r="BM9">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BN9">
-        <v>3.85</v>
+        <v>4.7</v>
       </c>
       <c r="BO9">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="BP9">
-        <v>12</v>
+        <v>18.5</v>
       </c>
       <c r="BQ9">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="BR9">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BS9">
+        <v>9.4</v>
+      </c>
+      <c r="BT9">
+        <v>8</v>
+      </c>
+      <c r="BU9">
+        <v>5.5</v>
+      </c>
+      <c r="BV9">
+        <v>55</v>
+      </c>
+      <c r="BW9">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BX9">
+        <v>85</v>
+      </c>
+      <c r="BY9">
+        <v>10</v>
+      </c>
+      <c r="BZ9">
+        <v>50</v>
+      </c>
+      <c r="CA9">
         <v>9.6</v>
       </c>
-      <c r="BT9">
-        <v>11.5</v>
-      </c>
-      <c r="BU9">
-        <v>6</v>
-      </c>
-      <c r="BV9">
-        <v>1000</v>
-      </c>
-      <c r="BW9">
-        <v>11</v>
-      </c>
-      <c r="BX9">
-        <v>1000</v>
-      </c>
-      <c r="BY9">
-        <v>11.5</v>
-      </c>
-      <c r="BZ9">
-        <v>1000</v>
-      </c>
-      <c r="CA9">
-        <v>9</v>
-      </c>
       <c r="CB9" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
     </row>
     <row r="10" spans="1:80">
       <c r="A10" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B10" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C10" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D10" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E10" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="F10">
-        <v>4.7</v>
+        <v>1.63</v>
       </c>
       <c r="G10">
-        <v>4.8</v>
+        <v>1.64</v>
       </c>
       <c r="H10">
-        <v>2.02</v>
+        <v>7.6</v>
       </c>
       <c r="I10">
-        <v>2.06</v>
+        <v>7.8</v>
       </c>
       <c r="J10">
-        <v>3.3</v>
+        <v>3.85</v>
       </c>
       <c r="K10">
-        <v>3.45</v>
+        <v>3.95</v>
       </c>
       <c r="L10">
         <v>1.53</v>
@@ -2903,13 +2915,13 @@
         <v>2.96</v>
       </c>
       <c r="O10">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="P10">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="Q10">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="R10">
         <v>1.23</v>
@@ -2918,133 +2930,133 @@
         <v>5</v>
       </c>
       <c r="T10">
-        <v>2.1</v>
+        <v>2.38</v>
       </c>
       <c r="U10">
-        <v>1.81</v>
+        <v>1.64</v>
       </c>
       <c r="V10">
-        <v>1.95</v>
+        <v>1.14</v>
       </c>
       <c r="W10">
-        <v>1.26</v>
+        <v>2.56</v>
       </c>
       <c r="X10">
+        <v>10</v>
+      </c>
+      <c r="Y10">
+        <v>32</v>
+      </c>
+      <c r="Z10">
+        <v>65</v>
+      </c>
+      <c r="AA10">
+        <v>310</v>
+      </c>
+      <c r="AB10">
+        <v>7</v>
+      </c>
+      <c r="AC10">
         <v>10.5</v>
       </c>
-      <c r="Y10">
-        <v>7</v>
-      </c>
-      <c r="Z10">
-        <v>12</v>
-      </c>
-      <c r="AA10">
-        <v>27</v>
-      </c>
-      <c r="AB10">
-        <v>15</v>
-      </c>
-      <c r="AC10">
+      <c r="AD10">
+        <v>34</v>
+      </c>
+      <c r="AE10">
+        <v>180</v>
+      </c>
+      <c r="AF10">
+        <v>8</v>
+      </c>
+      <c r="AG10">
+        <v>11</v>
+      </c>
+      <c r="AH10">
+        <v>34</v>
+      </c>
+      <c r="AI10">
+        <v>190</v>
+      </c>
+      <c r="AJ10">
+        <v>15.5</v>
+      </c>
+      <c r="AK10">
+        <v>22</v>
+      </c>
+      <c r="AL10">
+        <v>65</v>
+      </c>
+      <c r="AM10">
+        <v>700</v>
+      </c>
+      <c r="AN10">
+        <v>14.5</v>
+      </c>
+      <c r="AO10">
+        <v>310</v>
+      </c>
+      <c r="AP10">
+        <v>9</v>
+      </c>
+      <c r="AQ10">
+        <v>17</v>
+      </c>
+      <c r="AR10">
+        <v>50</v>
+      </c>
+      <c r="AS10">
+        <v>9.4</v>
+      </c>
+      <c r="AT10">
+        <v>5.4</v>
+      </c>
+      <c r="AU10">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV10">
+        <v>28</v>
+      </c>
+      <c r="AW10">
         <v>9.199999999999999</v>
       </c>
-      <c r="AD10">
-        <v>13</v>
-      </c>
-      <c r="AE10">
+      <c r="AX10">
+        <v>7.2</v>
+      </c>
+      <c r="AY10">
+        <v>9.6</v>
+      </c>
+      <c r="AZ10">
         <v>30</v>
       </c>
-      <c r="AF10">
-        <v>34</v>
-      </c>
-      <c r="AG10">
-        <v>22</v>
-      </c>
-      <c r="AH10">
-        <v>27</v>
-      </c>
-      <c r="AI10">
-        <v>55</v>
-      </c>
-      <c r="AJ10">
-        <v>130</v>
-      </c>
-      <c r="AK10">
-        <v>85</v>
-      </c>
-      <c r="AL10">
-        <v>110</v>
-      </c>
-      <c r="AM10">
-        <v>190</v>
-      </c>
-      <c r="AN10">
-        <v>120</v>
-      </c>
-      <c r="AO10">
-        <v>26</v>
-      </c>
-      <c r="AP10">
-        <v>8.6</v>
-      </c>
-      <c r="AQ10">
-        <v>6.4</v>
-      </c>
-      <c r="AR10">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AS10">
-        <v>21</v>
-      </c>
-      <c r="AT10">
-        <v>12</v>
-      </c>
-      <c r="AU10">
-        <v>7</v>
-      </c>
-      <c r="AV10">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AW10">
-        <v>23</v>
-      </c>
-      <c r="AX10">
-        <v>30</v>
-      </c>
-      <c r="AY10">
-        <v>17.5</v>
-      </c>
-      <c r="AZ10">
-        <v>22</v>
-      </c>
       <c r="BA10">
-        <v>44</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB10">
-        <v>7.6</v>
+        <v>13.5</v>
       </c>
       <c r="BC10">
-        <v>7.4</v>
+        <v>19.5</v>
       </c>
       <c r="BD10">
-        <v>7.6</v>
+        <v>50</v>
       </c>
       <c r="BE10">
-        <v>7.8</v>
+        <v>11</v>
       </c>
       <c r="BF10">
-        <v>7.6</v>
+        <v>12.5</v>
       </c>
       <c r="BG10">
-        <v>18.5</v>
+        <v>9.4</v>
       </c>
       <c r="BH10">
-        <v>2.9</v>
+        <v>2.98</v>
       </c>
       <c r="BI10">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="BJ10">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="BK10">
         <v>6.6</v>
@@ -3053,52 +3065,294 @@
         <v>1000</v>
       </c>
       <c r="BM10">
+        <v>12</v>
+      </c>
+      <c r="BN10">
+        <v>3.85</v>
+      </c>
+      <c r="BO10">
+        <v>3.3</v>
+      </c>
+      <c r="BP10">
+        <v>12</v>
+      </c>
+      <c r="BQ10">
+        <v>6.2</v>
+      </c>
+      <c r="BR10">
+        <v>1000</v>
+      </c>
+      <c r="BS10">
+        <v>9.6</v>
+      </c>
+      <c r="BT10">
+        <v>11.5</v>
+      </c>
+      <c r="BU10">
+        <v>6</v>
+      </c>
+      <c r="BV10">
+        <v>1000</v>
+      </c>
+      <c r="BW10">
+        <v>11</v>
+      </c>
+      <c r="BX10">
+        <v>1000</v>
+      </c>
+      <c r="BY10">
+        <v>11.5</v>
+      </c>
+      <c r="BZ10">
+        <v>1000</v>
+      </c>
+      <c r="CA10">
+        <v>9</v>
+      </c>
+      <c r="CB10" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="11" spans="1:80">
+      <c r="A11" t="s">
+        <v>85</v>
+      </c>
+      <c r="B11" t="s">
+        <v>86</v>
+      </c>
+      <c r="C11" t="s">
+        <v>93</v>
+      </c>
+      <c r="D11" t="s">
+        <v>103</v>
+      </c>
+      <c r="E11" t="s">
+        <v>113</v>
+      </c>
+      <c r="F11">
+        <v>4.7</v>
+      </c>
+      <c r="G11">
+        <v>4.8</v>
+      </c>
+      <c r="H11">
+        <v>2</v>
+      </c>
+      <c r="I11">
+        <v>2.02</v>
+      </c>
+      <c r="J11">
+        <v>3.35</v>
+      </c>
+      <c r="K11">
+        <v>3.5</v>
+      </c>
+      <c r="L11">
+        <v>1.53</v>
+      </c>
+      <c r="M11">
+        <v>1.11</v>
+      </c>
+      <c r="N11">
+        <v>3</v>
+      </c>
+      <c r="O11">
+        <v>1.48</v>
+      </c>
+      <c r="P11">
+        <v>1.65</v>
+      </c>
+      <c r="Q11">
+        <v>2.46</v>
+      </c>
+      <c r="R11">
+        <v>1.23</v>
+      </c>
+      <c r="S11">
+        <v>5</v>
+      </c>
+      <c r="T11">
+        <v>2.1</v>
+      </c>
+      <c r="U11">
+        <v>1.81</v>
+      </c>
+      <c r="V11">
+        <v>1.98</v>
+      </c>
+      <c r="W11">
+        <v>1.26</v>
+      </c>
+      <c r="X11">
+        <v>10.5</v>
+      </c>
+      <c r="Y11">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="Z11">
+        <v>12</v>
+      </c>
+      <c r="AA11">
+        <v>26</v>
+      </c>
+      <c r="AB11">
+        <v>15</v>
+      </c>
+      <c r="AC11">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD11">
+        <v>12.5</v>
+      </c>
+      <c r="AE11">
+        <v>29</v>
+      </c>
+      <c r="AF11">
+        <v>34</v>
+      </c>
+      <c r="AG11">
+        <v>22</v>
+      </c>
+      <c r="AH11">
+        <v>27</v>
+      </c>
+      <c r="AI11">
+        <v>55</v>
+      </c>
+      <c r="AJ11">
+        <v>130</v>
+      </c>
+      <c r="AK11">
+        <v>85</v>
+      </c>
+      <c r="AL11">
+        <v>100</v>
+      </c>
+      <c r="AM11">
+        <v>190</v>
+      </c>
+      <c r="AN11">
+        <v>110</v>
+      </c>
+      <c r="AO11">
+        <v>21</v>
+      </c>
+      <c r="AP11">
+        <v>8.6</v>
+      </c>
+      <c r="AQ11">
+        <v>6.8</v>
+      </c>
+      <c r="AR11">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AS11">
+        <v>21</v>
+      </c>
+      <c r="AT11">
+        <v>12</v>
+      </c>
+      <c r="AU11">
+        <v>7</v>
+      </c>
+      <c r="AV11">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AW11">
+        <v>23</v>
+      </c>
+      <c r="AX11">
         <v>14.5</v>
       </c>
-      <c r="BN10">
-        <v>8</v>
-      </c>
-      <c r="BO10">
-        <v>5.3</v>
-      </c>
-      <c r="BP10">
-        <v>1000</v>
-      </c>
-      <c r="BQ10">
+      <c r="AY11">
+        <v>17.5</v>
+      </c>
+      <c r="AZ11">
+        <v>22</v>
+      </c>
+      <c r="BA11">
+        <v>44</v>
+      </c>
+      <c r="BB11">
+        <v>7.4</v>
+      </c>
+      <c r="BC11">
+        <v>28</v>
+      </c>
+      <c r="BD11">
+        <v>7.2</v>
+      </c>
+      <c r="BE11">
+        <v>7.4</v>
+      </c>
+      <c r="BF11">
+        <v>7.2</v>
+      </c>
+      <c r="BG11">
+        <v>17.5</v>
+      </c>
+      <c r="BH11">
+        <v>2.86</v>
+      </c>
+      <c r="BI11">
+        <v>2.46</v>
+      </c>
+      <c r="BJ11">
         <v>11.5</v>
       </c>
-      <c r="BR10">
-        <v>1000</v>
-      </c>
-      <c r="BS10">
+      <c r="BK11">
+        <v>7</v>
+      </c>
+      <c r="BL11">
+        <v>1000</v>
+      </c>
+      <c r="BM11">
+        <v>16</v>
+      </c>
+      <c r="BN11">
+        <v>7.8</v>
+      </c>
+      <c r="BO11">
+        <v>5.8</v>
+      </c>
+      <c r="BP11">
+        <v>1000</v>
+      </c>
+      <c r="BQ11">
         <v>12.5</v>
       </c>
-      <c r="BT10">
+      <c r="BR11">
+        <v>1000</v>
+      </c>
+      <c r="BS11">
+        <v>13</v>
+      </c>
+      <c r="BT11">
         <v>4.5</v>
       </c>
-      <c r="BU10">
-        <v>3.5</v>
-      </c>
-      <c r="BV10">
-        <v>1000</v>
-      </c>
-      <c r="BW10">
-        <v>7.8</v>
-      </c>
-      <c r="BX10">
-        <v>1000</v>
-      </c>
-      <c r="BY10">
-        <v>11</v>
-      </c>
-      <c r="BZ10">
-        <v>1000</v>
-      </c>
-      <c r="CA10">
-        <v>11</v>
-      </c>
-      <c r="CB10" t="s">
-        <v>110</v>
+      <c r="BU11">
+        <v>3.6</v>
+      </c>
+      <c r="BV11">
+        <v>1000</v>
+      </c>
+      <c r="BW11">
+        <v>8.4</v>
+      </c>
+      <c r="BX11">
+        <v>1000</v>
+      </c>
+      <c r="BY11">
+        <v>12</v>
+      </c>
+      <c r="BZ11">
+        <v>1000</v>
+      </c>
+      <c r="CA11">
+        <v>12</v>
+      </c>
+      <c r="CB11" t="s">
+        <v>114</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-28.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-28.xlsx
@@ -358,7 +358,7 @@
     <t>Athletic Club</t>
   </si>
   <si>
-    <t>2026-07-28 03:58:18</t>
+    <t>2026-07-28 06:05:36</t>
   </si>
 </sst>
 </file>
@@ -952,22 +952,22 @@
         <v>104</v>
       </c>
       <c r="F2">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="G2">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="H2">
         <v>2.2</v>
       </c>
       <c r="I2">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="J2">
         <v>3.7</v>
       </c>
       <c r="K2">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L2">
         <v>1.34</v>
@@ -976,88 +976,88 @@
         <v>1.05</v>
       </c>
       <c r="N2">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="O2">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="P2">
-        <v>2.24</v>
+        <v>2.32</v>
       </c>
       <c r="Q2">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="R2">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="S2">
-        <v>2.94</v>
+        <v>2.82</v>
       </c>
       <c r="T2">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="U2">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="V2">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="W2">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="X2">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="Y2">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="Z2">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AA2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AB2">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AC2">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD2">
         <v>11.5</v>
       </c>
       <c r="AE2">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AF2">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="AG2">
         <v>15</v>
       </c>
       <c r="AH2">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AI2">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AJ2">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AK2">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AL2">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="AM2">
-        <v>190</v>
+        <v>70</v>
       </c>
       <c r="AN2">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="AO2">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AP2">
         <v>16</v>
@@ -1066,28 +1066,28 @@
         <v>11</v>
       </c>
       <c r="AR2">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AS2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AT2">
         <v>14</v>
       </c>
       <c r="AU2">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AV2">
         <v>10</v>
       </c>
       <c r="AW2">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AX2">
         <v>23</v>
       </c>
       <c r="AY2">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AZ2">
         <v>13.5</v>
@@ -1099,55 +1099,55 @@
         <v>46</v>
       </c>
       <c r="BC2">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BD2">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BE2">
         <v>55</v>
       </c>
       <c r="BF2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BG2">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BH2">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BI2">
         <v>3.6</v>
       </c>
       <c r="BJ2">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK2">
-        <v>5.9</v>
+        <v>5.6</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="BN2">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BO2">
         <v>6</v>
       </c>
       <c r="BP2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BQ2">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="BR2">
         <v>32</v>
       </c>
       <c r="BS2">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="BT2">
         <v>5.3</v>
@@ -1159,13 +1159,13 @@
         <v>15</v>
       </c>
       <c r="BW2">
-        <v>8.4</v>
+        <v>11.5</v>
       </c>
       <c r="BX2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BY2">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="BZ2">
         <v>0</v>
@@ -1200,16 +1200,16 @@
         <v>2.42</v>
       </c>
       <c r="H3">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="I3">
         <v>3.2</v>
       </c>
       <c r="J3">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="K3">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="L3">
         <v>1.33</v>
@@ -1218,70 +1218,70 @@
         <v>1.05</v>
       </c>
       <c r="N3">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="O3">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="P3">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="Q3">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="R3">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="S3">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="T3">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="U3">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="V3">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W3">
         <v>1.7</v>
       </c>
       <c r="X3">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="Y3">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="Z3">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AA3">
-        <v>280</v>
+        <v>48</v>
       </c>
       <c r="AB3">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AC3">
         <v>9</v>
       </c>
       <c r="AD3">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AE3">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="AF3">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AG3">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AH3">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AI3">
-        <v>70</v>
+        <v>36</v>
       </c>
       <c r="AJ3">
         <v>32</v>
@@ -1290,10 +1290,10 @@
         <v>23</v>
       </c>
       <c r="AL3">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AM3">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AN3">
         <v>13.5</v>
@@ -1302,61 +1302,61 @@
         <v>21</v>
       </c>
       <c r="AP3">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AQ3">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AR3">
         <v>21</v>
       </c>
       <c r="AS3">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="AT3">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AU3">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AV3">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AW3">
         <v>27</v>
       </c>
       <c r="AX3">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AY3">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ3">
+        <v>13.5</v>
+      </c>
+      <c r="BA3">
+        <v>32</v>
+      </c>
+      <c r="BB3">
+        <v>29</v>
+      </c>
+      <c r="BC3">
+        <v>20</v>
+      </c>
+      <c r="BD3">
+        <v>27</v>
+      </c>
+      <c r="BE3">
+        <v>55</v>
+      </c>
+      <c r="BF3">
         <v>12.5</v>
-      </c>
-      <c r="BA3">
-        <v>30</v>
-      </c>
-      <c r="BB3">
-        <v>27</v>
-      </c>
-      <c r="BC3">
-        <v>19.5</v>
-      </c>
-      <c r="BD3">
-        <v>26</v>
-      </c>
-      <c r="BE3">
-        <v>46</v>
-      </c>
-      <c r="BF3">
-        <v>11.5</v>
       </c>
       <c r="BG3">
         <v>19</v>
       </c>
       <c r="BH3">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BI3">
         <v>3.75</v>
@@ -1365,31 +1365,31 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BK3">
-        <v>5.9</v>
+        <v>5.6</v>
       </c>
       <c r="BL3">
         <v>80</v>
       </c>
       <c r="BM3">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="BN3">
         <v>5.6</v>
       </c>
       <c r="BO3">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BP3">
         <v>16</v>
       </c>
       <c r="BQ3">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="BR3">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BS3">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BT3">
         <v>6.6</v>
@@ -1401,19 +1401,19 @@
         <v>21</v>
       </c>
       <c r="BW3">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="BX3">
         <v>28</v>
       </c>
       <c r="BY3">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BZ3">
         <v>17.5</v>
       </c>
       <c r="CA3">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB3" t="s">
         <v>114</v>
@@ -1678,16 +1678,16 @@
         <v>107</v>
       </c>
       <c r="F5">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="G5">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="H5">
-        <v>2.42</v>
+        <v>2.48</v>
       </c>
       <c r="I5">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="J5">
         <v>3</v>
@@ -1696,22 +1696,22 @@
         <v>3.1</v>
       </c>
       <c r="L5">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="M5">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="N5">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="O5">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="P5">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="Q5">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="R5">
         <v>1.18</v>
@@ -1720,13 +1720,13 @@
         <v>5.8</v>
       </c>
       <c r="T5">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="U5">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="V5">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="W5">
         <v>1.35</v>
@@ -1744,7 +1744,7 @@
         <v>85</v>
       </c>
       <c r="AB5">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC5">
         <v>7.2</v>
@@ -1756,7 +1756,7 @@
         <v>85</v>
       </c>
       <c r="AF5">
-        <v>42</v>
+        <v>130</v>
       </c>
       <c r="AG5">
         <v>17</v>
@@ -1780,13 +1780,13 @@
         <v>500</v>
       </c>
       <c r="AN5">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AO5">
         <v>44</v>
       </c>
       <c r="AP5">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AQ5">
         <v>6.4</v>
@@ -1795,55 +1795,55 @@
         <v>12</v>
       </c>
       <c r="AS5">
-        <v>9.4</v>
+        <v>32</v>
       </c>
       <c r="AT5">
         <v>8.6</v>
       </c>
       <c r="AU5">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AV5">
         <v>10.5</v>
       </c>
       <c r="AW5">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AX5">
-        <v>9.4</v>
+        <v>11.5</v>
       </c>
       <c r="AY5">
         <v>14</v>
       </c>
       <c r="AZ5">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="BA5">
         <v>32</v>
       </c>
       <c r="BB5">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="BC5">
         <v>30</v>
       </c>
       <c r="BD5">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="BE5">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BF5">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="BG5">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BH5">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="BI5">
-        <v>2.42</v>
+        <v>2.24</v>
       </c>
       <c r="BJ5">
         <v>12</v>
@@ -1855,43 +1855,43 @@
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BN5">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BO5">
-        <v>5.8</v>
+        <v>5.2</v>
       </c>
       <c r="BP5">
         <v>1000</v>
       </c>
       <c r="BQ5">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BR5">
         <v>1000</v>
       </c>
       <c r="BS5">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BT5">
         <v>5.2</v>
       </c>
       <c r="BU5">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="BV5">
         <v>1000</v>
       </c>
       <c r="BW5">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BX5">
         <v>1000</v>
       </c>
       <c r="BY5">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BZ5">
         <v>0</v>
@@ -1920,22 +1920,22 @@
         <v>108</v>
       </c>
       <c r="F6">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="G6">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="H6">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="I6">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="J6">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="K6">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="L6">
         <v>1.2</v>
@@ -1944,103 +1944,103 @@
         <v>1.02</v>
       </c>
       <c r="N6">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="O6">
         <v>1.1</v>
       </c>
       <c r="P6">
-        <v>3.65</v>
+        <v>3.85</v>
       </c>
       <c r="Q6">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="R6">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="S6">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="T6">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="U6">
-        <v>2.72</v>
+        <v>2.78</v>
       </c>
       <c r="V6">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="W6">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="X6">
-        <v>950</v>
+        <v>130</v>
       </c>
       <c r="Y6">
         <v>21</v>
       </c>
       <c r="Z6">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AA6">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AB6">
-        <v>950</v>
+        <v>65</v>
       </c>
       <c r="AC6">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AD6">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AE6">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AF6">
         <v>450</v>
       </c>
       <c r="AG6">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="AH6">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="AI6">
         <v>22</v>
       </c>
       <c r="AJ6">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="AK6">
-        <v>400</v>
+        <v>85</v>
       </c>
       <c r="AL6">
-        <v>200</v>
+        <v>120</v>
       </c>
       <c r="AM6">
-        <v>160</v>
+        <v>65</v>
       </c>
       <c r="AN6">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="AO6">
         <v>4</v>
       </c>
       <c r="AP6">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="AQ6">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="AR6">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AS6">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="AT6">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="AU6">
         <v>13.5</v>
@@ -2052,46 +2052,46 @@
         <v>12</v>
       </c>
       <c r="AX6">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="AY6">
-        <v>18.5</v>
+        <v>23</v>
       </c>
       <c r="AZ6">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="BA6">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="BB6">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="BC6">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="BD6">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="BE6">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="BF6">
-        <v>7.6</v>
+        <v>26</v>
       </c>
       <c r="BG6">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="BH6">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BI6">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BJ6">
         <v>9.199999999999999</v>
       </c>
       <c r="BK6">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BL6">
         <v>1000</v>
@@ -2103,19 +2103,19 @@
         <v>11</v>
       </c>
       <c r="BO6">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BP6">
         <v>1000</v>
       </c>
       <c r="BQ6">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BR6">
         <v>1000</v>
       </c>
       <c r="BS6">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT6">
         <v>5</v>
@@ -2130,16 +2130,16 @@
         <v>5.3</v>
       </c>
       <c r="BX6">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BY6">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BZ6">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="CA6">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="CB6" t="s">
         <v>114</v>
@@ -2162,22 +2162,22 @@
         <v>109</v>
       </c>
       <c r="F7">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="G7">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="H7">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="I7">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="J7">
         <v>3.2</v>
       </c>
       <c r="K7">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="L7">
         <v>1.55</v>
@@ -2264,7 +2264,7 @@
         <v>580</v>
       </c>
       <c r="AN7">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AO7">
         <v>500</v>
@@ -2273,10 +2273,10 @@
         <v>4.9</v>
       </c>
       <c r="AQ7">
+        <v>1.35</v>
+      </c>
+      <c r="AR7">
         <v>1.36</v>
-      </c>
-      <c r="AR7">
-        <v>1.37</v>
       </c>
       <c r="AS7">
         <v>1.38</v>
@@ -2288,34 +2288,34 @@
         <v>4.4</v>
       </c>
       <c r="AV7">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AW7">
         <v>1.36</v>
       </c>
       <c r="AX7">
+        <v>1.37</v>
+      </c>
+      <c r="AY7">
+        <v>1.37</v>
+      </c>
+      <c r="AZ7">
+        <v>1.35</v>
+      </c>
+      <c r="BA7">
         <v>1.38</v>
       </c>
-      <c r="AY7">
+      <c r="BB7">
         <v>1.38</v>
       </c>
-      <c r="AZ7">
-        <v>1.36</v>
-      </c>
-      <c r="BA7">
-        <v>1.39</v>
-      </c>
-      <c r="BB7">
-        <v>1.39</v>
-      </c>
       <c r="BC7">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="BD7">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="BE7">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="BF7">
         <v>1.55</v>
@@ -2404,19 +2404,19 @@
         <v>110</v>
       </c>
       <c r="F8">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="G8">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="H8">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="I8">
         <v>4.8</v>
       </c>
       <c r="J8">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="K8">
         <v>3.2</v>
@@ -2428,49 +2428,49 @@
         <v>1.14</v>
       </c>
       <c r="N8">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="O8">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="P8">
         <v>1.49</v>
       </c>
       <c r="Q8">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="R8">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="S8">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="T8">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="U8">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="V8">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="W8">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="X8">
         <v>7.8</v>
       </c>
       <c r="Y8">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Z8">
         <v>50</v>
       </c>
       <c r="AA8">
-        <v>320</v>
+        <v>140</v>
       </c>
       <c r="AB8">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AC8">
         <v>7.8</v>
@@ -2479,34 +2479,34 @@
         <v>21</v>
       </c>
       <c r="AE8">
-        <v>250</v>
+        <v>95</v>
       </c>
       <c r="AF8">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AG8">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AH8">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="AI8">
-        <v>690</v>
+        <v>260</v>
       </c>
       <c r="AJ8">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AK8">
-        <v>60</v>
+        <v>34</v>
       </c>
       <c r="AL8">
-        <v>200</v>
+        <v>75</v>
       </c>
       <c r="AM8">
         <v>500</v>
       </c>
       <c r="AN8">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="AO8">
         <v>690</v>
@@ -2518,10 +2518,10 @@
         <v>10</v>
       </c>
       <c r="AR8">
-        <v>19.5</v>
+        <v>25</v>
       </c>
       <c r="AS8">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AT8">
         <v>5.8</v>
@@ -2530,43 +2530,43 @@
         <v>6.6</v>
       </c>
       <c r="AV8">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AW8">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="AX8">
         <v>9.4</v>
       </c>
       <c r="AY8">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AZ8">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="BA8">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="BB8">
-        <v>16.5</v>
+        <v>19.5</v>
       </c>
       <c r="BC8">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="BD8">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="BE8">
         <v>100</v>
       </c>
       <c r="BF8">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="BG8">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="BH8">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="BI8">
         <v>2.38</v>
@@ -2575,55 +2575,55 @@
         <v>12.5</v>
       </c>
       <c r="BK8">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="BL8">
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>2.24</v>
+        <v>15.5</v>
       </c>
       <c r="BN8">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BO8">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BP8">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BQ8">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BR8">
         <v>1000</v>
       </c>
       <c r="BS8">
+        <v>12</v>
+      </c>
+      <c r="BT8">
+        <v>7.8</v>
+      </c>
+      <c r="BU8">
+        <v>6.8</v>
+      </c>
+      <c r="BV8">
+        <v>55</v>
+      </c>
+      <c r="BW8">
+        <v>12.5</v>
+      </c>
+      <c r="BX8">
+        <v>1000</v>
+      </c>
+      <c r="BY8">
         <v>13.5</v>
       </c>
-      <c r="BT8">
-        <v>8</v>
-      </c>
-      <c r="BU8">
-        <v>6</v>
-      </c>
-      <c r="BV8">
-        <v>1000</v>
-      </c>
-      <c r="BW8">
-        <v>14</v>
-      </c>
-      <c r="BX8">
-        <v>1000</v>
-      </c>
-      <c r="BY8">
-        <v>15</v>
-      </c>
       <c r="BZ8">
         <v>1000</v>
       </c>
       <c r="CA8">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="CB8" t="s">
         <v>114</v>
@@ -2646,10 +2646,10 @@
         <v>111</v>
       </c>
       <c r="F9">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="G9">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="H9">
         <v>4.4</v>
@@ -2661,28 +2661,28 @@
         <v>3.1</v>
       </c>
       <c r="K9">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="L9">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="M9">
         <v>1.14</v>
       </c>
       <c r="N9">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="O9">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="P9">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="Q9">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="R9">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="S9">
         <v>6.2</v>
@@ -2691,22 +2691,22 @@
         <v>2.28</v>
       </c>
       <c r="U9">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="V9">
         <v>1.27</v>
       </c>
       <c r="W9">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="X9">
         <v>8.4</v>
       </c>
       <c r="Y9">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Z9">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AA9">
         <v>130</v>
@@ -2715,10 +2715,10 @@
         <v>6.6</v>
       </c>
       <c r="AC9">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AD9">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AE9">
         <v>95</v>
@@ -2733,7 +2733,7 @@
         <v>28</v>
       </c>
       <c r="AI9">
-        <v>530</v>
+        <v>130</v>
       </c>
       <c r="AJ9">
         <v>29</v>
@@ -2745,16 +2745,16 @@
         <v>75</v>
       </c>
       <c r="AM9">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN9">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AO9">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="AP9">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AQ9">
         <v>9.800000000000001</v>
@@ -2763,7 +2763,7 @@
         <v>24</v>
       </c>
       <c r="AS9">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AT9">
         <v>6</v>
@@ -2787,13 +2787,13 @@
         <v>23</v>
       </c>
       <c r="BA9">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="BB9">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BC9">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BD9">
         <v>50</v>
@@ -2805,19 +2805,19 @@
         <v>25</v>
       </c>
       <c r="BG9">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="BH9">
-        <v>2.72</v>
+        <v>2.82</v>
       </c>
       <c r="BI9">
-        <v>2.38</v>
+        <v>2.46</v>
       </c>
       <c r="BJ9">
         <v>12.5</v>
       </c>
       <c r="BK9">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BL9">
         <v>1000</v>
@@ -2826,46 +2826,46 @@
         <v>11</v>
       </c>
       <c r="BN9">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BO9">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="BP9">
         <v>18.5</v>
       </c>
       <c r="BQ9">
-        <v>7.2</v>
+        <v>14</v>
       </c>
       <c r="BR9">
         <v>46</v>
       </c>
       <c r="BS9">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT9">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BU9">
         <v>5.5</v>
       </c>
       <c r="BV9">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BW9">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BX9">
+        <v>1000</v>
+      </c>
+      <c r="BY9">
         <v>9.800000000000001</v>
-      </c>
-      <c r="BX9">
-        <v>85</v>
-      </c>
-      <c r="BY9">
-        <v>10</v>
       </c>
       <c r="BZ9">
         <v>50</v>
       </c>
       <c r="CA9">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB9" t="s">
         <v>114</v>
@@ -2888,64 +2888,64 @@
         <v>112</v>
       </c>
       <c r="F10">
+        <v>1.6</v>
+      </c>
+      <c r="G10">
         <v>1.63</v>
-      </c>
-      <c r="G10">
-        <v>1.64</v>
       </c>
       <c r="H10">
         <v>7.6</v>
       </c>
       <c r="I10">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="J10">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="K10">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="L10">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="M10">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="N10">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="O10">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="P10">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="Q10">
-        <v>2.46</v>
+        <v>2.4</v>
       </c>
       <c r="R10">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="S10">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="T10">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="U10">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="V10">
         <v>1.14</v>
       </c>
       <c r="W10">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="X10">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Y10">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="Z10">
         <v>65</v>
@@ -2960,7 +2960,7 @@
         <v>10.5</v>
       </c>
       <c r="AD10">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AE10">
         <v>180</v>
@@ -2972,7 +2972,7 @@
         <v>11</v>
       </c>
       <c r="AH10">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AI10">
         <v>190</v>
@@ -2984,7 +2984,7 @@
         <v>22</v>
       </c>
       <c r="AL10">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AM10">
         <v>700</v>
@@ -2996,28 +2996,28 @@
         <v>310</v>
       </c>
       <c r="AP10">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ10">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AR10">
         <v>50</v>
       </c>
       <c r="AS10">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AT10">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="AU10">
         <v>8.199999999999999</v>
       </c>
       <c r="AV10">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AW10">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX10">
         <v>7.2</v>
@@ -3026,31 +3026,31 @@
         <v>9.6</v>
       </c>
       <c r="AZ10">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="BA10">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB10">
         <v>13.5</v>
       </c>
       <c r="BC10">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BD10">
         <v>50</v>
       </c>
       <c r="BE10">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BF10">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BG10">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="BH10">
-        <v>2.98</v>
+        <v>3.1</v>
       </c>
       <c r="BI10">
         <v>2.42</v>
@@ -3059,16 +3059,16 @@
         <v>13.5</v>
       </c>
       <c r="BK10">
-        <v>6.6</v>
+        <v>5.9</v>
       </c>
       <c r="BL10">
         <v>1000</v>
       </c>
       <c r="BM10">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="BN10">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="BO10">
         <v>3.3</v>
@@ -3077,37 +3077,37 @@
         <v>12</v>
       </c>
       <c r="BQ10">
-        <v>6.2</v>
+        <v>5.6</v>
       </c>
       <c r="BR10">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BS10">
-        <v>9.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT10">
         <v>11.5</v>
       </c>
       <c r="BU10">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="BV10">
         <v>1000</v>
       </c>
       <c r="BW10">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="BX10">
         <v>1000</v>
       </c>
       <c r="BY10">
-        <v>11.5</v>
+        <v>9.6</v>
       </c>
       <c r="BZ10">
         <v>1000</v>
       </c>
       <c r="CA10">
-        <v>9</v>
+        <v>7.8</v>
       </c>
       <c r="CB10" t="s">
         <v>114</v>
@@ -3130,10 +3130,10 @@
         <v>113</v>
       </c>
       <c r="F11">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="G11">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="H11">
         <v>2</v>
@@ -3145,7 +3145,7 @@
         <v>3.35</v>
       </c>
       <c r="K11">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L11">
         <v>1.53</v>
@@ -3154,16 +3154,16 @@
         <v>1.11</v>
       </c>
       <c r="N11">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="O11">
         <v>1.48</v>
       </c>
       <c r="P11">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="Q11">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="R11">
         <v>1.23</v>
@@ -3181,7 +3181,7 @@
         <v>1.98</v>
       </c>
       <c r="W11">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="X11">
         <v>10.5</v>
@@ -3190,7 +3190,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="Z11">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AA11">
         <v>26</v>
@@ -3205,7 +3205,7 @@
         <v>12.5</v>
       </c>
       <c r="AE11">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AF11">
         <v>34</v>
@@ -3226,7 +3226,7 @@
         <v>85</v>
       </c>
       <c r="AL11">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AM11">
         <v>190</v>
@@ -3235,13 +3235,13 @@
         <v>110</v>
       </c>
       <c r="AO11">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="AP11">
         <v>8.6</v>
       </c>
       <c r="AQ11">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="AR11">
         <v>9.800000000000001</v>
@@ -3274,22 +3274,22 @@
         <v>44</v>
       </c>
       <c r="BB11">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC11">
         <v>28</v>
       </c>
       <c r="BD11">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="BE11">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="BF11">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="BG11">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BH11">
         <v>2.86</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-28.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-28.xlsx
@@ -358,7 +358,7 @@
     <t>Athletic Club</t>
   </si>
   <si>
-    <t>2026-07-28 06:05:36</t>
+    <t>2026-07-28 08:12:31</t>
   </si>
 </sst>
 </file>
@@ -952,19 +952,19 @@
         <v>104</v>
       </c>
       <c r="F2">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="G2">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="H2">
+        <v>2.18</v>
+      </c>
+      <c r="I2">
         <v>2.2</v>
       </c>
-      <c r="I2">
-        <v>2.26</v>
-      </c>
       <c r="J2">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="K2">
         <v>3.9</v>
@@ -976,19 +976,19 @@
         <v>1.05</v>
       </c>
       <c r="N2">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="O2">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P2">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="Q2">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="R2">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="S2">
         <v>2.82</v>
@@ -997,22 +997,22 @@
         <v>1.64</v>
       </c>
       <c r="U2">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="V2">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="W2">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="X2">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="Y2">
         <v>12.5</v>
       </c>
       <c r="Z2">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AA2">
         <v>29</v>
@@ -1021,61 +1021,61 @@
         <v>16.5</v>
       </c>
       <c r="AC2">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AD2">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AE2">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AF2">
         <v>26</v>
       </c>
       <c r="AG2">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AH2">
         <v>15.5</v>
       </c>
       <c r="AI2">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AJ2">
         <v>60</v>
       </c>
       <c r="AK2">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AL2">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AM2">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AN2">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AO2">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AP2">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AQ2">
         <v>11</v>
       </c>
       <c r="AR2">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="AS2">
         <v>25</v>
       </c>
       <c r="AT2">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AU2">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV2">
         <v>10</v>
@@ -1093,10 +1093,10 @@
         <v>13.5</v>
       </c>
       <c r="BA2">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BB2">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="BC2">
         <v>30</v>
@@ -1114,7 +1114,7 @@
         <v>11.5</v>
       </c>
       <c r="BH2">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="BI2">
         <v>3.6</v>
@@ -1123,37 +1123,37 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BK2">
-        <v>5.6</v>
+        <v>7.8</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>13</v>
+        <v>3.1</v>
       </c>
       <c r="BN2">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BO2">
         <v>6</v>
       </c>
       <c r="BP2">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BQ2">
-        <v>9.6</v>
+        <v>18</v>
       </c>
       <c r="BR2">
         <v>32</v>
       </c>
       <c r="BS2">
-        <v>10.5</v>
+        <v>2.92</v>
       </c>
       <c r="BT2">
         <v>5.3</v>
       </c>
       <c r="BU2">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BV2">
         <v>15</v>
@@ -1165,7 +1165,7 @@
         <v>25</v>
       </c>
       <c r="BY2">
-        <v>9.6</v>
+        <v>18</v>
       </c>
       <c r="BZ2">
         <v>0</v>
@@ -1194,10 +1194,10 @@
         <v>105</v>
       </c>
       <c r="F3">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="G3">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="H3">
         <v>3.1</v>
@@ -1209,34 +1209,34 @@
         <v>3.75</v>
       </c>
       <c r="K3">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L3">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="M3">
         <v>1.05</v>
       </c>
       <c r="N3">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="O3">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="P3">
-        <v>2.38</v>
+        <v>2.46</v>
       </c>
       <c r="Q3">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="R3">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="S3">
-        <v>2.72</v>
+        <v>2.64</v>
       </c>
       <c r="T3">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="U3">
         <v>2.56</v>
@@ -1245,82 +1245,82 @@
         <v>1.45</v>
       </c>
       <c r="W3">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="X3">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Y3">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="Z3">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AA3">
-        <v>48</v>
+        <v>100</v>
       </c>
       <c r="AB3">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AC3">
         <v>9</v>
       </c>
       <c r="AD3">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AE3">
+        <v>32</v>
+      </c>
+      <c r="AF3">
+        <v>19.5</v>
+      </c>
+      <c r="AG3">
+        <v>12</v>
+      </c>
+      <c r="AH3">
+        <v>16.5</v>
+      </c>
+      <c r="AI3">
+        <v>65</v>
+      </c>
+      <c r="AJ3">
+        <v>95</v>
+      </c>
+      <c r="AK3">
+        <v>22</v>
+      </c>
+      <c r="AL3">
+        <v>50</v>
+      </c>
+      <c r="AM3">
+        <v>200</v>
+      </c>
+      <c r="AN3">
+        <v>14</v>
+      </c>
+      <c r="AO3">
         <v>30</v>
       </c>
-      <c r="AF3">
-        <v>18.5</v>
-      </c>
-      <c r="AG3">
-        <v>11.5</v>
-      </c>
-      <c r="AH3">
-        <v>14.5</v>
-      </c>
-      <c r="AI3">
-        <v>36</v>
-      </c>
-      <c r="AJ3">
-        <v>32</v>
-      </c>
-      <c r="AK3">
-        <v>23</v>
-      </c>
-      <c r="AL3">
-        <v>32</v>
-      </c>
-      <c r="AM3">
-        <v>60</v>
-      </c>
-      <c r="AN3">
-        <v>13.5</v>
-      </c>
-      <c r="AO3">
-        <v>21</v>
-      </c>
       <c r="AP3">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AQ3">
         <v>15</v>
       </c>
       <c r="AR3">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AS3">
         <v>42</v>
       </c>
       <c r="AT3">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AU3">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV3">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AW3">
         <v>27</v>
@@ -1329,13 +1329,13 @@
         <v>16</v>
       </c>
       <c r="AY3">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AZ3">
         <v>13.5</v>
       </c>
       <c r="BA3">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BB3">
         <v>29</v>
@@ -1344,16 +1344,16 @@
         <v>20</v>
       </c>
       <c r="BD3">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BE3">
         <v>55</v>
       </c>
       <c r="BF3">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="BG3">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BH3">
         <v>4.2</v>
@@ -1365,7 +1365,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BK3">
-        <v>5.6</v>
+        <v>7.6</v>
       </c>
       <c r="BL3">
         <v>80</v>
@@ -1386,22 +1386,22 @@
         <v>7.8</v>
       </c>
       <c r="BR3">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BS3">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BT3">
         <v>6.6</v>
       </c>
       <c r="BU3">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BV3">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BW3">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX3">
         <v>28</v>
@@ -1678,40 +1678,40 @@
         <v>107</v>
       </c>
       <c r="F5">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="G5">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="H5">
-        <v>2.48</v>
+        <v>2.4</v>
       </c>
       <c r="I5">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="J5">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="K5">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="L5">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="M5">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="N5">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="O5">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="P5">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="Q5">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="R5">
         <v>1.18</v>
@@ -1720,19 +1720,19 @@
         <v>5.8</v>
       </c>
       <c r="T5">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="U5">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="V5">
         <v>1.64</v>
       </c>
       <c r="W5">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="X5">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="Y5">
         <v>7.4</v>
@@ -1744,7 +1744,7 @@
         <v>85</v>
       </c>
       <c r="AB5">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AC5">
         <v>7.2</v>
@@ -1753,28 +1753,28 @@
         <v>13</v>
       </c>
       <c r="AE5">
-        <v>85</v>
+        <v>55</v>
       </c>
       <c r="AF5">
         <v>130</v>
       </c>
       <c r="AG5">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AH5">
         <v>25</v>
       </c>
       <c r="AI5">
-        <v>230</v>
+        <v>150</v>
       </c>
       <c r="AJ5">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AK5">
-        <v>150</v>
+        <v>300</v>
       </c>
       <c r="AL5">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="AM5">
         <v>500</v>
@@ -1783,10 +1783,10 @@
         <v>600</v>
       </c>
       <c r="AO5">
-        <v>44</v>
+        <v>500</v>
       </c>
       <c r="AP5">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AQ5">
         <v>6.4</v>
@@ -1795,7 +1795,7 @@
         <v>12</v>
       </c>
       <c r="AS5">
-        <v>32</v>
+        <v>17.5</v>
       </c>
       <c r="AT5">
         <v>8.6</v>
@@ -1813,37 +1813,37 @@
         <v>11.5</v>
       </c>
       <c r="AY5">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AZ5">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BA5">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="BB5">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="BC5">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="BD5">
         <v>38</v>
       </c>
       <c r="BE5">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BF5">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="BG5">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="BH5">
-        <v>2.64</v>
+        <v>2.7</v>
       </c>
       <c r="BI5">
-        <v>2.24</v>
+        <v>2.42</v>
       </c>
       <c r="BJ5">
         <v>12</v>
@@ -1855,43 +1855,43 @@
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BN5">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BO5">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="BP5">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BQ5">
+        <v>10</v>
+      </c>
+      <c r="BR5">
+        <v>1000</v>
+      </c>
+      <c r="BS5">
+        <v>11</v>
+      </c>
+      <c r="BT5">
+        <v>5.1</v>
+      </c>
+      <c r="BU5">
+        <v>4.5</v>
+      </c>
+      <c r="BV5">
+        <v>1000</v>
+      </c>
+      <c r="BW5">
+        <v>8.6</v>
+      </c>
+      <c r="BX5">
+        <v>1000</v>
+      </c>
+      <c r="BY5">
         <v>10.5</v>
-      </c>
-      <c r="BR5">
-        <v>1000</v>
-      </c>
-      <c r="BS5">
-        <v>12</v>
-      </c>
-      <c r="BT5">
-        <v>5.2</v>
-      </c>
-      <c r="BU5">
-        <v>4.1</v>
-      </c>
-      <c r="BV5">
-        <v>1000</v>
-      </c>
-      <c r="BW5">
-        <v>9</v>
-      </c>
-      <c r="BX5">
-        <v>1000</v>
-      </c>
-      <c r="BY5">
-        <v>11.5</v>
       </c>
       <c r="BZ5">
         <v>0</v>
@@ -1923,13 +1923,13 @@
         <v>5.9</v>
       </c>
       <c r="G6">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="H6">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="I6">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="J6">
         <v>5.5</v>
@@ -1938,70 +1938,70 @@
         <v>6.2</v>
       </c>
       <c r="L6">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="M6">
         <v>1.02</v>
       </c>
       <c r="N6">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="O6">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="P6">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="Q6">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="R6">
-        <v>2.14</v>
+        <v>2.26</v>
       </c>
       <c r="S6">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="T6">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="U6">
-        <v>2.78</v>
+        <v>2.94</v>
       </c>
       <c r="V6">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="W6">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="X6">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="Y6">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="Z6">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA6">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AB6">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AC6">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AD6">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AE6">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AF6">
         <v>450</v>
       </c>
       <c r="AG6">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AH6">
         <v>19.5</v>
@@ -2013,37 +2013,37 @@
         <v>170</v>
       </c>
       <c r="AK6">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AL6">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="AM6">
         <v>65</v>
       </c>
       <c r="AN6">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AO6">
-        <v>4</v>
+        <v>3.65</v>
       </c>
       <c r="AP6">
         <v>29</v>
       </c>
       <c r="AQ6">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="AR6">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AS6">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AT6">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AU6">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AV6">
         <v>10</v>
@@ -2064,34 +2064,34 @@
         <v>18</v>
       </c>
       <c r="BB6">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="BC6">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="BD6">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BE6">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="BF6">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BG6">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="BH6">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BI6">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="BJ6">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BK6">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BL6">
         <v>1000</v>
@@ -2103,43 +2103,43 @@
         <v>11</v>
       </c>
       <c r="BO6">
-        <v>5.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BP6">
         <v>1000</v>
       </c>
       <c r="BQ6">
+        <v>10</v>
+      </c>
+      <c r="BR6">
+        <v>1000</v>
+      </c>
+      <c r="BS6">
         <v>9.6</v>
       </c>
-      <c r="BR6">
-        <v>1000</v>
-      </c>
-      <c r="BS6">
-        <v>9.199999999999999</v>
-      </c>
       <c r="BT6">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="BU6">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BV6">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BW6">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BX6">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="BY6">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BZ6">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="CA6">
-        <v>5</v>
+        <v>6.2</v>
       </c>
       <c r="CB6" t="s">
         <v>114</v>
@@ -2162,22 +2162,22 @@
         <v>109</v>
       </c>
       <c r="F7">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="G7">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="H7">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="I7">
         <v>2.22</v>
       </c>
       <c r="J7">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="K7">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L7">
         <v>1.55</v>
@@ -2195,13 +2195,13 @@
         <v>1.57</v>
       </c>
       <c r="Q7">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="R7">
         <v>1.2</v>
       </c>
       <c r="S7">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="T7">
         <v>1.11</v>
@@ -2216,7 +2216,7 @@
         <v>1.01</v>
       </c>
       <c r="X7">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="Y7">
         <v>950</v>
@@ -2267,55 +2267,55 @@
         <v>1000</v>
       </c>
       <c r="AO7">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP7">
         <v>4.9</v>
       </c>
       <c r="AQ7">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="AR7">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AS7">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="AT7">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AU7">
         <v>4.4</v>
       </c>
       <c r="AV7">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="AW7">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="AX7">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="AY7">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="AZ7">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="BA7">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="BB7">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="BC7">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="BD7">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="BE7">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="BF7">
         <v>1.55</v>
@@ -2407,55 +2407,55 @@
         <v>2.14</v>
       </c>
       <c r="G8">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="H8">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="I8">
         <v>4.8</v>
       </c>
       <c r="J8">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="K8">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="L8">
         <v>1.64</v>
       </c>
       <c r="M8">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="N8">
         <v>2.5</v>
       </c>
       <c r="O8">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="P8">
         <v>1.49</v>
       </c>
       <c r="Q8">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="R8">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="S8">
         <v>6.6</v>
       </c>
       <c r="T8">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="U8">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="V8">
         <v>1.27</v>
       </c>
       <c r="W8">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="X8">
         <v>7.8</v>
@@ -2464,16 +2464,16 @@
         <v>11</v>
       </c>
       <c r="Z8">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="AA8">
         <v>140</v>
       </c>
       <c r="AB8">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AC8">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AD8">
         <v>21</v>
@@ -2485,31 +2485,31 @@
         <v>11</v>
       </c>
       <c r="AG8">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH8">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AI8">
-        <v>260</v>
+        <v>130</v>
       </c>
       <c r="AJ8">
         <v>27</v>
       </c>
       <c r="AK8">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AL8">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AM8">
-        <v>500</v>
+        <v>290</v>
       </c>
       <c r="AN8">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AO8">
-        <v>690</v>
+        <v>150</v>
       </c>
       <c r="AP8">
         <v>7.2</v>
@@ -2518,70 +2518,70 @@
         <v>10</v>
       </c>
       <c r="AR8">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AS8">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="AT8">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AU8">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV8">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AW8">
         <v>48</v>
       </c>
       <c r="AX8">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AY8">
         <v>11</v>
       </c>
       <c r="AZ8">
+        <v>27</v>
+      </c>
+      <c r="BA8">
+        <v>46</v>
+      </c>
+      <c r="BB8">
         <v>24</v>
       </c>
-      <c r="BA8">
-        <v>50</v>
-      </c>
-      <c r="BB8">
-        <v>19.5</v>
-      </c>
       <c r="BC8">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="BD8">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="BE8">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="BF8">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="BG8">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="BH8">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="BI8">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="BJ8">
         <v>12.5</v>
       </c>
       <c r="BK8">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BL8">
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BN8">
         <v>4.6</v>
@@ -2590,16 +2590,16 @@
         <v>4.1</v>
       </c>
       <c r="BP8">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BQ8">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR8">
         <v>1000</v>
       </c>
       <c r="BS8">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BT8">
         <v>7.8</v>
@@ -2611,19 +2611,19 @@
         <v>55</v>
       </c>
       <c r="BW8">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BX8">
         <v>1000</v>
       </c>
       <c r="BY8">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BZ8">
         <v>1000</v>
       </c>
       <c r="CA8">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="CB8" t="s">
         <v>114</v>
@@ -2649,22 +2649,22 @@
         <v>2.12</v>
       </c>
       <c r="G9">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="H9">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="I9">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="J9">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="K9">
         <v>3.25</v>
       </c>
       <c r="L9">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="M9">
         <v>1.14</v>
@@ -2679,7 +2679,7 @@
         <v>1.51</v>
       </c>
       <c r="Q9">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="R9">
         <v>1.18</v>
@@ -2688,31 +2688,31 @@
         <v>6.2</v>
       </c>
       <c r="T9">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="U9">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="V9">
         <v>1.27</v>
       </c>
       <c r="W9">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="X9">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y9">
         <v>11</v>
       </c>
       <c r="Z9">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AA9">
         <v>130</v>
       </c>
       <c r="AB9">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AC9">
         <v>7.4</v>
@@ -2721,61 +2721,61 @@
         <v>21</v>
       </c>
       <c r="AE9">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AF9">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AG9">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH9">
         <v>28</v>
       </c>
       <c r="AI9">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AJ9">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AK9">
         <v>32</v>
       </c>
       <c r="AL9">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AM9">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="AN9">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AO9">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AP9">
         <v>7.6</v>
       </c>
       <c r="AQ9">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AR9">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AS9">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AT9">
         <v>6</v>
       </c>
       <c r="AU9">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV9">
         <v>18</v>
       </c>
       <c r="AW9">
-        <v>65</v>
+        <v>34</v>
       </c>
       <c r="AX9">
         <v>10</v>
@@ -2784,46 +2784,46 @@
         <v>11</v>
       </c>
       <c r="AZ9">
+        <v>25</v>
+      </c>
+      <c r="BA9">
+        <v>90</v>
+      </c>
+      <c r="BB9">
+        <v>22</v>
+      </c>
+      <c r="BC9">
         <v>23</v>
-      </c>
-      <c r="BA9">
-        <v>85</v>
-      </c>
-      <c r="BB9">
-        <v>21</v>
-      </c>
-      <c r="BC9">
-        <v>25</v>
       </c>
       <c r="BD9">
         <v>50</v>
       </c>
       <c r="BE9">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="BF9">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="BG9">
         <v>50</v>
       </c>
       <c r="BH9">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="BI9">
         <v>2.46</v>
       </c>
       <c r="BJ9">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BK9">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BL9">
         <v>1000</v>
       </c>
       <c r="BM9">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BN9">
         <v>4.6</v>
@@ -2835,13 +2835,13 @@
         <v>18.5</v>
       </c>
       <c r="BQ9">
-        <v>14</v>
+        <v>7.4</v>
       </c>
       <c r="BR9">
         <v>46</v>
       </c>
       <c r="BS9">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BT9">
         <v>7.8</v>
@@ -2853,19 +2853,19 @@
         <v>50</v>
       </c>
       <c r="BW9">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BX9">
         <v>1000</v>
       </c>
       <c r="BY9">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BZ9">
         <v>50</v>
       </c>
       <c r="CA9">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CB9" t="s">
         <v>114</v>
@@ -2888,13 +2888,13 @@
         <v>112</v>
       </c>
       <c r="F10">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="G10">
         <v>1.63</v>
       </c>
       <c r="H10">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="I10">
         <v>8</v>
@@ -2915,7 +2915,7 @@
         <v>3</v>
       </c>
       <c r="O10">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="P10">
         <v>1.67</v>
@@ -2930,7 +2930,7 @@
         <v>4.8</v>
       </c>
       <c r="T10">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="U10">
         <v>1.68</v>
@@ -2945,7 +2945,7 @@
         <v>11</v>
       </c>
       <c r="Y10">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="Z10">
         <v>65</v>
@@ -2954,22 +2954,22 @@
         <v>310</v>
       </c>
       <c r="AB10">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="AC10">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="AD10">
         <v>32</v>
       </c>
       <c r="AE10">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="AF10">
         <v>8</v>
       </c>
       <c r="AG10">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH10">
         <v>32</v>
@@ -2987,37 +2987,37 @@
         <v>60</v>
       </c>
       <c r="AM10">
-        <v>700</v>
+        <v>580</v>
       </c>
       <c r="AN10">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AO10">
         <v>310</v>
       </c>
       <c r="AP10">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ10">
         <v>17.5</v>
       </c>
       <c r="AR10">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AS10">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="AT10">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="AU10">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AV10">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AW10">
-        <v>8.800000000000001</v>
+        <v>14.5</v>
       </c>
       <c r="AX10">
         <v>7.2</v>
@@ -3029,7 +3029,7 @@
         <v>28</v>
       </c>
       <c r="BA10">
-        <v>8.800000000000001</v>
+        <v>15</v>
       </c>
       <c r="BB10">
         <v>13.5</v>
@@ -3041,73 +3041,73 @@
         <v>50</v>
       </c>
       <c r="BE10">
-        <v>10.5</v>
+        <v>15</v>
       </c>
       <c r="BF10">
         <v>12</v>
       </c>
       <c r="BG10">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="BH10">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="BI10">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="BJ10">
         <v>13.5</v>
       </c>
       <c r="BK10">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BL10">
         <v>1000</v>
       </c>
       <c r="BM10">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BN10">
         <v>3.9</v>
       </c>
       <c r="BO10">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="BP10">
         <v>12</v>
       </c>
       <c r="BQ10">
-        <v>5.6</v>
+        <v>9.4</v>
       </c>
       <c r="BR10">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BS10">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT10">
         <v>11.5</v>
       </c>
       <c r="BU10">
-        <v>8</v>
+        <v>5.8</v>
       </c>
       <c r="BV10">
         <v>1000</v>
       </c>
       <c r="BW10">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="BX10">
         <v>1000</v>
       </c>
       <c r="BY10">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="BZ10">
         <v>1000</v>
       </c>
       <c r="CA10">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="CB10" t="s">
         <v>114</v>
@@ -3133,19 +3133,19 @@
         <v>4.6</v>
       </c>
       <c r="G11">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="H11">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="I11">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="J11">
         <v>3.35</v>
       </c>
       <c r="K11">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L11">
         <v>1.53</v>
@@ -3157,13 +3157,13 @@
         <v>2.92</v>
       </c>
       <c r="O11">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="P11">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="Q11">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="R11">
         <v>1.23</v>
@@ -3172,22 +3172,22 @@
         <v>5</v>
       </c>
       <c r="T11">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="U11">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="V11">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="W11">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="X11">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y11">
-        <v>8.199999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="Z11">
         <v>11</v>
@@ -3196,16 +3196,16 @@
         <v>26</v>
       </c>
       <c r="AB11">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AC11">
         <v>9.199999999999999</v>
       </c>
       <c r="AD11">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AE11">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AF11">
         <v>34</v>
@@ -3214,7 +3214,7 @@
         <v>22</v>
       </c>
       <c r="AH11">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AI11">
         <v>55</v>
@@ -3226,13 +3226,13 @@
         <v>85</v>
       </c>
       <c r="AL11">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AM11">
         <v>190</v>
       </c>
       <c r="AN11">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AO11">
         <v>28</v>
@@ -3241,7 +3241,7 @@
         <v>8.6</v>
       </c>
       <c r="AQ11">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AR11">
         <v>9.800000000000001</v>
@@ -3256,40 +3256,40 @@
         <v>7</v>
       </c>
       <c r="AV11">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AW11">
         <v>23</v>
       </c>
       <c r="AX11">
-        <v>14.5</v>
+        <v>21</v>
       </c>
       <c r="AY11">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AZ11">
         <v>22</v>
       </c>
       <c r="BA11">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BB11">
-        <v>8.199999999999999</v>
+        <v>12</v>
       </c>
       <c r="BC11">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="BD11">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="BE11">
-        <v>8.4</v>
+        <v>12</v>
       </c>
       <c r="BF11">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="BG11">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="BH11">
         <v>2.86</v>
@@ -3325,7 +3325,7 @@
         <v>1000</v>
       </c>
       <c r="BS11">
-        <v>13</v>
+        <v>7.4</v>
       </c>
       <c r="BT11">
         <v>4.5</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-28.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-28.xlsx
@@ -358,7 +358,7 @@
     <t>Athletic Club</t>
   </si>
   <si>
-    <t>2026-07-28 08:12:31</t>
+    <t>2026-07-28 10:20:43</t>
   </si>
 </sst>
 </file>
@@ -952,10 +952,10 @@
         <v>104</v>
       </c>
       <c r="F2">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="G2">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="H2">
         <v>2.18</v>
@@ -964,28 +964,28 @@
         <v>2.2</v>
       </c>
       <c r="J2">
+        <v>3.75</v>
+      </c>
+      <c r="K2">
         <v>3.85</v>
       </c>
-      <c r="K2">
-        <v>3.9</v>
-      </c>
       <c r="L2">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="M2">
         <v>1.05</v>
       </c>
       <c r="N2">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="O2">
         <v>1.25</v>
       </c>
       <c r="P2">
-        <v>2.38</v>
+        <v>2.24</v>
       </c>
       <c r="Q2">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="R2">
         <v>1.54</v>
@@ -994,46 +994,46 @@
         <v>2.82</v>
       </c>
       <c r="T2">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="U2">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="V2">
         <v>1.83</v>
       </c>
       <c r="W2">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="X2">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="Y2">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Z2">
+        <v>15</v>
+      </c>
+      <c r="AA2">
+        <v>28</v>
+      </c>
+      <c r="AB2">
         <v>16</v>
       </c>
-      <c r="AA2">
-        <v>29</v>
-      </c>
-      <c r="AB2">
-        <v>16.5</v>
-      </c>
       <c r="AC2">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD2">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AE2">
         <v>21</v>
       </c>
       <c r="AF2">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AG2">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AH2">
         <v>15.5</v>
@@ -1042,40 +1042,40 @@
         <v>30</v>
       </c>
       <c r="AJ2">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AK2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AL2">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AM2">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AN2">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="AO2">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AP2">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AQ2">
         <v>11</v>
       </c>
       <c r="AR2">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AS2">
         <v>25</v>
       </c>
       <c r="AT2">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AU2">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AV2">
         <v>10</v>
@@ -1084,13 +1084,13 @@
         <v>19</v>
       </c>
       <c r="AX2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AY2">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AZ2">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BA2">
         <v>27</v>
@@ -1099,37 +1099,37 @@
         <v>50</v>
       </c>
       <c r="BC2">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BD2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BE2">
         <v>55</v>
       </c>
       <c r="BF2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BG2">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BH2">
-        <v>4.8</v>
+        <v>3.8</v>
       </c>
       <c r="BI2">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="BJ2">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BK2">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BL2">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="BM2">
-        <v>3.1</v>
+        <v>14</v>
       </c>
       <c r="BN2">
         <v>6.8</v>
@@ -1138,34 +1138,34 @@
         <v>6</v>
       </c>
       <c r="BP2">
+        <v>25</v>
+      </c>
+      <c r="BQ2">
+        <v>10</v>
+      </c>
+      <c r="BR2">
+        <v>34</v>
+      </c>
+      <c r="BS2">
         <v>24</v>
-      </c>
-      <c r="BQ2">
-        <v>18</v>
-      </c>
-      <c r="BR2">
-        <v>32</v>
-      </c>
-      <c r="BS2">
-        <v>2.92</v>
       </c>
       <c r="BT2">
         <v>5.3</v>
       </c>
       <c r="BU2">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BV2">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BW2">
-        <v>11.5</v>
+        <v>8</v>
       </c>
       <c r="BX2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BY2">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="BZ2">
         <v>0</v>
@@ -1197,13 +1197,13 @@
         <v>2.34</v>
       </c>
       <c r="G3">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="H3">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="I3">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="J3">
         <v>3.75</v>
@@ -1212,34 +1212,34 @@
         <v>3.9</v>
       </c>
       <c r="L3">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="M3">
         <v>1.05</v>
       </c>
       <c r="N3">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="O3">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="P3">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="Q3">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="R3">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="S3">
-        <v>2.64</v>
+        <v>2.74</v>
       </c>
       <c r="T3">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="U3">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="V3">
         <v>1.45</v>
@@ -1254,55 +1254,55 @@
         <v>17</v>
       </c>
       <c r="Z3">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AA3">
-        <v>100</v>
+        <v>55</v>
       </c>
       <c r="AB3">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AC3">
         <v>9</v>
       </c>
       <c r="AD3">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AE3">
         <v>32</v>
       </c>
       <c r="AF3">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="AG3">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH3">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="AI3">
-        <v>65</v>
+        <v>36</v>
       </c>
       <c r="AJ3">
-        <v>95</v>
+        <v>30</v>
       </c>
       <c r="AK3">
         <v>22</v>
       </c>
       <c r="AL3">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="AM3">
-        <v>200</v>
+        <v>60</v>
       </c>
       <c r="AN3">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AO3">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="AP3">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AQ3">
         <v>15</v>
@@ -1311,19 +1311,19 @@
         <v>22</v>
       </c>
       <c r="AS3">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AT3">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AU3">
         <v>8.199999999999999</v>
       </c>
       <c r="AV3">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AW3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AX3">
         <v>16</v>
@@ -1335,10 +1335,10 @@
         <v>13.5</v>
       </c>
       <c r="BA3">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BB3">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="BC3">
         <v>20</v>
@@ -1350,70 +1350,70 @@
         <v>55</v>
       </c>
       <c r="BF3">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BG3">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BH3">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="BI3">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="BJ3">
         <v>8.800000000000001</v>
       </c>
       <c r="BK3">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BL3">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="BM3">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="BN3">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="BO3">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BP3">
         <v>16</v>
       </c>
       <c r="BQ3">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="BR3">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BS3">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="BT3">
         <v>6.6</v>
       </c>
       <c r="BU3">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BV3">
         <v>22</v>
       </c>
       <c r="BW3">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BX3">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="BY3">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BZ3">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="CA3">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="CB3" t="s">
         <v>114</v>
@@ -1678,19 +1678,19 @@
         <v>107</v>
       </c>
       <c r="F5">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="G5">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="H5">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="I5">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
       <c r="J5">
-        <v>2.88</v>
+        <v>2.94</v>
       </c>
       <c r="K5">
         <v>3.05</v>
@@ -1702,49 +1702,49 @@
         <v>1.14</v>
       </c>
       <c r="N5">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="O5">
         <v>1.57</v>
       </c>
       <c r="P5">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="Q5">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="R5">
         <v>1.18</v>
       </c>
       <c r="S5">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="T5">
         <v>2.14</v>
       </c>
       <c r="U5">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="V5">
         <v>1.64</v>
       </c>
       <c r="W5">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="X5">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="Y5">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="Z5">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AA5">
         <v>85</v>
       </c>
       <c r="AB5">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AC5">
         <v>7.2</v>
@@ -1753,13 +1753,13 @@
         <v>13</v>
       </c>
       <c r="AE5">
-        <v>55</v>
+        <v>85</v>
       </c>
       <c r="AF5">
         <v>130</v>
       </c>
       <c r="AG5">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AH5">
         <v>25</v>
@@ -1774,16 +1774,16 @@
         <v>300</v>
       </c>
       <c r="AL5">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="AM5">
         <v>500</v>
       </c>
       <c r="AN5">
-        <v>600</v>
+        <v>140</v>
       </c>
       <c r="AO5">
-        <v>500</v>
+        <v>48</v>
       </c>
       <c r="AP5">
         <v>7.2</v>
@@ -1798,7 +1798,7 @@
         <v>17.5</v>
       </c>
       <c r="AT5">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AU5">
         <v>6.2</v>
@@ -1807,55 +1807,55 @@
         <v>10.5</v>
       </c>
       <c r="AW5">
-        <v>30</v>
+        <v>19.5</v>
       </c>
       <c r="AX5">
         <v>11.5</v>
       </c>
       <c r="AY5">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AZ5">
         <v>20</v>
       </c>
       <c r="BA5">
-        <v>42</v>
+        <v>9.6</v>
       </c>
       <c r="BB5">
+        <v>9.6</v>
+      </c>
+      <c r="BC5">
+        <v>9.4</v>
+      </c>
+      <c r="BD5">
+        <v>9.4</v>
+      </c>
+      <c r="BE5">
         <v>10</v>
       </c>
-      <c r="BC5">
-        <v>10</v>
-      </c>
-      <c r="BD5">
-        <v>38</v>
-      </c>
-      <c r="BE5">
-        <v>11</v>
-      </c>
       <c r="BF5">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BG5">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="BH5">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="BI5">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="BJ5">
         <v>12</v>
       </c>
       <c r="BK5">
-        <v>9</v>
+        <v>6.2</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BN5">
         <v>6.8</v>
@@ -1864,10 +1864,10 @@
         <v>5.8</v>
       </c>
       <c r="BP5">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BQ5">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BR5">
         <v>1000</v>
@@ -1876,16 +1876,16 @@
         <v>11</v>
       </c>
       <c r="BT5">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BU5">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BV5">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BW5">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BX5">
         <v>1000</v>
@@ -1920,22 +1920,22 @@
         <v>108</v>
       </c>
       <c r="F6">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="G6">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="H6">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="I6">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="J6">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="K6">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="L6">
         <v>1.18</v>
@@ -1944,97 +1944,97 @@
         <v>1.02</v>
       </c>
       <c r="N6">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="O6">
         <v>1.09</v>
       </c>
       <c r="P6">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="Q6">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="R6">
-        <v>2.26</v>
+        <v>2.18</v>
       </c>
       <c r="S6">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="T6">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="U6">
-        <v>2.94</v>
+        <v>2.88</v>
       </c>
       <c r="V6">
-        <v>2.92</v>
+        <v>2.84</v>
       </c>
       <c r="W6">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="X6">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="Y6">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="Z6">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AA6">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="AB6">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AC6">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AD6">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AE6">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AF6">
         <v>450</v>
       </c>
       <c r="AG6">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AH6">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="AI6">
         <v>22</v>
       </c>
       <c r="AJ6">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AK6">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AL6">
+        <v>55</v>
+      </c>
+      <c r="AM6">
         <v>60</v>
       </c>
-      <c r="AM6">
-        <v>65</v>
-      </c>
       <c r="AN6">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AO6">
-        <v>3.65</v>
+        <v>3.9</v>
       </c>
       <c r="AP6">
         <v>29</v>
       </c>
       <c r="AQ6">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AR6">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AS6">
         <v>15</v>
@@ -2043,100 +2043,100 @@
         <v>38</v>
       </c>
       <c r="AU6">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AV6">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AW6">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AX6">
         <v>55</v>
       </c>
       <c r="AY6">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AZ6">
         <v>15.5</v>
       </c>
       <c r="BA6">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BB6">
-        <v>36</v>
+        <v>13</v>
       </c>
       <c r="BC6">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="BD6">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BE6">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BF6">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BG6">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="BH6">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BI6">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BJ6">
         <v>9</v>
       </c>
       <c r="BK6">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BL6">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BM6">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BN6">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BO6">
-        <v>9.199999999999999</v>
+        <v>6.2</v>
       </c>
       <c r="BP6">
         <v>1000</v>
       </c>
       <c r="BQ6">
+        <v>10.5</v>
+      </c>
+      <c r="BR6">
+        <v>32</v>
+      </c>
+      <c r="BS6">
         <v>10</v>
       </c>
-      <c r="BR6">
-        <v>1000</v>
-      </c>
-      <c r="BS6">
-        <v>9.6</v>
-      </c>
       <c r="BT6">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BU6">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BV6">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BW6">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BX6">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="BY6">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BZ6">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="CA6">
         <v>6.2</v>
@@ -2162,13 +2162,13 @@
         <v>109</v>
       </c>
       <c r="F7">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="G7">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="H7">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="I7">
         <v>2.22</v>
@@ -2183,7 +2183,7 @@
         <v>1.55</v>
       </c>
       <c r="M7">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="N7">
         <v>2.78</v>
@@ -2192,19 +2192,19 @@
         <v>1.51</v>
       </c>
       <c r="P7">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="Q7">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="R7">
         <v>1.2</v>
       </c>
       <c r="S7">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="T7">
-        <v>1.11</v>
+        <v>2.08</v>
       </c>
       <c r="U7">
         <v>1.83</v>
@@ -2216,172 +2216,172 @@
         <v>1.01</v>
       </c>
       <c r="X7">
-        <v>500</v>
+        <v>9.4</v>
       </c>
       <c r="Y7">
-        <v>950</v>
+        <v>7.2</v>
       </c>
       <c r="Z7">
-        <v>500</v>
+        <v>12.5</v>
       </c>
       <c r="AA7">
-        <v>900</v>
+        <v>30</v>
       </c>
       <c r="AB7">
-        <v>950</v>
+        <v>12</v>
       </c>
       <c r="AC7">
-        <v>42</v>
+        <v>7.8</v>
       </c>
       <c r="AD7">
-        <v>500</v>
+        <v>12</v>
       </c>
       <c r="AE7">
-        <v>500</v>
+        <v>30</v>
       </c>
       <c r="AF7">
-        <v>500</v>
+        <v>32</v>
       </c>
       <c r="AG7">
-        <v>950</v>
+        <v>18.5</v>
       </c>
       <c r="AH7">
-        <v>950</v>
+        <v>26</v>
       </c>
       <c r="AI7">
-        <v>500</v>
+        <v>130</v>
       </c>
       <c r="AJ7">
         <v>900</v>
       </c>
       <c r="AK7">
-        <v>500</v>
+        <v>160</v>
       </c>
       <c r="AL7">
-        <v>500</v>
+        <v>350</v>
       </c>
       <c r="AM7">
         <v>580</v>
       </c>
       <c r="AN7">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AO7">
-        <v>600</v>
+        <v>29</v>
       </c>
       <c r="AP7">
-        <v>4.9</v>
+        <v>8</v>
       </c>
       <c r="AQ7">
-        <v>1.38</v>
+        <v>6.2</v>
       </c>
       <c r="AR7">
-        <v>1.4</v>
+        <v>10.5</v>
       </c>
       <c r="AS7">
-        <v>1.41</v>
+        <v>14</v>
       </c>
       <c r="AT7">
-        <v>1.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU7">
-        <v>4.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV7">
-        <v>1.37</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW7">
-        <v>1.39</v>
+        <v>14</v>
       </c>
       <c r="AX7">
-        <v>1.41</v>
+        <v>8</v>
       </c>
       <c r="AY7">
-        <v>1.41</v>
+        <v>15.5</v>
       </c>
       <c r="AZ7">
-        <v>1.39</v>
+        <v>21</v>
       </c>
       <c r="BA7">
-        <v>1.42</v>
+        <v>9</v>
       </c>
       <c r="BB7">
-        <v>1.42</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC7">
-        <v>1.42</v>
+        <v>9.4</v>
       </c>
       <c r="BD7">
-        <v>1.42</v>
+        <v>9.6</v>
       </c>
       <c r="BE7">
-        <v>1.42</v>
+        <v>10</v>
       </c>
       <c r="BF7">
-        <v>1.55</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG7">
-        <v>1.55</v>
+        <v>9.6</v>
       </c>
       <c r="BH7">
-        <v>1000</v>
+        <v>2.82</v>
       </c>
       <c r="BI7">
-        <v>1.04</v>
+        <v>2.32</v>
       </c>
       <c r="BJ7">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK7">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>1.04</v>
+        <v>12</v>
       </c>
       <c r="BN7">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="BO7">
-        <v>1.04</v>
+        <v>5.5</v>
       </c>
       <c r="BP7">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BQ7">
-        <v>1.04</v>
+        <v>10</v>
       </c>
       <c r="BR7">
         <v>1000</v>
       </c>
       <c r="BS7">
-        <v>1.04</v>
+        <v>10.5</v>
       </c>
       <c r="BT7">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="BU7">
-        <v>1.04</v>
+        <v>3.65</v>
       </c>
       <c r="BV7">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="BW7">
-        <v>1.04</v>
+        <v>7.6</v>
       </c>
       <c r="BX7">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BY7">
-        <v>1.04</v>
+        <v>10</v>
       </c>
       <c r="BZ7">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="CA7">
-        <v>1.04</v>
+        <v>10</v>
       </c>
       <c r="CB7" t="s">
         <v>114</v>
@@ -2404,10 +2404,10 @@
         <v>110</v>
       </c>
       <c r="F8">
-        <v>2.14</v>
+        <v>2.08</v>
       </c>
       <c r="G8">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="H8">
         <v>4.6</v>
@@ -2416,10 +2416,10 @@
         <v>4.8</v>
       </c>
       <c r="J8">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="K8">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="L8">
         <v>1.64</v>
@@ -2428,13 +2428,13 @@
         <v>1.15</v>
       </c>
       <c r="N8">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="O8">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="P8">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="Q8">
         <v>2.98</v>
@@ -2452,10 +2452,10 @@
         <v>1.67</v>
       </c>
       <c r="V8">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="W8">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="X8">
         <v>7.8</v>
@@ -2467,7 +2467,7 @@
         <v>32</v>
       </c>
       <c r="AA8">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AB8">
         <v>6.4</v>
@@ -2476,19 +2476,19 @@
         <v>7.4</v>
       </c>
       <c r="AD8">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AE8">
         <v>95</v>
       </c>
       <c r="AF8">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AG8">
         <v>12</v>
       </c>
       <c r="AH8">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AI8">
         <v>130</v>
@@ -2497,19 +2497,19 @@
         <v>27</v>
       </c>
       <c r="AK8">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AL8">
         <v>70</v>
       </c>
       <c r="AM8">
-        <v>290</v>
+        <v>270</v>
       </c>
       <c r="AN8">
         <v>32</v>
       </c>
       <c r="AO8">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="AP8">
         <v>7.2</v>
@@ -2521,7 +2521,7 @@
         <v>27</v>
       </c>
       <c r="AS8">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AT8">
         <v>6</v>
@@ -2533,10 +2533,10 @@
         <v>18.5</v>
       </c>
       <c r="AW8">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AX8">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY8">
         <v>11</v>
@@ -2548,82 +2548,82 @@
         <v>46</v>
       </c>
       <c r="BB8">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BC8">
         <v>29</v>
       </c>
       <c r="BD8">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="BE8">
         <v>110</v>
       </c>
       <c r="BF8">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="BG8">
         <v>46</v>
       </c>
       <c r="BH8">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="BI8">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="BJ8">
         <v>12.5</v>
       </c>
       <c r="BK8">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BL8">
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>16</v>
+        <v>2.22</v>
       </c>
       <c r="BN8">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BO8">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BP8">
         <v>18</v>
       </c>
       <c r="BQ8">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BR8">
         <v>1000</v>
       </c>
       <c r="BS8">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BT8">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BU8">
-        <v>6.8</v>
+        <v>6</v>
       </c>
       <c r="BV8">
         <v>55</v>
       </c>
       <c r="BW8">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BX8">
         <v>1000</v>
       </c>
       <c r="BY8">
-        <v>14</v>
+        <v>2.18</v>
       </c>
       <c r="BZ8">
         <v>1000</v>
       </c>
       <c r="CA8">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="CB8" t="s">
         <v>114</v>
@@ -2655,43 +2655,43 @@
         <v>4.5</v>
       </c>
       <c r="I9">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="J9">
         <v>3.15</v>
       </c>
       <c r="K9">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="L9">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="M9">
         <v>1.14</v>
       </c>
       <c r="N9">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="O9">
         <v>1.61</v>
       </c>
       <c r="P9">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="Q9">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="R9">
         <v>1.18</v>
       </c>
       <c r="S9">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="T9">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="U9">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="V9">
         <v>1.27</v>
@@ -2703,7 +2703,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="Y9">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="Z9">
         <v>32</v>
@@ -2712,7 +2712,7 @@
         <v>130</v>
       </c>
       <c r="AB9">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AC9">
         <v>7.4</v>
@@ -2721,13 +2721,13 @@
         <v>21</v>
       </c>
       <c r="AE9">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AF9">
         <v>11</v>
       </c>
       <c r="AG9">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH9">
         <v>28</v>
@@ -2745,22 +2745,22 @@
         <v>65</v>
       </c>
       <c r="AM9">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="AN9">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AO9">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="AP9">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AQ9">
         <v>10.5</v>
       </c>
       <c r="AR9">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AS9">
         <v>38</v>
@@ -2775,13 +2775,13 @@
         <v>18</v>
       </c>
       <c r="AW9">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="AX9">
         <v>10</v>
       </c>
       <c r="AY9">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AZ9">
         <v>25</v>
@@ -2790,28 +2790,28 @@
         <v>90</v>
       </c>
       <c r="BB9">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="BC9">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="BD9">
         <v>50</v>
       </c>
       <c r="BE9">
-        <v>110</v>
+        <v>70</v>
       </c>
       <c r="BF9">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BG9">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="BH9">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="BI9">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="BJ9">
         <v>12</v>
@@ -2829,31 +2829,31 @@
         <v>4.6</v>
       </c>
       <c r="BO9">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="BP9">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BQ9">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BR9">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BS9">
         <v>9.6</v>
       </c>
       <c r="BT9">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BU9">
         <v>5.5</v>
       </c>
       <c r="BV9">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BW9">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BX9">
         <v>1000</v>
@@ -2862,7 +2862,7 @@
         <v>10.5</v>
       </c>
       <c r="BZ9">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="CA9">
         <v>9.800000000000001</v>
@@ -2888,28 +2888,28 @@
         <v>112</v>
       </c>
       <c r="F10">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="G10">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="H10">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="I10">
         <v>8</v>
       </c>
       <c r="J10">
+        <v>3.75</v>
+      </c>
+      <c r="K10">
         <v>3.9</v>
-      </c>
-      <c r="K10">
-        <v>4</v>
       </c>
       <c r="L10">
         <v>1.52</v>
       </c>
       <c r="M10">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N10">
         <v>3</v>
@@ -2918,49 +2918,49 @@
         <v>1.47</v>
       </c>
       <c r="P10">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="Q10">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="R10">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="S10">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="T10">
         <v>2.34</v>
       </c>
       <c r="U10">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="V10">
         <v>1.14</v>
       </c>
       <c r="W10">
-        <v>2.6</v>
+        <v>2.48</v>
       </c>
       <c r="X10">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Y10">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="Z10">
         <v>65</v>
       </c>
       <c r="AA10">
-        <v>310</v>
+        <v>290</v>
       </c>
       <c r="AB10">
         <v>6.2</v>
       </c>
       <c r="AC10">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD10">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AE10">
         <v>160</v>
@@ -2972,7 +2972,7 @@
         <v>10.5</v>
       </c>
       <c r="AH10">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AI10">
         <v>190</v>
@@ -2990,22 +2990,22 @@
         <v>580</v>
       </c>
       <c r="AN10">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AO10">
-        <v>310</v>
+        <v>290</v>
       </c>
       <c r="AP10">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AQ10">
+        <v>17</v>
+      </c>
+      <c r="AR10">
+        <v>50</v>
+      </c>
+      <c r="AS10">
         <v>17.5</v>
-      </c>
-      <c r="AR10">
-        <v>55</v>
-      </c>
-      <c r="AS10">
-        <v>15</v>
       </c>
       <c r="AT10">
         <v>5.5</v>
@@ -3014,13 +3014,13 @@
         <v>8.4</v>
       </c>
       <c r="AV10">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AW10">
-        <v>14.5</v>
+        <v>17.5</v>
       </c>
       <c r="AX10">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AY10">
         <v>9.6</v>
@@ -3029,85 +3029,85 @@
         <v>28</v>
       </c>
       <c r="BA10">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="BB10">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BC10">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BD10">
         <v>50</v>
       </c>
       <c r="BE10">
-        <v>15</v>
+        <v>150</v>
       </c>
       <c r="BF10">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BG10">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="BH10">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="BI10">
-        <v>2.44</v>
+        <v>2.38</v>
       </c>
       <c r="BJ10">
         <v>13.5</v>
       </c>
       <c r="BK10">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BL10">
         <v>1000</v>
       </c>
       <c r="BM10">
-        <v>11</v>
+        <v>180</v>
       </c>
       <c r="BN10">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="BO10">
         <v>3.35</v>
       </c>
       <c r="BP10">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BQ10">
-        <v>9.4</v>
+        <v>5.9</v>
       </c>
       <c r="BR10">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BS10">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BT10">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BU10">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="BV10">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="BW10">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BX10">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="BY10">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BZ10">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="CA10">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB10" t="s">
         <v>114</v>
@@ -3130,22 +3130,22 @@
         <v>113</v>
       </c>
       <c r="F11">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="G11">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="H11">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="I11">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="J11">
         <v>3.35</v>
       </c>
       <c r="K11">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="L11">
         <v>1.53</v>
@@ -3154,7 +3154,7 @@
         <v>1.11</v>
       </c>
       <c r="N11">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="O11">
         <v>1.49</v>
@@ -3163,7 +3163,7 @@
         <v>1.63</v>
       </c>
       <c r="Q11">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="R11">
         <v>1.23</v>
@@ -3172,22 +3172,22 @@
         <v>5</v>
       </c>
       <c r="T11">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="U11">
         <v>1.82</v>
       </c>
       <c r="V11">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="W11">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="X11">
         <v>9.800000000000001</v>
       </c>
       <c r="Y11">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="Z11">
         <v>11</v>
@@ -3196,55 +3196,55 @@
         <v>26</v>
       </c>
       <c r="AB11">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="AC11">
-        <v>9.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD11">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AE11">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AF11">
         <v>34</v>
       </c>
       <c r="AG11">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="AH11">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AI11">
         <v>55</v>
       </c>
       <c r="AJ11">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AK11">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AL11">
         <v>100</v>
       </c>
       <c r="AM11">
-        <v>190</v>
+        <v>580</v>
       </c>
       <c r="AN11">
         <v>120</v>
       </c>
       <c r="AO11">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="AP11">
         <v>8.6</v>
       </c>
       <c r="AQ11">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AR11">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AS11">
         <v>21</v>
@@ -3262,10 +3262,10 @@
         <v>23</v>
       </c>
       <c r="AX11">
-        <v>21</v>
+        <v>16.5</v>
       </c>
       <c r="AY11">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AZ11">
         <v>22</v>
@@ -3274,82 +3274,82 @@
         <v>46</v>
       </c>
       <c r="BB11">
-        <v>12</v>
+        <v>17.5</v>
       </c>
       <c r="BC11">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="BD11">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="BE11">
-        <v>12</v>
+        <v>130</v>
       </c>
       <c r="BF11">
-        <v>10</v>
+        <v>17.5</v>
       </c>
       <c r="BG11">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BH11">
         <v>2.86</v>
       </c>
       <c r="BI11">
-        <v>2.46</v>
+        <v>2.4</v>
       </c>
       <c r="BJ11">
         <v>11.5</v>
       </c>
       <c r="BK11">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="BL11">
         <v>1000</v>
       </c>
       <c r="BM11">
-        <v>16</v>
+        <v>160</v>
       </c>
       <c r="BN11">
         <v>7.8</v>
       </c>
       <c r="BO11">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BP11">
         <v>1000</v>
       </c>
       <c r="BQ11">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="BR11">
         <v>1000</v>
       </c>
       <c r="BS11">
-        <v>7.4</v>
+        <v>12.5</v>
       </c>
       <c r="BT11">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BU11">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="BV11">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="BW11">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="BX11">
         <v>1000</v>
       </c>
       <c r="BY11">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BZ11">
         <v>1000</v>
       </c>
       <c r="CA11">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="CB11" t="s">
         <v>114</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-28.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-28.xlsx
@@ -358,7 +358,7 @@
     <t>Athletic Club</t>
   </si>
   <si>
-    <t>2026-07-28 10:20:43</t>
+    <t>2026-07-28 12:28:20</t>
   </si>
 </sst>
 </file>
@@ -952,22 +952,22 @@
         <v>104</v>
       </c>
       <c r="F2">
+        <v>3.4</v>
+      </c>
+      <c r="G2">
         <v>3.5</v>
       </c>
-      <c r="G2">
-        <v>3.55</v>
-      </c>
       <c r="H2">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="I2">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="J2">
         <v>3.75</v>
       </c>
       <c r="K2">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L2">
         <v>1.36</v>
@@ -979,31 +979,31 @@
         <v>4.7</v>
       </c>
       <c r="O2">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="P2">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="Q2">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="R2">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="S2">
-        <v>2.82</v>
+        <v>2.92</v>
       </c>
       <c r="T2">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="U2">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="V2">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="W2">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="X2">
         <v>18.5</v>
@@ -1015,13 +1015,13 @@
         <v>15</v>
       </c>
       <c r="AA2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AB2">
         <v>16</v>
       </c>
       <c r="AC2">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AD2">
         <v>11.5</v>
@@ -1030,7 +1030,7 @@
         <v>21</v>
       </c>
       <c r="AF2">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AG2">
         <v>15</v>
@@ -1054,7 +1054,7 @@
         <v>70</v>
       </c>
       <c r="AN2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AO2">
         <v>13.5</v>
@@ -1063,19 +1063,19 @@
         <v>16.5</v>
       </c>
       <c r="AQ2">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AR2">
+        <v>13.5</v>
+      </c>
+      <c r="AS2">
+        <v>26</v>
+      </c>
+      <c r="AT2">
         <v>14</v>
       </c>
-      <c r="AS2">
-        <v>25</v>
-      </c>
-      <c r="AT2">
-        <v>15</v>
-      </c>
       <c r="AU2">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AV2">
         <v>10</v>
@@ -1084,16 +1084,16 @@
         <v>19</v>
       </c>
       <c r="AX2">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AY2">
         <v>13.5</v>
       </c>
       <c r="AZ2">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BA2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BB2">
         <v>50</v>
@@ -1108,13 +1108,13 @@
         <v>55</v>
       </c>
       <c r="BF2">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="BG2">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BH2">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="BI2">
         <v>3.45</v>
@@ -1123,13 +1123,13 @@
         <v>9</v>
       </c>
       <c r="BK2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BL2">
         <v>95</v>
       </c>
       <c r="BM2">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="BN2">
         <v>6.8</v>
@@ -1141,16 +1141,16 @@
         <v>25</v>
       </c>
       <c r="BQ2">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BR2">
         <v>34</v>
       </c>
       <c r="BS2">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="BT2">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BU2">
         <v>4.7</v>
@@ -1159,13 +1159,13 @@
         <v>15.5</v>
       </c>
       <c r="BW2">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BX2">
         <v>26</v>
       </c>
       <c r="BY2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BZ2">
         <v>0</v>
@@ -1194,16 +1194,16 @@
         <v>105</v>
       </c>
       <c r="F3">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="G3">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="H3">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="I3">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="J3">
         <v>3.75</v>
@@ -1212,64 +1212,64 @@
         <v>3.9</v>
       </c>
       <c r="L3">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="M3">
         <v>1.05</v>
       </c>
       <c r="N3">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="O3">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="P3">
-        <v>2.44</v>
+        <v>2.36</v>
       </c>
       <c r="Q3">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="R3">
         <v>1.55</v>
       </c>
       <c r="S3">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="T3">
         <v>1.6</v>
       </c>
       <c r="U3">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
       <c r="V3">
         <v>1.45</v>
       </c>
       <c r="W3">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="X3">
         <v>21</v>
       </c>
       <c r="Y3">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Z3">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AA3">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AB3">
         <v>14</v>
       </c>
       <c r="AC3">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD3">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AE3">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AF3">
         <v>17.5</v>
@@ -1278,25 +1278,25 @@
         <v>11.5</v>
       </c>
       <c r="AH3">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AI3">
         <v>36</v>
       </c>
       <c r="AJ3">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AK3">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AL3">
         <v>30</v>
       </c>
       <c r="AM3">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AN3">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AO3">
         <v>22</v>
@@ -1305,25 +1305,25 @@
         <v>19</v>
       </c>
       <c r="AQ3">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AR3">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AS3">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="AT3">
         <v>12.5</v>
       </c>
       <c r="AU3">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AV3">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AW3">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AX3">
         <v>16</v>
@@ -1338,82 +1338,82 @@
         <v>32</v>
       </c>
       <c r="BB3">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="BC3">
         <v>20</v>
       </c>
       <c r="BD3">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BE3">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="BF3">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BG3">
         <v>20</v>
       </c>
       <c r="BH3">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BI3">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="BJ3">
         <v>8.800000000000001</v>
       </c>
       <c r="BK3">
-        <v>7.8</v>
+        <v>5.7</v>
       </c>
       <c r="BL3">
         <v>85</v>
       </c>
       <c r="BM3">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="BN3">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BO3">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BP3">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BQ3">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR3">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BS3">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BT3">
         <v>6.6</v>
       </c>
       <c r="BU3">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="BV3">
         <v>22</v>
       </c>
       <c r="BW3">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="BX3">
         <v>30</v>
       </c>
       <c r="BY3">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BZ3">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="CA3">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB3" t="s">
         <v>114</v>
@@ -1678,7 +1678,7 @@
         <v>107</v>
       </c>
       <c r="F5">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="G5">
         <v>3.9</v>
@@ -1687,64 +1687,64 @@
         <v>2.42</v>
       </c>
       <c r="I5">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="J5">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="K5">
         <v>3.05</v>
       </c>
       <c r="L5">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="M5">
         <v>1.14</v>
       </c>
       <c r="N5">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="O5">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="P5">
         <v>1.51</v>
       </c>
       <c r="Q5">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="R5">
         <v>1.18</v>
       </c>
       <c r="S5">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="T5">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="U5">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="V5">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="W5">
         <v>1.35</v>
       </c>
       <c r="X5">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="Y5">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="Z5">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AA5">
         <v>85</v>
       </c>
       <c r="AB5">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AC5">
         <v>7.2</v>
@@ -1756,13 +1756,13 @@
         <v>85</v>
       </c>
       <c r="AF5">
-        <v>130</v>
+        <v>30</v>
       </c>
       <c r="AG5">
-        <v>17</v>
+        <v>95</v>
       </c>
       <c r="AH5">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="AI5">
         <v>150</v>
@@ -1780,16 +1780,16 @@
         <v>500</v>
       </c>
       <c r="AN5">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="AO5">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AP5">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="AQ5">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AR5">
         <v>12</v>
@@ -1804,94 +1804,94 @@
         <v>6.2</v>
       </c>
       <c r="AV5">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AW5">
         <v>19.5</v>
       </c>
       <c r="AX5">
-        <v>11.5</v>
+        <v>21</v>
       </c>
       <c r="AY5">
-        <v>14</v>
+        <v>7.6</v>
       </c>
       <c r="AZ5">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BA5">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BB5">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BC5">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BD5">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BE5">
+        <v>10.5</v>
+      </c>
+      <c r="BF5">
         <v>10</v>
       </c>
-      <c r="BF5">
-        <v>9.6</v>
-      </c>
       <c r="BG5">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BH5">
-        <v>2.68</v>
+        <v>2.62</v>
       </c>
       <c r="BI5">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="BJ5">
         <v>12</v>
       </c>
       <c r="BK5">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="BN5">
         <v>6.8</v>
       </c>
       <c r="BO5">
-        <v>5.8</v>
+        <v>4.7</v>
       </c>
       <c r="BP5">
         <v>1000</v>
       </c>
       <c r="BQ5">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BR5">
         <v>1000</v>
       </c>
       <c r="BS5">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BT5">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BU5">
         <v>4.4</v>
       </c>
       <c r="BV5">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="BW5">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BX5">
         <v>1000</v>
       </c>
       <c r="BY5">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BZ5">
         <v>0</v>
@@ -1920,7 +1920,7 @@
         <v>108</v>
       </c>
       <c r="F6">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="G6">
         <v>6.4</v>
@@ -1932,10 +1932,10 @@
         <v>1.54</v>
       </c>
       <c r="J6">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="K6">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="L6">
         <v>1.18</v>
@@ -1944,46 +1944,46 @@
         <v>1.02</v>
       </c>
       <c r="N6">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="O6">
         <v>1.09</v>
       </c>
       <c r="P6">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="Q6">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="R6">
-        <v>2.18</v>
+        <v>2.26</v>
       </c>
       <c r="S6">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="T6">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="U6">
-        <v>2.88</v>
+        <v>2.96</v>
       </c>
       <c r="V6">
         <v>2.84</v>
       </c>
       <c r="W6">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="X6">
         <v>60</v>
       </c>
       <c r="Y6">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Z6">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AA6">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AB6">
         <v>65</v>
@@ -1998,16 +1998,16 @@
         <v>14.5</v>
       </c>
       <c r="AF6">
-        <v>450</v>
+        <v>100</v>
       </c>
       <c r="AG6">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AH6">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AI6">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AJ6">
         <v>160</v>
@@ -2025,7 +2025,7 @@
         <v>38</v>
       </c>
       <c r="AO6">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="AP6">
         <v>29</v>
@@ -2034,16 +2034,16 @@
         <v>18</v>
       </c>
       <c r="AR6">
+        <v>15</v>
+      </c>
+      <c r="AS6">
+        <v>16</v>
+      </c>
+      <c r="AT6">
+        <v>40</v>
+      </c>
+      <c r="AU6">
         <v>14</v>
-      </c>
-      <c r="AS6">
-        <v>15</v>
-      </c>
-      <c r="AT6">
-        <v>38</v>
-      </c>
-      <c r="AU6">
-        <v>13.5</v>
       </c>
       <c r="AV6">
         <v>10.5</v>
@@ -2052,10 +2052,10 @@
         <v>12.5</v>
       </c>
       <c r="AX6">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="AY6">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AZ6">
         <v>15.5</v>
@@ -2064,22 +2064,22 @@
         <v>18.5</v>
       </c>
       <c r="BB6">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BC6">
         <v>42</v>
       </c>
       <c r="BD6">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BE6">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BF6">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BG6">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="BH6">
         <v>6.4</v>
@@ -2088,34 +2088,34 @@
         <v>5.6</v>
       </c>
       <c r="BJ6">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK6">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BL6">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BM6">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BN6">
         <v>10.5</v>
       </c>
       <c r="BO6">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BP6">
         <v>1000</v>
       </c>
       <c r="BQ6">
+        <v>11</v>
+      </c>
+      <c r="BR6">
+        <v>30</v>
+      </c>
+      <c r="BS6">
         <v>10.5</v>
-      </c>
-      <c r="BR6">
-        <v>32</v>
-      </c>
-      <c r="BS6">
-        <v>10</v>
       </c>
       <c r="BT6">
         <v>5.2</v>
@@ -2127,19 +2127,19 @@
         <v>9</v>
       </c>
       <c r="BW6">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BX6">
         <v>15.5</v>
       </c>
       <c r="BY6">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BZ6">
         <v>7.8</v>
       </c>
       <c r="CA6">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="CB6" t="s">
         <v>114</v>
@@ -2162,13 +2162,13 @@
         <v>109</v>
       </c>
       <c r="F7">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="G7">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="H7">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="I7">
         <v>2.22</v>
@@ -2192,19 +2192,19 @@
         <v>1.51</v>
       </c>
       <c r="P7">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="Q7">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="R7">
         <v>1.2</v>
       </c>
       <c r="S7">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="T7">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="U7">
         <v>1.83</v>
@@ -2225,7 +2225,7 @@
         <v>12.5</v>
       </c>
       <c r="AA7">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AB7">
         <v>12</v>
@@ -2234,7 +2234,7 @@
         <v>7.8</v>
       </c>
       <c r="AD7">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AE7">
         <v>30</v>
@@ -2243,31 +2243,31 @@
         <v>32</v>
       </c>
       <c r="AG7">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AH7">
         <v>26</v>
       </c>
       <c r="AI7">
-        <v>130</v>
+        <v>60</v>
       </c>
       <c r="AJ7">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AK7">
-        <v>160</v>
+        <v>120</v>
       </c>
       <c r="AL7">
-        <v>350</v>
+        <v>210</v>
       </c>
       <c r="AM7">
         <v>580</v>
       </c>
       <c r="AN7">
-        <v>130</v>
+        <v>600</v>
       </c>
       <c r="AO7">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AP7">
         <v>8</v>
@@ -2276,13 +2276,13 @@
         <v>6.2</v>
       </c>
       <c r="AR7">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AS7">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AT7">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AU7">
         <v>6.6</v>
@@ -2294,94 +2294,94 @@
         <v>14</v>
       </c>
       <c r="AX7">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="AY7">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AZ7">
         <v>21</v>
       </c>
       <c r="BA7">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="BB7">
+        <v>10</v>
+      </c>
+      <c r="BC7">
         <v>9.800000000000001</v>
       </c>
-      <c r="BC7">
-        <v>9.4</v>
-      </c>
       <c r="BD7">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BE7">
+        <v>10.5</v>
+      </c>
+      <c r="BF7">
         <v>10</v>
       </c>
-      <c r="BF7">
-        <v>9.800000000000001</v>
-      </c>
       <c r="BG7">
-        <v>9.6</v>
+        <v>8</v>
       </c>
       <c r="BH7">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="BI7">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="BJ7">
         <v>11.5</v>
       </c>
       <c r="BK7">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BN7">
         <v>7.6</v>
       </c>
       <c r="BO7">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="BP7">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="BQ7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BR7">
         <v>1000</v>
       </c>
       <c r="BS7">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BT7">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BU7">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="BV7">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BW7">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BX7">
         <v>42</v>
       </c>
       <c r="BY7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BZ7">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="CA7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="CB7" t="s">
         <v>114</v>
@@ -2404,10 +2404,10 @@
         <v>110</v>
       </c>
       <c r="F8">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="G8">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="H8">
         <v>4.6</v>
@@ -2416,52 +2416,52 @@
         <v>4.8</v>
       </c>
       <c r="J8">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K8">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="L8">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="M8">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="N8">
-        <v>2.52</v>
+        <v>2.66</v>
       </c>
       <c r="O8">
-        <v>1.64</v>
+        <v>1.59</v>
       </c>
       <c r="P8">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="Q8">
-        <v>2.98</v>
+        <v>2.8</v>
       </c>
       <c r="R8">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="S8">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="T8">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="U8">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="V8">
         <v>1.26</v>
       </c>
       <c r="W8">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="X8">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="Y8">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Z8">
         <v>32</v>
@@ -2470,13 +2470,13 @@
         <v>130</v>
       </c>
       <c r="AB8">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AC8">
         <v>7.4</v>
       </c>
       <c r="AD8">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AE8">
         <v>95</v>
@@ -2488,31 +2488,31 @@
         <v>12</v>
       </c>
       <c r="AH8">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AI8">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AJ8">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AK8">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AL8">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AM8">
-        <v>270</v>
+        <v>250</v>
       </c>
       <c r="AN8">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AO8">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AP8">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AQ8">
         <v>10</v>
@@ -2533,16 +2533,16 @@
         <v>18.5</v>
       </c>
       <c r="AW8">
-        <v>44</v>
+        <v>75</v>
       </c>
       <c r="AX8">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AY8">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AZ8">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="BA8">
         <v>46</v>
@@ -2551,28 +2551,28 @@
         <v>23</v>
       </c>
       <c r="BC8">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="BD8">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="BE8">
         <v>110</v>
       </c>
       <c r="BF8">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="BG8">
         <v>46</v>
       </c>
       <c r="BH8">
-        <v>2.56</v>
+        <v>2.64</v>
       </c>
       <c r="BI8">
-        <v>2.38</v>
+        <v>2.46</v>
       </c>
       <c r="BJ8">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BK8">
         <v>7.4</v>
@@ -2581,7 +2581,7 @@
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="BN8">
         <v>4.5</v>
@@ -2590,40 +2590,40 @@
         <v>4</v>
       </c>
       <c r="BP8">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BQ8">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BR8">
         <v>1000</v>
       </c>
       <c r="BS8">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BT8">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BU8">
         <v>6</v>
       </c>
       <c r="BV8">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BW8">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BX8">
         <v>1000</v>
       </c>
       <c r="BY8">
-        <v>2.18</v>
+        <v>2.26</v>
       </c>
       <c r="BZ8">
         <v>1000</v>
       </c>
       <c r="CA8">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="CB8" t="s">
         <v>114</v>
@@ -2655,13 +2655,13 @@
         <v>4.5</v>
       </c>
       <c r="I9">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="J9">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K9">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="L9">
         <v>1.61</v>
@@ -2670,16 +2670,16 @@
         <v>1.14</v>
       </c>
       <c r="N9">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="O9">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="P9">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="Q9">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="R9">
         <v>1.18</v>
@@ -2688,19 +2688,19 @@
         <v>6</v>
       </c>
       <c r="T9">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="U9">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="V9">
         <v>1.27</v>
       </c>
       <c r="W9">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="X9">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="Y9">
         <v>11.5</v>
@@ -2709,31 +2709,31 @@
         <v>32</v>
       </c>
       <c r="AA9">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AB9">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AC9">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AD9">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AE9">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AF9">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AG9">
         <v>12</v>
       </c>
       <c r="AH9">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AI9">
-        <v>120</v>
+        <v>260</v>
       </c>
       <c r="AJ9">
         <v>28</v>
@@ -2742,25 +2742,25 @@
         <v>32</v>
       </c>
       <c r="AL9">
-        <v>65</v>
+        <v>150</v>
       </c>
       <c r="AM9">
-        <v>240</v>
+        <v>1000</v>
       </c>
       <c r="AN9">
         <v>30</v>
       </c>
       <c r="AO9">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="AP9">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AQ9">
         <v>10.5</v>
       </c>
       <c r="AR9">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AS9">
         <v>38</v>
@@ -2769,19 +2769,19 @@
         <v>6</v>
       </c>
       <c r="AU9">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AV9">
         <v>18</v>
       </c>
       <c r="AW9">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="AX9">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY9">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AZ9">
         <v>25</v>
@@ -2808,64 +2808,64 @@
         <v>42</v>
       </c>
       <c r="BH9">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="BI9">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="BJ9">
         <v>12</v>
       </c>
       <c r="BK9">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BL9">
         <v>1000</v>
       </c>
       <c r="BM9">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BN9">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BO9">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="BP9">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BQ9">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BR9">
         <v>44</v>
       </c>
       <c r="BS9">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT9">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BU9">
         <v>5.5</v>
       </c>
       <c r="BV9">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BW9">
+        <v>9.4</v>
+      </c>
+      <c r="BX9">
+        <v>75</v>
+      </c>
+      <c r="BY9">
         <v>10</v>
-      </c>
-      <c r="BX9">
-        <v>1000</v>
-      </c>
-      <c r="BY9">
-        <v>10.5</v>
       </c>
       <c r="BZ9">
         <v>48</v>
       </c>
       <c r="CA9">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB9" t="s">
         <v>114</v>
@@ -2888,28 +2888,28 @@
         <v>112</v>
       </c>
       <c r="F10">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="G10">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="H10">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="I10">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="J10">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="K10">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="L10">
         <v>1.52</v>
       </c>
       <c r="M10">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="N10">
         <v>3</v>
@@ -2918,13 +2918,13 @@
         <v>1.47</v>
       </c>
       <c r="P10">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="Q10">
         <v>2.44</v>
       </c>
       <c r="R10">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="S10">
         <v>4.9</v>
@@ -2933,19 +2933,19 @@
         <v>2.34</v>
       </c>
       <c r="U10">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="V10">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="W10">
-        <v>2.48</v>
+        <v>2.54</v>
       </c>
       <c r="X10">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="Y10">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="Z10">
         <v>65</v>
@@ -2957,7 +2957,7 @@
         <v>6.2</v>
       </c>
       <c r="AC10">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AD10">
         <v>30</v>
@@ -2966,7 +2966,7 @@
         <v>160</v>
       </c>
       <c r="AF10">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AG10">
         <v>10.5</v>
@@ -2975,10 +2975,10 @@
         <v>30</v>
       </c>
       <c r="AI10">
-        <v>190</v>
+        <v>170</v>
       </c>
       <c r="AJ10">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AK10">
         <v>22</v>
@@ -2987,37 +2987,37 @@
         <v>60</v>
       </c>
       <c r="AM10">
-        <v>580</v>
+        <v>700</v>
       </c>
       <c r="AN10">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AO10">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="AP10">
         <v>9.4</v>
       </c>
       <c r="AQ10">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AR10">
         <v>50</v>
       </c>
       <c r="AS10">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AT10">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="AU10">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="AV10">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AW10">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="AX10">
         <v>7.4</v>
@@ -3029,7 +3029,7 @@
         <v>28</v>
       </c>
       <c r="BA10">
-        <v>36</v>
+        <v>15.5</v>
       </c>
       <c r="BB10">
         <v>14</v>
@@ -3047,13 +3047,13 @@
         <v>12.5</v>
       </c>
       <c r="BG10">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="BH10">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="BI10">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="BJ10">
         <v>13.5</v>
@@ -3068,34 +3068,34 @@
         <v>180</v>
       </c>
       <c r="BN10">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BO10">
         <v>3.35</v>
       </c>
       <c r="BP10">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BQ10">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BR10">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BS10">
         <v>8.6</v>
       </c>
       <c r="BT10">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BU10">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BV10">
         <v>90</v>
       </c>
       <c r="BW10">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BX10">
         <v>100</v>
@@ -3104,7 +3104,7 @@
         <v>10</v>
       </c>
       <c r="BZ10">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="CA10">
         <v>8.199999999999999</v>
@@ -3133,16 +3133,16 @@
         <v>4.5</v>
       </c>
       <c r="G11">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="H11">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="I11">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="J11">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K11">
         <v>3.45</v>
@@ -3154,28 +3154,28 @@
         <v>1.11</v>
       </c>
       <c r="N11">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="O11">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="P11">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="Q11">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="R11">
         <v>1.23</v>
       </c>
       <c r="S11">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="T11">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="U11">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="V11">
         <v>1.94</v>
@@ -3193,7 +3193,7 @@
         <v>11</v>
       </c>
       <c r="AA11">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AB11">
         <v>12.5</v>
@@ -3202,7 +3202,7 @@
         <v>8</v>
       </c>
       <c r="AD11">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AE11">
         <v>27</v>
@@ -3211,10 +3211,10 @@
         <v>34</v>
       </c>
       <c r="AG11">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AH11">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI11">
         <v>55</v>
@@ -3223,37 +3223,37 @@
         <v>120</v>
       </c>
       <c r="AK11">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AL11">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="AM11">
         <v>580</v>
       </c>
       <c r="AN11">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AO11">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AP11">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AQ11">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AR11">
         <v>10</v>
       </c>
       <c r="AS11">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AT11">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AU11">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV11">
         <v>10</v>
@@ -3262,10 +3262,10 @@
         <v>23</v>
       </c>
       <c r="AX11">
-        <v>16.5</v>
+        <v>28</v>
       </c>
       <c r="AY11">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AZ11">
         <v>22</v>
@@ -3274,19 +3274,19 @@
         <v>46</v>
       </c>
       <c r="BB11">
-        <v>17.5</v>
+        <v>28</v>
       </c>
       <c r="BC11">
-        <v>28</v>
+        <v>65</v>
       </c>
       <c r="BD11">
-        <v>44</v>
+        <v>18.5</v>
       </c>
       <c r="BE11">
         <v>130</v>
       </c>
       <c r="BF11">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="BG11">
         <v>20</v>
@@ -3295,7 +3295,7 @@
         <v>2.86</v>
       </c>
       <c r="BI11">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="BJ11">
         <v>11.5</v>
@@ -3313,7 +3313,7 @@
         <v>7.8</v>
       </c>
       <c r="BO11">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BP11">
         <v>1000</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-28.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-28.xlsx
@@ -358,7 +358,7 @@
     <t>Athletic Club</t>
   </si>
   <si>
-    <t>2026-07-28 12:28:20</t>
+    <t>2026-07-28 14:35:52</t>
   </si>
 </sst>
 </file>
@@ -952,220 +952,220 @@
         <v>104</v>
       </c>
       <c r="F2">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="G2">
-        <v>3.5</v>
+        <v>3.85</v>
       </c>
       <c r="H2">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="I2">
-        <v>2.24</v>
+        <v>2.42</v>
       </c>
       <c r="J2">
-        <v>3.75</v>
+        <v>3.05</v>
       </c>
       <c r="K2">
-        <v>3.9</v>
+        <v>3.1</v>
       </c>
       <c r="L2">
-        <v>1.36</v>
+        <v>2.62</v>
       </c>
       <c r="M2">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="N2">
-        <v>4.7</v>
+        <v>2.56</v>
       </c>
       <c r="O2">
-        <v>1.26</v>
+        <v>1.62</v>
       </c>
       <c r="P2">
-        <v>2.2</v>
+        <v>1.47</v>
       </c>
       <c r="Q2">
-        <v>1.8</v>
+        <v>3.05</v>
       </c>
       <c r="R2">
-        <v>1.5</v>
+        <v>1.16</v>
       </c>
       <c r="S2">
-        <v>2.92</v>
+        <v>7</v>
       </c>
       <c r="T2">
-        <v>1.67</v>
+        <v>2.42</v>
       </c>
       <c r="U2">
-        <v>2.4</v>
+        <v>1.64</v>
       </c>
       <c r="V2">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="W2">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="X2">
+        <v>7.2</v>
+      </c>
+      <c r="Y2">
+        <v>6.8</v>
+      </c>
+      <c r="Z2">
+        <v>12.5</v>
+      </c>
+      <c r="AA2">
+        <v>36</v>
+      </c>
+      <c r="AB2">
+        <v>9.4</v>
+      </c>
+      <c r="AC2">
+        <v>7.2</v>
+      </c>
+      <c r="AD2">
+        <v>13.5</v>
+      </c>
+      <c r="AE2">
+        <v>40</v>
+      </c>
+      <c r="AF2">
+        <v>23</v>
+      </c>
+      <c r="AG2">
         <v>18.5</v>
       </c>
-      <c r="Y2">
+      <c r="AH2">
+        <v>29</v>
+      </c>
+      <c r="AI2">
+        <v>100</v>
+      </c>
+      <c r="AJ2">
+        <v>95</v>
+      </c>
+      <c r="AK2">
+        <v>90</v>
+      </c>
+      <c r="AL2">
+        <v>160</v>
+      </c>
+      <c r="AM2">
+        <v>330</v>
+      </c>
+      <c r="AN2">
+        <v>120</v>
+      </c>
+      <c r="AO2">
+        <v>46</v>
+      </c>
+      <c r="AP2">
+        <v>6.8</v>
+      </c>
+      <c r="AQ2">
+        <v>6.4</v>
+      </c>
+      <c r="AR2">
+        <v>11</v>
+      </c>
+      <c r="AS2">
+        <v>29</v>
+      </c>
+      <c r="AT2">
+        <v>8.6</v>
+      </c>
+      <c r="AU2">
+        <v>6.6</v>
+      </c>
+      <c r="AV2">
         <v>12</v>
       </c>
-      <c r="Z2">
-        <v>15</v>
-      </c>
-      <c r="AA2">
-        <v>29</v>
-      </c>
-      <c r="AB2">
-        <v>16</v>
-      </c>
-      <c r="AC2">
-        <v>8.4</v>
-      </c>
-      <c r="AD2">
-        <v>11.5</v>
-      </c>
-      <c r="AE2">
-        <v>21</v>
-      </c>
-      <c r="AF2">
-        <v>26</v>
-      </c>
-      <c r="AG2">
-        <v>15</v>
-      </c>
-      <c r="AH2">
-        <v>15.5</v>
-      </c>
-      <c r="AI2">
-        <v>30</v>
-      </c>
-      <c r="AJ2">
+      <c r="AW2">
+        <v>34</v>
+      </c>
+      <c r="AX2">
+        <v>20</v>
+      </c>
+      <c r="AY2">
+        <v>16.5</v>
+      </c>
+      <c r="AZ2">
+        <v>27</v>
+      </c>
+      <c r="BA2">
+        <v>75</v>
+      </c>
+      <c r="BB2">
+        <v>75</v>
+      </c>
+      <c r="BC2">
+        <v>60</v>
+      </c>
+      <c r="BD2">
+        <v>110</v>
+      </c>
+      <c r="BE2">
+        <v>240</v>
+      </c>
+      <c r="BF2">
+        <v>95</v>
+      </c>
+      <c r="BG2">
+        <v>38</v>
+      </c>
+      <c r="BH2">
+        <v>1.57</v>
+      </c>
+      <c r="BI2">
+        <v>1.52</v>
+      </c>
+      <c r="BJ2">
+        <v>42</v>
+      </c>
+      <c r="BK2">
+        <v>32</v>
+      </c>
+      <c r="BL2">
+        <v>1000</v>
+      </c>
+      <c r="BM2">
+        <v>25</v>
+      </c>
+      <c r="BN2">
+        <v>8.6</v>
+      </c>
+      <c r="BO2">
+        <v>7.8</v>
+      </c>
+      <c r="BP2">
+        <v>130</v>
+      </c>
+      <c r="BQ2">
+        <v>90</v>
+      </c>
+      <c r="BR2">
+        <v>690</v>
+      </c>
+      <c r="BS2">
+        <v>24</v>
+      </c>
+      <c r="BT2">
+        <v>6.4</v>
+      </c>
+      <c r="BU2">
+        <v>5.6</v>
+      </c>
+      <c r="BV2">
         <v>65</v>
       </c>
-      <c r="AK2">
-        <v>36</v>
-      </c>
-      <c r="AL2">
-        <v>42</v>
-      </c>
-      <c r="AM2">
-        <v>70</v>
-      </c>
-      <c r="AN2">
-        <v>30</v>
-      </c>
-      <c r="AO2">
-        <v>13.5</v>
-      </c>
-      <c r="AP2">
-        <v>16.5</v>
-      </c>
-      <c r="AQ2">
-        <v>10.5</v>
-      </c>
-      <c r="AR2">
-        <v>13.5</v>
-      </c>
-      <c r="AS2">
-        <v>26</v>
-      </c>
-      <c r="AT2">
-        <v>14</v>
-      </c>
-      <c r="AU2">
-        <v>7.8</v>
-      </c>
-      <c r="AV2">
-        <v>10</v>
-      </c>
-      <c r="AW2">
-        <v>19</v>
-      </c>
-      <c r="AX2">
-        <v>23</v>
-      </c>
-      <c r="AY2">
-        <v>13.5</v>
-      </c>
-      <c r="AZ2">
-        <v>14.5</v>
-      </c>
-      <c r="BA2">
-        <v>28</v>
-      </c>
-      <c r="BB2">
+      <c r="BW2">
         <v>50</v>
       </c>
-      <c r="BC2">
-        <v>32</v>
-      </c>
-      <c r="BD2">
-        <v>36</v>
-      </c>
-      <c r="BE2">
-        <v>55</v>
-      </c>
-      <c r="BF2">
-        <v>26</v>
-      </c>
-      <c r="BG2">
-        <v>12.5</v>
-      </c>
-      <c r="BH2">
-        <v>3.75</v>
-      </c>
-      <c r="BI2">
-        <v>3.45</v>
-      </c>
-      <c r="BJ2">
-        <v>9</v>
-      </c>
-      <c r="BK2">
-        <v>6</v>
-      </c>
-      <c r="BL2">
+      <c r="BX2">
+        <v>460</v>
+      </c>
+      <c r="BY2">
         <v>95</v>
-      </c>
-      <c r="BM2">
-        <v>15.5</v>
-      </c>
-      <c r="BN2">
-        <v>6.8</v>
-      </c>
-      <c r="BO2">
-        <v>6</v>
-      </c>
-      <c r="BP2">
-        <v>25</v>
-      </c>
-      <c r="BQ2">
-        <v>10.5</v>
-      </c>
-      <c r="BR2">
-        <v>34</v>
-      </c>
-      <c r="BS2">
-        <v>12</v>
-      </c>
-      <c r="BT2">
-        <v>5.2</v>
-      </c>
-      <c r="BU2">
-        <v>4.7</v>
-      </c>
-      <c r="BV2">
-        <v>15.5</v>
-      </c>
-      <c r="BW2">
-        <v>8.4</v>
-      </c>
-      <c r="BX2">
-        <v>26</v>
-      </c>
-      <c r="BY2">
-        <v>11</v>
       </c>
       <c r="BZ2">
         <v>0</v>
@@ -1194,226 +1194,226 @@
         <v>105</v>
       </c>
       <c r="F3">
-        <v>2.36</v>
+        <v>2.24</v>
       </c>
       <c r="G3">
-        <v>2.42</v>
+        <v>2.28</v>
       </c>
       <c r="H3">
+        <v>4.1</v>
+      </c>
+      <c r="I3">
+        <v>4.3</v>
+      </c>
+      <c r="J3">
         <v>3.1</v>
       </c>
-      <c r="I3">
-        <v>3.2</v>
-      </c>
-      <c r="J3">
-        <v>3.75</v>
-      </c>
       <c r="K3">
-        <v>3.9</v>
+        <v>3.15</v>
       </c>
       <c r="L3">
-        <v>1.34</v>
+        <v>3</v>
       </c>
       <c r="M3">
-        <v>1.05</v>
+        <v>1.15</v>
       </c>
       <c r="N3">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="O3">
-        <v>1.23</v>
+        <v>1.64</v>
       </c>
       <c r="P3">
-        <v>2.36</v>
+        <v>1.49</v>
       </c>
       <c r="Q3">
-        <v>1.71</v>
+        <v>2.98</v>
       </c>
       <c r="R3">
-        <v>1.55</v>
+        <v>1.15</v>
       </c>
       <c r="S3">
-        <v>2.78</v>
+        <v>7.2</v>
       </c>
       <c r="T3">
-        <v>1.6</v>
+        <v>2.4</v>
       </c>
       <c r="U3">
-        <v>2.54</v>
+        <v>1.67</v>
       </c>
       <c r="V3">
-        <v>1.45</v>
+        <v>1.31</v>
       </c>
       <c r="W3">
-        <v>1.7</v>
+        <v>1.79</v>
       </c>
       <c r="X3">
-        <v>21</v>
+        <v>7.8</v>
       </c>
       <c r="Y3">
-        <v>16</v>
+        <v>10.5</v>
       </c>
       <c r="Z3">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="AA3">
+        <v>110</v>
+      </c>
+      <c r="AB3">
+        <v>6.6</v>
+      </c>
+      <c r="AC3">
+        <v>7.4</v>
+      </c>
+      <c r="AD3">
+        <v>19</v>
+      </c>
+      <c r="AE3">
+        <v>95</v>
+      </c>
+      <c r="AF3">
+        <v>11.5</v>
+      </c>
+      <c r="AG3">
+        <v>12.5</v>
+      </c>
+      <c r="AH3">
+        <v>29</v>
+      </c>
+      <c r="AI3">
+        <v>140</v>
+      </c>
+      <c r="AJ3">
+        <v>29</v>
+      </c>
+      <c r="AK3">
+        <v>36</v>
+      </c>
+      <c r="AL3">
+        <v>95</v>
+      </c>
+      <c r="AM3">
+        <v>350</v>
+      </c>
+      <c r="AN3">
+        <v>36</v>
+      </c>
+      <c r="AO3">
+        <v>150</v>
+      </c>
+      <c r="AP3">
+        <v>7.2</v>
+      </c>
+      <c r="AQ3">
+        <v>9.4</v>
+      </c>
+      <c r="AR3">
+        <v>22</v>
+      </c>
+      <c r="AS3">
+        <v>80</v>
+      </c>
+      <c r="AT3">
+        <v>6.2</v>
+      </c>
+      <c r="AU3">
+        <v>6.8</v>
+      </c>
+      <c r="AV3">
+        <v>17</v>
+      </c>
+      <c r="AW3">
+        <v>65</v>
+      </c>
+      <c r="AX3">
+        <v>10</v>
+      </c>
+      <c r="AY3">
+        <v>11</v>
+      </c>
+      <c r="AZ3">
+        <v>25</v>
+      </c>
+      <c r="BA3">
+        <v>100</v>
+      </c>
+      <c r="BB3">
+        <v>25</v>
+      </c>
+      <c r="BC3">
+        <v>28</v>
+      </c>
+      <c r="BD3">
+        <v>65</v>
+      </c>
+      <c r="BE3">
+        <v>230</v>
+      </c>
+      <c r="BF3">
+        <v>30</v>
+      </c>
+      <c r="BG3">
+        <v>100</v>
+      </c>
+      <c r="BH3">
+        <v>1.51</v>
+      </c>
+      <c r="BI3">
+        <v>1.47</v>
+      </c>
+      <c r="BJ3">
         <v>50</v>
       </c>
-      <c r="AB3">
-        <v>14</v>
-      </c>
-      <c r="AC3">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AD3">
-        <v>13</v>
-      </c>
-      <c r="AE3">
-        <v>30</v>
-      </c>
-      <c r="AF3">
-        <v>17.5</v>
-      </c>
-      <c r="AG3">
-        <v>11.5</v>
-      </c>
-      <c r="AH3">
-        <v>15</v>
-      </c>
-      <c r="AI3">
+      <c r="BK3">
         <v>36</v>
       </c>
-      <c r="AJ3">
-        <v>32</v>
-      </c>
-      <c r="AK3">
-        <v>23</v>
-      </c>
-      <c r="AL3">
-        <v>30</v>
-      </c>
-      <c r="AM3">
-        <v>65</v>
-      </c>
-      <c r="AN3">
-        <v>14</v>
-      </c>
-      <c r="AO3">
+      <c r="BL3">
+        <v>1000</v>
+      </c>
+      <c r="BM3">
         <v>22</v>
       </c>
-      <c r="AP3">
-        <v>19</v>
-      </c>
-      <c r="AQ3">
-        <v>14.5</v>
-      </c>
-      <c r="AR3">
-        <v>21</v>
-      </c>
-      <c r="AS3">
-        <v>44</v>
-      </c>
-      <c r="AT3">
-        <v>12.5</v>
-      </c>
-      <c r="AU3">
-        <v>8</v>
-      </c>
-      <c r="AV3">
-        <v>12</v>
-      </c>
-      <c r="AW3">
+      <c r="BN3">
+        <v>6.4</v>
+      </c>
+      <c r="BO3">
+        <v>5.6</v>
+      </c>
+      <c r="BP3">
+        <v>75</v>
+      </c>
+      <c r="BQ3">
+        <v>55</v>
+      </c>
+      <c r="BR3">
+        <v>1000</v>
+      </c>
+      <c r="BS3">
+        <v>22</v>
+      </c>
+      <c r="BT3">
+        <v>9.6</v>
+      </c>
+      <c r="BU3">
+        <v>8.6</v>
+      </c>
+      <c r="BV3">
+        <v>160</v>
+      </c>
+      <c r="BW3">
+        <v>100</v>
+      </c>
+      <c r="BX3">
+        <v>900</v>
+      </c>
+      <c r="BY3">
+        <v>22</v>
+      </c>
+      <c r="BZ3">
+        <v>890</v>
+      </c>
+      <c r="CA3">
         <v>27</v>
-      </c>
-      <c r="AX3">
-        <v>16</v>
-      </c>
-      <c r="AY3">
-        <v>10</v>
-      </c>
-      <c r="AZ3">
-        <v>13.5</v>
-      </c>
-      <c r="BA3">
-        <v>32</v>
-      </c>
-      <c r="BB3">
-        <v>29</v>
-      </c>
-      <c r="BC3">
-        <v>20</v>
-      </c>
-      <c r="BD3">
-        <v>27</v>
-      </c>
-      <c r="BE3">
-        <v>36</v>
-      </c>
-      <c r="BF3">
-        <v>12.5</v>
-      </c>
-      <c r="BG3">
-        <v>20</v>
-      </c>
-      <c r="BH3">
-        <v>3.95</v>
-      </c>
-      <c r="BI3">
-        <v>3.65</v>
-      </c>
-      <c r="BJ3">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BK3">
-        <v>5.7</v>
-      </c>
-      <c r="BL3">
-        <v>85</v>
-      </c>
-      <c r="BM3">
-        <v>13.5</v>
-      </c>
-      <c r="BN3">
-        <v>5.6</v>
-      </c>
-      <c r="BO3">
-        <v>5</v>
-      </c>
-      <c r="BP3">
-        <v>16.5</v>
-      </c>
-      <c r="BQ3">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BR3">
-        <v>26</v>
-      </c>
-      <c r="BS3">
-        <v>10</v>
-      </c>
-      <c r="BT3">
-        <v>6.6</v>
-      </c>
-      <c r="BU3">
-        <v>5.8</v>
-      </c>
-      <c r="BV3">
-        <v>22</v>
-      </c>
-      <c r="BW3">
-        <v>9.4</v>
-      </c>
-      <c r="BX3">
-        <v>30</v>
-      </c>
-      <c r="BY3">
-        <v>10.5</v>
-      </c>
-      <c r="BZ3">
-        <v>19</v>
-      </c>
-      <c r="CA3">
-        <v>8.800000000000001</v>
       </c>
       <c r="CB3" t="s">
         <v>114</v>
@@ -1678,64 +1678,64 @@
         <v>107</v>
       </c>
       <c r="F5">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="G5">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="H5">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="I5">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="J5">
-        <v>2.96</v>
+        <v>2.86</v>
       </c>
       <c r="K5">
         <v>3.05</v>
       </c>
       <c r="L5">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="M5">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="N5">
         <v>2.56</v>
       </c>
       <c r="O5">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="P5">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="Q5">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="R5">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="S5">
         <v>6</v>
       </c>
       <c r="T5">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="U5">
         <v>1.76</v>
       </c>
       <c r="V5">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="W5">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="X5">
         <v>8</v>
       </c>
       <c r="Y5">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="Z5">
         <v>14.5</v>
@@ -1744,7 +1744,7 @@
         <v>85</v>
       </c>
       <c r="AB5">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC5">
         <v>7.2</v>
@@ -1753,10 +1753,10 @@
         <v>13</v>
       </c>
       <c r="AE5">
-        <v>85</v>
+        <v>60</v>
       </c>
       <c r="AF5">
-        <v>30</v>
+        <v>500</v>
       </c>
       <c r="AG5">
         <v>95</v>
@@ -1765,25 +1765,25 @@
         <v>42</v>
       </c>
       <c r="AI5">
-        <v>150</v>
+        <v>230</v>
       </c>
       <c r="AJ5">
         <v>900</v>
       </c>
       <c r="AK5">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="AL5">
-        <v>500</v>
+        <v>420</v>
       </c>
       <c r="AM5">
         <v>500</v>
       </c>
       <c r="AN5">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="AO5">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AP5">
         <v>6.8</v>
@@ -1795,10 +1795,10 @@
         <v>12</v>
       </c>
       <c r="AS5">
-        <v>17.5</v>
+        <v>32</v>
       </c>
       <c r="AT5">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AU5">
         <v>6.2</v>
@@ -1807,7 +1807,7 @@
         <v>11</v>
       </c>
       <c r="AW5">
-        <v>19.5</v>
+        <v>32</v>
       </c>
       <c r="AX5">
         <v>21</v>
@@ -1819,31 +1819,31 @@
         <v>21</v>
       </c>
       <c r="BA5">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="BB5">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BC5">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="BD5">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BE5">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BF5">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BG5">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="BH5">
         <v>2.62</v>
       </c>
       <c r="BI5">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="BJ5">
         <v>12</v>
@@ -1891,7 +1891,7 @@
         <v>1000</v>
       </c>
       <c r="BY5">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BZ5">
         <v>0</v>
@@ -1923,49 +1923,49 @@
         <v>5.7</v>
       </c>
       <c r="G6">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="H6">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="I6">
         <v>1.54</v>
       </c>
       <c r="J6">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="K6">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="L6">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="M6">
         <v>1.02</v>
       </c>
       <c r="N6">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O6">
         <v>1.09</v>
       </c>
       <c r="P6">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="Q6">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="R6">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="S6">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="T6">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="U6">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="V6">
         <v>2.84</v>
@@ -1974,7 +1974,7 @@
         <v>1.19</v>
       </c>
       <c r="X6">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="Y6">
         <v>22</v>
@@ -1983,67 +1983,67 @@
         <v>17</v>
       </c>
       <c r="AA6">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AB6">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AC6">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AD6">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AE6">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AF6">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AG6">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="AH6">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AI6">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AJ6">
-        <v>160</v>
+        <v>230</v>
       </c>
       <c r="AK6">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="AL6">
         <v>55</v>
       </c>
       <c r="AM6">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="AN6">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AO6">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="AP6">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AQ6">
         <v>18</v>
       </c>
       <c r="AR6">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AS6">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AT6">
         <v>40</v>
       </c>
       <c r="AU6">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AV6">
         <v>10.5</v>
@@ -2052,7 +2052,7 @@
         <v>12.5</v>
       </c>
       <c r="AX6">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="AY6">
         <v>23</v>
@@ -2064,37 +2064,37 @@
         <v>18.5</v>
       </c>
       <c r="BB6">
-        <v>14</v>
+        <v>90</v>
       </c>
       <c r="BC6">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="BD6">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BE6">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BF6">
         <v>23</v>
       </c>
       <c r="BG6">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="BH6">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BI6">
-        <v>5.6</v>
+        <v>5.1</v>
       </c>
       <c r="BJ6">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BK6">
-        <v>5.8</v>
+        <v>7.2</v>
       </c>
       <c r="BL6">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BM6">
         <v>13</v>
@@ -2103,22 +2103,22 @@
         <v>10.5</v>
       </c>
       <c r="BO6">
-        <v>6.4</v>
+        <v>9</v>
       </c>
       <c r="BP6">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BQ6">
         <v>11</v>
       </c>
       <c r="BR6">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BS6">
         <v>10.5</v>
       </c>
       <c r="BT6">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BU6">
         <v>4.6</v>
@@ -2127,19 +2127,19 @@
         <v>9</v>
       </c>
       <c r="BW6">
-        <v>5.9</v>
+        <v>7.4</v>
       </c>
       <c r="BX6">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BY6">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BZ6">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="CA6">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="CB6" t="s">
         <v>114</v>
@@ -2162,52 +2162,52 @@
         <v>109</v>
       </c>
       <c r="F7">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="G7">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="H7">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="I7">
-        <v>2.22</v>
+        <v>2.14</v>
       </c>
       <c r="J7">
         <v>3.15</v>
       </c>
       <c r="K7">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="L7">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="M7">
         <v>1.12</v>
       </c>
       <c r="N7">
-        <v>2.78</v>
+        <v>2.72</v>
       </c>
       <c r="O7">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="P7">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="Q7">
-        <v>2.54</v>
+        <v>2.66</v>
       </c>
       <c r="R7">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="S7">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="T7">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="U7">
-        <v>1.83</v>
+        <v>1.72</v>
       </c>
       <c r="V7">
         <v>1.01</v>
@@ -2216,19 +2216,19 @@
         <v>1.01</v>
       </c>
       <c r="X7">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="Y7">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="Z7">
+        <v>11.5</v>
+      </c>
+      <c r="AA7">
+        <v>26</v>
+      </c>
+      <c r="AB7">
         <v>12.5</v>
-      </c>
-      <c r="AA7">
-        <v>29</v>
-      </c>
-      <c r="AB7">
-        <v>12</v>
       </c>
       <c r="AC7">
         <v>7.8</v>
@@ -2237,25 +2237,25 @@
         <v>11.5</v>
       </c>
       <c r="AE7">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AF7">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AG7">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AH7">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AI7">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="AJ7">
         <v>500</v>
       </c>
       <c r="AK7">
-        <v>120</v>
+        <v>160</v>
       </c>
       <c r="AL7">
         <v>210</v>
@@ -2267,19 +2267,19 @@
         <v>600</v>
       </c>
       <c r="AO7">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AP7">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AQ7">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="AR7">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AS7">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AT7">
         <v>10</v>
@@ -2291,97 +2291,97 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AW7">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="AX7">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AY7">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AZ7">
         <v>21</v>
       </c>
       <c r="BA7">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="BB7">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BC7">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="BD7">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="BE7">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BF7">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BG7">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="BH7">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="BI7">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="BJ7">
         <v>11.5</v>
       </c>
       <c r="BK7">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BN7">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BO7">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BP7">
         <v>1000</v>
       </c>
       <c r="BQ7">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BR7">
         <v>1000</v>
       </c>
       <c r="BS7">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BT7">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BU7">
         <v>3.6</v>
       </c>
       <c r="BV7">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BW7">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX7">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="BY7">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BZ7">
         <v>1000</v>
       </c>
       <c r="CA7">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="CB7" t="s">
         <v>114</v>
@@ -2410,7 +2410,7 @@
         <v>2.1</v>
       </c>
       <c r="H8">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="I8">
         <v>4.8</v>
@@ -2425,31 +2425,31 @@
         <v>1.62</v>
       </c>
       <c r="M8">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="N8">
-        <v>2.66</v>
+        <v>2.74</v>
       </c>
       <c r="O8">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="P8">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="Q8">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="R8">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="S8">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="T8">
-        <v>2.34</v>
+        <v>2.28</v>
       </c>
       <c r="U8">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="V8">
         <v>1.26</v>
@@ -2458,7 +2458,7 @@
         <v>1.9</v>
       </c>
       <c r="X8">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y8">
         <v>12</v>
@@ -2470,34 +2470,34 @@
         <v>130</v>
       </c>
       <c r="AB8">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AC8">
         <v>7.4</v>
       </c>
       <c r="AD8">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AE8">
         <v>95</v>
       </c>
       <c r="AF8">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AG8">
         <v>12</v>
       </c>
       <c r="AH8">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AI8">
         <v>120</v>
       </c>
       <c r="AJ8">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AK8">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AL8">
         <v>65</v>
@@ -2506,13 +2506,13 @@
         <v>250</v>
       </c>
       <c r="AN8">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AO8">
         <v>150</v>
       </c>
       <c r="AP8">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AQ8">
         <v>10</v>
@@ -2521,19 +2521,19 @@
         <v>27</v>
       </c>
       <c r="AS8">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AT8">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AU8">
         <v>6.8</v>
       </c>
       <c r="AV8">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AW8">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AX8">
         <v>9.6</v>
@@ -2542,46 +2542,46 @@
         <v>10.5</v>
       </c>
       <c r="AZ8">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="BA8">
-        <v>46</v>
+        <v>90</v>
       </c>
       <c r="BB8">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BC8">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BD8">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="BE8">
         <v>110</v>
       </c>
       <c r="BF8">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BG8">
-        <v>46</v>
+        <v>80</v>
       </c>
       <c r="BH8">
-        <v>2.64</v>
+        <v>2.7</v>
       </c>
       <c r="BI8">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="BJ8">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BK8">
-        <v>7.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BL8">
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>2.3</v>
+        <v>20</v>
       </c>
       <c r="BN8">
         <v>4.5</v>
@@ -2590,40 +2590,40 @@
         <v>4</v>
       </c>
       <c r="BP8">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BQ8">
-        <v>9.199999999999999</v>
+        <v>13.5</v>
       </c>
       <c r="BR8">
         <v>1000</v>
       </c>
       <c r="BS8">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BT8">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BU8">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="BV8">
         <v>1000</v>
       </c>
       <c r="BW8">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BX8">
         <v>1000</v>
       </c>
       <c r="BY8">
-        <v>2.26</v>
+        <v>2.32</v>
       </c>
       <c r="BZ8">
         <v>1000</v>
       </c>
       <c r="CA8">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="CB8" t="s">
         <v>114</v>
@@ -2649,49 +2649,49 @@
         <v>2.12</v>
       </c>
       <c r="G9">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="H9">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="I9">
         <v>4.6</v>
       </c>
       <c r="J9">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="K9">
         <v>3.25</v>
       </c>
       <c r="L9">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="M9">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="N9">
-        <v>2.62</v>
+        <v>2.78</v>
       </c>
       <c r="O9">
-        <v>1.59</v>
+        <v>1.54</v>
       </c>
       <c r="P9">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="Q9">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="R9">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="S9">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="T9">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="U9">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="V9">
         <v>1.27</v>
@@ -2700,10 +2700,10 @@
         <v>1.87</v>
       </c>
       <c r="X9">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y9">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="Z9">
         <v>32</v>
@@ -2712,13 +2712,13 @@
         <v>120</v>
       </c>
       <c r="AB9">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AC9">
         <v>7.2</v>
       </c>
       <c r="AD9">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AE9">
         <v>85</v>
@@ -2730,61 +2730,61 @@
         <v>12</v>
       </c>
       <c r="AH9">
+        <v>26</v>
+      </c>
+      <c r="AI9">
+        <v>250</v>
+      </c>
+      <c r="AJ9">
         <v>27</v>
       </c>
-      <c r="AI9">
-        <v>260</v>
-      </c>
-      <c r="AJ9">
-        <v>28</v>
-      </c>
       <c r="AK9">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AL9">
-        <v>150</v>
+        <v>60</v>
       </c>
       <c r="AM9">
         <v>1000</v>
       </c>
       <c r="AN9">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AO9">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AP9">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AQ9">
         <v>10.5</v>
       </c>
       <c r="AR9">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AS9">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="AT9">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AU9">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV9">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AW9">
         <v>65</v>
       </c>
       <c r="AX9">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AY9">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AZ9">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="BA9">
         <v>90</v>
@@ -2793,7 +2793,7 @@
         <v>24</v>
       </c>
       <c r="BC9">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BD9">
         <v>50</v>
@@ -2802,46 +2802,46 @@
         <v>70</v>
       </c>
       <c r="BF9">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="BG9">
-        <v>42</v>
+        <v>90</v>
       </c>
       <c r="BH9">
         <v>2.82</v>
       </c>
       <c r="BI9">
-        <v>2.46</v>
+        <v>2.52</v>
       </c>
       <c r="BJ9">
         <v>12</v>
       </c>
       <c r="BK9">
-        <v>5.9</v>
+        <v>9.6</v>
       </c>
       <c r="BL9">
         <v>1000</v>
       </c>
       <c r="BM9">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BN9">
         <v>4.7</v>
       </c>
       <c r="BO9">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BP9">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BQ9">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BR9">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BS9">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BT9">
         <v>7.8</v>
@@ -2850,22 +2850,22 @@
         <v>5.5</v>
       </c>
       <c r="BV9">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="BW9">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BX9">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="BY9">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BZ9">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="CA9">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CB9" t="s">
         <v>114</v>
@@ -2888,85 +2888,85 @@
         <v>112</v>
       </c>
       <c r="F10">
-        <v>1.64</v>
+        <v>1.71</v>
       </c>
       <c r="G10">
+        <v>1.72</v>
+      </c>
+      <c r="H10">
+        <v>6.4</v>
+      </c>
+      <c r="I10">
+        <v>6.8</v>
+      </c>
+      <c r="J10">
+        <v>3.75</v>
+      </c>
+      <c r="K10">
+        <v>3.8</v>
+      </c>
+      <c r="L10">
+        <v>1.53</v>
+      </c>
+      <c r="M10">
+        <v>1.11</v>
+      </c>
+      <c r="N10">
+        <v>3.05</v>
+      </c>
+      <c r="O10">
+        <v>1.48</v>
+      </c>
+      <c r="P10">
         <v>1.65</v>
-      </c>
-      <c r="H10">
-        <v>7.4</v>
-      </c>
-      <c r="I10">
-        <v>7.8</v>
-      </c>
-      <c r="J10">
-        <v>3.85</v>
-      </c>
-      <c r="K10">
-        <v>3.95</v>
-      </c>
-      <c r="L10">
-        <v>1.52</v>
-      </c>
-      <c r="M10">
-        <v>1.1</v>
-      </c>
-      <c r="N10">
-        <v>3</v>
-      </c>
-      <c r="O10">
-        <v>1.47</v>
-      </c>
-      <c r="P10">
-        <v>1.66</v>
       </c>
       <c r="Q10">
         <v>2.44</v>
       </c>
       <c r="R10">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="S10">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="T10">
-        <v>2.34</v>
+        <v>2.28</v>
       </c>
       <c r="U10">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="V10">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="W10">
-        <v>2.54</v>
+        <v>2.38</v>
       </c>
       <c r="X10">
         <v>10.5</v>
       </c>
       <c r="Y10">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Z10">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AA10">
-        <v>290</v>
+        <v>240</v>
       </c>
       <c r="AB10">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AC10">
         <v>8.6</v>
       </c>
       <c r="AD10">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AE10">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="AF10">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AG10">
         <v>10.5</v>
@@ -2975,10 +2975,10 @@
         <v>30</v>
       </c>
       <c r="AI10">
-        <v>170</v>
+        <v>700</v>
       </c>
       <c r="AJ10">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AK10">
         <v>22</v>
@@ -2987,79 +2987,79 @@
         <v>60</v>
       </c>
       <c r="AM10">
-        <v>700</v>
+        <v>580</v>
       </c>
       <c r="AN10">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="AO10">
-        <v>280</v>
+        <v>240</v>
       </c>
       <c r="AP10">
         <v>9.4</v>
       </c>
       <c r="AQ10">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AR10">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AS10">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="AT10">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AU10">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AV10">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AW10">
-        <v>15.5</v>
+        <v>75</v>
       </c>
       <c r="AX10">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AY10">
         <v>9.6</v>
       </c>
       <c r="AZ10">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="BA10">
+        <v>14</v>
+      </c>
+      <c r="BB10">
         <v>15.5</v>
-      </c>
-      <c r="BB10">
-        <v>14</v>
       </c>
       <c r="BC10">
         <v>19.5</v>
       </c>
       <c r="BD10">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BE10">
         <v>150</v>
       </c>
       <c r="BF10">
+        <v>14</v>
+      </c>
+      <c r="BG10">
+        <v>14.5</v>
+      </c>
+      <c r="BH10">
+        <v>2.94</v>
+      </c>
+      <c r="BI10">
+        <v>2.6</v>
+      </c>
+      <c r="BJ10">
         <v>12.5</v>
       </c>
-      <c r="BG10">
-        <v>16.5</v>
-      </c>
-      <c r="BH10">
-        <v>3.05</v>
-      </c>
-      <c r="BI10">
-        <v>2.42</v>
-      </c>
-      <c r="BJ10">
-        <v>13.5</v>
-      </c>
       <c r="BK10">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="BL10">
         <v>1000</v>
@@ -3071,43 +3071,43 @@
         <v>3.95</v>
       </c>
       <c r="BO10">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="BP10">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BQ10">
-        <v>5.8</v>
+        <v>7</v>
       </c>
       <c r="BR10">
         <v>36</v>
       </c>
       <c r="BS10">
-        <v>8.6</v>
+        <v>10.5</v>
       </c>
       <c r="BT10">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="BU10">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BV10">
+        <v>75</v>
+      </c>
+      <c r="BW10">
+        <v>12.5</v>
+      </c>
+      <c r="BX10">
         <v>90</v>
       </c>
-      <c r="BW10">
-        <v>10</v>
-      </c>
-      <c r="BX10">
-        <v>100</v>
-      </c>
       <c r="BY10">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="BZ10">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="CA10">
-        <v>8.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="CB10" t="s">
         <v>114</v>
@@ -3130,124 +3130,124 @@
         <v>113</v>
       </c>
       <c r="F11">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="G11">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="H11">
         <v>2.02</v>
       </c>
       <c r="I11">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="J11">
+        <v>3.35</v>
+      </c>
+      <c r="K11">
         <v>3.4</v>
       </c>
-      <c r="K11">
-        <v>3.45</v>
-      </c>
       <c r="L11">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="M11">
         <v>1.11</v>
       </c>
       <c r="N11">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="O11">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="P11">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="Q11">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="R11">
         <v>1.23</v>
       </c>
       <c r="S11">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="T11">
         <v>2.14</v>
       </c>
       <c r="U11">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="V11">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="W11">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="X11">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="Y11">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="Z11">
         <v>11</v>
       </c>
       <c r="AA11">
+        <v>24</v>
+      </c>
+      <c r="AB11">
+        <v>13</v>
+      </c>
+      <c r="AC11">
+        <v>7.8</v>
+      </c>
+      <c r="AD11">
+        <v>11</v>
+      </c>
+      <c r="AE11">
         <v>28</v>
-      </c>
-      <c r="AB11">
-        <v>12.5</v>
-      </c>
-      <c r="AC11">
-        <v>8</v>
-      </c>
-      <c r="AD11">
-        <v>10.5</v>
-      </c>
-      <c r="AE11">
-        <v>27</v>
       </c>
       <c r="AF11">
         <v>34</v>
       </c>
       <c r="AG11">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AH11">
         <v>25</v>
       </c>
       <c r="AI11">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AJ11">
+        <v>180</v>
+      </c>
+      <c r="AK11">
+        <v>80</v>
+      </c>
+      <c r="AL11">
+        <v>150</v>
+      </c>
+      <c r="AM11">
+        <v>500</v>
+      </c>
+      <c r="AN11">
         <v>120</v>
       </c>
-      <c r="AK11">
-        <v>75</v>
-      </c>
-      <c r="AL11">
-        <v>500</v>
-      </c>
-      <c r="AM11">
-        <v>580</v>
-      </c>
-      <c r="AN11">
-        <v>110</v>
-      </c>
       <c r="AO11">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AP11">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="AQ11">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AR11">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AS11">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AT11">
         <v>11.5</v>
@@ -3262,7 +3262,7 @@
         <v>23</v>
       </c>
       <c r="AX11">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AY11">
         <v>17</v>
@@ -3271,7 +3271,7 @@
         <v>22</v>
       </c>
       <c r="BA11">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BB11">
         <v>28</v>
@@ -3280,28 +3280,28 @@
         <v>65</v>
       </c>
       <c r="BD11">
-        <v>18.5</v>
+        <v>55</v>
       </c>
       <c r="BE11">
         <v>130</v>
       </c>
       <c r="BF11">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="BG11">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BH11">
-        <v>2.86</v>
+        <v>2.8</v>
       </c>
       <c r="BI11">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="BJ11">
         <v>11.5</v>
       </c>
       <c r="BK11">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BL11">
         <v>1000</v>
@@ -3310,46 +3310,46 @@
         <v>160</v>
       </c>
       <c r="BN11">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BO11">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="BP11">
         <v>1000</v>
       </c>
       <c r="BQ11">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="BR11">
         <v>1000</v>
       </c>
       <c r="BS11">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="BT11">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="BU11">
         <v>3.55</v>
       </c>
       <c r="BV11">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BW11">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX11">
         <v>1000</v>
       </c>
       <c r="BY11">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="BZ11">
         <v>1000</v>
       </c>
       <c r="CA11">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="CB11" t="s">
         <v>114</v>
